--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -17,8 +17,8 @@
     <sheet name="PEÇAS E CORTE" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COTAÇÃO'!$A$3:$V$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ESPECIFICAÇÕES'!$A$3:$I$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COTAÇÃO'!$A$3:$V$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ESPECIFICAÇÕES'!$A$3:$I$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PEÇAS E CORTE'!$A$4:$F$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -680,69 +680,36 @@
 NORMAS: NBR 14762 item 8.4</t>
       </text>
     </comment>
-    <comment ref="C78" authorId="0" shapeId="0">
+    <comment ref="C83" authorId="0" shapeId="0">
       <text>
         <t>hora de equipe, com encargos e EPI
 LACUNA: convencao coletiva vigente e composicao de encargos</t>
       </text>
     </comment>
-    <comment ref="C79" authorId="0" shapeId="0">
+    <comment ref="C84" authorId="0" shapeId="0">
       <text>
         <t>hora de equipe, com encargos e EPI
 LACUNA: convencao coletiva vigente e composicao de encargos</t>
       </text>
     </comment>
-    <comment ref="C80" authorId="0" shapeId="0">
+    <comment ref="C85" authorId="0" shapeId="0">
       <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C81" authorId="0" shapeId="0">
+    <comment ref="C86" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C82" authorId="0" shapeId="0">
+    <comment ref="C87" authorId="0" shapeId="0">
       <text>
         <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
 LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
-      </text>
-    </comment>
-    <comment ref="C83" authorId="0" shapeId="0">
-      <text>
-        <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
-NORMAS: NBR 11702, NBR 13245</t>
-      </text>
-    </comment>
-    <comment ref="C84" authorId="0" shapeId="0">
-      <text>
-        <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
-NORMAS: NBR 13818, NBR 15463
-LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
-      </text>
-    </comment>
-    <comment ref="C85" authorId="0" shapeId="0">
-      <text>
-        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
-NORMAS: NBR 16401, Portaria INMETRO de eficiencia
-LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
-      </text>
-    </comment>
-    <comment ref="C86" authorId="0" shapeId="0">
-      <text>
-        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
-LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
-      </text>
-    </comment>
-    <comment ref="C87" authorId="0" shapeId="0">
-      <text>
-        <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
-NORMAS: NBR 13818, NBR 15463
-LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
     <comment ref="C88" authorId="0" shapeId="0">
@@ -760,49 +727,48 @@
     </comment>
     <comment ref="C90" authorId="0" shapeId="0">
       <text>
-        <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
-NORMAS: NBR 11702, NBR 13245</t>
-      </text>
-    </comment>
-    <comment ref="C91" authorId="0" shapeId="0">
-      <text>
-        <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
-NORMAS: NBR 11702, NBR 13245</t>
-      </text>
-    </comment>
-    <comment ref="C92" authorId="0" shapeId="0">
-      <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
 NORMAS: NBR 16401, Portaria INMETRO de eficiencia
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
-    <comment ref="C93" authorId="0" shapeId="0">
-      <text>
-        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
-NORMAS: NBR 14136, NBR 5410
-LACUNA: fluxo luminoso e temperatura de cor por ambiente: depende de projeto luminotecnico, que e pendencia aberta — a quantidade aqui e regra declarada</t>
-      </text>
-    </comment>
-    <comment ref="C94" authorId="0" shapeId="0">
-      <text>
-        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
-NORMAS: NBR 16401, Portaria INMETRO de eficiencia
-LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
-      </text>
-    </comment>
-    <comment ref="C95" authorId="0" shapeId="0">
+    <comment ref="C91" authorId="0" shapeId="0">
       <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
+    <comment ref="C92" authorId="0" shapeId="0">
+      <text>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+      </text>
+    </comment>
+    <comment ref="C93" authorId="0" shapeId="0">
+      <text>
+        <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
+NORMAS: NBR 13818, NBR 15463
+LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+      </text>
+    </comment>
+    <comment ref="C94" authorId="0" shapeId="0">
+      <text>
+        <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
+NORMAS: NBR 11702, NBR 13245</t>
+      </text>
+    </comment>
+    <comment ref="C95" authorId="0" shapeId="0">
+      <text>
+        <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
+NORMAS: NBR 11702, NBR 13245</t>
+      </text>
+    </comment>
     <comment ref="C96" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
+NORMAS: NBR 16401, Portaria INMETRO de eficiencia
+LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
     <comment ref="C97" authorId="0" shapeId="0">
@@ -813,27 +779,30 @@
     </comment>
     <comment ref="C98" authorId="0" shapeId="0">
       <text>
-        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
-LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
+NORMAS: NBR 14136, NBR 5410
+LACUNA: fluxo luminoso e temperatura de cor por ambiente: depende de projeto luminotecnico, que e pendencia aberta — a quantidade aqui e regra declarada</t>
       </text>
     </comment>
     <comment ref="C99" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
+NORMAS: NBR 16401, Portaria INMETRO de eficiencia
+LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
     <comment ref="C100" authorId="0" shapeId="0">
       <text>
-        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
-LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+        <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
+NORMAS: NBR 13818, NBR 15463
+LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
     <comment ref="C101" authorId="0" shapeId="0">
       <text>
-        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
-LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
     <comment ref="C102" authorId="0" shapeId="0">
@@ -844,9 +813,8 @@
     </comment>
     <comment ref="C103" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
+LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
     <comment ref="C104" authorId="0" shapeId="0">
@@ -858,34 +826,34 @@
     </comment>
     <comment ref="C105" authorId="0" shapeId="0">
       <text>
-        <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
-NORMAS: NBR 11702, NBR 13245</t>
+        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
+LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
     <comment ref="C106" authorId="0" shapeId="0">
+      <text>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+      </text>
+    </comment>
+    <comment ref="C107" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C107" authorId="0" shapeId="0">
-      <text>
-        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
-NORMAS: NBR 14136, NBR 5410</t>
-      </text>
-    </comment>
     <comment ref="C108" authorId="0" shapeId="0">
       <text>
-        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
-LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
     <comment ref="C109" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
+NORMAS: NBR 11702, NBR 13245</t>
       </text>
     </comment>
     <comment ref="C110" authorId="0" shapeId="0">
@@ -903,15 +871,15 @@
     </comment>
     <comment ref="C112" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
+LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
     <comment ref="C113" authorId="0" shapeId="0">
       <text>
-        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
-NORMAS: NBR 14136, NBR 5410</t>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
     <comment ref="C114" authorId="0" shapeId="0">
@@ -936,9 +904,8 @@
     </comment>
     <comment ref="C117" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
+NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
     <comment ref="C118" authorId="0" shapeId="0">
@@ -950,9 +917,8 @@
     </comment>
     <comment ref="C119" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
+NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
     <comment ref="C120" authorId="0" shapeId="0">
@@ -963,6 +929,34 @@
       </text>
     </comment>
     <comment ref="C121" authorId="0" shapeId="0">
+      <text>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+      </text>
+    </comment>
+    <comment ref="C122" authorId="0" shapeId="0">
+      <text>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+      </text>
+    </comment>
+    <comment ref="C123" authorId="0" shapeId="0">
+      <text>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+      </text>
+    </comment>
+    <comment ref="C124" authorId="0" shapeId="0">
+      <text>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+      </text>
+    </comment>
+    <comment ref="C125" authorId="0" shapeId="0">
       <text>
         <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
 NORMAS: NBR 14136, NBR 5410</t>
@@ -1278,7 +1272,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R57</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R58</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V125"/>
+  <dimension ref="A1:V129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1535,11 +1529,11 @@
         </is>
       </c>
       <c r="Q2" s="4">
-        <f>COUNTIF(V4:V121,"COMPLETO")&amp;" de "&amp;118&amp;" itens com 5 propostas"</f>
+        <f>COUNTIF(V4:V125,"COMPLETO")&amp;" de "&amp;122&amp;" itens com 5 propostas"</f>
         <v/>
       </c>
       <c r="T2" s="7">
-        <f>IF(I122=0,0,SUMIF(V4:V121,"COMPLETO",I4:I121)/I122)</f>
+        <f>IF(I126=0,0,SUMIF(V4:V125,"COMPLETO",I4:I125)/I126)</f>
         <v/>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -6006,7 +6000,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>BRI-RIPA</t>
+          <t>FAC-BASE</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -6016,16 +6010,16 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Ripa de fachada: tubular de aluminio 50 x 20 x 1,2 mm</t>
+          <t>Basecoat de regularizacao sobre placa cimenticia</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>205.5</v>
+        <v>309.2</v>
       </c>
       <c r="F61" s="13" t="n">
         <v>0</v>
@@ -6035,7 +6029,7 @@
         <v/>
       </c>
       <c r="H61" s="15" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I61" s="16">
         <f>G61*H61</f>
@@ -6082,7 +6076,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>BRI-MEC</t>
+          <t>FAC-MAO</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -6092,16 +6086,16 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Mecanismo de brise movel: guia, roldana e trava</t>
+          <t>Mao de obra de fachada (basecoat, tela, junta e pintura)</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>cj</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>2</v>
+        <v>309.2</v>
       </c>
       <c r="F62" s="13" t="n">
         <v>0</v>
@@ -6111,7 +6105,7 @@
         <v/>
       </c>
       <c r="H62" s="15" t="n">
-        <v>2400</v>
+        <v>34</v>
       </c>
       <c r="I62" s="16">
         <f>G62*H62</f>
@@ -6158,7 +6152,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>BRI-TRAV</t>
+          <t>BRI-RIPA</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -6168,7 +6162,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Travessa de brise: U 50x25x1,2 aluminio</t>
+          <t>Ripa de fachada: tubular de aluminio 50 x 20 x 1,2 mm</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -6177,7 +6171,7 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>33.6</v>
+        <v>205.5</v>
       </c>
       <c r="F63" s="13" t="n">
         <v>0</v>
@@ -6187,7 +6181,7 @@
         <v/>
       </c>
       <c r="H63" s="15" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I63" s="16">
         <f>G63*H63</f>
@@ -6234,7 +6228,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>BRI-FIX</t>
+          <t>FAC-TINTA</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -6244,16 +6238,16 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Fixacao de travessa no montante</t>
+          <t>Tinta acrilica elastomerica lisa com biocida, 2 demaos</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>66</v>
+        <v>88.3</v>
       </c>
       <c r="F64" s="13" t="n">
         <v>0</v>
@@ -6263,7 +6257,7 @@
         <v/>
       </c>
       <c r="H64" s="15" t="n">
-        <v>6.5</v>
+        <v>68</v>
       </c>
       <c r="I64" s="16">
         <f>G64*H64</f>
@@ -6310,26 +6304,26 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO2</t>
+          <t>FAC-JUNTA</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
+          <t>Tratamento de junta externa: fundo de junta e selante PU</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>76.31999999999999</v>
+        <v>386.5</v>
       </c>
       <c r="F65" s="13" t="n">
         <v>0</v>
@@ -6339,7 +6333,7 @@
         <v/>
       </c>
       <c r="H65" s="15" t="n">
-        <v>320</v>
+        <v>14</v>
       </c>
       <c r="I65" s="16">
         <f>G65*H65</f>
@@ -6386,26 +6380,26 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>EXT-BLOCO</t>
+          <t>BRI-MEC</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
+          <t>Mecanismo de brise movel: guia, roldana e trava</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>cj</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>3118</v>
+        <v>2</v>
       </c>
       <c r="F66" s="13" t="n">
         <v>0</v>
@@ -6415,7 +6409,7 @@
         <v/>
       </c>
       <c r="H66" s="15" t="n">
-        <v>4.8</v>
+        <v>2400</v>
       </c>
       <c r="I66" s="16">
         <f>G66*H66</f>
@@ -6462,26 +6456,26 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-EST</t>
+          <t>FAC-TELA</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Piscina: casca de concreto armado 150 mm</t>
+          <t>Tela de fibra de vidro alcali-resistente, embutida no basecoat</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>4.57</v>
+        <v>340.1</v>
       </c>
       <c r="F67" s="13" t="n">
         <v>0</v>
@@ -6491,7 +6485,7 @@
         <v/>
       </c>
       <c r="H67" s="15" t="n">
-        <v>1450</v>
+        <v>9</v>
       </c>
       <c r="I67" s="16">
         <f>G67*H67</f>
@@ -6538,26 +6532,26 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-REV</t>
+          <t>BRI-TRAV</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Piscina: revestimento de fundo e paredes</t>
+          <t>Travessa de brise: U 50x25x1,2 aluminio</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>30.43</v>
+        <v>33.6</v>
       </c>
       <c r="F68" s="13" t="n">
         <v>0</v>
@@ -6567,7 +6561,7 @@
         <v/>
       </c>
       <c r="H68" s="15" t="n">
-        <v>210</v>
+        <v>38</v>
       </c>
       <c r="I68" s="16">
         <f>G68*H68</f>
@@ -6614,17 +6608,17 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>EXT-VASO</t>
+          <t>BRI-FIX</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Vaso e planta em vaso</t>
+          <t>Fixacao de travessa no montante</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -6633,7 +6627,7 @@
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="F69" s="13" t="n">
         <v>0</v>
@@ -6643,7 +6637,7 @@
         <v/>
       </c>
       <c r="H69" s="15" t="n">
-        <v>240</v>
+        <v>6.5</v>
       </c>
       <c r="I69" s="16">
         <f>G69*H69</f>
@@ -6690,7 +6684,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>EXT-GRAMA</t>
+          <t>EXT-PISO2</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -6700,7 +6694,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Grama e canteiro</t>
+          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -6709,7 +6703,7 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>137.16</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F70" s="13" t="n">
         <v>0</v>
@@ -6719,7 +6713,7 @@
         <v/>
       </c>
       <c r="H70" s="15" t="n">
-        <v>38</v>
+        <v>320</v>
       </c>
       <c r="I70" s="16">
         <f>G70*H70</f>
@@ -6766,7 +6760,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>EXT-HIDROF</t>
+          <t>EXT-BLOCO</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -6776,16 +6770,16 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Hidrofugante incolor no muro aparente</t>
+          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>249.5</v>
+        <v>3118</v>
       </c>
       <c r="F71" s="13" t="n">
         <v>0</v>
@@ -6795,7 +6789,7 @@
         <v/>
       </c>
       <c r="H71" s="15" t="n">
-        <v>18</v>
+        <v>4.8</v>
       </c>
       <c r="I71" s="16">
         <f>G71*H71</f>
@@ -6842,7 +6836,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>EXT-ARV</t>
+          <t>EXT-PISC-EST</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -6852,16 +6846,16 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Arvore de porte</t>
+          <t>Piscina: casca de concreto armado 150 mm</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="F72" s="13" t="n">
         <v>0</v>
@@ -6871,7 +6865,7 @@
         <v/>
       </c>
       <c r="H72" s="15" t="n">
-        <v>780</v>
+        <v>1450</v>
       </c>
       <c r="I72" s="16">
         <f>G72*H72</f>
@@ -6918,7 +6912,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO1</t>
+          <t>EXT-PISC-REV</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -6928,7 +6922,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>faixa seca da piscina: porcelanato externo claro R11</t>
+          <t>Piscina: revestimento de fundo e paredes</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -6937,7 +6931,7 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>24.3</v>
+        <v>30.43</v>
       </c>
       <c r="F73" s="13" t="n">
         <v>0</v>
@@ -6947,7 +6941,7 @@
         <v/>
       </c>
       <c r="H73" s="15" t="n">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="I73" s="16">
         <f>G73*H73</f>
@@ -6994,7 +6988,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>EXT-BORDA</t>
+          <t>EXT-VASO</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -7004,16 +6998,16 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Borda de piscina</t>
+          <t>Vaso e planta em vaso</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>17.4</v>
+        <v>24</v>
       </c>
       <c r="F74" s="13" t="n">
         <v>0</v>
@@ -7023,7 +7017,7 @@
         <v/>
       </c>
       <c r="H74" s="15" t="n">
-        <v>185</v>
+        <v>240</v>
       </c>
       <c r="I74" s="16">
         <f>G74*H74</f>
@@ -7070,7 +7064,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO3</t>
+          <t>EXT-GRAMA</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -7080,7 +7074,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>passeio e acesso: piso drenante intertravado claro</t>
+          <t>Grama e canteiro</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -7089,7 +7083,7 @@
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>30.96</v>
+        <v>137.16</v>
       </c>
       <c r="F75" s="13" t="n">
         <v>0</v>
@@ -7099,7 +7093,7 @@
         <v/>
       </c>
       <c r="H75" s="15" t="n">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="I75" s="16">
         <f>G75*H75</f>
@@ -7146,7 +7140,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO4</t>
+          <t>EXT-HIDROF</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -7156,7 +7150,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>varanda do pavimento superior: porcelanato externo claro R11</t>
+          <t>Hidrofugante incolor no muro aparente</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -7165,7 +7159,7 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>14.04</v>
+        <v>249.5</v>
       </c>
       <c r="F76" s="13" t="n">
         <v>0</v>
@@ -7175,7 +7169,7 @@
         <v/>
       </c>
       <c r="H76" s="15" t="n">
-        <v>148</v>
+        <v>18</v>
       </c>
       <c r="I76" s="16">
         <f>G76*H76</f>
@@ -7222,7 +7216,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>EXT-GRAUTE</t>
+          <t>EXT-ARV</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -7232,16 +7226,16 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Graute de cinta e pilarete do muro</t>
+          <t>Arvore de porte</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="F77" s="13" t="n">
         <v>0</v>
@@ -7251,7 +7245,7 @@
         <v/>
       </c>
       <c r="H77" s="15" t="n">
-        <v>620</v>
+        <v>780</v>
       </c>
       <c r="I77" s="16">
         <f>G77*H77</f>
@@ -7298,26 +7292,26 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>MO-MON</t>
+          <t>EXT-PISO1</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Mao de obra de montagem</t>
+          <t>faixa seca da piscina: porcelanato externo claro R11</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>681</v>
+        <v>24.3</v>
       </c>
       <c r="F78" s="13" t="n">
         <v>0</v>
@@ -7327,7 +7321,7 @@
         <v/>
       </c>
       <c r="H78" s="15" t="n">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="I78" s="16">
         <f>G78*H78</f>
@@ -7374,26 +7368,26 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>MO-FAB</t>
+          <t>EXT-BORDA</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Mao de obra de fabrica</t>
+          <t>Borda de piscina</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>46.4</v>
+        <v>17.4</v>
       </c>
       <c r="F79" s="13" t="n">
         <v>0</v>
@@ -7403,7 +7397,7 @@
         <v/>
       </c>
       <c r="H79" s="15" t="n">
-        <v>38</v>
+        <v>185</v>
       </c>
       <c r="I79" s="16">
         <f>G79*H79</f>
@@ -7450,17 +7444,17 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>REV-PISO</t>
+          <t>EXT-PISO3</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Piso interno (porcelanato retificado)</t>
+          <t>passeio e acesso: piso drenante intertravado claro</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -7469,7 +7463,7 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>355.6</v>
+        <v>30.96</v>
       </c>
       <c r="F80" s="13" t="n">
         <v>0</v>
@@ -7479,7 +7473,7 @@
         <v/>
       </c>
       <c r="H80" s="15" t="n">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="I80" s="16">
         <f>G80*H80</f>
@@ -7526,17 +7520,17 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>LOU-BOX</t>
+          <t>EXT-PISO4</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Box de vidro temperado 8 mm, 1.900 mm de altura</t>
+          <t>varanda do pavimento superior: porcelanato externo claro R11</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -7545,7 +7539,7 @@
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>32.3</v>
+        <v>14.04</v>
       </c>
       <c r="F81" s="13" t="n">
         <v>0</v>
@@ -7555,7 +7549,7 @@
         <v/>
       </c>
       <c r="H81" s="15" t="n">
-        <v>620</v>
+        <v>148</v>
       </c>
       <c r="I81" s="16">
         <f>G81*H81</f>
@@ -7602,26 +7596,26 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>MAR-GAB</t>
+          <t>EXT-GRAUTE</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Gabinete sob bancada, sob medida</t>
+          <t>Graute de cinta e pilarete do muro</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>12</v>
+        <v>2.99</v>
       </c>
       <c r="F82" s="13" t="n">
         <v>0</v>
@@ -7631,7 +7625,7 @@
         <v/>
       </c>
       <c r="H82" s="15" t="n">
-        <v>1450</v>
+        <v>620</v>
       </c>
       <c r="I82" s="16">
         <f>G82*H82</f>
@@ -7678,26 +7672,26 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>PIN-PAREDE</t>
+          <t>MO-MON</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Pintura de parede interna (latex acrilico, 2 demaos)</t>
+          <t>Mao de obra de montagem</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>558.7</v>
+        <v>681</v>
       </c>
       <c r="F83" s="13" t="n">
         <v>0</v>
@@ -7707,7 +7701,7 @@
         <v/>
       </c>
       <c r="H83" s="15" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="I83" s="16">
         <f>G83*H83</f>
@@ -7754,26 +7748,26 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>REV-PAREDE</t>
+          <t>MO-FAB</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Revestimento ceramico de parede em area molhada</t>
+          <t>Mao de obra de fabrica</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>137.9</v>
+        <v>46.4</v>
       </c>
       <c r="F84" s="13" t="n">
         <v>0</v>
@@ -7783,7 +7777,7 @@
         <v/>
       </c>
       <c r="H84" s="15" t="n">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="I84" s="16">
         <f>G84*H84</f>
@@ -7830,26 +7824,26 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT18</t>
+          <t>REV-PISO</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 18.000 BTU/h</t>
+          <t>Piso interno (porcelanato retificado)</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>4</v>
+        <v>355.6</v>
       </c>
       <c r="F85" s="13" t="n">
         <v>0</v>
@@ -7859,7 +7853,7 @@
         <v/>
       </c>
       <c r="H85" s="15" t="n">
-        <v>3200</v>
+        <v>118</v>
       </c>
       <c r="I85" s="16">
         <f>G85*H85</f>
@@ -7906,17 +7900,17 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>MAR-TAMPO</t>
+          <t>LOU-BOX</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Tampo de bancada (quartzo/granito)</t>
+          <t>Box de vidro temperado 8 mm, 1.900 mm de altura</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -7925,7 +7919,7 @@
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>7.17</v>
+        <v>32.3</v>
       </c>
       <c r="F86" s="13" t="n">
         <v>0</v>
@@ -7935,7 +7929,7 @@
         <v/>
       </c>
       <c r="H86" s="15" t="n">
-        <v>1250</v>
+        <v>620</v>
       </c>
       <c r="I86" s="16">
         <f>G86*H86</f>
@@ -7982,26 +7976,26 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>REV-ARG</t>
+          <t>MAR-GAB</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Argamassa colante AC-III e regularizacao</t>
+          <t>Gabinete sob bancada, sob medida</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>493.5</v>
+        <v>12</v>
       </c>
       <c r="F87" s="13" t="n">
         <v>0</v>
@@ -8011,7 +8005,7 @@
         <v/>
       </c>
       <c r="H87" s="15" t="n">
-        <v>18</v>
+        <v>1450</v>
       </c>
       <c r="I87" s="16">
         <f>G87*H87</f>
@@ -8058,7 +8052,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>REV-RODAPE</t>
+          <t>REV-PAREDE</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -8068,16 +8062,16 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Rodape (poliestireno 100 mm, pintado)</t>
+          <t>Revestimento ceramico de parede em area molhada</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>253.2</v>
+        <v>155.5</v>
       </c>
       <c r="F88" s="13" t="n">
         <v>0</v>
@@ -8087,7 +8081,7 @@
         <v/>
       </c>
       <c r="H88" s="15" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="I88" s="16">
         <f>G88*H88</f>
@@ -8134,7 +8128,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>PIN-FORRO</t>
+          <t>PIN-PAREDE</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -8144,7 +8138,7 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Pintura de forro (latex PVA fosco)</t>
+          <t>Pintura de parede interna (latex acrilico, 2 demaos)</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -8153,7 +8147,7 @@
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>323.3</v>
+        <v>558.7</v>
       </c>
       <c r="F89" s="13" t="n">
         <v>0</v>
@@ -8210,26 +8204,26 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>PIN-TINTA</t>
+          <t>EQP-SPLIT18</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
+          <t>Split inverter 18.000 BTU/h</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>176.4</v>
+        <v>4</v>
       </c>
       <c r="F90" s="13" t="n">
         <v>0</v>
@@ -8239,7 +8233,7 @@
         <v/>
       </c>
       <c r="H90" s="15" t="n">
-        <v>42</v>
+        <v>3200</v>
       </c>
       <c r="I90" s="16">
         <f>G90*H90</f>
@@ -8286,17 +8280,17 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>PIN-EXT</t>
+          <t>REV-ARG</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Pintura externa (acrilico elastomerico no muro)</t>
+          <t>Argamassa colante AC-III e regularizacao</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -8305,7 +8299,7 @@
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>249.5</v>
+        <v>511.1</v>
       </c>
       <c r="F91" s="13" t="n">
         <v>0</v>
@@ -8315,7 +8309,7 @@
         <v/>
       </c>
       <c r="H91" s="15" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I91" s="16">
         <f>G91*H91</f>
@@ -8362,26 +8356,26 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT9</t>
+          <t>MAR-TAMPO</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 9.000 BTU/h</t>
+          <t>Tampo de bancada (quartzo/granito)</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>3</v>
+        <v>7.17</v>
       </c>
       <c r="F92" s="13" t="n">
         <v>0</v>
@@ -8391,7 +8385,7 @@
         <v/>
       </c>
       <c r="H92" s="15" t="n">
-        <v>2100</v>
+        <v>1250</v>
       </c>
       <c r="I92" s="16">
         <f>G92*H92</f>
@@ -8438,26 +8432,26 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>ELE-LUM</t>
+          <t>REV-RODAPE</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Luminaria LED embutida no forro</t>
+          <t>Rodape (poliestireno 100 mm, pintado)</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>58</v>
+        <v>253.2</v>
       </c>
       <c r="F93" s="13" t="n">
         <v>0</v>
@@ -8467,7 +8461,7 @@
         <v/>
       </c>
       <c r="H93" s="15" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="I93" s="16">
         <f>G93*H93</f>
@@ -8514,26 +8508,26 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT30</t>
+          <t>PIN-FORRO</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 30.000 BTU/h</t>
+          <t>Pintura de forro (latex PVA fosco)</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>1</v>
+        <v>323.3</v>
       </c>
       <c r="F94" s="13" t="n">
         <v>0</v>
@@ -8543,7 +8537,7 @@
         <v/>
       </c>
       <c r="H94" s="15" t="n">
-        <v>5400</v>
+        <v>26</v>
       </c>
       <c r="I94" s="16">
         <f>G94*H94</f>
@@ -8590,26 +8584,26 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>REV-REJ</t>
+          <t>PIN-TINTA</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Rejunte epoxi/acrilico</t>
+          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>493.5</v>
+        <v>176.4</v>
       </c>
       <c r="F95" s="13" t="n">
         <v>0</v>
@@ -8619,7 +8613,7 @@
         <v/>
       </c>
       <c r="H95" s="15" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="I95" s="16">
         <f>G95*H95</f>
@@ -8666,17 +8660,17 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>LOU-VASO</t>
+          <t>EQP-SPLIT9</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Bacia sanitaria com caixa acoplada</t>
+          <t>Split inverter 9.000 BTU/h</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -8685,7 +8679,7 @@
         </is>
       </c>
       <c r="E96" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F96" s="13" t="n">
         <v>0</v>
@@ -8695,7 +8689,7 @@
         <v/>
       </c>
       <c r="H96" s="15" t="n">
-        <v>780</v>
+        <v>2100</v>
       </c>
       <c r="I96" s="16">
         <f>G96*H96</f>
@@ -8742,7 +8736,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>MAR-CAB</t>
+          <t>MAR-ARM</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -8752,16 +8746,16 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Cabideiro e gaveteiro de closet</t>
+          <t>Armario de MDF sob medida</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>12</v>
+        <v>5.94</v>
       </c>
       <c r="F97" s="13" t="n">
         <v>0</v>
@@ -8771,7 +8765,7 @@
         <v/>
       </c>
       <c r="H97" s="15" t="n">
-        <v>320</v>
+        <v>980</v>
       </c>
       <c r="I97" s="16">
         <f>G97*H97</f>
@@ -8818,26 +8812,26 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>EQP-PISC</t>
+          <t>ELE-LUM</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
+          <t>Luminaria LED embutida no forro</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>cj</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="F98" s="13" t="n">
         <v>0</v>
@@ -8847,7 +8841,7 @@
         <v/>
       </c>
       <c r="H98" s="15" t="n">
-        <v>2800</v>
+        <v>95</v>
       </c>
       <c r="I98" s="16">
         <f>G98*H98</f>
@@ -8894,17 +8888,17 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN</t>
+          <t>EQP-SPLIT30</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Torneira de bancada (lavatorio e cuba)</t>
+          <t>Split inverter 30.000 BTU/h</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -8913,7 +8907,7 @@
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F99" s="13" t="n">
         <v>0</v>
@@ -8923,7 +8917,7 @@
         <v/>
       </c>
       <c r="H99" s="15" t="n">
-        <v>340</v>
+        <v>5400</v>
       </c>
       <c r="I99" s="16">
         <f>G99*H99</f>
@@ -8970,26 +8964,26 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>EQP-PORTAO</t>
+          <t>REV-REJ</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Automatizador de portao de correr</t>
+          <t>Rejunte epoxi/acrilico</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1</v>
+        <v>511.1</v>
       </c>
       <c r="F100" s="13" t="n">
         <v>0</v>
@@ -8999,7 +8993,7 @@
         <v/>
       </c>
       <c r="H100" s="15" t="n">
-        <v>2400</v>
+        <v>9</v>
       </c>
       <c r="I100" s="16">
         <f>G100*H100</f>
@@ -9046,26 +9040,26 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>MAR-ARM</t>
+          <t>LOU-VASO</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Armario de MDF sob medida</t>
+          <t>Bacia sanitaria com caixa acoplada</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E101" s="12" t="n">
-        <v>2.34</v>
+        <v>5</v>
       </c>
       <c r="F101" s="13" t="n">
         <v>0</v>
@@ -9075,7 +9069,7 @@
         <v/>
       </c>
       <c r="H101" s="15" t="n">
-        <v>980</v>
+        <v>780</v>
       </c>
       <c r="I101" s="16">
         <f>G101*H101</f>
@@ -9122,7 +9116,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>MAR-PRAT</t>
+          <t>MAR-CAB</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -9132,7 +9126,7 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Prateleira e nicho</t>
+          <t>Cabideiro e gaveteiro de closet</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -9141,7 +9135,7 @@
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="F102" s="13" t="n">
         <v>0</v>
@@ -9151,7 +9145,7 @@
         <v/>
       </c>
       <c r="H102" s="15" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="I102" s="16">
         <f>G102*H102</f>
@@ -9198,26 +9192,26 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>LOU-LAV</t>
+          <t>EQP-PISC</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Lavatorio / cuba de banheiro</t>
+          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>cj</t>
         </is>
       </c>
       <c r="E103" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F103" s="13" t="n">
         <v>0</v>
@@ -9227,7 +9221,7 @@
         <v/>
       </c>
       <c r="H103" s="15" t="n">
-        <v>420</v>
+        <v>2800</v>
       </c>
       <c r="I103" s="16">
         <f>G103*H103</f>
@@ -9274,7 +9268,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>LOU-CUBA</t>
+          <t>MET-TORN</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -9284,7 +9278,7 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
+          <t>Torneira de bancada (lavatorio e cuba)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -9293,7 +9287,7 @@
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F104" s="13" t="n">
         <v>0</v>
@@ -9303,7 +9297,7 @@
         <v/>
       </c>
       <c r="H104" s="15" t="n">
-        <v>690</v>
+        <v>340</v>
       </c>
       <c r="I104" s="16">
         <f>G104*H104</f>
@@ -9350,26 +9344,26 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>PIN-SELADOR</t>
+          <t>EQP-PORTAO</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Selador acrilico</t>
+          <t>Automatizador de portao de correr</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E105" s="12" t="n">
-        <v>73.5</v>
+        <v>1</v>
       </c>
       <c r="F105" s="13" t="n">
         <v>0</v>
@@ -9379,7 +9373,7 @@
         <v/>
       </c>
       <c r="H105" s="15" t="n">
-        <v>28</v>
+        <v>2400</v>
       </c>
       <c r="I105" s="16">
         <f>G105*H105</f>
@@ -9426,26 +9420,26 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>MET-ACESS</t>
+          <t>MAR-PRAT</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
+          <t>Prateleira e nicho</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F106" s="13" t="n">
         <v>0</v>
@@ -9455,7 +9449,7 @@
         <v/>
       </c>
       <c r="H106" s="15" t="n">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="I106" s="16">
         <f>G106*H106</f>
@@ -9502,17 +9496,17 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUG</t>
+          <t>LOU-LAV</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Tomada 2P+T 10 A com placa</t>
+          <t>Lavatorio / cuba de banheiro</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
@@ -9521,7 +9515,7 @@
         </is>
       </c>
       <c r="E107" s="12" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="F107" s="13" t="n">
         <v>0</v>
@@ -9531,7 +9525,7 @@
         <v/>
       </c>
       <c r="H107" s="15" t="n">
-        <v>28</v>
+        <v>420</v>
       </c>
       <c r="I107" s="16">
         <f>G107*H107</f>
@@ -9578,17 +9572,17 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>EQP-EXAUST</t>
+          <t>LOU-CUBA</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Exaustor / coifa</t>
+          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -9597,7 +9591,7 @@
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F108" s="13" t="n">
         <v>0</v>
@@ -9607,7 +9601,7 @@
         <v/>
       </c>
       <c r="H108" s="15" t="n">
-        <v>260</v>
+        <v>690</v>
       </c>
       <c r="I108" s="16">
         <f>G108*H108</f>
@@ -9654,26 +9648,26 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>MET-CHUV</t>
+          <t>PIN-SELADOR</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Chuveiro eletrico 220 V</t>
+          <t>Selador acrilico</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
-        <v>4</v>
+        <v>73.5</v>
       </c>
       <c r="F109" s="13" t="n">
         <v>0</v>
@@ -9683,7 +9677,7 @@
         <v/>
       </c>
       <c r="H109" s="15" t="n">
-        <v>320</v>
+        <v>28</v>
       </c>
       <c r="I109" s="16">
         <f>G109*H109</f>
@@ -9730,7 +9724,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>MET-REG</t>
+          <t>MET-ACESS</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -9740,7 +9734,7 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Registro de gaveta e de pressao</t>
+          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
@@ -9749,7 +9743,7 @@
         </is>
       </c>
       <c r="E110" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F110" s="13" t="n">
         <v>0</v>
@@ -9759,7 +9753,7 @@
         <v/>
       </c>
       <c r="H110" s="15" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="I110" s="16">
         <f>G110*H110</f>
@@ -9806,7 +9800,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>ELE-DR</t>
+          <t>ELE-TUG</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -9816,7 +9810,7 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor diferencial residual 30 mA</t>
+          <t>Tomada 2P+T 10 A com placa</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -9825,7 +9819,7 @@
         </is>
       </c>
       <c r="E111" s="12" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="F111" s="13" t="n">
         <v>0</v>
@@ -9835,7 +9829,7 @@
         <v/>
       </c>
       <c r="H111" s="15" t="n">
-        <v>180</v>
+        <v>28</v>
       </c>
       <c r="I111" s="16">
         <f>G111*H111</f>
@@ -9882,17 +9876,17 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>MET-DUCHA</t>
+          <t>EQP-EXAUST</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Ducha higienica com registro</t>
+          <t>Exaustor / coifa</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -9901,7 +9895,7 @@
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F112" s="13" t="n">
         <v>0</v>
@@ -9911,7 +9905,7 @@
         <v/>
       </c>
       <c r="H112" s="15" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="I112" s="16">
         <f>G112*H112</f>
@@ -9958,17 +9952,17 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>ELE-INT</t>
+          <t>MET-CHUV</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Interruptor simples e paralelo com placa</t>
+          <t>Chuveiro eletrico 220 V</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -9977,7 +9971,7 @@
         </is>
       </c>
       <c r="E113" s="12" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F113" s="13" t="n">
         <v>0</v>
@@ -9987,7 +9981,7 @@
         <v/>
       </c>
       <c r="H113" s="15" t="n">
-        <v>32</v>
+        <v>320</v>
       </c>
       <c r="I113" s="16">
         <f>G113*H113</f>
@@ -10034,7 +10028,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>LOU-ASSENTO</t>
+          <t>MET-REG</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -10044,7 +10038,7 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Assento sanitario com amortecedor</t>
+          <t>Registro de gaveta e de pressao</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -10053,7 +10047,7 @@
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F114" s="13" t="n">
         <v>0</v>
@@ -10063,7 +10057,7 @@
         <v/>
       </c>
       <c r="H114" s="15" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="I114" s="16">
         <f>G114*H114</f>
@@ -10110,7 +10104,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUE</t>
+          <t>ELE-DR</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -10120,7 +10114,7 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Tomada de uso especifico 20 A com placa</t>
+          <t>Disjuntor diferencial residual 30 mA</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
@@ -10129,7 +10123,7 @@
         </is>
       </c>
       <c r="E115" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F115" s="13" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v/>
       </c>
       <c r="H115" s="15" t="n">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="I115" s="16">
         <f>G115*H115</f>
@@ -10186,7 +10180,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>MET-ENGATE</t>
+          <t>MET-DUCHA</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -10196,7 +10190,7 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Engate flexivel</t>
+          <t>Ducha higienica com registro</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
@@ -10205,7 +10199,7 @@
         </is>
       </c>
       <c r="E116" s="12" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F116" s="13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v/>
       </c>
       <c r="H116" s="15" t="n">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="I116" s="16">
         <f>G116*H116</f>
@@ -10262,17 +10256,17 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN-T</t>
+          <t>ELE-INT</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Torneira de tanque e de jardim</t>
+          <t>Interruptor simples e paralelo com placa</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
@@ -10281,7 +10275,7 @@
         </is>
       </c>
       <c r="E117" s="12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F117" s="13" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v/>
       </c>
       <c r="H117" s="15" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="I117" s="16">
         <f>G117*H117</f>
@@ -10338,7 +10332,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>MET-VALV</t>
+          <t>LOU-ASSENTO</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -10348,7 +10342,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Valvula de escoamento e de lavatorio</t>
+          <t>Assento sanitario com amortecedor</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -10357,7 +10351,7 @@
         </is>
       </c>
       <c r="E118" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F118" s="13" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v/>
       </c>
       <c r="H118" s="15" t="n">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="I118" s="16">
         <f>G118*H118</f>
@@ -10414,17 +10408,17 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>MET-SIFAO</t>
+          <t>ELE-TUE</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Sifao flexivel</t>
+          <t>Tomada de uso especifico 20 A com placa</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -10433,7 +10427,7 @@
         </is>
       </c>
       <c r="E119" s="12" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F119" s="13" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v/>
       </c>
       <c r="H119" s="15" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="I119" s="16">
         <f>G119*H119</f>
@@ -10490,7 +10484,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>LOU-TANQUE</t>
+          <t>MET-ENGATE</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -10500,7 +10494,7 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Tanque de lavanderia</t>
+          <t>Engate flexivel</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -10509,7 +10503,7 @@
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F120" s="13" t="n">
         <v>0</v>
@@ -10519,7 +10513,7 @@
         <v/>
       </c>
       <c r="H120" s="15" t="n">
-        <v>320</v>
+        <v>22</v>
       </c>
       <c r="I120" s="16">
         <f>G120*H120</f>
@@ -10566,17 +10560,17 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>ELE-DPS</t>
+          <t>MET-TORN-T</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Dispositivo de protecao contra surtos</t>
+          <t>Torneira de tanque e de jardim</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -10585,7 +10579,7 @@
         </is>
       </c>
       <c r="E121" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="13" t="n">
         <v>0</v>
@@ -10595,7 +10589,7 @@
         <v/>
       </c>
       <c r="H121" s="15" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="I121" s="16">
         <f>G121*H121</f>
@@ -10640,59 +10634,363 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="22" t="n"/>
-      <c r="B122" s="22" t="n"/>
-      <c r="C122" s="23" t="inlineStr">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>MET-VALV</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>loucas</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>Valvula de escoamento e de lavatorio</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="14">
+        <f>E122*(1+F122)</f>
+        <v/>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="I122" s="16">
+        <f>G122*H122</f>
+        <v/>
+      </c>
+      <c r="J122" s="17" t="n"/>
+      <c r="K122" s="17" t="n"/>
+      <c r="L122" s="17" t="n"/>
+      <c r="M122" s="17" t="n"/>
+      <c r="N122" s="17" t="n"/>
+      <c r="O122" s="18">
+        <f>COUNT(J122:N122)</f>
+        <v/>
+      </c>
+      <c r="P122" s="19">
+        <f>IF(O122=0,"",MIN(J122:N122))</f>
+        <v/>
+      </c>
+      <c r="Q122" s="10">
+        <f>IF(O122=0,"",INDEX($J$3:$N$3,MATCH(P122,J122:N122,0)))</f>
+        <v/>
+      </c>
+      <c r="R122" s="16">
+        <f>IF(O122=0,"",AVERAGE(J122:N122))</f>
+        <v/>
+      </c>
+      <c r="S122" s="20">
+        <f>IF(O122&lt;2,"",MAX(J122:N122)/P122)</f>
+        <v/>
+      </c>
+      <c r="T122" s="19">
+        <f>IF(O122=0,"",G122*P122)</f>
+        <v/>
+      </c>
+      <c r="U122" s="21">
+        <f>IF(OR(O122=0,I122=0),"",T122/I122-1)</f>
+        <v/>
+      </c>
+      <c r="V122" s="18">
+        <f>IF(O122=0,"PENDENTE",IF(O122&gt;=5,"COMPLETO","PARCIAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>MET-SIFAO</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>loucas</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>Sifao flexivel</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F123" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="14">
+        <f>E123*(1+F123)</f>
+        <v/>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="I123" s="16">
+        <f>G123*H123</f>
+        <v/>
+      </c>
+      <c r="J123" s="17" t="n"/>
+      <c r="K123" s="17" t="n"/>
+      <c r="L123" s="17" t="n"/>
+      <c r="M123" s="17" t="n"/>
+      <c r="N123" s="17" t="n"/>
+      <c r="O123" s="18">
+        <f>COUNT(J123:N123)</f>
+        <v/>
+      </c>
+      <c r="P123" s="19">
+        <f>IF(O123=0,"",MIN(J123:N123))</f>
+        <v/>
+      </c>
+      <c r="Q123" s="10">
+        <f>IF(O123=0,"",INDEX($J$3:$N$3,MATCH(P123,J123:N123,0)))</f>
+        <v/>
+      </c>
+      <c r="R123" s="16">
+        <f>IF(O123=0,"",AVERAGE(J123:N123))</f>
+        <v/>
+      </c>
+      <c r="S123" s="20">
+        <f>IF(O123&lt;2,"",MAX(J123:N123)/P123)</f>
+        <v/>
+      </c>
+      <c r="T123" s="19">
+        <f>IF(O123=0,"",G123*P123)</f>
+        <v/>
+      </c>
+      <c r="U123" s="21">
+        <f>IF(OR(O123=0,I123=0),"",T123/I123-1)</f>
+        <v/>
+      </c>
+      <c r="V123" s="18">
+        <f>IF(O123=0,"PENDENTE",IF(O123&gt;=5,"COMPLETO","PARCIAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>LOU-TANQUE</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>loucas</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>Tanque de lavanderia</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="14">
+        <f>E124*(1+F124)</f>
+        <v/>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>320</v>
+      </c>
+      <c r="I124" s="16">
+        <f>G124*H124</f>
+        <v/>
+      </c>
+      <c r="J124" s="17" t="n"/>
+      <c r="K124" s="17" t="n"/>
+      <c r="L124" s="17" t="n"/>
+      <c r="M124" s="17" t="n"/>
+      <c r="N124" s="17" t="n"/>
+      <c r="O124" s="18">
+        <f>COUNT(J124:N124)</f>
+        <v/>
+      </c>
+      <c r="P124" s="19">
+        <f>IF(O124=0,"",MIN(J124:N124))</f>
+        <v/>
+      </c>
+      <c r="Q124" s="10">
+        <f>IF(O124=0,"",INDEX($J$3:$N$3,MATCH(P124,J124:N124,0)))</f>
+        <v/>
+      </c>
+      <c r="R124" s="16">
+        <f>IF(O124=0,"",AVERAGE(J124:N124))</f>
+        <v/>
+      </c>
+      <c r="S124" s="20">
+        <f>IF(O124&lt;2,"",MAX(J124:N124)/P124)</f>
+        <v/>
+      </c>
+      <c r="T124" s="19">
+        <f>IF(O124=0,"",G124*P124)</f>
+        <v/>
+      </c>
+      <c r="U124" s="21">
+        <f>IF(OR(O124=0,I124=0),"",T124/I124-1)</f>
+        <v/>
+      </c>
+      <c r="V124" s="18">
+        <f>IF(O124=0,"PENDENTE",IF(O124&gt;=5,"COMPLETO","PARCIAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>ELE-DPS</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>eletrica</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>Dispositivo de protecao contra surtos</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="14">
+        <f>E125*(1+F125)</f>
+        <v/>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="I125" s="16">
+        <f>G125*H125</f>
+        <v/>
+      </c>
+      <c r="J125" s="17" t="n"/>
+      <c r="K125" s="17" t="n"/>
+      <c r="L125" s="17" t="n"/>
+      <c r="M125" s="17" t="n"/>
+      <c r="N125" s="17" t="n"/>
+      <c r="O125" s="18">
+        <f>COUNT(J125:N125)</f>
+        <v/>
+      </c>
+      <c r="P125" s="19">
+        <f>IF(O125=0,"",MIN(J125:N125))</f>
+        <v/>
+      </c>
+      <c r="Q125" s="10">
+        <f>IF(O125=0,"",INDEX($J$3:$N$3,MATCH(P125,J125:N125,0)))</f>
+        <v/>
+      </c>
+      <c r="R125" s="16">
+        <f>IF(O125=0,"",AVERAGE(J125:N125))</f>
+        <v/>
+      </c>
+      <c r="S125" s="20">
+        <f>IF(O125&lt;2,"",MAX(J125:N125)/P125)</f>
+        <v/>
+      </c>
+      <c r="T125" s="19">
+        <f>IF(O125=0,"",G125*P125)</f>
+        <v/>
+      </c>
+      <c r="U125" s="21">
+        <f>IF(OR(O125=0,I125=0),"",T125/I125-1)</f>
+        <v/>
+      </c>
+      <c r="V125" s="18">
+        <f>IF(O125=0,"PENDENTE",IF(O125&gt;=5,"COMPLETO","PARCIAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="22" t="n"/>
+      <c r="B126" s="22" t="n"/>
+      <c r="C126" s="23" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="D122" s="22" t="n"/>
-      <c r="E122" s="22" t="n"/>
-      <c r="F122" s="22" t="n"/>
-      <c r="G122" s="22" t="n"/>
-      <c r="H122" s="22" t="n"/>
-      <c r="I122" s="24">
-        <f>SUM(I4:I121)</f>
-        <v/>
-      </c>
-      <c r="J122" s="22" t="n"/>
-      <c r="K122" s="22" t="n"/>
-      <c r="L122" s="22" t="n"/>
-      <c r="M122" s="22" t="n"/>
-      <c r="N122" s="22" t="n"/>
-      <c r="O122" s="22" t="n"/>
-      <c r="P122" s="22" t="n"/>
-      <c r="Q122" s="22" t="n"/>
-      <c r="R122" s="22" t="n"/>
-      <c r="S122" s="22" t="n"/>
-      <c r="T122" s="24">
-        <f>SUM(T4:T121)</f>
-        <v/>
-      </c>
-      <c r="U122" s="25">
-        <f>IF(T122=0,"",T122/I122-1)</f>
-        <v/>
-      </c>
-      <c r="V122" s="22" t="n"/>
-    </row>
-    <row r="124">
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Itens: 118 · linhas cotáveis com especificação completa: 98 · com lacuna a esclarecer com o fornecedor: 64</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="C125" s="2" t="inlineStr">
+      <c r="D126" s="22" t="n"/>
+      <c r="E126" s="22" t="n"/>
+      <c r="F126" s="22" t="n"/>
+      <c r="G126" s="22" t="n"/>
+      <c r="H126" s="22" t="n"/>
+      <c r="I126" s="24">
+        <f>SUM(I4:I125)</f>
+        <v/>
+      </c>
+      <c r="J126" s="22" t="n"/>
+      <c r="K126" s="22" t="n"/>
+      <c r="L126" s="22" t="n"/>
+      <c r="M126" s="22" t="n"/>
+      <c r="N126" s="22" t="n"/>
+      <c r="O126" s="22" t="n"/>
+      <c r="P126" s="22" t="n"/>
+      <c r="Q126" s="22" t="n"/>
+      <c r="R126" s="22" t="n"/>
+      <c r="S126" s="22" t="n"/>
+      <c r="T126" s="24">
+        <f>SUM(T4:T125)</f>
+        <v/>
+      </c>
+      <c r="U126" s="25">
+        <f>IF(T126=0,"",T126/I126-1)</f>
+        <v/>
+      </c>
+      <c r="V126" s="22" t="n"/>
+    </row>
+    <row r="128">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Itens: 122 · linhas cotáveis com especificação completa: 97 · com lacuna a esclarecer com o fornecedor: 69</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>Passe o mouse sobre a DESCRIÇÃO para ver a especificação completa, as normas e a lacuna de cada item.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:V121"/>
-  <conditionalFormatting sqref="V4:V121">
+  <autoFilter ref="A3:V125"/>
+  <conditionalFormatting sqref="V4:V125">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PENDENTE"</formula>
     </cfRule>
@@ -10703,7 +11001,7 @@
       <formula>"COMPLETO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U121">
+  <conditionalFormatting sqref="U4:U125">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0.15</formula>
     </cfRule>
@@ -10711,7 +11009,7 @@
       <formula>-0.15</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S121">
+  <conditionalFormatting sqref="S4:S125">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>1.5</formula>
     </cfRule>
@@ -10812,7 +11110,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A5,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A5,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D5" s="21">
@@ -10824,7 +11122,7 @@
         <v/>
       </c>
       <c r="F5" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A5,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A5,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G5" s="21">
@@ -10832,7 +11130,7 @@
         <v/>
       </c>
       <c r="H5" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A5,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A5,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I5" s="21">
@@ -10850,7 +11148,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A6,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A6,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D6" s="21">
@@ -10862,7 +11160,7 @@
         <v/>
       </c>
       <c r="F6" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A6,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A6,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G6" s="21">
@@ -10870,7 +11168,7 @@
         <v/>
       </c>
       <c r="H6" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A6,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A6,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I6" s="21">
@@ -10888,7 +11186,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A7,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A7,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D7" s="21">
@@ -10900,7 +11198,7 @@
         <v/>
       </c>
       <c r="F7" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A7,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A7,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G7" s="21">
@@ -10908,7 +11206,7 @@
         <v/>
       </c>
       <c r="H7" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A7,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A7,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I7" s="21">
@@ -10926,7 +11224,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A8,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A8,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D8" s="21">
@@ -10938,7 +11236,7 @@
         <v/>
       </c>
       <c r="F8" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A8,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A8,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G8" s="21">
@@ -10946,7 +11244,7 @@
         <v/>
       </c>
       <c r="H8" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A8,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A8,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I8" s="21">
@@ -10964,7 +11262,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A9,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A9,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D9" s="21">
@@ -10976,7 +11274,7 @@
         <v/>
       </c>
       <c r="F9" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A9,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A9,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G9" s="21">
@@ -10984,7 +11282,7 @@
         <v/>
       </c>
       <c r="H9" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A9,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A9,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I9" s="21">
@@ -11002,7 +11300,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A10,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A10,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D10" s="21">
@@ -11014,7 +11312,7 @@
         <v/>
       </c>
       <c r="F10" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A10,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A10,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G10" s="21">
@@ -11022,7 +11320,7 @@
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A10,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A10,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I10" s="21">
@@ -11033,14 +11331,14 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B11" s="18" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C11" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A11,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A11,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D11" s="21">
@@ -11052,7 +11350,7 @@
         <v/>
       </c>
       <c r="F11" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A11,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A11,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G11" s="21">
@@ -11060,7 +11358,7 @@
         <v/>
       </c>
       <c r="H11" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A11,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A11,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I11" s="21">
@@ -11071,14 +11369,14 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B12" s="18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C12" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A12,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A12,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D12" s="21">
@@ -11090,7 +11388,7 @@
         <v/>
       </c>
       <c r="F12" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A12,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A12,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G12" s="21">
@@ -11098,7 +11396,7 @@
         <v/>
       </c>
       <c r="H12" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A12,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A12,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I12" s="21">
@@ -11109,14 +11407,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C13" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A13,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A13,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D13" s="21">
@@ -11128,7 +11426,7 @@
         <v/>
       </c>
       <c r="F13" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A13,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A13,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G13" s="21">
@@ -11136,7 +11434,7 @@
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A13,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A13,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I13" s="21">
@@ -11147,14 +11445,14 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C14" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A14,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A14,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D14" s="21">
@@ -11166,7 +11464,7 @@
         <v/>
       </c>
       <c r="F14" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A14,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A14,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G14" s="21">
@@ -11174,7 +11472,7 @@
         <v/>
       </c>
       <c r="H14" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A14,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A14,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I14" s="21">
@@ -11185,14 +11483,14 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C15" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A15,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A15,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D15" s="21">
@@ -11204,7 +11502,7 @@
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A15,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A15,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G15" s="21">
@@ -11212,7 +11510,7 @@
         <v/>
       </c>
       <c r="H15" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A15,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A15,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I15" s="21">
@@ -11223,14 +11521,14 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C16" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A16,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A16,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D16" s="21">
@@ -11242,7 +11540,7 @@
         <v/>
       </c>
       <c r="F16" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A16,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A16,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G16" s="21">
@@ -11250,7 +11548,7 @@
         <v/>
       </c>
       <c r="H16" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A16,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A16,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I16" s="21">
@@ -11261,14 +11559,14 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>cobertura</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C17" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A17,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A17,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D17" s="21">
@@ -11280,7 +11578,7 @@
         <v/>
       </c>
       <c r="F17" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A17,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A17,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G17" s="21">
@@ -11288,7 +11586,7 @@
         <v/>
       </c>
       <c r="H17" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A17,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A17,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I17" s="21">
@@ -11299,14 +11597,14 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>cobertura</t>
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C18" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A18,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A18,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D18" s="21">
@@ -11318,7 +11616,7 @@
         <v/>
       </c>
       <c r="F18" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A18,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A18,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G18" s="21">
@@ -11326,7 +11624,7 @@
         <v/>
       </c>
       <c r="H18" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A18,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A18,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I18" s="21">
@@ -11344,7 +11642,7 @@
         <v>6</v>
       </c>
       <c r="C19" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A19,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A19,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D19" s="21">
@@ -11356,7 +11654,7 @@
         <v/>
       </c>
       <c r="F19" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A19,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A19,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G19" s="21">
@@ -11364,7 +11662,7 @@
         <v/>
       </c>
       <c r="H19" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A19,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A19,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I19" s="21">
@@ -11382,7 +11680,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A20,COTAÇÃO!$I$4:$I$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A20,COTAÇÃO!$I$4:$I$125)</f>
         <v/>
       </c>
       <c r="D20" s="21">
@@ -11394,7 +11692,7 @@
         <v/>
       </c>
       <c r="F20" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$121,$A20,COTAÇÃO!$T$4:$T$121)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$125,$A20,COTAÇÃO!$T$4:$T$125)</f>
         <v/>
       </c>
       <c r="G20" s="21">
@@ -11402,7 +11700,7 @@
         <v/>
       </c>
       <c r="H20" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$121,$A20,COTAÇÃO!$O$4:$O$121,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$125,$A20,COTAÇÃO!$O$4:$O$125,"&gt;0")</f>
         <v/>
       </c>
       <c r="I20" s="21">
@@ -11575,7 +11873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14018,7 +14316,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>BRI-RIPA</t>
+          <t>FAC-BASE</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -14028,16 +14326,16 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Ripa de fachada: tubular de aluminio 50 x 20 x 1,2 mm</t>
+          <t>Basecoat de regularizacao sobre placa cimenticia</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E61" s="14" t="n">
-        <v>205.5</v>
+        <v>309.2</v>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
       <c r="G61" s="11" t="inlineStr"/>
@@ -14055,7 +14353,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>BRI-MEC</t>
+          <t>FAC-MAO</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -14065,16 +14363,16 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Mecanismo de brise movel: guia, roldana e trava</t>
+          <t>Mao de obra de fachada (basecoat, tela, junta e pintura)</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>cj</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E62" s="14" t="n">
-        <v>2</v>
+        <v>309.2</v>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
       <c r="G62" s="11" t="inlineStr"/>
@@ -14092,7 +14390,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>BRI-TRAV</t>
+          <t>BRI-RIPA</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -14102,7 +14400,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Travessa de brise: U 50x25x1,2 aluminio</t>
+          <t>Ripa de fachada: tubular de aluminio 50 x 20 x 1,2 mm</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -14111,7 +14409,7 @@
         </is>
       </c>
       <c r="E63" s="14" t="n">
-        <v>33.6</v>
+        <v>205.5</v>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr"/>
@@ -14129,7 +14427,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>BRI-FIX</t>
+          <t>FAC-TINTA</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -14139,16 +14437,16 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Fixacao de travessa no montante</t>
+          <t>Tinta acrilica elastomerica lisa com biocida, 2 demaos</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E64" s="14" t="n">
-        <v>66</v>
+        <v>88.3</v>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
       <c r="G64" s="11" t="inlineStr"/>
@@ -14166,26 +14464,26 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO2</t>
+          <t>FAC-JUNTA</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
+          <t>Tratamento de junta externa: fundo de junta e selante PU</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E65" s="14" t="n">
-        <v>76.31999999999999</v>
+        <v>386.5</v>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
       <c r="G65" s="11" t="inlineStr"/>
@@ -14203,26 +14501,26 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>EXT-BLOCO</t>
+          <t>BRI-MEC</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
+          <t>Mecanismo de brise movel: guia, roldana e trava</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>cj</t>
         </is>
       </c>
       <c r="E66" s="14" t="n">
-        <v>3118</v>
+        <v>2</v>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
       <c r="G66" s="11" t="inlineStr"/>
@@ -14240,26 +14538,26 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-EST</t>
+          <t>FAC-TELA</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Piscina: casca de concreto armado 150 mm</t>
+          <t>Tela de fibra de vidro alcali-resistente, embutida no basecoat</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E67" s="14" t="n">
-        <v>4.57</v>
+        <v>340.1</v>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
       <c r="G67" s="11" t="inlineStr"/>
@@ -14277,26 +14575,26 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-REV</t>
+          <t>BRI-TRAV</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Piscina: revestimento de fundo e paredes</t>
+          <t>Travessa de brise: U 50x25x1,2 aluminio</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E68" s="14" t="n">
-        <v>30.43</v>
+        <v>33.6</v>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
       <c r="G68" s="11" t="inlineStr"/>
@@ -14314,17 +14612,17 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>EXT-VASO</t>
+          <t>BRI-FIX</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Vaso e planta em vaso</t>
+          <t>Fixacao de travessa no montante</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -14333,7 +14631,7 @@
         </is>
       </c>
       <c r="E69" s="14" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
       <c r="G69" s="11" t="inlineStr"/>
@@ -14351,7 +14649,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>EXT-GRAMA</t>
+          <t>EXT-PISO2</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -14361,7 +14659,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Grama e canteiro</t>
+          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -14370,7 +14668,7 @@
         </is>
       </c>
       <c r="E70" s="14" t="n">
-        <v>137.16</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
       <c r="G70" s="11" t="inlineStr"/>
@@ -14388,7 +14686,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>EXT-HIDROF</t>
+          <t>EXT-BLOCO</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -14398,16 +14696,16 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Hidrofugante incolor no muro aparente</t>
+          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E71" s="14" t="n">
-        <v>249.5</v>
+        <v>3118</v>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr"/>
@@ -14425,7 +14723,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>EXT-ARV</t>
+          <t>EXT-PISC-EST</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -14435,16 +14733,16 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Arvore de porte</t>
+          <t>Piscina: casca de concreto armado 150 mm</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E72" s="14" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr"/>
@@ -14462,7 +14760,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO1</t>
+          <t>EXT-PISC-REV</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -14472,7 +14770,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>faixa seca da piscina: porcelanato externo claro R11</t>
+          <t>Piscina: revestimento de fundo e paredes</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -14481,7 +14779,7 @@
         </is>
       </c>
       <c r="E73" s="14" t="n">
-        <v>24.3</v>
+        <v>30.43</v>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
       <c r="G73" s="11" t="inlineStr"/>
@@ -14499,7 +14797,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>EXT-BORDA</t>
+          <t>EXT-VASO</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -14509,16 +14807,16 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>Borda de piscina</t>
+          <t>Vaso e planta em vaso</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E74" s="14" t="n">
-        <v>17.4</v>
+        <v>24</v>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
       <c r="G74" s="11" t="inlineStr"/>
@@ -14536,7 +14834,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO3</t>
+          <t>EXT-GRAMA</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -14546,7 +14844,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>passeio e acesso: piso drenante intertravado claro</t>
+          <t>Grama e canteiro</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -14555,7 +14853,7 @@
         </is>
       </c>
       <c r="E75" s="14" t="n">
-        <v>30.96</v>
+        <v>137.16</v>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
       <c r="G75" s="11" t="inlineStr"/>
@@ -14573,7 +14871,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO4</t>
+          <t>EXT-HIDROF</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -14583,7 +14881,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>varanda do pavimento superior: porcelanato externo claro R11</t>
+          <t>Hidrofugante incolor no muro aparente</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -14592,7 +14890,7 @@
         </is>
       </c>
       <c r="E76" s="14" t="n">
-        <v>14.04</v>
+        <v>249.5</v>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
       <c r="G76" s="11" t="inlineStr"/>
@@ -14610,7 +14908,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>EXT-GRAUTE</t>
+          <t>EXT-ARV</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -14620,16 +14918,16 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Graute de cinta e pilarete do muro</t>
+          <t>Arvore de porte</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E77" s="14" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="F77" s="11" t="inlineStr"/>
       <c r="G77" s="11" t="inlineStr"/>
@@ -14647,99 +14945,91 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>MO-MON</t>
+          <t>EXT-PISO1</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>Mao de obra de montagem</t>
+          <t>faixa seca da piscina: porcelanato externo claro R11</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E78" s="14" t="n">
-        <v>681</v>
-      </c>
-      <c r="F78" s="11" t="inlineStr">
-        <is>
-          <t>hora de equipe, com encargos e EPI</t>
-        </is>
-      </c>
+        <v>24.3</v>
+      </c>
+      <c r="F78" s="11" t="inlineStr"/>
       <c r="G78" s="11" t="inlineStr"/>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>convencao coletiva vigente e composicao de encargos</t>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
         </is>
       </c>
       <c r="I78" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>MO-FAB</t>
+          <t>EXT-BORDA</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Mao de obra de fabrica</t>
+          <t>Borda de piscina</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E79" s="14" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="F79" s="11" t="inlineStr">
-        <is>
-          <t>hora de equipe, com encargos e EPI</t>
-        </is>
-      </c>
+        <v>17.4</v>
+      </c>
+      <c r="F79" s="11" t="inlineStr"/>
       <c r="G79" s="11" t="inlineStr"/>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>convencao coletiva vigente e composicao de encargos</t>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
         </is>
       </c>
       <c r="I79" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>REV-PISO</t>
+          <t>EXT-PISO3</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>Piso interno (porcelanato retificado)</t>
+          <t>passeio e acesso: piso drenante intertravado claro</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -14748,43 +15038,35 @@
         </is>
       </c>
       <c r="E80" s="14" t="n">
-        <v>355.6</v>
-      </c>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
-        </is>
-      </c>
-      <c r="G80" s="11" t="inlineStr">
-        <is>
-          <t>NBR 13818, NBR 15463</t>
-        </is>
-      </c>
+        <v>30.96</v>
+      </c>
+      <c r="F80" s="11" t="inlineStr"/>
+      <c r="G80" s="11" t="inlineStr"/>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
         </is>
       </c>
       <c r="I80" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>LOU-BOX</t>
+          <t>EXT-PISO4</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Box de vidro temperado 8 mm, 1.900 mm de altura</t>
+          <t>varanda do pavimento superior: porcelanato externo claro R11</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -14793,105 +15075,93 @@
         </is>
       </c>
       <c r="E81" s="14" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="F81" s="11" t="inlineStr">
-        <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
-        </is>
-      </c>
-      <c r="G81" s="11" t="inlineStr">
-        <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
+        <v>14.04</v>
+      </c>
+      <c r="F81" s="11" t="inlineStr"/>
+      <c r="G81" s="11" t="inlineStr"/>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
         </is>
       </c>
       <c r="I81" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>MAR-GAB</t>
+          <t>EXT-GRAUTE</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>Gabinete sob bancada, sob medida</t>
+          <t>Graute de cinta e pilarete do muro</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E82" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="F82" s="11" t="inlineStr">
-        <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
+        <v>2.99</v>
+      </c>
+      <c r="F82" s="11" t="inlineStr"/>
       <c r="G82" s="11" t="inlineStr"/>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
         </is>
       </c>
       <c r="I82" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>PIN-PAREDE</t>
+          <t>MO-MON</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Pintura de parede interna (latex acrilico, 2 demaos)</t>
+          <t>Mao de obra de montagem</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E83" s="14" t="n">
-        <v>558.7</v>
+        <v>681</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
-        </is>
-      </c>
-      <c r="G83" s="11" t="inlineStr">
-        <is>
-          <t>NBR 11702, NBR 13245</t>
-        </is>
-      </c>
-      <c r="H83" s="11" t="inlineStr"/>
+          <t>hora de equipe, com encargos e EPI</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr"/>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>convencao coletiva vigente e composicao de encargos</t>
+        </is>
+      </c>
       <c r="I83" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -14901,40 +15171,36 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>REV-PAREDE</t>
+          <t>MO-FAB</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Revestimento ceramico de parede em area molhada</t>
+          <t>Mao de obra de fabrica</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E84" s="14" t="n">
-        <v>137.9</v>
+        <v>46.4</v>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
-        </is>
-      </c>
-      <c r="G84" s="11" t="inlineStr">
-        <is>
-          <t>NBR 13818, NBR 15463</t>
-        </is>
-      </c>
+          <t>hora de equipe, com encargos e EPI</t>
+        </is>
+      </c>
+      <c r="G84" s="11" t="inlineStr"/>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>convencao coletiva vigente e composicao de encargos</t>
         </is>
       </c>
       <c r="I84" s="18" t="inlineStr">
@@ -14946,40 +15212,40 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT18</t>
+          <t>REV-PISO</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 18.000 BTU/h</t>
+          <t>Piso interno (porcelanato retificado)</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E85" s="14" t="n">
-        <v>4</v>
+        <v>355.6</v>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I85" s="18" t="inlineStr">
@@ -14991,17 +15257,17 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>MAR-TAMPO</t>
+          <t>LOU-BOX</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>Tampo de bancada (quartzo/granito)</t>
+          <t>Box de vidro temperado 8 mm, 1.900 mm de altura</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -15010,17 +15276,21 @@
         </is>
       </c>
       <c r="E86" s="14" t="n">
-        <v>7.17</v>
+        <v>32.3</v>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G86" s="11" t="inlineStr"/>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I86" s="18" t="inlineStr">
@@ -15032,40 +15302,36 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>REV-ARG</t>
+          <t>MAR-GAB</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Argamassa colante AC-III e regularizacao</t>
+          <t>Gabinete sob bancada, sob medida</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E87" s="14" t="n">
-        <v>493.5</v>
+        <v>12</v>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
-        </is>
-      </c>
-      <c r="G87" s="11" t="inlineStr">
-        <is>
-          <t>NBR 13818, NBR 15463</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr"/>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I87" s="18" t="inlineStr">
@@ -15077,7 +15343,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>REV-RODAPE</t>
+          <t>REV-PAREDE</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -15087,16 +15353,16 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Rodape (poliestireno 100 mm, pintado)</t>
+          <t>Revestimento ceramico de parede em area molhada</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
-        <v>253.2</v>
+        <v>155.5</v>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
@@ -15122,7 +15388,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>PIN-FORRO</t>
+          <t>PIN-PAREDE</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -15132,7 +15398,7 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Pintura de forro (latex PVA fosco)</t>
+          <t>Pintura de parede interna (latex acrilico, 2 demaos)</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -15141,7 +15407,7 @@
         </is>
       </c>
       <c r="E89" s="14" t="n">
-        <v>323.3</v>
+        <v>558.7</v>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
@@ -15163,38 +15429,42 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>PIN-TINTA</t>
+          <t>EQP-SPLIT18</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
+          <t>Split inverter 18.000 BTU/h</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
-        <v>176.4</v>
+        <v>4</v>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>NBR 11702, NBR 13245</t>
-        </is>
-      </c>
-      <c r="H90" s="11" t="inlineStr"/>
+          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
+        </is>
+      </c>
+      <c r="H90" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+        </is>
+      </c>
       <c r="I90" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -15204,17 +15474,17 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>PIN-EXT</t>
+          <t>REV-ARG</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Pintura externa (acrilico elastomerico no muro)</t>
+          <t>Argamassa colante AC-III e regularizacao</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -15223,19 +15493,23 @@
         </is>
       </c>
       <c r="E91" s="14" t="n">
-        <v>249.5</v>
+        <v>511.1</v>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>NBR 11702, NBR 13245</t>
-        </is>
-      </c>
-      <c r="H91" s="11" t="inlineStr"/>
+          <t>NBR 13818, NBR 15463</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+        </is>
+      </c>
       <c r="I91" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -15245,40 +15519,36 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT9</t>
+          <t>MAR-TAMPO</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 9.000 BTU/h</t>
+          <t>Tampo de bancada (quartzo/granito)</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
-        <v>3</v>
+        <v>7.17</v>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
-        </is>
-      </c>
-      <c r="G92" s="11" t="inlineStr">
-        <is>
-          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G92" s="11" t="inlineStr"/>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I92" s="18" t="inlineStr">
@@ -15290,40 +15560,40 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>ELE-LUM</t>
+          <t>REV-RODAPE</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Luminaria LED embutida no forro</t>
+          <t>Rodape (poliestireno 100 mm, pintado)</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E93" s="14" t="n">
-        <v>58</v>
+        <v>253.2</v>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>fluxo luminoso e temperatura de cor por ambiente: depende de projeto luminotecnico, que e pendencia aberta — a quantidade aqui e regra declarada</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I93" s="18" t="inlineStr">
@@ -15335,42 +15605,38 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT30</t>
+          <t>PIN-FORRO</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 30.000 BTU/h</t>
+          <t>Pintura de forro (latex PVA fosco)</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
-        <v>1</v>
+        <v>323.3</v>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
+          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
-        </is>
-      </c>
-      <c r="H94" s="11" t="inlineStr">
-        <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
-        </is>
-      </c>
+          <t>NBR 11702, NBR 13245</t>
+        </is>
+      </c>
+      <c r="H94" s="11" t="inlineStr"/>
       <c r="I94" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -15380,42 +15646,38 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>REV-REJ</t>
+          <t>PIN-TINTA</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Rejunte epoxi/acrilico</t>
+          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E95" s="14" t="n">
-        <v>493.5</v>
+        <v>176.4</v>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
+          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
         </is>
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>NBR 13818, NBR 15463</t>
-        </is>
-      </c>
-      <c r="H95" s="11" t="inlineStr">
-        <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
-        </is>
-      </c>
+          <t>NBR 11702, NBR 13245</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr"/>
       <c r="I95" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -15425,17 +15687,17 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>LOU-VASO</t>
+          <t>EQP-SPLIT9</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>Bacia sanitaria com caixa acoplada</t>
+          <t>Split inverter 9.000 BTU/h</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -15444,21 +15706,21 @@
         </is>
       </c>
       <c r="E96" s="14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I96" s="18" t="inlineStr">
@@ -15470,7 +15732,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>MAR-CAB</t>
+          <t>MAR-ARM</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
@@ -15480,16 +15742,16 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Cabideiro e gaveteiro de closet</t>
+          <t>Armario de MDF sob medida</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E97" s="14" t="n">
-        <v>12</v>
+        <v>5.94</v>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
@@ -15511,36 +15773,40 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>EQP-PISC</t>
+          <t>ELE-LUM</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
+          <t>Luminaria LED embutida no forro</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>cj</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
-        </is>
-      </c>
-      <c r="G98" s="11" t="inlineStr"/>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>fluxo luminoso e temperatura de cor por ambiente: depende de projeto luminotecnico, que e pendencia aberta — a quantidade aqui e regra declarada</t>
         </is>
       </c>
       <c r="I98" s="18" t="inlineStr">
@@ -15552,17 +15818,17 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN</t>
+          <t>EQP-SPLIT30</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Torneira de bancada (lavatorio e cuba)</t>
+          <t>Split inverter 30.000 BTU/h</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -15571,21 +15837,21 @@
         </is>
       </c>
       <c r="E99" s="14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I99" s="18" t="inlineStr">
@@ -15597,36 +15863,40 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>EQP-PORTAO</t>
+          <t>REV-REJ</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Automatizador de portao de correr</t>
+          <t>Rejunte epoxi/acrilico</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
-        <v>1</v>
+        <v>511.1</v>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
-        </is>
-      </c>
-      <c r="G100" s="11" t="inlineStr"/>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>NBR 13818, NBR 15463</t>
+        </is>
+      </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I100" s="18" t="inlineStr">
@@ -15638,36 +15908,40 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>MAR-ARM</t>
+          <t>LOU-VASO</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Armario de MDF sob medida</t>
+          <t>Bacia sanitaria com caixa acoplada</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E101" s="14" t="n">
-        <v>2.34</v>
+        <v>5</v>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G101" s="11" t="inlineStr"/>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I101" s="18" t="inlineStr">
@@ -15679,7 +15953,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>MAR-PRAT</t>
+          <t>MAR-CAB</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -15689,7 +15963,7 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Prateleira e nicho</t>
+          <t>Cabideiro e gaveteiro de closet</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -15698,7 +15972,7 @@
         </is>
       </c>
       <c r="E102" s="14" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
@@ -15720,40 +15994,36 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>LOU-LAV</t>
+          <t>EQP-PISC</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Lavatorio / cuba de banheiro</t>
+          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>cj</t>
         </is>
       </c>
       <c r="E103" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
-        </is>
-      </c>
-      <c r="G103" s="11" t="inlineStr">
-        <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr"/>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I103" s="18" t="inlineStr">
@@ -15765,7 +16035,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>LOU-CUBA</t>
+          <t>MET-TORN</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -15775,7 +16045,7 @@
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
+          <t>Torneira de bancada (lavatorio e cuba)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -15784,7 +16054,7 @@
         </is>
       </c>
       <c r="E104" s="14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
@@ -15810,38 +16080,38 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>PIN-SELADOR</t>
+          <t>EQP-PORTAO</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Selador acrilico</t>
+          <t>Automatizador de portao de correr</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E105" s="14" t="n">
-        <v>73.5</v>
+        <v>1</v>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
-        </is>
-      </c>
-      <c r="G105" s="11" t="inlineStr">
-        <is>
-          <t>NBR 11702, NBR 13245</t>
-        </is>
-      </c>
-      <c r="H105" s="11" t="inlineStr"/>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr"/>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+        </is>
+      </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -15851,40 +16121,36 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>MET-ACESS</t>
+          <t>MAR-PRAT</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
+          <t>Prateleira e nicho</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
-        <v>24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
-        </is>
-      </c>
-      <c r="G106" s="11" t="inlineStr">
-        <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr"/>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I106" s="18" t="inlineStr">
@@ -15896,17 +16162,17 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUG</t>
+          <t>LOU-LAV</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Tomada 2P+T 10 A com placa</t>
+          <t>Lavatorio / cuba de banheiro</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
@@ -15915,19 +16181,23 @@
         </is>
       </c>
       <c r="E107" s="14" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H107" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I107" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -15937,17 +16207,17 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>EQP-EXAUST</t>
+          <t>LOU-CUBA</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Exaustor / coifa</t>
+          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -15956,17 +16226,21 @@
         </is>
       </c>
       <c r="E108" s="14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
-        </is>
-      </c>
-      <c r="G108" s="11" t="inlineStr"/>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I108" s="18" t="inlineStr">
@@ -15978,42 +16252,38 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>MET-CHUV</t>
+          <t>PIN-SELADOR</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Chuveiro eletrico 220 V</t>
+          <t>Selador acrilico</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E109" s="14" t="n">
-        <v>4</v>
+        <v>73.5</v>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
         </is>
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
-      <c r="H109" s="11" t="inlineStr">
-        <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-        </is>
-      </c>
+          <t>NBR 11702, NBR 13245</t>
+        </is>
+      </c>
+      <c r="H109" s="11" t="inlineStr"/>
       <c r="I109" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -16023,7 +16293,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>MET-REG</t>
+          <t>MET-ACESS</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -16033,7 +16303,7 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Registro de gaveta e de pressao</t>
+          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
@@ -16042,7 +16312,7 @@
         </is>
       </c>
       <c r="E110" s="14" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
@@ -16068,7 +16338,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>ELE-DR</t>
+          <t>ELE-TUG</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -16078,7 +16348,7 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor diferencial residual 30 mA</t>
+          <t>Tomada 2P+T 10 A com placa</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -16087,7 +16357,7 @@
         </is>
       </c>
       <c r="E111" s="14" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
@@ -16109,17 +16379,17 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>MET-DUCHA</t>
+          <t>EQP-EXAUST</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Ducha higienica com registro</t>
+          <t>Exaustor / coifa</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -16128,21 +16398,17 @@
         </is>
       </c>
       <c r="E112" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
-        </is>
-      </c>
-      <c r="G112" s="11" t="inlineStr">
-        <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr"/>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I112" s="18" t="inlineStr">
@@ -16154,17 +16420,17 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>ELE-INT</t>
+          <t>MET-CHUV</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Interruptor simples e paralelo com placa</t>
+          <t>Chuveiro eletrico 220 V</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -16173,19 +16439,23 @@
         </is>
       </c>
       <c r="E113" s="14" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H113" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I113" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -16195,7 +16465,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>LOU-ASSENTO</t>
+          <t>MET-REG</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -16205,7 +16475,7 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Assento sanitario com amortecedor</t>
+          <t>Registro de gaveta e de pressao</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -16214,7 +16484,7 @@
         </is>
       </c>
       <c r="E114" s="14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
@@ -16240,7 +16510,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUE</t>
+          <t>ELE-DR</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -16250,7 +16520,7 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Tomada de uso especifico 20 A com placa</t>
+          <t>Disjuntor diferencial residual 30 mA</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
@@ -16259,7 +16529,7 @@
         </is>
       </c>
       <c r="E115" s="14" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
@@ -16281,7 +16551,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>MET-ENGATE</t>
+          <t>MET-DUCHA</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -16291,7 +16561,7 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Engate flexivel</t>
+          <t>Ducha higienica com registro</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
@@ -16300,7 +16570,7 @@
         </is>
       </c>
       <c r="E116" s="14" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
@@ -16326,17 +16596,17 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN-T</t>
+          <t>ELE-INT</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Torneira de tanque e de jardim</t>
+          <t>Interruptor simples e paralelo com placa</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
@@ -16345,23 +16615,19 @@
         </is>
       </c>
       <c r="E117" s="14" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
-      <c r="H117" s="11" t="inlineStr">
-        <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr"/>
       <c r="I117" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -16371,7 +16637,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>MET-VALV</t>
+          <t>LOU-ASSENTO</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -16381,7 +16647,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Valvula de escoamento e de lavatorio</t>
+          <t>Assento sanitario com amortecedor</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -16390,7 +16656,7 @@
         </is>
       </c>
       <c r="E118" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
@@ -16416,17 +16682,17 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>MET-SIFAO</t>
+          <t>ELE-TUE</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Sifao flexivel</t>
+          <t>Tomada de uso especifico 20 A com placa</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -16435,23 +16701,19 @@
         </is>
       </c>
       <c r="E119" s="14" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
-      <c r="H119" s="11" t="inlineStr">
-        <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr"/>
       <c r="I119" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -16461,7 +16723,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>LOU-TANQUE</t>
+          <t>MET-ENGATE</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -16471,7 +16733,7 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Tanque de lavanderia</t>
+          <t>Engate flexivel</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -16480,7 +16742,7 @@
         </is>
       </c>
       <c r="E120" s="14" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
@@ -16506,219 +16768,279 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
+          <t>MET-TORN-T</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>loucas</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>Torneira de tanque e de jardim</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
+      <c r="I121" s="18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>MET-VALV</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>loucas</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>Valvula de escoamento e de lavatorio</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H122" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
+      <c r="I122" s="18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>MET-SIFAO</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>loucas</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>Sifao flexivel</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
+      <c r="I123" s="18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>LOU-TANQUE</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>loucas</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>Tanque de lavanderia</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G124" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H124" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
+      <c r="I124" s="18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
           <t>ELE-DPS</t>
         </is>
       </c>
-      <c r="B121" s="10" t="inlineStr">
+      <c r="B125" s="10" t="inlineStr">
         <is>
           <t>eletrica</t>
         </is>
       </c>
-      <c r="C121" s="11" t="inlineStr">
+      <c r="C125" s="11" t="inlineStr">
         <is>
           <t>Dispositivo de protecao contra surtos</t>
         </is>
       </c>
-      <c r="D121" s="10" t="inlineStr">
+      <c r="D125" s="10" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E121" s="14" t="n">
+      <c r="E125" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F121" s="11" t="inlineStr">
+      <c r="F125" s="11" t="inlineStr">
         <is>
           <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
-      <c r="G121" s="11" t="inlineStr">
+      <c r="G125" s="11" t="inlineStr">
         <is>
           <t>NBR 14136, NBR 5410</t>
         </is>
       </c>
-      <c r="H121" s="11" t="inlineStr"/>
-      <c r="I121" s="18" t="inlineStr">
+      <c r="H125" s="11" t="inlineStr"/>
+      <c r="I125" s="18" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>ROTA ALTERNATIVA — peça cortada e furada em vez de barra</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Estes itens NÃO entram no total: são a mesma estrutura comprada pronta. Cotar os dois e comparar contra o custo de corte próprio.</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="26" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="26" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="B125" s="26" t="inlineStr">
+      <c r="B129" s="26" t="inlineStr">
         <is>
           <t>DESCRIÇÃO</t>
         </is>
       </c>
-      <c r="C125" s="26" t="inlineStr">
+      <c r="C129" s="26" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="D125" s="26" t="inlineStr">
+      <c r="D129" s="26" t="inlineStr">
         <is>
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E125" s="26" t="inlineStr">
+      <c r="E129" s="26" t="inlineStr">
         <is>
           <t>ESPECIFICAÇÃO</t>
         </is>
       </c>
-      <c r="F125" s="26" t="inlineStr">
+      <c r="F129" s="26" t="inlineStr">
         <is>
           <t>NORMAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>PF-Ue 90x40x12x0,95</t>
-        </is>
-      </c>
-      <c r="B126" s="11" t="inlineStr">
-        <is>
-          <t>Ue 90x40x12x0,95</t>
-        </is>
-      </c>
-      <c r="C126" s="10" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="D126" s="14" t="n">
-        <v>535</v>
-      </c>
-      <c r="E126" s="11" t="inlineStr">
-        <is>
-          <t>peca cortada e furada conforme Ue 90x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
-        </is>
-      </c>
-      <c r="F126" s="10" t="inlineStr">
-        <is>
-          <t>NBR 15253</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>PF-Ue 250x40x15x3,00</t>
-        </is>
-      </c>
-      <c r="B127" s="11" t="inlineStr">
-        <is>
-          <t>Ue 250x40x15x3,00</t>
-        </is>
-      </c>
-      <c r="C127" s="10" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="D127" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="E127" s="11" t="inlineStr">
-        <is>
-          <t>peca cortada e furada conforme Ue 250x40x15x3,00; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
-        </is>
-      </c>
-      <c r="F127" s="10" t="inlineStr">
-        <is>
-          <t>NBR 15253</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="9" t="inlineStr">
-        <is>
-          <t>PF-U 92x38x0,95</t>
-        </is>
-      </c>
-      <c r="B128" s="11" t="inlineStr">
-        <is>
-          <t>U 92x38x0,95</t>
-        </is>
-      </c>
-      <c r="C128" s="10" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="D128" s="14" t="n">
-        <v>234</v>
-      </c>
-      <c r="E128" s="11" t="inlineStr">
-        <is>
-          <t>peca cortada e furada conforme U 92x38x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
-        </is>
-      </c>
-      <c r="F128" s="10" t="inlineStr">
-        <is>
-          <t>NBR 15253</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t>PF-Ue 250x40x12x2,25</t>
-        </is>
-      </c>
-      <c r="B129" s="11" t="inlineStr">
-        <is>
-          <t>Ue 250x40x12x2,25</t>
-        </is>
-      </c>
-      <c r="C129" s="10" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="D129" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="E129" s="11" t="inlineStr">
-        <is>
-          <t>peca cortada e furada conforme Ue 250x40x12x2,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
-        </is>
-      </c>
-      <c r="F129" s="10" t="inlineStr">
-        <is>
-          <t>NBR 15253</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 200x40x12x1,25</t>
+          <t>PF-Ue 90x40x12x0,95</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x1,25</t>
+          <t>Ue 90x40x12x0,95</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
@@ -16727,11 +17049,11 @@
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>33</v>
+        <v>535</v>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 200x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 90x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
@@ -16743,12 +17065,12 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 200x40x12x0,95</t>
+          <t>PF-Ue 250x40x15x3,00</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x0,95</t>
+          <t>Ue 250x40x15x3,00</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
@@ -16757,11 +17079,11 @@
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 200x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 250x40x15x3,00; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
@@ -16773,12 +17095,12 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 140x40x12x0,80</t>
+          <t>PF-U 92x38x0,95</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x0,80</t>
+          <t>U 92x38x0,95</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
@@ -16787,11 +17109,11 @@
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 140x40x12x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme U 92x38x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -16803,12 +17125,12 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 90x40x12x1,25</t>
+          <t>PF-Ue 250x40x12x2,25</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>Ue 90x40x12x1,25</t>
+          <t>Ue 250x40x12x2,25</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
@@ -16817,11 +17139,11 @@
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 90x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 250x40x12x2,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr">
@@ -16833,12 +17155,12 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 140x40x12x1,25</t>
+          <t>PF-Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x1,25</t>
+          <t>Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
@@ -16847,11 +17169,11 @@
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 140x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 200x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
@@ -16863,12 +17185,12 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>PF-Fita 38x0,80</t>
+          <t>PF-Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Fita 38x0,80</t>
+          <t>Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
@@ -16877,11 +17199,11 @@
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Fita 38x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 200x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
@@ -16893,36 +17215,156 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
+          <t>PF-Ue 140x40x12x0,80</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>Ue 140x40x12x0,80</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>peca cortada e furada conforme Ue 140x40x12x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>NBR 15253</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>PF-Ue 90x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>Ue 90x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>peca cortada e furada conforme Ue 90x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+        </is>
+      </c>
+      <c r="F137" s="10" t="inlineStr">
+        <is>
+          <t>NBR 15253</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>PF-Ue 140x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>Ue 140x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>peca cortada e furada conforme Ue 140x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+        </is>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>NBR 15253</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>PF-Fita 38x0,80</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>Fita 38x0,80</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>peca cortada e furada conforme Fita 38x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+        </is>
+      </c>
+      <c r="F139" s="10" t="inlineStr">
+        <is>
+          <t>NBR 15253</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
           <t>PLACA</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>Placa (gesso, RU e cimenticia)</t>
         </is>
       </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>pc</t>
         </is>
       </c>
-      <c r="D136" s="14" t="n">
+      <c r="D140" s="14" t="n">
         <v>702</v>
       </c>
-      <c r="E136" s="11" t="inlineStr">
+      <c r="E140" s="11" t="inlineStr">
         <is>
           <t>placa inteira, por formato — rota alternativa a compra por m2; formatos: 1200 x 2400, 1200 x 25000, 600 x 1250</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F140" s="10" t="inlineStr">
         <is>
           <t>NBR 15758</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I121"/>
-  <conditionalFormatting sqref="I4:I121">
+  <autoFilter ref="A3:I125"/>
+  <conditionalFormatting sqref="I4:I125">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"com lacuna"</formula>
     </cfRule>
@@ -18062,7 +18504,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B35" s="18" t="n">
@@ -18070,17 +18512,17 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Deca / Duratex</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Metalurgica Aluminova</t>
+        </is>
+      </c>
+      <c r="D35" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>louca e metal, fabricante</t>
+          <t>ripado e brise em aluminio</t>
         </is>
       </c>
       <c r="F35" s="37" t="n"/>
@@ -18095,7 +18537,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B36" s="18" t="n">
@@ -18103,7 +18545,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Docol</t>
+          <t>Alubrasil / Hydro</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -18113,7 +18555,7 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>metal sanitario</t>
+          <t>perfil de aluminio extrudado</t>
         </is>
       </c>
       <c r="F36" s="37" t="n"/>
@@ -18128,7 +18570,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B37" s="18" t="n">
@@ -18136,7 +18578,7 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Roca / Celite</t>
+          <t>Fabricantes de brise movel</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -18146,7 +18588,7 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>louca sanitaria</t>
+          <t>mecanismo e guia</t>
         </is>
       </c>
       <c r="F37" s="37" t="n"/>
@@ -18161,7 +18603,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B38" s="18" t="n">
@@ -18169,7 +18611,7 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Lojas de acabamento de Manaus</t>
+          <t>Serralherias de Manaus</t>
         </is>
       </c>
       <c r="D38" s="36" t="inlineStr">
@@ -18179,7 +18621,7 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>louca e metal</t>
+          <t>montagem e fixacao</t>
         </is>
       </c>
       <c r="F38" s="37" t="n"/>
@@ -18194,7 +18636,7 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B39" s="18" t="n">
@@ -18202,7 +18644,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Du Norte Comercio</t>
+          <t>Esquadrias Alufynestra</t>
         </is>
       </c>
       <c r="D39" s="36" t="inlineStr">
@@ -18212,7 +18654,7 @@
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>louca, metal e acessorio</t>
+          <t>perfis e acabamento</t>
         </is>
       </c>
       <c r="F39" s="37" t="n"/>
@@ -18227,7 +18669,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B40" s="18" t="n">
@@ -18235,17 +18677,17 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Empreiteiras de pintura de Manaus</t>
-        </is>
-      </c>
-      <c r="D40" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Deca / Duratex</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>material e mao de obra</t>
+          <t>louca e metal, fabricante</t>
         </is>
       </c>
       <c r="F40" s="37" t="n"/>
@@ -18260,7 +18702,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B41" s="18" t="n">
@@ -18268,7 +18710,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Suvinil / BASF</t>
+          <t>Docol</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -18278,7 +18720,7 @@
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>tinta, fabricante</t>
+          <t>metal sanitario</t>
         </is>
       </c>
       <c r="F41" s="37" t="n"/>
@@ -18293,7 +18735,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B42" s="18" t="n">
@@ -18301,7 +18743,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Coral / AkzoNobel</t>
+          <t>Roca / Celite</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -18311,7 +18753,7 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>tinta, fabricante</t>
+          <t>louca sanitaria</t>
         </is>
       </c>
       <c r="F42" s="37" t="n"/>
@@ -18326,7 +18768,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B43" s="18" t="n">
@@ -18334,17 +18776,17 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Lojas de acabamento de Manaus</t>
+        </is>
+      </c>
+      <c r="D43" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>tinta, fabricante</t>
+          <t>louca e metal</t>
         </is>
       </c>
       <c r="F43" s="37" t="n"/>
@@ -18359,7 +18801,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B44" s="18" t="n">
@@ -18377,7 +18819,7 @@
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>tinta e material de pintura</t>
+          <t>louca, metal e acessorio</t>
         </is>
       </c>
       <c r="F44" s="37" t="n"/>
@@ -18392,7 +18834,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B45" s="18" t="n">
@@ -18400,7 +18842,7 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Du Norte Comercio</t>
+          <t>Marcenarias de Manaus</t>
         </is>
       </c>
       <c r="D45" s="36" t="inlineStr">
@@ -18410,7 +18852,7 @@
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>tubo, conexao e eletroduto</t>
+          <t>movel sob medida</t>
         </is>
       </c>
       <c r="F45" s="37" t="n"/>
@@ -18425,7 +18867,7 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B46" s="18" t="n">
@@ -18433,7 +18875,7 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Todeschini / Dell Anno</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -18443,7 +18885,7 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>tubos e conexoes PVC</t>
+          <t>movel planejado, rede</t>
         </is>
       </c>
       <c r="F46" s="37" t="n"/>
@@ -18458,7 +18900,7 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B47" s="18" t="n">
@@ -18466,7 +18908,7 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Amanco / Wavin</t>
+          <t>Italinea / Favorita</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -18476,7 +18918,7 @@
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>tubos e conexoes</t>
+          <t>movel planejado</t>
         </is>
       </c>
       <c r="F47" s="37" t="n"/>
@@ -18491,7 +18933,7 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B48" s="18" t="n">
@@ -18499,17 +18941,17 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Prysmian / Cobrecom / Sil</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Marmorarias de Manaus</t>
+        </is>
+      </c>
+      <c r="D48" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>cabo de cobre</t>
+          <t>tampo em quartzo e granito</t>
         </is>
       </c>
       <c r="F48" s="37" t="n"/>
@@ -18524,7 +18966,7 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B49" s="18" t="n">
@@ -18532,7 +18974,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Schneider / Siemens / Steck</t>
+          <t>Duratex / Guararapes</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -18542,7 +18984,7 @@
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>disjuntor e quadro</t>
+          <t>MDF, fabricante de chapa</t>
         </is>
       </c>
       <c r="F49" s="37" t="n"/>
@@ -18557,7 +18999,7 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B50" s="18" t="n">
@@ -18565,7 +19007,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Marcenarias de Manaus</t>
+          <t>Du Norte Comercio</t>
         </is>
       </c>
       <c r="D50" s="36" t="inlineStr">
@@ -18575,7 +19017,7 @@
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>movel sob medida</t>
+          <t>tubo, conexao e eletroduto</t>
         </is>
       </c>
       <c r="F50" s="37" t="n"/>
@@ -18590,7 +19032,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B51" s="18" t="n">
@@ -18598,7 +19040,7 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Todeschini / Dell Anno</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -18608,7 +19050,7 @@
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>movel planejado, rede</t>
+          <t>tubos e conexoes PVC</t>
         </is>
       </c>
       <c r="F51" s="37" t="n"/>
@@ -18623,7 +19065,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B52" s="18" t="n">
@@ -18631,7 +19073,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Italinea / Favorita</t>
+          <t>Amanco / Wavin</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
@@ -18641,7 +19083,7 @@
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>movel planejado</t>
+          <t>tubos e conexoes</t>
         </is>
       </c>
       <c r="F52" s="37" t="n"/>
@@ -18656,7 +19098,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B53" s="18" t="n">
@@ -18664,17 +19106,17 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Marmorarias de Manaus</t>
-        </is>
-      </c>
-      <c r="D53" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Prysmian / Cobrecom / Sil</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>tampo em quartzo e granito</t>
+          <t>cabo de cobre</t>
         </is>
       </c>
       <c r="F53" s="37" t="n"/>
@@ -18689,7 +19131,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B54" s="18" t="n">
@@ -18697,7 +19139,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Duratex / Guararapes</t>
+          <t>Schneider / Siemens / Steck</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -18707,7 +19149,7 @@
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>MDF, fabricante de chapa</t>
+          <t>disjuntor e quadro</t>
         </is>
       </c>
       <c r="F54" s="37" t="n"/>
@@ -18722,7 +19164,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B55" s="18" t="n">
@@ -18730,7 +19172,7 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Lojas de climatizacao de Manaus</t>
+          <t>Empreiteiras de pintura de Manaus</t>
         </is>
       </c>
       <c r="D55" s="36" t="inlineStr">
@@ -18740,7 +19182,7 @@
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>split com instalacao</t>
+          <t>material e mao de obra</t>
         </is>
       </c>
       <c r="F55" s="37" t="n"/>
@@ -18755,7 +19197,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B56" s="18" t="n">
@@ -18763,7 +19205,7 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>LG / Samsung / Daikin</t>
+          <t>Suvinil / BASF</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
@@ -18773,7 +19215,7 @@
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>split inverter, fabricante</t>
+          <t>tinta, fabricante</t>
         </is>
       </c>
       <c r="F56" s="37" t="n"/>
@@ -18788,7 +19230,7 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B57" s="18" t="n">
@@ -18796,7 +19238,7 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Midea / Elgin</t>
+          <t>Coral / AkzoNobel</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
@@ -18806,7 +19248,7 @@
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>split inverter</t>
+          <t>tinta, fabricante</t>
         </is>
       </c>
       <c r="F57" s="37" t="n"/>
@@ -18821,7 +19263,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B58" s="18" t="n">
@@ -18829,7 +19271,7 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Jacuzzi / Sodramar</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -18839,7 +19281,7 @@
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>bomba e filtro de piscina</t>
+          <t>tinta, fabricante</t>
         </is>
       </c>
       <c r="F58" s="37" t="n"/>
@@ -18854,7 +19296,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B59" s="18" t="n">
@@ -18862,17 +19304,17 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>PPA / Garen / Rossi</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Du Norte Comercio</t>
+        </is>
+      </c>
+      <c r="D59" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>automatizador de portao</t>
+          <t>tinta e material de pintura</t>
         </is>
       </c>
       <c r="F59" s="37" t="n"/>
@@ -18887,7 +19329,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B60" s="18" t="n">
@@ -18895,7 +19337,7 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Tecnoframe</t>
+          <t>Lojas de climatizacao de Manaus</t>
         </is>
       </c>
       <c r="D60" s="36" t="inlineStr">
@@ -18905,7 +19347,7 @@
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>fornecimento com montagem, praca local</t>
+          <t>split com instalacao</t>
         </is>
       </c>
       <c r="F60" s="37" t="n"/>
@@ -18920,7 +19362,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B61" s="18" t="n">
@@ -18928,7 +19370,7 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Barbieri do Brasil</t>
+          <t>LG / Samsung / Daikin</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -18938,7 +19380,7 @@
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>fornecimento; montagem por rede credenciada</t>
+          <t>split inverter, fabricante</t>
         </is>
       </c>
       <c r="F61" s="37" t="n"/>
@@ -18953,7 +19395,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B62" s="18" t="n">
@@ -18961,7 +19403,7 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Naframe</t>
+          <t>Midea / Elgin</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -18971,7 +19413,7 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>projeto, fornecimento e montagem</t>
+          <t>split inverter</t>
         </is>
       </c>
       <c r="F62" s="37" t="n"/>
@@ -18986,7 +19428,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B63" s="18" t="n">
@@ -18994,7 +19436,7 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>MPS Steel</t>
+          <t>Jacuzzi / Sodramar</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -19004,7 +19446,7 @@
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>fornecimento e montagem</t>
+          <t>bomba e filtro de piscina</t>
         </is>
       </c>
       <c r="F63" s="37" t="n"/>
@@ -19019,7 +19461,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B64" s="18" t="n">
@@ -19027,7 +19469,7 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Alge Steel</t>
+          <t>PPA / Garen / Rossi</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
@@ -19037,7 +19479,7 @@
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>fornecimento; montagem por parceiro</t>
+          <t>automatizador de portao</t>
         </is>
       </c>
       <c r="F64" s="37" t="n"/>
@@ -19052,7 +19494,7 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>cobertura</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B65" s="18" t="n">
@@ -19060,17 +19502,17 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Kingspan Isoeste</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Tecnoframe</t>
+        </is>
+      </c>
+      <c r="D65" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>painel e telha PIR, fabricante</t>
+          <t>fornecimento com montagem, praca local</t>
         </is>
       </c>
       <c r="F65" s="37" t="n"/>
@@ -19085,7 +19527,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>cobertura</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B66" s="18" t="n">
@@ -19093,7 +19535,7 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Regional Telhas</t>
+          <t>Barbieri do Brasil</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -19103,7 +19545,7 @@
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>termoacustica RT PIR</t>
+          <t>fornecimento; montagem por rede credenciada</t>
         </is>
       </c>
       <c r="F66" s="37" t="n"/>
@@ -19118,7 +19560,7 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>cobertura</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B67" s="18" t="n">
@@ -19126,7 +19568,7 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>ThermoValle</t>
+          <t>Naframe</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -19136,7 +19578,7 @@
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>telha termoacustica</t>
+          <t>projeto, fornecimento e montagem</t>
         </is>
       </c>
       <c r="F67" s="37" t="n"/>
@@ -19151,7 +19593,7 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>cobertura</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B68" s="18" t="n">
@@ -19159,7 +19601,7 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Gravia</t>
+          <t>MPS Steel</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -19169,7 +19611,7 @@
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>telha termica com nucleo PIR</t>
+          <t>fornecimento e montagem</t>
         </is>
       </c>
       <c r="F68" s="37" t="n"/>
@@ -19184,7 +19626,7 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>cobertura</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B69" s="18" t="n">
@@ -19192,7 +19634,7 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Coberminas</t>
+          <t>Alge Steel</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -19202,7 +19644,7 @@
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>telhas termoacusticas</t>
+          <t>fornecimento; montagem por parceiro</t>
         </is>
       </c>
       <c r="F69" s="37" t="n"/>
@@ -19217,7 +19659,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>cobertura</t>
         </is>
       </c>
       <c r="B70" s="18" t="n">
@@ -19225,17 +19667,17 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Metalurgica Aluminova</t>
-        </is>
-      </c>
-      <c r="D70" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Kingspan Isoeste</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>ripado e brise em aluminio</t>
+          <t>painel e telha PIR, fabricante</t>
         </is>
       </c>
       <c r="F70" s="37" t="n"/>
@@ -19250,7 +19692,7 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>cobertura</t>
         </is>
       </c>
       <c r="B71" s="18" t="n">
@@ -19258,7 +19700,7 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Alubrasil / Hydro</t>
+          <t>Regional Telhas</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -19268,7 +19710,7 @@
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>perfil de aluminio extrudado</t>
+          <t>termoacustica RT PIR</t>
         </is>
       </c>
       <c r="F71" s="37" t="n"/>
@@ -19283,7 +19725,7 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>cobertura</t>
         </is>
       </c>
       <c r="B72" s="18" t="n">
@@ -19291,7 +19733,7 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Fabricantes de brise movel</t>
+          <t>ThermoValle</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -19301,7 +19743,7 @@
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>mecanismo e guia</t>
+          <t>telha termoacustica</t>
         </is>
       </c>
       <c r="F72" s="37" t="n"/>
@@ -19316,7 +19758,7 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>cobertura</t>
         </is>
       </c>
       <c r="B73" s="18" t="n">
@@ -19324,17 +19766,17 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Serralherias de Manaus</t>
-        </is>
-      </c>
-      <c r="D73" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Gravia</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>montagem e fixacao</t>
+          <t>telha termica com nucleo PIR</t>
         </is>
       </c>
       <c r="F73" s="37" t="n"/>
@@ -19349,7 +19791,7 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>cobertura</t>
         </is>
       </c>
       <c r="B74" s="18" t="n">
@@ -19357,17 +19799,17 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Esquadrias Alufynestra</t>
-        </is>
-      </c>
-      <c r="D74" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Coberminas</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>perfis e acabamento</t>
+          <t>telhas termoacusticas</t>
         </is>
       </c>
       <c r="F74" s="37" t="n"/>
@@ -20067,7 +20509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -20331,25 +20773,52 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Rota de conformidade termica da parede externa</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15220-3 (tabela da ZB8) x NBR 15575-4 (desempenho)</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>aprovacao</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>A parede PE-1 tem U = 0,532 W/m2.K, sete vezes melhor que o U &lt;= 3,60 da linha 'parede leve refletora' da ZB8 — e por isso mesmo seu atraso termico (4,90 h) passa dos 4,3 h que a MESMA linha admite. Nao ha defeito a corrigir: ha categoria a escolher. A leitura tecnica e que a tabela prescritiva da 15220-3 foi escrita para paredes de U alto, e que em clima quente-umido inercia e passivo e nao ativo — mas a confirmacao disso depende do TEXTO da 15575-4, que este projeto nao tem acesso para ler. Enquanto nao for lido, a classificacao entra (H) e a verificacao registra ATENCAO, nunca aprovacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B16" s="43" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>Cotacao dos materiais: 100 % dos precos sao (H)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Lei 14.133 art. 23 (parametro de 3 propostas)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>contrato</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>O mapa de cotacao existe e esta pronto para sair; enquanto nao voltar, o custo e ordem de grandeza para auditar quantidade, nunca base de contrato</t>
         </is>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -834,22 +834,22 @@
     </comment>
     <comment ref="C103" authorId="0" shapeId="0">
       <text>
-        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
-NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
-LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
       </text>
     </comment>
     <comment ref="C104" authorId="0" shapeId="0">
       <text>
-        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
-LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
+NORMAS: NBR 16401, Portaria INMETRO de eficiencia
+LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
     <comment ref="C105" authorId="0" shapeId="0">
       <text>
-        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
-NORMAS: NBR 16401, Portaria INMETRO de eficiencia
-LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
+NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
+LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
     <comment ref="C106" authorId="0" shapeId="0">
@@ -966,9 +966,9 @@
     </comment>
     <comment ref="C123" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
+NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
+LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
     <comment ref="C124" authorId="0" shapeId="0">
@@ -980,22 +980,22 @@
     </comment>
     <comment ref="C125" authorId="0" shapeId="0">
       <text>
-        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
-NORMAS: NBR 14136, NBR 5410</t>
-      </text>
-    </comment>
-    <comment ref="C126" authorId="0" shapeId="0">
-      <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
+    <comment ref="C126" authorId="0" shapeId="0">
+      <text>
+        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
+NORMAS: NBR 14136, NBR 5410</t>
+      </text>
+    </comment>
     <comment ref="C127" authorId="0" shapeId="0">
       <text>
-        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
-NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
-LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
     <comment ref="C128" authorId="0" shapeId="0">
@@ -1007,28 +1007,28 @@
     </comment>
     <comment ref="C129" authorId="0" shapeId="0">
       <text>
+        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
+NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
+LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+      </text>
+    </comment>
+    <comment ref="C130" authorId="0" shapeId="0">
+      <text>
         <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
 NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
-    <comment ref="C130" authorId="0" shapeId="0">
+    <comment ref="C131" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C131" authorId="0" shapeId="0">
+    <comment ref="C132" authorId="0" shapeId="0">
       <text>
         <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
 NORMAS: NBR 14136, NBR 5410</t>
-      </text>
-    </comment>
-    <comment ref="C132" authorId="0" shapeId="0">
-      <text>
-        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
-NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
-LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
     <comment ref="C133" authorId="0" shapeId="0">
@@ -1389,7 +1389,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R59</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R60</t>
         </is>
       </c>
     </row>
@@ -9309,26 +9309,26 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>LUM-DOWNLIGHT18</t>
+          <t>MAR-ARM</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Downlight LED embutido 18 W</t>
+          <t>Armario de MDF sob medida</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E103" s="12" t="n">
-        <v>47</v>
+        <v>5.94</v>
       </c>
       <c r="F103" s="13" t="n">
         <v>0</v>
@@ -9338,7 +9338,7 @@
         <v/>
       </c>
       <c r="H103" s="15" t="n">
-        <v>128</v>
+        <v>980</v>
       </c>
       <c r="I103" s="16">
         <f>G103*H103</f>
@@ -9385,26 +9385,26 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>MAR-ARM</t>
+          <t>EQP-SPLIT30</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Armario de MDF sob medida</t>
+          <t>Split inverter 30.000 BTU/h</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>5.94</v>
+        <v>1</v>
       </c>
       <c r="F104" s="13" t="n">
         <v>0</v>
@@ -9414,7 +9414,7 @@
         <v/>
       </c>
       <c r="H104" s="15" t="n">
-        <v>980</v>
+        <v>5400</v>
       </c>
       <c r="I104" s="16">
         <f>G104*H104</f>
@@ -9461,17 +9461,17 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT30</t>
+          <t>LUM-DOWNLIGHT18</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 30.000 BTU/h</t>
+          <t>Downlight LED embutido 18 W</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="E105" s="12" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F105" s="13" t="n">
         <v>0</v>
@@ -9490,7 +9490,7 @@
         <v/>
       </c>
       <c r="H105" s="15" t="n">
-        <v>5400</v>
+        <v>128</v>
       </c>
       <c r="I105" s="16">
         <f>G105*H105</f>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="E107" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F107" s="13" t="n">
         <v>0</v>
@@ -10829,17 +10829,17 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>MET-CHUV</t>
+          <t>LUM-DOWNLIGHT12</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Chuveiro eletrico 220 V</t>
+          <t>Downlight LED embutido 12 W</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -10848,7 +10848,7 @@
         </is>
       </c>
       <c r="E123" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F123" s="13" t="n">
         <v>0</v>
@@ -10858,7 +10858,7 @@
         <v/>
       </c>
       <c r="H123" s="15" t="n">
-        <v>320</v>
+        <v>95</v>
       </c>
       <c r="I123" s="16">
         <f>G123*H123</f>
@@ -10905,7 +10905,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>MET-REG</t>
+          <t>MET-CHUV</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Registro de gaveta e de pressao</t>
+          <t>Chuveiro eletrico 220 V</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F124" s="13" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
         <v/>
       </c>
       <c r="H124" s="15" t="n">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="I124" s="16">
         <f>G124*H124</f>
@@ -10981,17 +10981,17 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>ELE-DR</t>
+          <t>MET-REG</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor diferencial residual 30 mA</t>
+          <t>Registro de gaveta e de pressao</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="E125" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F125" s="13" t="n">
         <v>0</v>
@@ -11010,7 +11010,7 @@
         <v/>
       </c>
       <c r="H125" s="15" t="n">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="I125" s="16">
         <f>G125*H125</f>
@@ -11057,17 +11057,17 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>MET-DUCHA</t>
+          <t>ELE-DR</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Ducha higienica com registro</t>
+          <t>Disjuntor diferencial residual 30 mA</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
@@ -11076,7 +11076,7 @@
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F126" s="13" t="n">
         <v>0</v>
@@ -11086,7 +11086,7 @@
         <v/>
       </c>
       <c r="H126" s="15" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="I126" s="16">
         <f>G126*H126</f>
@@ -11133,17 +11133,17 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>LUM-ARANDELA</t>
+          <t>MET-DUCHA</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Arandela LED IP44 de espelho, 8 W</t>
+          <t>Ducha higienica com registro</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="E127" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F127" s="13" t="n">
         <v>0</v>
@@ -11162,7 +11162,7 @@
         <v/>
       </c>
       <c r="H127" s="15" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="I127" s="16">
         <f>G127*H127</f>
@@ -11209,7 +11209,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>LUM-PENDENTE40</t>
+          <t>LUM-ARANDELA</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Pendente LED de pe-direito duplo, 40 W</t>
+          <t>Arandela LED IP44 de espelho, 8 W</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F128" s="13" t="n">
         <v>0</v>
@@ -11238,7 +11238,7 @@
         <v/>
       </c>
       <c r="H128" s="15" t="n">
-        <v>420</v>
+        <v>160</v>
       </c>
       <c r="I128" s="16">
         <f>G128*H128</f>
@@ -11285,7 +11285,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>ELE-INT</t>
+          <t>LUM-PENDENTE40</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Interruptor simples e paralelo com placa</t>
+          <t>Pendente LED de pe-direito duplo, 40 W</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -11304,7 +11304,7 @@
         </is>
       </c>
       <c r="E129" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F129" s="13" t="n">
         <v>0</v>
@@ -11314,7 +11314,7 @@
         <v/>
       </c>
       <c r="H129" s="15" t="n">
-        <v>32</v>
+        <v>420</v>
       </c>
       <c r="I129" s="16">
         <f>G129*H129</f>
@@ -11361,17 +11361,17 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>LOU-ASSENTO</t>
+          <t>ELE-INT</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Assento sanitario com amortecedor</t>
+          <t>Interruptor simples e paralelo com placa</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F130" s="13" t="n">
         <v>0</v>
@@ -11390,7 +11390,7 @@
         <v/>
       </c>
       <c r="H130" s="15" t="n">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="I130" s="16">
         <f>G130*H130</f>
@@ -11437,17 +11437,17 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUE</t>
+          <t>LOU-ASSENTO</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Tomada de uso especifico 20 A com placa</t>
+          <t>Assento sanitario com amortecedor</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="E131" s="12" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F131" s="13" t="n">
         <v>0</v>
@@ -11466,7 +11466,7 @@
         <v/>
       </c>
       <c r="H131" s="15" t="n">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="I131" s="16">
         <f>G131*H131</f>
@@ -11513,7 +11513,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>LUM-DOWNLIGHT12</t>
+          <t>ELE-TUE</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Downlight LED embutido 12 W</t>
+          <t>Tomada de uso especifico 20 A com placa</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -11532,7 +11532,7 @@
         </is>
       </c>
       <c r="E132" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F132" s="13" t="n">
         <v>0</v>
@@ -11542,7 +11542,7 @@
         <v/>
       </c>
       <c r="H132" s="15" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="I132" s="16">
         <f>G132*H132</f>
@@ -17179,40 +17179,36 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>LUM-DOWNLIGHT18</t>
+          <t>MAR-ARM</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Downlight LED embutido 18 W</t>
+          <t>Armario de MDF sob medida</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E103" s="14" t="n">
-        <v>47</v>
+        <v>5.94</v>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
-        </is>
-      </c>
-      <c r="G103" s="11" t="inlineStr">
-        <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr"/>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I103" s="18" t="inlineStr">
@@ -17224,36 +17220,40 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>MAR-ARM</t>
+          <t>EQP-SPLIT30</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Armario de MDF sob medida</t>
+          <t>Split inverter 30.000 BTU/h</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
-        <v>5.94</v>
+        <v>1</v>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G104" s="11" t="inlineStr"/>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
+        </is>
+      </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I104" s="18" t="inlineStr">
@@ -17265,17 +17265,17 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT30</t>
+          <t>LUM-DOWNLIGHT18</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 30.000 BTU/h</t>
+          <t>Downlight LED embutido 18 W</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
@@ -17284,21 +17284,21 @@
         </is>
       </c>
       <c r="E105" s="14" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I105" s="18" t="inlineStr">
@@ -17374,7 +17374,7 @@
         </is>
       </c>
       <c r="E107" s="14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
@@ -18047,17 +18047,17 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>MET-CHUV</t>
+          <t>LUM-DOWNLIGHT12</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Chuveiro eletrico 220 V</t>
+          <t>Downlight LED embutido 12 W</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -18066,21 +18066,21 @@
         </is>
       </c>
       <c r="E123" s="14" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I123" s="18" t="inlineStr">
@@ -18092,7 +18092,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>MET-REG</t>
+          <t>MET-CHUV</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Registro de gaveta e de pressao</t>
+          <t>Chuveiro eletrico 220 V</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -18111,7 +18111,7 @@
         </is>
       </c>
       <c r="E124" s="14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
@@ -18137,17 +18137,17 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>ELE-DR</t>
+          <t>MET-REG</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor diferencial residual 30 mA</t>
+          <t>Registro de gaveta e de pressao</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -18156,19 +18156,23 @@
         </is>
       </c>
       <c r="E125" s="14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I125" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18178,17 +18182,17 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>MET-DUCHA</t>
+          <t>ELE-DR</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Ducha higienica com registro</t>
+          <t>Disjuntor diferencial residual 30 mA</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
@@ -18197,23 +18201,19 @@
         </is>
       </c>
       <c r="E126" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
-      <c r="H126" s="11" t="inlineStr">
-        <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr"/>
       <c r="I126" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18223,17 +18223,17 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>LUM-ARANDELA</t>
+          <t>MET-DUCHA</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Arandela LED IP44 de espelho, 8 W</t>
+          <t>Ducha higienica com registro</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
@@ -18242,21 +18242,21 @@
         </is>
       </c>
       <c r="E127" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I127" s="18" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>LUM-PENDENTE40</t>
+          <t>LUM-ARANDELA</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Pendente LED de pe-direito duplo, 40 W</t>
+          <t>Arandela LED IP44 de espelho, 8 W</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -18287,7 +18287,7 @@
         </is>
       </c>
       <c r="E128" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>ELE-INT</t>
+          <t>LUM-PENDENTE40</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Interruptor simples e paralelo com placa</t>
+          <t>Pendente LED de pe-direito duplo, 40 W</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -18332,19 +18332,23 @@
         </is>
       </c>
       <c r="E129" s="14" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H129" s="11" t="inlineStr"/>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+        </is>
+      </c>
       <c r="I129" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18354,17 +18358,17 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>LOU-ASSENTO</t>
+          <t>ELE-INT</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Assento sanitario com amortecedor</t>
+          <t>Interruptor simples e paralelo com placa</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -18373,23 +18377,19 @@
         </is>
       </c>
       <c r="E130" s="14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
-      <c r="H130" s="11" t="inlineStr">
-        <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H130" s="11" t="inlineStr"/>
       <c r="I130" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18399,17 +18399,17 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUE</t>
+          <t>LOU-ASSENTO</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Tomada de uso especifico 20 A com placa</t>
+          <t>Assento sanitario com amortecedor</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -18418,19 +18418,23 @@
         </is>
       </c>
       <c r="E131" s="14" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H131" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H131" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I131" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18440,7 +18444,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>LUM-DOWNLIGHT12</t>
+          <t>ELE-TUE</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -18450,7 +18454,7 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Downlight LED embutido 12 W</t>
+          <t>Tomada de uso especifico 20 A com placa</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -18459,23 +18463,19 @@
         </is>
       </c>
       <c r="E132" s="14" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
-        </is>
-      </c>
-      <c r="H132" s="11" t="inlineStr">
-        <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr"/>
       <c r="I132" s="18" t="inlineStr">
         <is>
           <t>sim</t>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1487,7 +1487,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R61</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R62</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -17,8 +17,8 @@
     <sheet name="PEÇAS E CORTE" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COTAÇÃO'!$A$3:$V$153</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ESPECIFICAÇÕES'!$A$3:$I$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COTAÇÃO'!$A$3:$V$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ESPECIFICAÇÕES'!$A$3:$I$156</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PEÇAS E CORTE'!$A$4:$F$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -647,7 +647,7 @@
     </comment>
     <comment ref="C55" authorId="0" shapeId="0">
       <text>
-        <t>tubo, conexao ou condutor conforme descricao
+        <t>tubo, conexao ou condutor conforme descricao; DN50
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
       </text>
     </comment>
@@ -659,7 +659,7 @@
     </comment>
     <comment ref="C57" authorId="0" shapeId="0">
       <text>
-        <t>tubo, conexao ou condutor conforme descricao; DN50
+        <t>tubo, conexao ou condutor conforme descricao
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
       </text>
     </comment>
@@ -809,22 +809,21 @@
     </comment>
     <comment ref="C99" authorId="0" shapeId="0">
       <text>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+      </text>
+    </comment>
+    <comment ref="C100" authorId="0" shapeId="0">
+      <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C100" authorId="0" shapeId="0">
+    <comment ref="C101" authorId="0" shapeId="0">
       <text>
         <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
 LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
-      </text>
-    </comment>
-    <comment ref="C101" authorId="0" shapeId="0">
-      <text>
-        <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
-NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
-LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
       </text>
     </comment>
     <comment ref="C102" authorId="0" shapeId="0">
@@ -836,48 +835,49 @@
     </comment>
     <comment ref="C103" authorId="0" shapeId="0">
       <text>
+        <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
+NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
+LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+      </text>
+    </comment>
+    <comment ref="C104" authorId="0" shapeId="0">
+      <text>
         <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
 NORMAS: NBR 11702, NBR 13245</t>
       </text>
     </comment>
-    <comment ref="C104" authorId="0" shapeId="0">
+    <comment ref="C105" authorId="0" shapeId="0">
       <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C105" authorId="0" shapeId="0">
+    <comment ref="C106" authorId="0" shapeId="0">
       <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
       </text>
     </comment>
-    <comment ref="C106" authorId="0" shapeId="0">
+    <comment ref="C107" authorId="0" shapeId="0">
       <text>
         <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
 NORMAS: NBR 11702, NBR 13245</t>
       </text>
     </comment>
-    <comment ref="C107" authorId="0" shapeId="0">
+    <comment ref="C108" authorId="0" shapeId="0">
       <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
 NORMAS: NBR 16401, Portaria INMETRO de eficiencia
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
-    <comment ref="C108" authorId="0" shapeId="0">
+    <comment ref="C109" authorId="0" shapeId="0">
       <text>
         <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
 NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
 LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
-      </text>
-    </comment>
-    <comment ref="C109" authorId="0" shapeId="0">
-      <text>
-        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
-LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
       </text>
     </comment>
     <comment ref="C110" authorId="0" shapeId="0">
@@ -903,22 +903,22 @@
     </comment>
     <comment ref="C113" authorId="0" shapeId="0">
       <text>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+      </text>
+    </comment>
+    <comment ref="C114" authorId="0" shapeId="0">
+      <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C114" authorId="0" shapeId="0">
+    <comment ref="C115" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-      </text>
-    </comment>
-    <comment ref="C115" authorId="0" shapeId="0">
-      <text>
-        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
-LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
       </text>
     </comment>
     <comment ref="C116" authorId="0" shapeId="0">
@@ -930,41 +930,42 @@
     </comment>
     <comment ref="C117" authorId="0" shapeId="0">
       <text>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+      </text>
+    </comment>
+    <comment ref="C118" authorId="0" shapeId="0">
+      <text>
         <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
 NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
 LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
-    <comment ref="C118" authorId="0" shapeId="0">
+    <comment ref="C119" authorId="0" shapeId="0">
       <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C119" authorId="0" shapeId="0">
+    <comment ref="C120" authorId="0" shapeId="0">
       <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
-    <comment ref="C120" authorId="0" shapeId="0">
+    <comment ref="C121" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C121" authorId="0" shapeId="0">
+    <comment ref="C122" authorId="0" shapeId="0">
       <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
-      </text>
-    </comment>
-    <comment ref="C122" authorId="0" shapeId="0">
-      <text>
-        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
-LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
       </text>
     </comment>
     <comment ref="C123" authorId="0" shapeId="0">
@@ -976,68 +977,67 @@
     </comment>
     <comment ref="C124" authorId="0" shapeId="0">
       <text>
+        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
+NORMAS: NBR 14136, NBR 5410</t>
+      </text>
+    </comment>
+    <comment ref="C125" authorId="0" shapeId="0">
+      <text>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+      </text>
+    </comment>
+    <comment ref="C126" authorId="0" shapeId="0">
+      <text>
         <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
 NORMAS: NBR 11702, NBR 13245</t>
       </text>
     </comment>
-    <comment ref="C125" authorId="0" shapeId="0">
+    <comment ref="C127" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C126" authorId="0" shapeId="0">
+    <comment ref="C128" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0">
-      <text>
-        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
-NORMAS: NBR 14136, NBR 5410</t>
-      </text>
-    </comment>
-    <comment ref="C128" authorId="0" shapeId="0">
+    <comment ref="C129" authorId="0" shapeId="0">
       <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
-    <comment ref="C129" authorId="0" shapeId="0">
+    <comment ref="C130" authorId="0" shapeId="0">
       <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
       </text>
     </comment>
-    <comment ref="C130" authorId="0" shapeId="0">
+    <comment ref="C131" authorId="0" shapeId="0">
       <text>
         <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
 NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
 LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C131" authorId="0" shapeId="0">
+    <comment ref="C132" authorId="0" shapeId="0">
+      <text>
+        <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
+NORMAS: NBR 13818, NBR 15463
+LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+      </text>
+    </comment>
+    <comment ref="C133" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-      </text>
-    </comment>
-    <comment ref="C132" authorId="0" shapeId="0">
-      <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-      </text>
-    </comment>
-    <comment ref="C133" authorId="0" shapeId="0">
-      <text>
-        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
-NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
     <comment ref="C134" authorId="0" shapeId="0">
@@ -1049,16 +1049,15 @@
     </comment>
     <comment ref="C135" authorId="0" shapeId="0">
       <text>
-        <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
-NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
-LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
+NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
     <comment ref="C136" authorId="0" shapeId="0">
       <text>
-        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
-NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
-LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
     <comment ref="C137" authorId="0" shapeId="0">
@@ -1077,8 +1076,9 @@
     </comment>
     <comment ref="C139" authorId="0" shapeId="0">
       <text>
-        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
-NORMAS: NBR 14136, NBR 5410</t>
+        <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
+NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
+LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
     <comment ref="C140" authorId="0" shapeId="0">
@@ -1090,9 +1090,9 @@
     </comment>
     <comment ref="C141" authorId="0" shapeId="0">
       <text>
-        <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
-NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
-LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
+NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
+LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
     <comment ref="C142" authorId="0" shapeId="0">
@@ -1103,44 +1103,43 @@
     </comment>
     <comment ref="C143" authorId="0" shapeId="0">
       <text>
-        <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
-NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
-LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
     <comment ref="C144" authorId="0" shapeId="0">
+      <text>
+        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
+NORMAS: NBR 14136, NBR 5410</t>
+      </text>
+    </comment>
+    <comment ref="C145" authorId="0" shapeId="0">
       <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
       </text>
     </comment>
-    <comment ref="C145" authorId="0" shapeId="0">
+    <comment ref="C146" authorId="0" shapeId="0">
       <text>
-        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
-NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
-LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+        <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
+NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
+LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
-    <comment ref="C146" authorId="0" shapeId="0">
+    <comment ref="C147" authorId="0" shapeId="0">
+      <text>
+        <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
+NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
+LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+      </text>
+    </comment>
+    <comment ref="C148" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-      </text>
-    </comment>
-    <comment ref="C147" authorId="0" shapeId="0">
-      <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-      </text>
-    </comment>
-    <comment ref="C148" authorId="0" shapeId="0">
-      <text>
-        <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
-NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
-LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
     <comment ref="C149" authorId="0" shapeId="0">
@@ -1152,16 +1151,16 @@
     </comment>
     <comment ref="C150" authorId="0" shapeId="0">
       <text>
-        <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
-NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
-LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
     <comment ref="C151" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
+NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
+LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
     <comment ref="C152" authorId="0" shapeId="0">
@@ -1172,6 +1171,27 @@
       </text>
     </comment>
     <comment ref="C153" authorId="0" shapeId="0">
+      <text>
+        <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
+NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
+LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+      </text>
+    </comment>
+    <comment ref="C154" authorId="0" shapeId="0">
+      <text>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+      </text>
+    </comment>
+    <comment ref="C155" authorId="0" shapeId="0">
+      <text>
+        <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
+NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
+LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+      </text>
+    </comment>
+    <comment ref="C156" authorId="0" shapeId="0">
       <text>
         <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
 NORMAS: NBR 14136, NBR 5410</t>
@@ -1487,7 +1507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R62</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R63</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V157"/>
+  <dimension ref="A1:V160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1744,11 +1764,11 @@
         </is>
       </c>
       <c r="Q2" s="4">
-        <f>COUNTIF(V4:V153,"COMPLETO")&amp;" de "&amp;150&amp;" itens com 5 propostas"</f>
+        <f>COUNTIF(V4:V156,"COMPLETO")&amp;" de "&amp;153&amp;" itens com 5 propostas"</f>
         <v/>
       </c>
       <c r="T2" s="7">
-        <f>IF(I154=0,0,SUMIF(V4:V153,"COMPLETO",I4:I153)/I154)</f>
+        <f>IF(I157=0,0,SUMIF(V4:V156,"COMPLETO",I4:I156)/I157)</f>
         <v/>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -3954,7 +3974,7 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>18.72</v>
+        <v>25.92</v>
       </c>
       <c r="F31" s="13" t="n">
         <v>0</v>
@@ -5322,7 +5342,7 @@
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>2834.4</v>
+        <v>3272</v>
       </c>
       <c r="F49" s="13" t="n">
         <v>0</v>
@@ -5398,7 +5418,7 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>885.8</v>
+        <v>1022.5</v>
       </c>
       <c r="F50" s="13" t="n">
         <v>0</v>
@@ -5550,7 +5570,7 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>188.1</v>
+        <v>192.4</v>
       </c>
       <c r="F52" s="13" t="n">
         <v>0</v>
@@ -5626,7 +5646,7 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F53" s="13" t="n">
         <v>0</v>
@@ -5759,7 +5779,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>MEP-ISOL</t>
+          <t>MEP-ESGO50</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -5769,7 +5789,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Isolamento de linha</t>
+          <t>Tubo esgoto DN50</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -5778,7 +5798,7 @@
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>112</v>
+        <v>60.5</v>
       </c>
       <c r="F55" s="13" t="n">
         <v>0</v>
@@ -5788,7 +5808,7 @@
         <v/>
       </c>
       <c r="H55" s="15" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I55" s="16">
         <f>G55*H55</f>
@@ -5835,7 +5855,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>MEP-DISJ</t>
+          <t>MEP-ISOL</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -5845,16 +5865,16 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor</t>
+          <t>Isolamento de linha</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="F56" s="13" t="n">
         <v>0</v>
@@ -5864,7 +5884,7 @@
         <v/>
       </c>
       <c r="H56" s="15" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="I56" s="16">
         <f>G56*H56</f>
@@ -5911,7 +5931,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>MEP-ESGO50</t>
+          <t>MEP-DISJ</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -5921,16 +5941,16 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Tubo esgoto DN50</t>
+          <t>Disjuntor</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>50.6</v>
+        <v>37</v>
       </c>
       <c r="F57" s="13" t="n">
         <v>0</v>
@@ -5940,7 +5960,7 @@
         <v/>
       </c>
       <c r="H57" s="15" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I57" s="16">
         <f>G57*H57</f>
@@ -6006,7 +6026,7 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F58" s="13" t="n">
         <v>0</v>
@@ -9103,17 +9123,17 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>REV-ARG</t>
+          <t>MAR-ARM</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Argamassa colante AC-III e regularizacao</t>
+          <t>Armario de MDF sob medida</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -9122,7 +9142,7 @@
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>511.1</v>
+        <v>9.42</v>
       </c>
       <c r="F99" s="13" t="n">
         <v>0</v>
@@ -9132,7 +9152,7 @@
         <v/>
       </c>
       <c r="H99" s="15" t="n">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="I99" s="16">
         <f>G99*H99</f>
@@ -9179,17 +9199,17 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>MAR-TAMPO</t>
+          <t>REV-ARG</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Tampo de bancada (quartzo/granito)</t>
+          <t>Argamassa colante AC-III e regularizacao</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -9198,7 +9218,7 @@
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>7.17</v>
+        <v>511.1</v>
       </c>
       <c r="F100" s="13" t="n">
         <v>0</v>
@@ -9208,7 +9228,7 @@
         <v/>
       </c>
       <c r="H100" s="15" t="n">
-        <v>1250</v>
+        <v>18</v>
       </c>
       <c r="I100" s="16">
         <f>G100*H100</f>
@@ -9255,26 +9275,26 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>FV-INSTAL</t>
+          <t>MAR-TAMPO</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Instalacao e comissionamento</t>
+          <t>Tampo de bancada (quartzo/granito)</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>kWp</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E101" s="12" t="n">
-        <v>15.95</v>
+        <v>7.17</v>
       </c>
       <c r="F101" s="13" t="n">
         <v>0</v>
@@ -9284,7 +9304,7 @@
         <v/>
       </c>
       <c r="H101" s="15" t="n">
-        <v>550</v>
+        <v>1250</v>
       </c>
       <c r="I101" s="16">
         <f>G101*H101</f>
@@ -9331,7 +9351,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>FV-ESTRUTURA</t>
+          <t>FV-INSTAL</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -9341,16 +9361,16 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Estrutura de fixacao em aluminio sobre terca</t>
+          <t>Instalacao e comissionamento</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>kWp</t>
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>86.2</v>
+        <v>15.95</v>
       </c>
       <c r="F102" s="13" t="n">
         <v>0</v>
@@ -9360,7 +9380,7 @@
         <v/>
       </c>
       <c r="H102" s="15" t="n">
-        <v>95</v>
+        <v>550</v>
       </c>
       <c r="I102" s="16">
         <f>G102*H102</f>
@@ -9407,26 +9427,26 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>PIN-TINTA</t>
+          <t>FV-ESTRUTURA</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
+          <t>Estrutura de fixacao em aluminio sobre terca</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E103" s="12" t="n">
-        <v>179.6</v>
+        <v>86.2</v>
       </c>
       <c r="F103" s="13" t="n">
         <v>0</v>
@@ -9436,7 +9456,7 @@
         <v/>
       </c>
       <c r="H103" s="15" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="I103" s="16">
         <f>G103*H103</f>
@@ -9483,26 +9503,26 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>REV-RODAPE</t>
+          <t>PIN-TINTA</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Rodape (poliestireno 100 mm, pintado)</t>
+          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>220.9</v>
+        <v>179.6</v>
       </c>
       <c r="F104" s="13" t="n">
         <v>0</v>
@@ -9512,7 +9532,7 @@
         <v/>
       </c>
       <c r="H104" s="15" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I104" s="16">
         <f>G104*H104</f>
@@ -9559,26 +9579,26 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>FV-INVERSOR</t>
+          <t>REV-RODAPE</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Inversor string 12 kW, trifasico 220 V</t>
+          <t>Rodape (poliestireno 100 mm, pintado)</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E105" s="12" t="n">
-        <v>12</v>
+        <v>220.9</v>
       </c>
       <c r="F105" s="13" t="n">
         <v>0</v>
@@ -9588,7 +9608,7 @@
         <v/>
       </c>
       <c r="H105" s="15" t="n">
-        <v>620</v>
+        <v>34</v>
       </c>
       <c r="I105" s="16">
         <f>G105*H105</f>
@@ -9635,26 +9655,26 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>PIN-FORRO</t>
+          <t>FV-INVERSOR</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Pintura de forro (latex PVA fosco)</t>
+          <t>Inversor string 12 kW, trifasico 220 V</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>kW</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>257</v>
+        <v>12</v>
       </c>
       <c r="F106" s="13" t="n">
         <v>0</v>
@@ -9664,7 +9684,7 @@
         <v/>
       </c>
       <c r="H106" s="15" t="n">
-        <v>26</v>
+        <v>620</v>
       </c>
       <c r="I106" s="16">
         <f>G106*H106</f>
@@ -9711,26 +9731,26 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT9</t>
+          <t>PIN-FORRO</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 9.000 BTU/h</t>
+          <t>Pintura de forro (latex PVA fosco)</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E107" s="12" t="n">
-        <v>3</v>
+        <v>257</v>
       </c>
       <c r="F107" s="13" t="n">
         <v>0</v>
@@ -9740,7 +9760,7 @@
         <v/>
       </c>
       <c r="H107" s="15" t="n">
-        <v>2100</v>
+        <v>26</v>
       </c>
       <c r="I107" s="16">
         <f>G107*H107</f>
@@ -9787,26 +9807,26 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>SPD-CAPTOR</t>
+          <t>EQP-SPLIT9</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
+          <t>Split inverter 9.000 BTU/h</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>160.8</v>
+        <v>3</v>
       </c>
       <c r="F108" s="13" t="n">
         <v>0</v>
@@ -9816,7 +9836,7 @@
         <v/>
       </c>
       <c r="H108" s="15" t="n">
-        <v>38</v>
+        <v>2100</v>
       </c>
       <c r="I108" s="16">
         <f>G108*H108</f>
@@ -9863,26 +9883,26 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>MAR-ARM</t>
+          <t>SPD-CAPTOR</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Armario de MDF sob medida</t>
+          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
-        <v>5.94</v>
+        <v>160.8</v>
       </c>
       <c r="F109" s="13" t="n">
         <v>0</v>
@@ -9892,7 +9912,7 @@
         <v/>
       </c>
       <c r="H109" s="15" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="I109" s="16">
         <f>G109*H109</f>
@@ -10167,26 +10187,26 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>REV-REJ</t>
+          <t>MAR-CORT</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Rejunte epoxi/acrilico</t>
+          <t>Cortina blackout com trilho, dormitorios</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
-        <v>511.1</v>
+        <v>13.2</v>
       </c>
       <c r="F113" s="13" t="n">
         <v>0</v>
@@ -10196,7 +10216,7 @@
         <v/>
       </c>
       <c r="H113" s="15" t="n">
-        <v>9</v>
+        <v>380</v>
       </c>
       <c r="I113" s="16">
         <f>G113*H113</f>
@@ -10243,26 +10263,26 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>LOU-VASO</t>
+          <t>REV-REJ</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Bacia sanitaria com caixa acoplada</t>
+          <t>Rejunte epoxi/acrilico</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>5</v>
+        <v>511.1</v>
       </c>
       <c r="F114" s="13" t="n">
         <v>0</v>
@@ -10272,7 +10292,7 @@
         <v/>
       </c>
       <c r="H114" s="15" t="n">
-        <v>780</v>
+        <v>9</v>
       </c>
       <c r="I114" s="16">
         <f>G114*H114</f>
@@ -10319,26 +10339,26 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>MAR-CAB</t>
+          <t>LOU-VASO</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Cabideiro e gaveteiro de closet</t>
+          <t>Bacia sanitaria com caixa acoplada</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F115" s="13" t="n">
         <v>0</v>
@@ -10348,7 +10368,7 @@
         <v/>
       </c>
       <c r="H115" s="15" t="n">
-        <v>320</v>
+        <v>780</v>
       </c>
       <c r="I115" s="16">
         <f>G115*H115</f>
@@ -10414,7 +10434,7 @@
         </is>
       </c>
       <c r="E116" s="12" t="n">
-        <v>17.4</v>
+        <v>15.6</v>
       </c>
       <c r="F116" s="13" t="n">
         <v>0</v>
@@ -10471,26 +10491,26 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>SPD-ANEL</t>
+          <t>MET-TORN</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Anel de aterramento: cobre nu 50 mm2 no perimetro do radier</t>
+          <t>Torneira de bancada (lavatorio e cuba)</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
-        <v>63.6</v>
+        <v>9</v>
       </c>
       <c r="F117" s="13" t="n">
         <v>0</v>
@@ -10500,7 +10520,7 @@
         <v/>
       </c>
       <c r="H117" s="15" t="n">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="I117" s="16">
         <f>G117*H117</f>
@@ -10547,26 +10567,26 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>REV-FORRO-ACUST</t>
+          <t>SPD-ANEL</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Forro absorvente perfurado (alfa 0,70), acabado de fabrica</t>
+          <t>Anel de aterramento: cobre nu 50 mm2 no perimetro do radier</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E118" s="12" t="n">
-        <v>30.2</v>
+        <v>63.6</v>
       </c>
       <c r="F118" s="13" t="n">
         <v>0</v>
@@ -10576,7 +10596,7 @@
         <v/>
       </c>
       <c r="H118" s="15" t="n">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="I118" s="16">
         <f>G118*H118</f>
@@ -10623,26 +10643,26 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>EQP-PISC</t>
+          <t>REV-FORRO-ACUST</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
+          <t>Forro absorvente perfurado (alfa 0,70), acabado de fabrica</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>cj</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
-        <v>1</v>
+        <v>30.2</v>
       </c>
       <c r="F119" s="13" t="n">
         <v>0</v>
@@ -10652,7 +10672,7 @@
         <v/>
       </c>
       <c r="H119" s="15" t="n">
-        <v>2800</v>
+        <v>96</v>
       </c>
       <c r="I119" s="16">
         <f>G119*H119</f>
@@ -10699,26 +10719,26 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN</t>
+          <t>EQP-PISC</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Torneira de bancada (lavatorio e cuba)</t>
+          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>cj</t>
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F120" s="13" t="n">
         <v>0</v>
@@ -10728,7 +10748,7 @@
         <v/>
       </c>
       <c r="H120" s="15" t="n">
-        <v>340</v>
+        <v>2800</v>
       </c>
       <c r="I120" s="16">
         <f>G120*H120</f>
@@ -10775,17 +10795,17 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>EQP-PORTAO</t>
+          <t>LOU-LAV</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Automatizador de portao de correr</t>
+          <t>Lavatorio / cuba de banheiro</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -10794,7 +10814,7 @@
         </is>
       </c>
       <c r="E121" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F121" s="13" t="n">
         <v>0</v>
@@ -10804,7 +10824,7 @@
         <v/>
       </c>
       <c r="H121" s="15" t="n">
-        <v>2400</v>
+        <v>420</v>
       </c>
       <c r="I121" s="16">
         <f>G121*H121</f>
@@ -10851,26 +10871,26 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>MAR-PRAT</t>
+          <t>EQP-PORTAO</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Prateleira e nicho</t>
+          <t>Automatizador de portao de correr</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E122" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="F122" s="13" t="n">
         <v>0</v>
@@ -10880,7 +10900,7 @@
         <v/>
       </c>
       <c r="H122" s="15" t="n">
-        <v>260</v>
+        <v>2400</v>
       </c>
       <c r="I122" s="16">
         <f>G122*H122</f>
@@ -10927,7 +10947,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>LOU-LAV</t>
+          <t>MET-ACESS</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -10937,7 +10957,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Lavatorio / cuba de banheiro</t>
+          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -10946,7 +10966,7 @@
         </is>
       </c>
       <c r="E123" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F123" s="13" t="n">
         <v>0</v>
@@ -10956,7 +10976,7 @@
         <v/>
       </c>
       <c r="H123" s="15" t="n">
-        <v>420</v>
+        <v>85</v>
       </c>
       <c r="I123" s="16">
         <f>G123*H123</f>
@@ -11003,26 +11023,26 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>PIN-SELADOR</t>
+          <t>ELE-TUG</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Selador acrilico</t>
+          <t>Tomada 2P+T 10 A com placa</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>74.8</v>
+        <v>82</v>
       </c>
       <c r="F124" s="13" t="n">
         <v>0</v>
@@ -11079,26 +11099,26 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>LOU-CUBA</t>
+          <t>MAR-PRAT</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
+          <t>Prateleira e nicho</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F125" s="13" t="n">
         <v>0</v>
@@ -11108,7 +11128,7 @@
         <v/>
       </c>
       <c r="H125" s="15" t="n">
-        <v>690</v>
+        <v>260</v>
       </c>
       <c r="I125" s="16">
         <f>G125*H125</f>
@@ -11155,26 +11175,26 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>MET-ACESS</t>
+          <t>PIN-SELADOR</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
+          <t>Selador acrilico</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>24</v>
+        <v>74.8</v>
       </c>
       <c r="F126" s="13" t="n">
         <v>0</v>
@@ -11184,7 +11204,7 @@
         <v/>
       </c>
       <c r="H126" s="15" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="I126" s="16">
         <f>G126*H126</f>
@@ -11231,17 +11251,17 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUG</t>
+          <t>LOU-CUBA</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Tomada 2P+T 10 A com placa</t>
+          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
@@ -11250,7 +11270,7 @@
         </is>
       </c>
       <c r="E127" s="12" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="F127" s="13" t="n">
         <v>0</v>
@@ -11260,7 +11280,7 @@
         <v/>
       </c>
       <c r="H127" s="15" t="n">
-        <v>28</v>
+        <v>690</v>
       </c>
       <c r="I127" s="16">
         <f>G127*H127</f>
@@ -11307,26 +11327,26 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>EQP-EXAUST</t>
+          <t>MAR-CAB</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Exaustor / coifa</t>
+          <t>Cabideiro e gaveteiro de closet</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F128" s="13" t="n">
         <v>0</v>
@@ -11336,7 +11356,7 @@
         <v/>
       </c>
       <c r="H128" s="15" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="I128" s="16">
         <f>G128*H128</f>
@@ -11383,17 +11403,17 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>FV-HOMOLOG</t>
+          <t>EQP-EXAUST</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Projeto e homologacao na concessionaria (REN 1.000)</t>
+          <t>Exaustor / coifa</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -11402,7 +11422,7 @@
         </is>
       </c>
       <c r="E129" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F129" s="13" t="n">
         <v>0</v>
@@ -11412,7 +11432,7 @@
         <v/>
       </c>
       <c r="H129" s="15" t="n">
-        <v>1800</v>
+        <v>260</v>
       </c>
       <c r="I129" s="16">
         <f>G129*H129</f>
@@ -11459,7 +11479,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>LUM-SOBREPOR24</t>
+          <t>FV-HOMOLOG</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -11469,7 +11489,7 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Plafon LED de sobrepor 24 W</t>
+          <t>Projeto e homologacao na concessionaria (REN 1.000)</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -11478,7 +11498,7 @@
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F130" s="13" t="n">
         <v>0</v>
@@ -11488,7 +11508,7 @@
         <v/>
       </c>
       <c r="H130" s="15" t="n">
-        <v>175</v>
+        <v>1800</v>
       </c>
       <c r="I130" s="16">
         <f>G130*H130</f>
@@ -11535,17 +11555,17 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>MET-CHUV</t>
+          <t>LUM-SOBREPOR24</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Chuveiro eletrico 220 V</t>
+          <t>Plafon LED de sobrepor 24 W</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -11554,7 +11574,7 @@
         </is>
       </c>
       <c r="E131" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F131" s="13" t="n">
         <v>0</v>
@@ -11564,7 +11584,7 @@
         <v/>
       </c>
       <c r="H131" s="15" t="n">
-        <v>320</v>
+        <v>175</v>
       </c>
       <c r="I131" s="16">
         <f>G131*H131</f>
@@ -11611,7 +11631,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>MET-REG</t>
+          <t>REV-NICHO</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -11621,7 +11641,7 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Registro de gaveta e de pressao</t>
+          <t>Nicho de box 300 x 900 mm entre montantes (RU + ceramica)</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -11630,7 +11650,7 @@
         </is>
       </c>
       <c r="E132" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F132" s="13" t="n">
         <v>0</v>
@@ -11640,7 +11660,7 @@
         <v/>
       </c>
       <c r="H132" s="15" t="n">
-        <v>95</v>
+        <v>420</v>
       </c>
       <c r="I132" s="16">
         <f>G132*H132</f>
@@ -11687,17 +11707,17 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>ELE-DR</t>
+          <t>MET-REG</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor diferencial residual 30 mA</t>
+          <t>Registro de gaveta e de pressao</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
@@ -11706,7 +11726,7 @@
         </is>
       </c>
       <c r="E133" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F133" s="13" t="n">
         <v>0</v>
@@ -11716,7 +11736,7 @@
         <v/>
       </c>
       <c r="H133" s="15" t="n">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="I133" s="16">
         <f>G133*H133</f>
@@ -11763,7 +11783,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>MET-DUCHA</t>
+          <t>MET-CHUV</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -11773,7 +11793,7 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Ducha higienica com registro</t>
+          <t>Chuveiro eletrico 220 V</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
@@ -11782,7 +11802,7 @@
         </is>
       </c>
       <c r="E134" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F134" s="13" t="n">
         <v>0</v>
@@ -11792,7 +11812,7 @@
         <v/>
       </c>
       <c r="H134" s="15" t="n">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="I134" s="16">
         <f>G134*H134</f>
@@ -11839,7 +11859,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>SPD-DESCIDA</t>
+          <t>ELE-DR</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -11849,7 +11869,7 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Descida natural pela estrutura LSF: conector de teste e ligacao</t>
+          <t>Disjuntor diferencial residual 30 mA</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -11858,7 +11878,7 @@
         </is>
       </c>
       <c r="E135" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F135" s="13" t="n">
         <v>0</v>
@@ -11868,7 +11888,7 @@
         <v/>
       </c>
       <c r="H135" s="15" t="n">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="I135" s="16">
         <f>G135*H135</f>
@@ -11915,17 +11935,17 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>LUM-ARANDELA</t>
+          <t>MET-DUCHA</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Arandela LED IP44 de espelho, 8 W</t>
+          <t>Ducha higienica com registro</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -11934,7 +11954,7 @@
         </is>
       </c>
       <c r="E136" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F136" s="13" t="n">
         <v>0</v>
@@ -11944,7 +11964,7 @@
         <v/>
       </c>
       <c r="H136" s="15" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="I136" s="16">
         <f>G136*H136</f>
@@ -11991,7 +12011,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>SPD-DPS1</t>
+          <t>SPD-DESCIDA</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -12001,7 +12021,7 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>DPS classe I, 12,5 kA, 3F+N, na entrada</t>
+          <t>Descida natural pela estrutura LSF: conector de teste e ligacao</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -12010,7 +12030,7 @@
         </is>
       </c>
       <c r="E137" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F137" s="13" t="n">
         <v>0</v>
@@ -12020,7 +12040,7 @@
         <v/>
       </c>
       <c r="H137" s="15" t="n">
-        <v>890</v>
+        <v>260</v>
       </c>
       <c r="I137" s="16">
         <f>G137*H137</f>
@@ -12067,7 +12087,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>LUM-PENDENTE40</t>
+          <t>LUM-ARANDELA</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -12077,7 +12097,7 @@
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Pendente LED de pe-direito duplo, 40 W</t>
+          <t>Arandela LED IP44 de espelho, 8 W</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -12086,7 +12106,7 @@
         </is>
       </c>
       <c r="E138" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F138" s="13" t="n">
         <v>0</v>
@@ -12096,7 +12116,7 @@
         <v/>
       </c>
       <c r="H138" s="15" t="n">
-        <v>420</v>
+        <v>160</v>
       </c>
       <c r="I138" s="16">
         <f>G138*H138</f>
@@ -12143,7 +12163,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>ELE-INT</t>
+          <t>SPD-DPS1</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -12153,7 +12173,7 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Interruptor simples e paralelo com placa</t>
+          <t>DPS classe I, 12,5 kA, 3F+N, na entrada</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
@@ -12162,7 +12182,7 @@
         </is>
       </c>
       <c r="E139" s="12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F139" s="13" t="n">
         <v>0</v>
@@ -12172,7 +12192,7 @@
         <v/>
       </c>
       <c r="H139" s="15" t="n">
-        <v>32</v>
+        <v>890</v>
       </c>
       <c r="I139" s="16">
         <f>G139*H139</f>
@@ -12219,7 +12239,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>LOU-ASSENTO</t>
+          <t>MET-DUCHA-TETO</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -12229,7 +12249,7 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>Assento sanitario com amortecedor</t>
+          <t>Ducha de teto 250 mm com desviador (box &gt;= 1.400)</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -12238,7 +12258,7 @@
         </is>
       </c>
       <c r="E140" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F140" s="13" t="n">
         <v>0</v>
@@ -12248,7 +12268,7 @@
         <v/>
       </c>
       <c r="H140" s="15" t="n">
-        <v>140</v>
+        <v>890</v>
       </c>
       <c r="I140" s="16">
         <f>G140*H140</f>
@@ -12295,7 +12315,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>FV-STRINGBOX</t>
+          <t>LUM-PENDENTE40</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -12305,7 +12325,7 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>String box CC com DPS e seccionadora</t>
+          <t>Pendente LED de pe-direito duplo, 40 W</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -12314,7 +12334,7 @@
         </is>
       </c>
       <c r="E141" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="13" t="n">
         <v>0</v>
@@ -12324,7 +12344,7 @@
         <v/>
       </c>
       <c r="H141" s="15" t="n">
-        <v>680</v>
+        <v>420</v>
       </c>
       <c r="I141" s="16">
         <f>G141*H141</f>
@@ -12371,7 +12391,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUE</t>
+          <t>ELE-INT</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -12381,7 +12401,7 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Tomada de uso especifico 20 A com placa</t>
+          <t>Interruptor simples e paralelo com placa</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
@@ -12390,7 +12410,7 @@
         </is>
       </c>
       <c r="E142" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F142" s="13" t="n">
         <v>0</v>
@@ -12400,7 +12420,7 @@
         <v/>
       </c>
       <c r="H142" s="15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I142" s="16">
         <f>G142*H142</f>
@@ -12447,17 +12467,17 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>SPD-ENSAIO</t>
+          <t>LOU-ASSENTO</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Ensaio de continuidade e resistencia de aterramento</t>
+          <t>Assento sanitario com amortecedor</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
@@ -12466,7 +12486,7 @@
         </is>
       </c>
       <c r="E143" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F143" s="13" t="n">
         <v>0</v>
@@ -12476,7 +12496,7 @@
         <v/>
       </c>
       <c r="H143" s="15" t="n">
-        <v>650</v>
+        <v>140</v>
       </c>
       <c r="I143" s="16">
         <f>G143*H143</f>
@@ -12523,7 +12543,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>FV-CABO</t>
+          <t>ELE-TUE</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -12533,16 +12553,16 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
+          <t>Tomada de uso especifico 20 A com placa</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E144" s="12" t="n">
-        <v>46.3</v>
+        <v>25</v>
       </c>
       <c r="F144" s="13" t="n">
         <v>0</v>
@@ -12552,7 +12572,7 @@
         <v/>
       </c>
       <c r="H144" s="15" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I144" s="16">
         <f>G144*H144</f>
@@ -12599,7 +12619,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>LUM-BALIZADOR</t>
+          <t>FV-STRINGBOX</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
@@ -12609,7 +12629,7 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Balizador LED de escada, 3 W</t>
+          <t>String box CC com DPS e seccionadora</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
@@ -12618,7 +12638,7 @@
         </is>
       </c>
       <c r="E145" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F145" s="13" t="n">
         <v>0</v>
@@ -12628,7 +12648,7 @@
         <v/>
       </c>
       <c r="H145" s="15" t="n">
-        <v>85</v>
+        <v>680</v>
       </c>
       <c r="I145" s="16">
         <f>G145*H145</f>
@@ -12675,17 +12695,17 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>MET-ENGATE</t>
+          <t>SPD-ENSAIO</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>Engate flexivel</t>
+          <t>Ensaio de continuidade e resistencia de aterramento</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
@@ -12694,7 +12714,7 @@
         </is>
       </c>
       <c r="E146" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F146" s="13" t="n">
         <v>0</v>
@@ -12704,7 +12724,7 @@
         <v/>
       </c>
       <c r="H146" s="15" t="n">
-        <v>22</v>
+        <v>650</v>
       </c>
       <c r="I146" s="16">
         <f>G146*H146</f>
@@ -12751,26 +12771,26 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN-T</t>
+          <t>FV-CABO</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Torneira de tanque e de jardim</t>
+          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
-        <v>3</v>
+        <v>46.3</v>
       </c>
       <c r="F147" s="13" t="n">
         <v>0</v>
@@ -12780,7 +12800,7 @@
         <v/>
       </c>
       <c r="H147" s="15" t="n">
-        <v>160</v>
+        <v>14</v>
       </c>
       <c r="I147" s="16">
         <f>G147*H147</f>
@@ -12827,17 +12847,17 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>SPD-BEP</t>
+          <t>LOU-TANQUE</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Barramento de equipotencializacao principal</t>
+          <t>Tanque de lavanderia</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
@@ -12846,7 +12866,7 @@
         </is>
       </c>
       <c r="E148" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="13" t="n">
         <v>0</v>
@@ -12856,7 +12876,7 @@
         <v/>
       </c>
       <c r="H148" s="15" t="n">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="I148" s="16">
         <f>G148*H148</f>
@@ -12903,7 +12923,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>MET-VALV</t>
+          <t>MET-TORN-T</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
@@ -12913,7 +12933,7 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Valvula de escoamento e de lavatorio</t>
+          <t>Torneira de tanque e de jardim</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
@@ -12922,7 +12942,7 @@
         </is>
       </c>
       <c r="E149" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F149" s="13" t="n">
         <v>0</v>
@@ -12932,7 +12952,7 @@
         <v/>
       </c>
       <c r="H149" s="15" t="n">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="I149" s="16">
         <f>G149*H149</f>
@@ -12979,17 +12999,17 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>SPD-HASTE</t>
+          <t>MET-ENGATE</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>Haste de aterramento 5/8 x 2.400 mm</t>
+          <t>Engate flexivel</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
@@ -12998,7 +13018,7 @@
         </is>
       </c>
       <c r="E150" s="12" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F150" s="13" t="n">
         <v>0</v>
@@ -13008,7 +13028,7 @@
         <v/>
       </c>
       <c r="H150" s="15" t="n">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="I150" s="16">
         <f>G150*H150</f>
@@ -13055,17 +13075,17 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>MET-SIFAO</t>
+          <t>LUM-BALIZADOR</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Sifao flexivel</t>
+          <t>Balizador LED de escada, 3 W</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
@@ -13074,7 +13094,7 @@
         </is>
       </c>
       <c r="E151" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F151" s="13" t="n">
         <v>0</v>
@@ -13084,7 +13104,7 @@
         <v/>
       </c>
       <c r="H151" s="15" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="I151" s="16">
         <f>G151*H151</f>
@@ -13131,7 +13151,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>LOU-TANQUE</t>
+          <t>MET-VALV</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -13141,7 +13161,7 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Tanque de lavanderia</t>
+          <t>Valvula de escoamento e de lavatorio</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
@@ -13150,7 +13170,7 @@
         </is>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F152" s="13" t="n">
         <v>0</v>
@@ -13160,7 +13180,7 @@
         <v/>
       </c>
       <c r="H152" s="15" t="n">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="I152" s="16">
         <f>G152*H152</f>
@@ -13207,7 +13227,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>ELE-DPS</t>
+          <t>SPD-BEP</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
@@ -13217,7 +13237,7 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Dispositivo de protecao contra surtos</t>
+          <t>Barramento de equipotencializacao principal</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
@@ -13226,7 +13246,7 @@
         </is>
       </c>
       <c r="E153" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F153" s="13" t="n">
         <v>0</v>
@@ -13236,7 +13256,7 @@
         <v/>
       </c>
       <c r="H153" s="15" t="n">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="I153" s="16">
         <f>G153*H153</f>
@@ -13281,59 +13301,287 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="22" t="n"/>
-      <c r="B154" s="22" t="n"/>
-      <c r="C154" s="23" t="inlineStr">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>MET-SIFAO</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>loucas</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>Sifao flexivel</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F154" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" s="14">
+        <f>E154*(1+F154)</f>
+        <v/>
+      </c>
+      <c r="H154" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="I154" s="16">
+        <f>G154*H154</f>
+        <v/>
+      </c>
+      <c r="J154" s="17" t="n"/>
+      <c r="K154" s="17" t="n"/>
+      <c r="L154" s="17" t="n"/>
+      <c r="M154" s="17" t="n"/>
+      <c r="N154" s="17" t="n"/>
+      <c r="O154" s="18">
+        <f>COUNT(J154:N154)</f>
+        <v/>
+      </c>
+      <c r="P154" s="19">
+        <f>IF(O154=0,"",MIN(J154:N154))</f>
+        <v/>
+      </c>
+      <c r="Q154" s="10">
+        <f>IF(O154=0,"",INDEX($J$3:$N$3,MATCH(P154,J154:N154,0)))</f>
+        <v/>
+      </c>
+      <c r="R154" s="16">
+        <f>IF(O154=0,"",AVERAGE(J154:N154))</f>
+        <v/>
+      </c>
+      <c r="S154" s="20">
+        <f>IF(O154&lt;2,"",MAX(J154:N154)/P154)</f>
+        <v/>
+      </c>
+      <c r="T154" s="19">
+        <f>IF(O154=0,"",G154*P154)</f>
+        <v/>
+      </c>
+      <c r="U154" s="21">
+        <f>IF(OR(O154=0,I154=0),"",T154/I154-1)</f>
+        <v/>
+      </c>
+      <c r="V154" s="18">
+        <f>IF(O154=0,"PENDENTE",IF(O154&gt;=5,"COMPLETO","PARCIAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>SPD-HASTE</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>eletrica</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
+        <is>
+          <t>Haste de aterramento 5/8 x 2.400 mm</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F155" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="14">
+        <f>E155*(1+F155)</f>
+        <v/>
+      </c>
+      <c r="H155" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="I155" s="16">
+        <f>G155*H155</f>
+        <v/>
+      </c>
+      <c r="J155" s="17" t="n"/>
+      <c r="K155" s="17" t="n"/>
+      <c r="L155" s="17" t="n"/>
+      <c r="M155" s="17" t="n"/>
+      <c r="N155" s="17" t="n"/>
+      <c r="O155" s="18">
+        <f>COUNT(J155:N155)</f>
+        <v/>
+      </c>
+      <c r="P155" s="19">
+        <f>IF(O155=0,"",MIN(J155:N155))</f>
+        <v/>
+      </c>
+      <c r="Q155" s="10">
+        <f>IF(O155=0,"",INDEX($J$3:$N$3,MATCH(P155,J155:N155,0)))</f>
+        <v/>
+      </c>
+      <c r="R155" s="16">
+        <f>IF(O155=0,"",AVERAGE(J155:N155))</f>
+        <v/>
+      </c>
+      <c r="S155" s="20">
+        <f>IF(O155&lt;2,"",MAX(J155:N155)/P155)</f>
+        <v/>
+      </c>
+      <c r="T155" s="19">
+        <f>IF(O155=0,"",G155*P155)</f>
+        <v/>
+      </c>
+      <c r="U155" s="21">
+        <f>IF(OR(O155=0,I155=0),"",T155/I155-1)</f>
+        <v/>
+      </c>
+      <c r="V155" s="18">
+        <f>IF(O155=0,"PENDENTE",IF(O155&gt;=5,"COMPLETO","PARCIAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>ELE-DPS</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>eletrica</t>
+        </is>
+      </c>
+      <c r="C156" s="11" t="inlineStr">
+        <is>
+          <t>Dispositivo de protecao contra surtos</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="14">
+        <f>E156*(1+F156)</f>
+        <v/>
+      </c>
+      <c r="H156" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="I156" s="16">
+        <f>G156*H156</f>
+        <v/>
+      </c>
+      <c r="J156" s="17" t="n"/>
+      <c r="K156" s="17" t="n"/>
+      <c r="L156" s="17" t="n"/>
+      <c r="M156" s="17" t="n"/>
+      <c r="N156" s="17" t="n"/>
+      <c r="O156" s="18">
+        <f>COUNT(J156:N156)</f>
+        <v/>
+      </c>
+      <c r="P156" s="19">
+        <f>IF(O156=0,"",MIN(J156:N156))</f>
+        <v/>
+      </c>
+      <c r="Q156" s="10">
+        <f>IF(O156=0,"",INDEX($J$3:$N$3,MATCH(P156,J156:N156,0)))</f>
+        <v/>
+      </c>
+      <c r="R156" s="16">
+        <f>IF(O156=0,"",AVERAGE(J156:N156))</f>
+        <v/>
+      </c>
+      <c r="S156" s="20">
+        <f>IF(O156&lt;2,"",MAX(J156:N156)/P156)</f>
+        <v/>
+      </c>
+      <c r="T156" s="19">
+        <f>IF(O156=0,"",G156*P156)</f>
+        <v/>
+      </c>
+      <c r="U156" s="21">
+        <f>IF(OR(O156=0,I156=0),"",T156/I156-1)</f>
+        <v/>
+      </c>
+      <c r="V156" s="18">
+        <f>IF(O156=0,"PENDENTE",IF(O156&gt;=5,"COMPLETO","PARCIAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="22" t="n"/>
+      <c r="B157" s="22" t="n"/>
+      <c r="C157" s="23" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="D154" s="22" t="n"/>
-      <c r="E154" s="22" t="n"/>
-      <c r="F154" s="22" t="n"/>
-      <c r="G154" s="22" t="n"/>
-      <c r="H154" s="22" t="n"/>
-      <c r="I154" s="24">
-        <f>SUM(I4:I153)</f>
-        <v/>
-      </c>
-      <c r="J154" s="22" t="n"/>
-      <c r="K154" s="22" t="n"/>
-      <c r="L154" s="22" t="n"/>
-      <c r="M154" s="22" t="n"/>
-      <c r="N154" s="22" t="n"/>
-      <c r="O154" s="22" t="n"/>
-      <c r="P154" s="22" t="n"/>
-      <c r="Q154" s="22" t="n"/>
-      <c r="R154" s="22" t="n"/>
-      <c r="S154" s="22" t="n"/>
-      <c r="T154" s="24">
-        <f>SUM(T4:T153)</f>
-        <v/>
-      </c>
-      <c r="U154" s="25">
-        <f>IF(T154=0,"",T154/I154-1)</f>
-        <v/>
-      </c>
-      <c r="V154" s="22" t="n"/>
-    </row>
-    <row r="156">
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Itens: 150 · linhas cotáveis com especificação completa: 129 · com lacuna a esclarecer com o fornecedor: 88</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="C157" s="2" t="inlineStr">
+      <c r="D157" s="22" t="n"/>
+      <c r="E157" s="22" t="n"/>
+      <c r="F157" s="22" t="n"/>
+      <c r="G157" s="22" t="n"/>
+      <c r="H157" s="22" t="n"/>
+      <c r="I157" s="24">
+        <f>SUM(I4:I156)</f>
+        <v/>
+      </c>
+      <c r="J157" s="22" t="n"/>
+      <c r="K157" s="22" t="n"/>
+      <c r="L157" s="22" t="n"/>
+      <c r="M157" s="22" t="n"/>
+      <c r="N157" s="22" t="n"/>
+      <c r="O157" s="22" t="n"/>
+      <c r="P157" s="22" t="n"/>
+      <c r="Q157" s="22" t="n"/>
+      <c r="R157" s="22" t="n"/>
+      <c r="S157" s="22" t="n"/>
+      <c r="T157" s="24">
+        <f>SUM(T4:T156)</f>
+        <v/>
+      </c>
+      <c r="U157" s="25">
+        <f>IF(T157=0,"",T157/I157-1)</f>
+        <v/>
+      </c>
+      <c r="V157" s="22" t="n"/>
+    </row>
+    <row r="159">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Itens: 153 · linhas cotáveis com especificação completa: 132 · com lacuna a esclarecer com o fornecedor: 91</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>Passe o mouse sobre a DESCRIÇÃO para ver a especificação completa, as normas e a lacuna de cada item.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:V153"/>
-  <conditionalFormatting sqref="V4:V153">
+  <autoFilter ref="A3:V156"/>
+  <conditionalFormatting sqref="V4:V156">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PENDENTE"</formula>
     </cfRule>
@@ -13344,7 +13592,7 @@
       <formula>"COMPLETO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U153">
+  <conditionalFormatting sqref="U4:U156">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0.15</formula>
     </cfRule>
@@ -13352,7 +13600,7 @@
       <formula>-0.15</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S153">
+  <conditionalFormatting sqref="S4:S156">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>1.5</formula>
     </cfRule>
@@ -13453,7 +13701,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A5,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A5,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D5" s="21">
@@ -13465,7 +13713,7 @@
         <v/>
       </c>
       <c r="F5" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A5,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A5,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G5" s="21">
@@ -13473,7 +13721,7 @@
         <v/>
       </c>
       <c r="H5" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A5,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A5,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I5" s="21">
@@ -13491,7 +13739,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A6,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A6,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D6" s="21">
@@ -13503,7 +13751,7 @@
         <v/>
       </c>
       <c r="F6" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A6,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A6,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G6" s="21">
@@ -13511,7 +13759,7 @@
         <v/>
       </c>
       <c r="H6" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A6,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A6,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I6" s="21">
@@ -13529,7 +13777,7 @@
         <v>26</v>
       </c>
       <c r="C7" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A7,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A7,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D7" s="21">
@@ -13541,7 +13789,7 @@
         <v/>
       </c>
       <c r="F7" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A7,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A7,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G7" s="21">
@@ -13549,7 +13797,7 @@
         <v/>
       </c>
       <c r="H7" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A7,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A7,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I7" s="21">
@@ -13567,7 +13815,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A8,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A8,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D8" s="21">
@@ -13579,7 +13827,7 @@
         <v/>
       </c>
       <c r="F8" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A8,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A8,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G8" s="21">
@@ -13587,7 +13835,7 @@
         <v/>
       </c>
       <c r="H8" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A8,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A8,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I8" s="21">
@@ -13605,7 +13853,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A9,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A9,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D9" s="21">
@@ -13617,7 +13865,7 @@
         <v/>
       </c>
       <c r="F9" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A9,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A9,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G9" s="21">
@@ -13625,7 +13873,7 @@
         <v/>
       </c>
       <c r="H9" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A9,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A9,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I9" s="21">
@@ -13643,7 +13891,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A10,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A10,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D10" s="21">
@@ -13655,7 +13903,7 @@
         <v/>
       </c>
       <c r="F10" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A10,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A10,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G10" s="21">
@@ -13663,7 +13911,7 @@
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A10,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A10,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I10" s="21">
@@ -13681,7 +13929,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A11,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A11,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D11" s="21">
@@ -13693,7 +13941,7 @@
         <v/>
       </c>
       <c r="F11" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A11,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A11,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G11" s="21">
@@ -13701,7 +13949,7 @@
         <v/>
       </c>
       <c r="H11" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A11,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A11,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I11" s="21">
@@ -13719,7 +13967,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A12,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A12,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D12" s="21">
@@ -13731,7 +13979,7 @@
         <v/>
       </c>
       <c r="F12" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A12,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A12,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G12" s="21">
@@ -13739,7 +13987,7 @@
         <v/>
       </c>
       <c r="H12" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A12,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A12,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I12" s="21">
@@ -13754,10 +14002,10 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A13,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A13,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D13" s="21">
@@ -13769,7 +14017,7 @@
         <v/>
       </c>
       <c r="F13" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A13,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A13,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G13" s="21">
@@ -13777,7 +14025,7 @@
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A13,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A13,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I13" s="21">
@@ -13788,14 +14036,14 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C14" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A14,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A14,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D14" s="21">
@@ -13807,7 +14055,7 @@
         <v/>
       </c>
       <c r="F14" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A14,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A14,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G14" s="21">
@@ -13815,7 +14063,7 @@
         <v/>
       </c>
       <c r="H14" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A14,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A14,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I14" s="21">
@@ -13826,14 +14074,14 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C15" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A15,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A15,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D15" s="21">
@@ -13845,7 +14093,7 @@
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A15,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A15,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G15" s="21">
@@ -13853,7 +14101,7 @@
         <v/>
       </c>
       <c r="H15" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A15,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A15,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I15" s="21">
@@ -13864,14 +14112,14 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C16" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A16,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A16,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D16" s="21">
@@ -13883,7 +14131,7 @@
         <v/>
       </c>
       <c r="F16" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A16,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A16,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G16" s="21">
@@ -13891,7 +14139,7 @@
         <v/>
       </c>
       <c r="H16" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A16,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A16,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I16" s="21">
@@ -13902,14 +14150,14 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C17" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A17,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A17,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D17" s="21">
@@ -13921,7 +14169,7 @@
         <v/>
       </c>
       <c r="F17" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A17,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A17,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G17" s="21">
@@ -13929,7 +14177,7 @@
         <v/>
       </c>
       <c r="H17" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A17,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A17,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I17" s="21">
@@ -13940,14 +14188,14 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C18" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A18,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A18,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D18" s="21">
@@ -13959,7 +14207,7 @@
         <v/>
       </c>
       <c r="F18" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A18,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A18,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G18" s="21">
@@ -13967,7 +14215,7 @@
         <v/>
       </c>
       <c r="H18" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A18,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A18,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I18" s="21">
@@ -13985,7 +14233,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A19,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A19,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D19" s="21">
@@ -13997,7 +14245,7 @@
         <v/>
       </c>
       <c r="F19" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A19,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A19,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G19" s="21">
@@ -14005,7 +14253,7 @@
         <v/>
       </c>
       <c r="H19" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A19,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A19,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I19" s="21">
@@ -14023,7 +14271,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A20,COTAÇÃO!$I$4:$I$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A20,COTAÇÃO!$I$4:$I$156)</f>
         <v/>
       </c>
       <c r="D20" s="21">
@@ -14035,7 +14283,7 @@
         <v/>
       </c>
       <c r="F20" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$153,$A20,COTAÇÃO!$T$4:$T$153)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$156,$A20,COTAÇÃO!$T$4:$T$156)</f>
         <v/>
       </c>
       <c r="G20" s="21">
@@ -14043,7 +14291,7 @@
         <v/>
       </c>
       <c r="H20" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$153,$A20,COTAÇÃO!$O$4:$O$153,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$156,$A20,COTAÇÃO!$O$4:$O$156,"&gt;0")</f>
         <v/>
       </c>
       <c r="I20" s="21">
@@ -14216,7 +14464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15424,7 +15672,7 @@
         </is>
       </c>
       <c r="E31" s="14" t="n">
-        <v>18.72</v>
+        <v>25.92</v>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
@@ -16190,7 +16438,7 @@
         </is>
       </c>
       <c r="E49" s="14" t="n">
-        <v>2834.4</v>
+        <v>3272</v>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
@@ -16231,7 +16479,7 @@
         </is>
       </c>
       <c r="E50" s="14" t="n">
-        <v>885.8</v>
+        <v>1022.5</v>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
@@ -16313,7 +16561,7 @@
         </is>
       </c>
       <c r="E52" s="14" t="n">
-        <v>188.1</v>
+        <v>192.4</v>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
@@ -16354,7 +16602,7 @@
         </is>
       </c>
       <c r="E53" s="14" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
@@ -16417,7 +16665,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>MEP-ISOL</t>
+          <t>MEP-ESGO50</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -16427,7 +16675,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Isolamento de linha</t>
+          <t>Tubo esgoto DN50</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -16436,11 +16684,11 @@
         </is>
       </c>
       <c r="E55" s="14" t="n">
-        <v>112</v>
+        <v>60.5</v>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>tubo, conexao ou condutor conforme descricao</t>
+          <t>tubo, conexao ou condutor conforme descricao; DN50</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -16458,7 +16706,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>MEP-DISJ</t>
+          <t>MEP-ISOL</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -16468,16 +16716,16 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor</t>
+          <t>Isolamento de linha</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E56" s="14" t="n">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
@@ -16499,7 +16747,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>MEP-ESGO50</t>
+          <t>MEP-DISJ</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -16509,20 +16757,20 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Tubo esgoto DN50</t>
+          <t>Disjuntor</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E57" s="14" t="n">
-        <v>50.6</v>
+        <v>37</v>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>tubo, conexao ou condutor conforme descricao; DN50</t>
+          <t>tubo, conexao ou condutor conforme descricao</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -16559,7 +16807,7 @@
         </is>
       </c>
       <c r="E58" s="14" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
@@ -18173,17 +18421,17 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>REV-ARG</t>
+          <t>MAR-ARM</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Argamassa colante AC-III e regularizacao</t>
+          <t>Armario de MDF sob medida</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -18192,21 +18440,17 @@
         </is>
       </c>
       <c r="E99" s="14" t="n">
-        <v>511.1</v>
+        <v>9.42</v>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
-        </is>
-      </c>
-      <c r="G99" s="11" t="inlineStr">
-        <is>
-          <t>NBR 13818, NBR 15463</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr"/>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I99" s="18" t="inlineStr">
@@ -18218,17 +18462,17 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>MAR-TAMPO</t>
+          <t>REV-ARG</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Tampo de bancada (quartzo/granito)</t>
+          <t>Argamassa colante AC-III e regularizacao</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -18237,17 +18481,21 @@
         </is>
       </c>
       <c r="E100" s="14" t="n">
-        <v>7.17</v>
+        <v>511.1</v>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G100" s="11" t="inlineStr"/>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>NBR 13818, NBR 15463</t>
+        </is>
+      </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I100" s="18" t="inlineStr">
@@ -18259,40 +18507,36 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>FV-INSTAL</t>
+          <t>MAR-TAMPO</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Instalacao e comissionamento</t>
+          <t>Tampo de bancada (quartzo/granito)</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>kWp</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E101" s="14" t="n">
-        <v>15.95</v>
+        <v>7.17</v>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
-        </is>
-      </c>
-      <c r="G101" s="11" t="inlineStr">
-        <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr"/>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I101" s="18" t="inlineStr">
@@ -18304,7 +18548,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>FV-ESTRUTURA</t>
+          <t>FV-INSTAL</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -18314,16 +18558,16 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Estrutura de fixacao em aluminio sobre terca</t>
+          <t>Instalacao e comissionamento</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>kWp</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
-        <v>86.2</v>
+        <v>15.95</v>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
@@ -18349,38 +18593,42 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>PIN-TINTA</t>
+          <t>FV-ESTRUTURA</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
+          <t>Estrutura de fixacao em aluminio sobre terca</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E103" s="14" t="n">
-        <v>179.6</v>
+        <v>86.2</v>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>NBR 11702, NBR 13245</t>
-        </is>
-      </c>
-      <c r="H103" s="11" t="inlineStr"/>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+        </is>
+      </c>
       <c r="I103" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18390,42 +18638,38 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>REV-RODAPE</t>
+          <t>PIN-TINTA</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Rodape (poliestireno 100 mm, pintado)</t>
+          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
-        <v>220.9</v>
+        <v>179.6</v>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
+          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
         <is>
-          <t>NBR 13818, NBR 15463</t>
-        </is>
-      </c>
-      <c r="H104" s="11" t="inlineStr">
-        <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
-        </is>
-      </c>
+          <t>NBR 11702, NBR 13245</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr"/>
       <c r="I104" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18435,40 +18679,40 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>FV-INVERSOR</t>
+          <t>REV-RODAPE</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Inversor string 12 kW, trifasico 220 V</t>
+          <t>Rodape (poliestireno 100 mm, pintado)</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E105" s="14" t="n">
-        <v>12</v>
+        <v>220.9</v>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I105" s="18" t="inlineStr">
@@ -18480,38 +18724,42 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>PIN-FORRO</t>
+          <t>FV-INVERSOR</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Pintura de forro (latex PVA fosco)</t>
+          <t>Inversor string 12 kW, trifasico 220 V</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>kW</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
-        <v>257</v>
+        <v>12</v>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
-          <t>NBR 11702, NBR 13245</t>
-        </is>
-      </c>
-      <c r="H106" s="11" t="inlineStr"/>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+        </is>
+      </c>
       <c r="I106" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18521,42 +18769,38 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT9</t>
+          <t>PIN-FORRO</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 9.000 BTU/h</t>
+          <t>Pintura de forro (latex PVA fosco)</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E107" s="14" t="n">
-        <v>3</v>
+        <v>257</v>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
+          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
-        </is>
-      </c>
-      <c r="H107" s="11" t="inlineStr">
-        <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
-        </is>
-      </c>
+          <t>NBR 11702, NBR 13245</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr"/>
       <c r="I107" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18566,40 +18810,40 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>SPD-CAPTOR</t>
+          <t>EQP-SPLIT9</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
+          <t>Split inverter 9.000 BTU/h</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
-        <v>160.8</v>
+        <v>3</v>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I108" s="18" t="inlineStr">
@@ -18611,36 +18855,40 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>MAR-ARM</t>
+          <t>SPD-CAPTOR</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Armario de MDF sob medida</t>
+          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E109" s="14" t="n">
-        <v>5.94</v>
+        <v>160.8</v>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G109" s="11" t="inlineStr"/>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+        </is>
+      </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
         </is>
       </c>
       <c r="I109" s="18" t="inlineStr">
@@ -18787,40 +19035,36 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>REV-REJ</t>
+          <t>MAR-CORT</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Rejunte epoxi/acrilico</t>
+          <t>Cortina blackout com trilho, dormitorios</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E113" s="14" t="n">
-        <v>511.1</v>
+        <v>13.2</v>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
-        </is>
-      </c>
-      <c r="G113" s="11" t="inlineStr">
-        <is>
-          <t>NBR 13818, NBR 15463</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr"/>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I113" s="18" t="inlineStr">
@@ -18832,40 +19076,40 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>LOU-VASO</t>
+          <t>REV-REJ</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Bacia sanitaria com caixa acoplada</t>
+          <t>Rejunte epoxi/acrilico</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
-        <v>5</v>
+        <v>511.1</v>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I114" s="18" t="inlineStr">
@@ -18877,36 +19121,40 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>MAR-CAB</t>
+          <t>LOU-VASO</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Cabideiro e gaveteiro de closet</t>
+          <t>Bacia sanitaria com caixa acoplada</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E115" s="14" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G115" s="11" t="inlineStr"/>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I115" s="18" t="inlineStr">
@@ -18937,7 +19185,7 @@
         </is>
       </c>
       <c r="E116" s="14" t="n">
-        <v>17.4</v>
+        <v>15.6</v>
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
@@ -18963,40 +19211,40 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>SPD-ANEL</t>
+          <t>MET-TORN</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Anel de aterramento: cobre nu 50 mm2 no perimetro do radier</t>
+          <t>Torneira de bancada (lavatorio e cuba)</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E117" s="14" t="n">
-        <v>63.6</v>
+        <v>9</v>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I117" s="18" t="inlineStr">
@@ -19008,40 +19256,40 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>REV-FORRO-ACUST</t>
+          <t>SPD-ANEL</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Forro absorvente perfurado (alfa 0,70), acabado de fabrica</t>
+          <t>Anel de aterramento: cobre nu 50 mm2 no perimetro do radier</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
-        <v>30.2</v>
+        <v>63.6</v>
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
         </is>
       </c>
       <c r="G118" s="11" t="inlineStr">
         <is>
-          <t>NBR 13818, NBR 15463</t>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
         </is>
       </c>
       <c r="I118" s="18" t="inlineStr">
@@ -19053,36 +19301,40 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>EQP-PISC</t>
+          <t>REV-FORRO-ACUST</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
+          <t>Forro absorvente perfurado (alfa 0,70), acabado de fabrica</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>cj</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E119" s="14" t="n">
-        <v>1</v>
+        <v>30.2</v>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
-        </is>
-      </c>
-      <c r="G119" s="11" t="inlineStr"/>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>NBR 13818, NBR 15463</t>
+        </is>
+      </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I119" s="18" t="inlineStr">
@@ -19094,40 +19346,36 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN</t>
+          <t>EQP-PISC</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Torneira de bancada (lavatorio e cuba)</t>
+          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>cj</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
-        </is>
-      </c>
-      <c r="G120" s="11" t="inlineStr">
-        <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr"/>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I120" s="18" t="inlineStr">
@@ -19139,17 +19387,17 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>EQP-PORTAO</t>
+          <t>LOU-LAV</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Automatizador de portao de correr</t>
+          <t>Lavatorio / cuba de banheiro</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -19158,17 +19406,21 @@
         </is>
       </c>
       <c r="E121" s="14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
-        </is>
-      </c>
-      <c r="G121" s="11" t="inlineStr"/>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I121" s="18" t="inlineStr">
@@ -19180,36 +19432,36 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>MAR-PRAT</t>
+          <t>EQP-PORTAO</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Prateleira e nicho</t>
+          <t>Automatizador de portao de correr</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr"/>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I122" s="18" t="inlineStr">
@@ -19221,7 +19473,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>LOU-LAV</t>
+          <t>MET-ACESS</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
@@ -19231,7 +19483,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Lavatorio / cuba de banheiro</t>
+          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -19240,7 +19492,7 @@
         </is>
       </c>
       <c r="E123" s="14" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
@@ -19266,35 +19518,35 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>PIN-SELADOR</t>
+          <t>ELE-TUG</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Selador acrilico</t>
+          <t>Tomada 2P+T 10 A com placa</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
-        <v>74.8</v>
+        <v>82</v>
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr">
         <is>
-          <t>NBR 11702, NBR 13245</t>
+          <t>NBR 14136, NBR 5410</t>
         </is>
       </c>
       <c r="H124" s="11" t="inlineStr"/>
@@ -19307,40 +19559,36 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>LOU-CUBA</t>
+          <t>MAR-PRAT</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
+          <t>Prateleira e nicho</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E125" s="14" t="n">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
-        </is>
-      </c>
-      <c r="G125" s="11" t="inlineStr">
-        <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr"/>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I125" s="18" t="inlineStr">
@@ -19352,42 +19600,38 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>MET-ACESS</t>
+          <t>PIN-SELADOR</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
+          <t>Selador acrilico</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
-        <v>24</v>
+        <v>74.8</v>
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
-      <c r="H126" s="11" t="inlineStr">
-        <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-        </is>
-      </c>
+          <t>NBR 11702, NBR 13245</t>
+        </is>
+      </c>
+      <c r="H126" s="11" t="inlineStr"/>
       <c r="I126" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -19397,17 +19641,17 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUG</t>
+          <t>LOU-CUBA</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Tomada 2P+T 10 A com placa</t>
+          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
@@ -19416,19 +19660,23 @@
         </is>
       </c>
       <c r="E127" s="14" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H127" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I127" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -19438,36 +19686,36 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>EQP-EXAUST</t>
+          <t>MAR-CAB</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Exaustor / coifa</t>
+          <t>Cabideiro e gaveteiro de closet</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr"/>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I128" s="18" t="inlineStr">
@@ -19479,17 +19727,17 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>FV-HOMOLOG</t>
+          <t>EQP-EXAUST</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Projeto e homologacao na concessionaria (REN 1.000)</t>
+          <t>Exaustor / coifa</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -19498,21 +19746,17 @@
         </is>
       </c>
       <c r="E129" s="14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
-        </is>
-      </c>
-      <c r="G129" s="11" t="inlineStr">
-        <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
-        </is>
-      </c>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr"/>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I129" s="18" t="inlineStr">
@@ -19524,7 +19768,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>LUM-SOBREPOR24</t>
+          <t>FV-HOMOLOG</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
@@ -19534,7 +19778,7 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Plafon LED de sobrepor 24 W</t>
+          <t>Projeto e homologacao na concessionaria (REN 1.000)</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -19543,21 +19787,21 @@
         </is>
       </c>
       <c r="E130" s="14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
         </is>
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
         </is>
       </c>
       <c r="I130" s="18" t="inlineStr">
@@ -19569,17 +19813,17 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>MET-CHUV</t>
+          <t>LUM-SOBREPOR24</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Chuveiro eletrico 220 V</t>
+          <t>Plafon LED de sobrepor 24 W</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -19588,21 +19832,21 @@
         </is>
       </c>
       <c r="E131" s="14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I131" s="18" t="inlineStr">
@@ -19614,7 +19858,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>MET-REG</t>
+          <t>REV-NICHO</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -19624,7 +19868,7 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Registro de gaveta e de pressao</t>
+          <t>Nicho de box 300 x 900 mm entre montantes (RU + ceramica)</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -19633,21 +19877,21 @@
         </is>
       </c>
       <c r="E132" s="14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I132" s="18" t="inlineStr">
@@ -19659,17 +19903,17 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>ELE-DR</t>
+          <t>MET-REG</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor diferencial residual 30 mA</t>
+          <t>Registro de gaveta e de pressao</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
@@ -19678,19 +19922,23 @@
         </is>
       </c>
       <c r="E133" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H133" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I133" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -19700,7 +19948,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>MET-DUCHA</t>
+          <t>MET-CHUV</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -19710,7 +19958,7 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Ducha higienica com registro</t>
+          <t>Chuveiro eletrico 220 V</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
@@ -19719,7 +19967,7 @@
         </is>
       </c>
       <c r="E134" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
@@ -19745,7 +19993,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>SPD-DESCIDA</t>
+          <t>ELE-DR</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -19755,7 +20003,7 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Descida natural pela estrutura LSF: conector de teste e ligacao</t>
+          <t>Disjuntor diferencial residual 30 mA</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -19764,23 +20012,19 @@
         </is>
       </c>
       <c r="E135" s="14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
-        </is>
-      </c>
-      <c r="H135" s="11" t="inlineStr">
-        <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr"/>
       <c r="I135" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -19790,17 +20034,17 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>LUM-ARANDELA</t>
+          <t>MET-DUCHA</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Arandela LED IP44 de espelho, 8 W</t>
+          <t>Ducha higienica com registro</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -19809,21 +20053,21 @@
         </is>
       </c>
       <c r="E136" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I136" s="18" t="inlineStr">
@@ -19835,7 +20079,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>SPD-DPS1</t>
+          <t>SPD-DESCIDA</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
@@ -19845,7 +20089,7 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>DPS classe I, 12,5 kA, 3F+N, na entrada</t>
+          <t>Descida natural pela estrutura LSF: conector de teste e ligacao</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -19854,7 +20098,7 @@
         </is>
       </c>
       <c r="E137" s="14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
@@ -19880,7 +20124,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>LUM-PENDENTE40</t>
+          <t>LUM-ARANDELA</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -19890,7 +20134,7 @@
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Pendente LED de pe-direito duplo, 40 W</t>
+          <t>Arandela LED IP44 de espelho, 8 W</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -19899,7 +20143,7 @@
         </is>
       </c>
       <c r="E138" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
@@ -19925,7 +20169,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>ELE-INT</t>
+          <t>SPD-DPS1</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -19935,7 +20179,7 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Interruptor simples e paralelo com placa</t>
+          <t>DPS classe I, 12,5 kA, 3F+N, na entrada</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
@@ -19944,19 +20188,23 @@
         </is>
       </c>
       <c r="E139" s="14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H139" s="11" t="inlineStr"/>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr">
+        <is>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+        </is>
+      </c>
       <c r="I139" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -19966,7 +20214,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>LOU-ASSENTO</t>
+          <t>MET-DUCHA-TETO</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -19976,7 +20224,7 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>Assento sanitario com amortecedor</t>
+          <t>Ducha de teto 250 mm com desviador (box &gt;= 1.400)</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -19985,7 +20233,7 @@
         </is>
       </c>
       <c r="E140" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F140" s="11" t="inlineStr">
         <is>
@@ -20011,7 +20259,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>FV-STRINGBOX</t>
+          <t>LUM-PENDENTE40</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -20021,7 +20269,7 @@
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>String box CC com DPS e seccionadora</t>
+          <t>Pendente LED de pe-direito duplo, 40 W</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -20030,21 +20278,21 @@
         </is>
       </c>
       <c r="E141" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I141" s="18" t="inlineStr">
@@ -20056,7 +20304,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUE</t>
+          <t>ELE-INT</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -20066,7 +20314,7 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Tomada de uso especifico 20 A com placa</t>
+          <t>Interruptor simples e paralelo com placa</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
@@ -20075,7 +20323,7 @@
         </is>
       </c>
       <c r="E142" s="14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F142" s="11" t="inlineStr">
         <is>
@@ -20097,17 +20345,17 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>SPD-ENSAIO</t>
+          <t>LOU-ASSENTO</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Ensaio de continuidade e resistencia de aterramento</t>
+          <t>Assento sanitario com amortecedor</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
@@ -20116,21 +20364,21 @@
         </is>
       </c>
       <c r="E143" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I143" s="18" t="inlineStr">
@@ -20142,7 +20390,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>FV-CABO</t>
+          <t>ELE-TUE</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -20152,32 +20400,28 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
+          <t>Tomada de uso especifico 20 A com placa</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E144" s="14" t="n">
-        <v>46.3</v>
+        <v>25</v>
       </c>
       <c r="F144" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
-        </is>
-      </c>
-      <c r="H144" s="11" t="inlineStr">
-        <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H144" s="11" t="inlineStr"/>
       <c r="I144" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -20187,7 +20431,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>LUM-BALIZADOR</t>
+          <t>FV-STRINGBOX</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
@@ -20197,7 +20441,7 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Balizador LED de escada, 3 W</t>
+          <t>String box CC com DPS e seccionadora</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
@@ -20206,21 +20450,21 @@
         </is>
       </c>
       <c r="E145" s="14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
         </is>
       </c>
       <c r="I145" s="18" t="inlineStr">
@@ -20232,17 +20476,17 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>MET-ENGATE</t>
+          <t>SPD-ENSAIO</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>Engate flexivel</t>
+          <t>Ensaio de continuidade e resistencia de aterramento</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
@@ -20251,21 +20495,21 @@
         </is>
       </c>
       <c r="E146" s="14" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
         </is>
       </c>
       <c r="H146" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
         </is>
       </c>
       <c r="I146" s="18" t="inlineStr">
@@ -20277,40 +20521,40 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN-T</t>
+          <t>FV-CABO</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Torneira de tanque e de jardim</t>
+          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E147" s="14" t="n">
-        <v>3</v>
+        <v>46.3</v>
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
         </is>
       </c>
       <c r="I147" s="18" t="inlineStr">
@@ -20322,17 +20566,17 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>SPD-BEP</t>
+          <t>LOU-TANQUE</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Barramento de equipotencializacao principal</t>
+          <t>Tanque de lavanderia</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
@@ -20341,21 +20585,21 @@
         </is>
       </c>
       <c r="E148" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H148" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I148" s="18" t="inlineStr">
@@ -20367,7 +20611,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>MET-VALV</t>
+          <t>MET-TORN-T</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
@@ -20377,7 +20621,7 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Valvula de escoamento e de lavatorio</t>
+          <t>Torneira de tanque e de jardim</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
@@ -20386,7 +20630,7 @@
         </is>
       </c>
       <c r="E149" s="14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F149" s="11" t="inlineStr">
         <is>
@@ -20412,17 +20656,17 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>SPD-HASTE</t>
+          <t>MET-ENGATE</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>Haste de aterramento 5/8 x 2.400 mm</t>
+          <t>Engate flexivel</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
@@ -20431,21 +20675,21 @@
         </is>
       </c>
       <c r="E150" s="14" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F150" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H150" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I150" s="18" t="inlineStr">
@@ -20457,17 +20701,17 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>MET-SIFAO</t>
+          <t>LUM-BALIZADOR</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Sifao flexivel</t>
+          <t>Balizador LED de escada, 3 W</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
@@ -20476,21 +20720,21 @@
         </is>
       </c>
       <c r="E151" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I151" s="18" t="inlineStr">
@@ -20502,7 +20746,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>LOU-TANQUE</t>
+          <t>MET-VALV</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -20512,7 +20756,7 @@
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Tanque de lavanderia</t>
+          <t>Valvula de escoamento e de lavatorio</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
@@ -20521,7 +20765,7 @@
         </is>
       </c>
       <c r="E152" s="14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F152" s="11" t="inlineStr">
         <is>
@@ -20547,189 +20791,234 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
+          <t>SPD-BEP</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>eletrica</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr">
+        <is>
+          <t>Barramento de equipotencializacao principal</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E153" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+        </is>
+      </c>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr">
+        <is>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+        </is>
+      </c>
+      <c r="I153" s="18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>MET-SIFAO</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>loucas</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>Sifao flexivel</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G154" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H154" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
+      <c r="I154" s="18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>SPD-HASTE</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>eletrica</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
+        <is>
+          <t>Haste de aterramento 5/8 x 2.400 mm</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+        </is>
+      </c>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr">
+        <is>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+        </is>
+      </c>
+      <c r="I155" s="18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
           <t>ELE-DPS</t>
         </is>
       </c>
-      <c r="B153" s="10" t="inlineStr">
+      <c r="B156" s="10" t="inlineStr">
         <is>
           <t>eletrica</t>
         </is>
       </c>
-      <c r="C153" s="11" t="inlineStr">
+      <c r="C156" s="11" t="inlineStr">
         <is>
           <t>Dispositivo de protecao contra surtos</t>
         </is>
       </c>
-      <c r="D153" s="10" t="inlineStr">
+      <c r="D156" s="10" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E153" s="14" t="n">
+      <c r="E156" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F153" s="11" t="inlineStr">
+      <c r="F156" s="11" t="inlineStr">
         <is>
           <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
-      <c r="G153" s="11" t="inlineStr">
+      <c r="G156" s="11" t="inlineStr">
         <is>
           <t>NBR 14136, NBR 5410</t>
         </is>
       </c>
-      <c r="H153" s="11" t="inlineStr"/>
-      <c r="I153" s="18" t="inlineStr">
+      <c r="H156" s="11" t="inlineStr"/>
+      <c r="I156" s="18" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="3" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t>ROTA ALTERNATIVA — peça cortada e furada em vez de barra</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Estes itens NÃO entram no total: são a mesma estrutura comprada pronta. Cotar os dois e comparar contra o custo de corte próprio.</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="26" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="26" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="B157" s="26" t="inlineStr">
+      <c r="B160" s="26" t="inlineStr">
         <is>
           <t>DESCRIÇÃO</t>
         </is>
       </c>
-      <c r="C157" s="26" t="inlineStr">
+      <c r="C160" s="26" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="D157" s="26" t="inlineStr">
+      <c r="D160" s="26" t="inlineStr">
         <is>
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E157" s="26" t="inlineStr">
+      <c r="E160" s="26" t="inlineStr">
         <is>
           <t>ESPECIFICAÇÃO</t>
         </is>
       </c>
-      <c r="F157" s="26" t="inlineStr">
+      <c r="F160" s="26" t="inlineStr">
         <is>
           <t>NORMAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="9" t="inlineStr">
-        <is>
-          <t>PF-Ue 90x40x12x0,95</t>
-        </is>
-      </c>
-      <c r="B158" s="11" t="inlineStr">
-        <is>
-          <t>Ue 90x40x12x0,95</t>
-        </is>
-      </c>
-      <c r="C158" s="10" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="D158" s="14" t="n">
-        <v>547</v>
-      </c>
-      <c r="E158" s="11" t="inlineStr">
-        <is>
-          <t>peca cortada e furada conforme Ue 90x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
-        </is>
-      </c>
-      <c r="F158" s="10" t="inlineStr">
-        <is>
-          <t>NBR 15253</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="9" t="inlineStr">
-        <is>
-          <t>PF-Ue 250x40x15x3,00</t>
-        </is>
-      </c>
-      <c r="B159" s="11" t="inlineStr">
-        <is>
-          <t>Ue 250x40x15x3,00</t>
-        </is>
-      </c>
-      <c r="C159" s="10" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="D159" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="E159" s="11" t="inlineStr">
-        <is>
-          <t>peca cortada e furada conforme Ue 250x40x15x3,00; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
-        </is>
-      </c>
-      <c r="F159" s="10" t="inlineStr">
-        <is>
-          <t>NBR 15253</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="9" t="inlineStr">
-        <is>
-          <t>PF-U 92x38x0,95</t>
-        </is>
-      </c>
-      <c r="B160" s="11" t="inlineStr">
-        <is>
-          <t>U 92x38x0,95</t>
-        </is>
-      </c>
-      <c r="C160" s="10" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="D160" s="14" t="n">
-        <v>299</v>
-      </c>
-      <c r="E160" s="11" t="inlineStr">
-        <is>
-          <t>peca cortada e furada conforme U 92x38x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
-        </is>
-      </c>
-      <c r="F160" s="10" t="inlineStr">
-        <is>
-          <t>NBR 15253</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 250x40x12x2,25</t>
+          <t>PF-Ue 90x40x12x0,95</t>
         </is>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x2,25</t>
+          <t>Ue 90x40x12x0,95</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
@@ -20738,11 +21027,11 @@
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>24</v>
+        <v>547</v>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 250x40x12x2,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 90x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
@@ -20754,12 +21043,12 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 200x40x12x1,25</t>
+          <t>PF-Ue 250x40x15x3,00</t>
         </is>
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x1,25</t>
+          <t>Ue 250x40x15x3,00</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
@@ -20768,11 +21057,11 @@
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 200x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 250x40x15x3,00; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F162" s="10" t="inlineStr">
@@ -20784,12 +21073,12 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 200x40x12x0,95</t>
+          <t>PF-U 92x38x0,95</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x0,95</t>
+          <t>U 92x38x0,95</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
@@ -20798,11 +21087,11 @@
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>24</v>
+        <v>299</v>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 200x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme U 92x38x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
@@ -20814,12 +21103,12 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 140x40x12x0,80</t>
+          <t>PF-Ue 250x40x12x2,25</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x0,80</t>
+          <t>Ue 250x40x12x2,25</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
@@ -20828,11 +21117,11 @@
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 140x40x12x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 250x40x12x2,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
@@ -20844,12 +21133,12 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 90x40x12x1,25</t>
+          <t>PF-Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>Ue 90x40x12x1,25</t>
+          <t>Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
@@ -20858,11 +21147,11 @@
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 90x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 200x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
@@ -20874,12 +21163,12 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 140x40x12x1,25</t>
+          <t>PF-Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x1,25</t>
+          <t>Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
@@ -20888,11 +21177,11 @@
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 140x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 200x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F166" s="10" t="inlineStr">
@@ -20904,12 +21193,12 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 250x40x12x1,25</t>
+          <t>PF-Ue 140x40x12x0,80</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x1,25</t>
+          <t>Ue 140x40x12x0,80</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
@@ -20918,11 +21207,11 @@
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 250x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 140x40x12x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
@@ -20934,12 +21223,12 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>PF-Fita 38x0,80</t>
+          <t>PF-Ue 90x40x12x1,25</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>Fita 38x0,80</t>
+          <t>Ue 90x40x12x1,25</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
@@ -20948,11 +21237,11 @@
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Fita 38x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 90x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F168" s="10" t="inlineStr">
@@ -20964,36 +21253,126 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
+          <t>PF-Ue 140x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>Ue 140x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="D169" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>peca cortada e furada conforme Ue 140x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+        </is>
+      </c>
+      <c r="F169" s="10" t="inlineStr">
+        <is>
+          <t>NBR 15253</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>PF-Ue 250x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t>Ue 250x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="D170" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>peca cortada e furada conforme Ue 250x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+        </is>
+      </c>
+      <c r="F170" s="10" t="inlineStr">
+        <is>
+          <t>NBR 15253</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>PF-Fita 38x0,80</t>
+        </is>
+      </c>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t>Fita 38x0,80</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="D171" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>peca cortada e furada conforme Fita 38x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+        </is>
+      </c>
+      <c r="F171" s="10" t="inlineStr">
+        <is>
+          <t>NBR 15253</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
           <t>PLACA</t>
         </is>
       </c>
-      <c r="B169" s="11" t="inlineStr">
+      <c r="B172" s="11" t="inlineStr">
         <is>
           <t>Placa (gesso, RU e cimenticia)</t>
         </is>
       </c>
-      <c r="C169" s="10" t="inlineStr">
+      <c r="C172" s="10" t="inlineStr">
         <is>
           <t>pc</t>
         </is>
       </c>
-      <c r="D169" s="14" t="n">
+      <c r="D172" s="14" t="n">
         <v>837</v>
       </c>
-      <c r="E169" s="11" t="inlineStr">
+      <c r="E172" s="11" t="inlineStr">
         <is>
           <t>placa inteira, por formato — rota alternativa a compra por m2; formatos: 1200 x 2400, 1200 x 25000, 600 x 1250</t>
         </is>
       </c>
-      <c r="F169" s="10" t="inlineStr">
+      <c r="F172" s="10" t="inlineStr">
         <is>
           <t>NBR 15758</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I153"/>
-  <conditionalFormatting sqref="I4:I153">
+  <autoFilter ref="A3:I156"/>
+  <conditionalFormatting sqref="I4:I156">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"com lacuna"</formula>
     </cfRule>
@@ -22628,7 +23007,7 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B50" s="18" t="n">
@@ -22636,7 +23015,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Tecnoframe</t>
+          <t>Du Norte Comercio</t>
         </is>
       </c>
       <c r="D50" s="36" t="inlineStr">
@@ -22646,7 +23025,7 @@
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>fornecimento com montagem, praca local</t>
+          <t>tubo, conexao e eletroduto</t>
         </is>
       </c>
       <c r="F50" s="37" t="n"/>
@@ -22661,7 +23040,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B51" s="18" t="n">
@@ -22669,7 +23048,7 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Barbieri do Brasil</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -22679,7 +23058,7 @@
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>fornecimento; montagem por rede credenciada</t>
+          <t>tubos e conexoes PVC</t>
         </is>
       </c>
       <c r="F51" s="37" t="n"/>
@@ -22694,7 +23073,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B52" s="18" t="n">
@@ -22702,7 +23081,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Naframe</t>
+          <t>Amanco / Wavin</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
@@ -22712,7 +23091,7 @@
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>projeto, fornecimento e montagem</t>
+          <t>tubos e conexoes</t>
         </is>
       </c>
       <c r="F52" s="37" t="n"/>
@@ -22727,7 +23106,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B53" s="18" t="n">
@@ -22735,7 +23114,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>MPS Steel</t>
+          <t>Prysmian / Cobrecom / Sil</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
@@ -22745,7 +23124,7 @@
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>fornecimento e montagem</t>
+          <t>cabo de cobre</t>
         </is>
       </c>
       <c r="F53" s="37" t="n"/>
@@ -22760,7 +23139,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>servico</t>
+          <t>instalacao</t>
         </is>
       </c>
       <c r="B54" s="18" t="n">
@@ -22768,7 +23147,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Alge Steel</t>
+          <t>Schneider / Siemens / Steck</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -22778,7 +23157,7 @@
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>fornecimento; montagem por parceiro</t>
+          <t>disjuntor e quadro</t>
         </is>
       </c>
       <c r="F54" s="37" t="n"/>
@@ -22793,7 +23172,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B55" s="18" t="n">
@@ -22801,7 +23180,7 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Du Norte Comercio</t>
+          <t>Tecnoframe</t>
         </is>
       </c>
       <c r="D55" s="36" t="inlineStr">
@@ -22811,7 +23190,7 @@
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>tubo, conexao e eletroduto</t>
+          <t>fornecimento com montagem, praca local</t>
         </is>
       </c>
       <c r="F55" s="37" t="n"/>
@@ -22826,7 +23205,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B56" s="18" t="n">
@@ -22834,7 +23213,7 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Barbieri do Brasil</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
@@ -22844,7 +23223,7 @@
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>tubos e conexoes PVC</t>
+          <t>fornecimento; montagem por rede credenciada</t>
         </is>
       </c>
       <c r="F56" s="37" t="n"/>
@@ -22859,7 +23238,7 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B57" s="18" t="n">
@@ -22867,7 +23246,7 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Amanco / Wavin</t>
+          <t>Naframe</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
@@ -22877,7 +23256,7 @@
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>tubos e conexoes</t>
+          <t>projeto, fornecimento e montagem</t>
         </is>
       </c>
       <c r="F57" s="37" t="n"/>
@@ -22892,7 +23271,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B58" s="18" t="n">
@@ -22900,7 +23279,7 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Prysmian / Cobrecom / Sil</t>
+          <t>MPS Steel</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -22910,7 +23289,7 @@
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>cabo de cobre</t>
+          <t>fornecimento e montagem</t>
         </is>
       </c>
       <c r="F58" s="37" t="n"/>
@@ -22925,7 +23304,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>instalacao</t>
+          <t>servico</t>
         </is>
       </c>
       <c r="B59" s="18" t="n">
@@ -22933,7 +23312,7 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Schneider / Siemens / Steck</t>
+          <t>Alge Steel</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -22943,7 +23322,7 @@
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>disjuntor e quadro</t>
+          <t>fornecimento; montagem por parceiro</t>
         </is>
       </c>
       <c r="F59" s="37" t="n"/>
@@ -22958,7 +23337,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B60" s="18" t="n">
@@ -22966,17 +23345,17 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Empreiteiras de pintura de Manaus</t>
-        </is>
-      </c>
-      <c r="D60" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Deca / Duratex</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>material e mao de obra</t>
+          <t>louca e metal, fabricante</t>
         </is>
       </c>
       <c r="F60" s="37" t="n"/>
@@ -22991,7 +23370,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B61" s="18" t="n">
@@ -22999,7 +23378,7 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Suvinil / BASF</t>
+          <t>Docol</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -23009,7 +23388,7 @@
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>tinta, fabricante</t>
+          <t>metal sanitario</t>
         </is>
       </c>
       <c r="F61" s="37" t="n"/>
@@ -23024,7 +23403,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B62" s="18" t="n">
@@ -23032,7 +23411,7 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Coral / AkzoNobel</t>
+          <t>Roca / Celite</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -23042,7 +23421,7 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>tinta, fabricante</t>
+          <t>louca sanitaria</t>
         </is>
       </c>
       <c r="F62" s="37" t="n"/>
@@ -23057,7 +23436,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B63" s="18" t="n">
@@ -23065,17 +23444,17 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Lojas de acabamento de Manaus</t>
+        </is>
+      </c>
+      <c r="D63" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>tinta, fabricante</t>
+          <t>louca e metal</t>
         </is>
       </c>
       <c r="F63" s="37" t="n"/>
@@ -23090,7 +23469,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B64" s="18" t="n">
@@ -23108,7 +23487,7 @@
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>tinta e material de pintura</t>
+          <t>louca, metal e acessorio</t>
         </is>
       </c>
       <c r="F64" s="37" t="n"/>
@@ -23123,7 +23502,7 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B65" s="18" t="n">
@@ -23131,7 +23510,7 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Lojas de climatizacao de Manaus</t>
+          <t>Empreiteiras de pintura de Manaus</t>
         </is>
       </c>
       <c r="D65" s="36" t="inlineStr">
@@ -23141,7 +23520,7 @@
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>split com instalacao</t>
+          <t>material e mao de obra</t>
         </is>
       </c>
       <c r="F65" s="37" t="n"/>
@@ -23156,7 +23535,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B66" s="18" t="n">
@@ -23164,7 +23543,7 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>LG / Samsung / Daikin</t>
+          <t>Suvinil / BASF</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -23174,7 +23553,7 @@
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>split inverter, fabricante</t>
+          <t>tinta, fabricante</t>
         </is>
       </c>
       <c r="F66" s="37" t="n"/>
@@ -23189,7 +23568,7 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B67" s="18" t="n">
@@ -23197,7 +23576,7 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Midea / Elgin</t>
+          <t>Coral / AkzoNobel</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -23207,7 +23586,7 @@
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>split inverter</t>
+          <t>tinta, fabricante</t>
         </is>
       </c>
       <c r="F67" s="37" t="n"/>
@@ -23222,7 +23601,7 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B68" s="18" t="n">
@@ -23230,7 +23609,7 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Jacuzzi / Sodramar</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -23240,7 +23619,7 @@
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>bomba e filtro de piscina</t>
+          <t>tinta, fabricante</t>
         </is>
       </c>
       <c r="F68" s="37" t="n"/>
@@ -23255,7 +23634,7 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B69" s="18" t="n">
@@ -23263,17 +23642,17 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>PPA / Garen / Rossi</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Du Norte Comercio</t>
+        </is>
+      </c>
+      <c r="D69" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>automatizador de portao</t>
+          <t>tinta e material de pintura</t>
         </is>
       </c>
       <c r="F69" s="37" t="n"/>
@@ -23288,7 +23667,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B70" s="18" t="n">
@@ -23296,17 +23675,17 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Deca / Duratex</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Lojas de climatizacao de Manaus</t>
+        </is>
+      </c>
+      <c r="D70" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>louca e metal, fabricante</t>
+          <t>split com instalacao</t>
         </is>
       </c>
       <c r="F70" s="37" t="n"/>
@@ -23321,7 +23700,7 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B71" s="18" t="n">
@@ -23329,7 +23708,7 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Docol</t>
+          <t>LG / Samsung / Daikin</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -23339,7 +23718,7 @@
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>metal sanitario</t>
+          <t>split inverter, fabricante</t>
         </is>
       </c>
       <c r="F71" s="37" t="n"/>
@@ -23354,7 +23733,7 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B72" s="18" t="n">
@@ -23362,7 +23741,7 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Roca / Celite</t>
+          <t>Midea / Elgin</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -23372,7 +23751,7 @@
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>louca sanitaria</t>
+          <t>split inverter</t>
         </is>
       </c>
       <c r="F72" s="37" t="n"/>
@@ -23387,7 +23766,7 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B73" s="18" t="n">
@@ -23395,17 +23774,17 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Lojas de acabamento de Manaus</t>
-        </is>
-      </c>
-      <c r="D73" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Jacuzzi / Sodramar</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>louca e metal</t>
+          <t>bomba e filtro de piscina</t>
         </is>
       </c>
       <c r="F73" s="37" t="n"/>
@@ -23420,7 +23799,7 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="B74" s="18" t="n">
@@ -23428,17 +23807,17 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Du Norte Comercio</t>
-        </is>
-      </c>
-      <c r="D74" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>PPA / Garen / Rossi</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>louca, metal e acessorio</t>
+          <t>automatizador de portao</t>
         </is>
       </c>
       <c r="F74" s="37" t="n"/>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1507,7 +1507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R63</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R64</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1507,7 +1507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R64</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R65</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1507,7 +1507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R65</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R66</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1513,7 +1513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R67</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R68</t>
         </is>
       </c>
     </row>
@@ -24640,7 +24640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -24769,71 +24769,67 @@
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B11" s="43" t="inlineStr">
         <is>
-          <t>Certidao oficial do SU16 (CAMT, taxa de ocupacao, gabarito)</t>
+          <t>Convencao de lateral esquerda/direita para os recuos</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lei 1.838/2014</t>
+          <t>Lei 1.838/2014 (SU16) — texto do recuo lateral</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>obra</t>
+          <t>aprovacao</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Condiciona toda a implantacao</t>
+          <t>A casa tem 2,40 m de recuo ao SUL e 4,40 m ao NORTE. O caso declara RECUO_ESQ = 2,40 (sul) e RECUO_DIR_MIN = 3,00 (norte) pela convencao do observador na rua. A descricao do proprietario usa a convencao oposta. Se a certidao adotar a segunda, o lado que precisa de 3,00 passa a ser o SUL, onde ha 2,40: infracao de 600 mm. Resolve-se lendo o texto legal, nao medindo nada</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B12" s="43" t="inlineStr">
         <is>
-          <t>Calculo estrutural do hibrido LSF + laminado, com ART</t>
+          <t>Levantamento planialtimetrico do lote</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>NBR 8800 / 14762</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>fabricacao</t>
-        </is>
-      </c>
+          <t>NBR 13133</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Estrutura e balanco; inclui o apoio da caixa d'agua. O pre-dimensionamento por flecha nao substitui verificacao de flambagem lateral</t>
+          <t>A topografia entrou como FAIXA declarada pelo proprietario (1 % a 2 % para a rua), nao como poligonal medida. O projeto usa o pior caso em volume de terra e o melhor caso em caimento, e nucleo/terreno mostra que a faixa inteira cabe dentro da troca de solo que o SPT ja obrigou. Um levantamento real fecha as cotas de locacao e o RN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" s="43" t="inlineStr">
         <is>
-          <t>Regulamento especifico do condominio</t>
+          <t>Certidao oficial do SU16 (CAMT, taxa de ocupacao, gabarito)</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lei 1.838/2014</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
@@ -24843,24 +24839,24 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Fachada, muros, recuos e especie vegetal</t>
+          <t>Condiciona toda a implantacao</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" s="43" t="inlineStr">
         <is>
-          <t>Nesting codificado dos paineis LSF</t>
+          <t>Calculo estrutural do hibrido LSF + laminado, com ART</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>fabricante</t>
+          <t>NBR 8800 / 14762</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
@@ -24870,82 +24866,136 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>A paginacao atual e de estudo, nao de corte</t>
+          <t>Estrutura e balanco; inclui o apoio da caixa d'agua. O pre-dimensionamento por flecha nao substitui verificacao de flambagem lateral</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B15" s="43" t="inlineStr">
         <is>
-          <t>Dados de sitio da energia: raios, sol e tarifa</t>
+          <t>Regulamento especifico do condominio</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>NBR 5419-2 (Ng) · Atlas Brasileiro de Energia Solar (HSP) · ANEEL/Amazonas Energia (tarifa)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>obra</t>
+        </is>
+      </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>O SPDA e a fotovoltaica sao dimensionados com tres numeros de sitio que entraram (H): densidade de descargas Ng = 12/km2.ano, irradiacao 4,6 kWh/m2.dia e tarifa R$ 0,95/kWh. Nenhum muda a casa; os tres mudam o payback e a classe de protecao. Confirmar no mapa RINDAT/ELAT, no Atlas INPE e na fatura</t>
+          <t>Fachada, muros, recuos e especie vegetal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B16" s="43" t="inlineStr">
         <is>
-          <t>Rota de conformidade termica da parede externa</t>
+          <t>Nesting codificado dos paineis LSF</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>NBR 15220-3 (tabela da ZB8) x NBR 15575-4 (desempenho)</t>
+          <t>fabricante</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>aprovacao</t>
+          <t>fabricacao</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>A parede PE-1 tem U = 0,532 W/m2.K, sete vezes melhor que o U &lt;= 3,60 da linha 'parede leve refletora' da ZB8 — e por isso mesmo seu atraso termico (4,90 h) passa dos 4,3 h que a MESMA linha admite. Nao ha defeito a corrigir: ha categoria a escolher. A leitura tecnica e que a tabela prescritiva da 15220-3 foi escrita para paredes de U alto, e que em clima quente-umido inercia e passivo e nao ativo — mas a confirmacao disso depende do TEXTO da 15575-4, que este projeto nao tem acesso para ler. Enquanto nao for lido, a classificacao entra (H) e a verificacao registra ATENCAO, nunca aprovacao</t>
+          <t>A paginacao atual e de estudo, nao de corte</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Dados de sitio da energia: raios, sol e tarifa</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>NBR 5419-2 (Ng) · Atlas Brasileiro de Energia Solar (HSP) · ANEEL/Amazonas Energia (tarifa)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>O SPDA e a fotovoltaica sao dimensionados com tres numeros de sitio que entraram (H): densidade de descargas Ng = 12/km2.ano, irradiacao 4,6 kWh/m2.dia e tarifa R$ 0,95/kWh. Nenhum muda a casa; os tres mudam o payback e a classe de protecao. Confirmar no mapa RINDAT/ELAT, no Atlas INPE e na fatura</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>Rota de conformidade termica da parede externa</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15220-3 (tabela da ZB8) x NBR 15575-4 (desempenho)</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>aprovacao</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>A parede PE-1 tem U = 0,532 W/m2.K, sete vezes melhor que o U &lt;= 3,60 da linha 'parede leve refletora' da ZB8 — e por isso mesmo seu atraso termico (4,90 h) passa dos 4,3 h que a MESMA linha admite. Nao ha defeito a corrigir: ha categoria a escolher. A leitura tecnica e que a tabela prescritiva da 15220-3 foi escrita para paredes de U alto, e que em clima quente-umido inercia e passivo e nao ativo — mas a confirmacao disso depende do TEXTO da 15575-4, que este projeto nao tem acesso para ler. Enquanto nao for lido, a classificacao entra (H) e a verificacao registra ATENCAO, nunca aprovacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>Cotacao dos materiais: 100 % dos precos sao (H)</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Lei 14.133 art. 23 (parametro de 3 propostas)</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>contrato</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>O mapa de cotacao existe e esta pronto para sair; enquanto nao voltar, o custo e ordem de grandeza para auditar quantidade, nunca base de contrato</t>
         </is>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1513,7 +1513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R68</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R69</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1513,7 +1513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R69</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R70</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -17,8 +17,8 @@
     <sheet name="PEÇAS E CORTE" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COTAÇÃO'!$A$3:$V$157</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ESPECIFICAÇÕES'!$A$3:$I$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COTAÇÃO'!$A$3:$V$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ESPECIFICAÇÕES'!$A$3:$I$158</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PEÇAS E CORTE'!$A$4:$F$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -768,22 +768,22 @@
     </comment>
     <comment ref="C93" authorId="0" shapeId="0">
       <text>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+      </text>
+    </comment>
+    <comment ref="C94" authorId="0" shapeId="0">
+      <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C94" authorId="0" shapeId="0">
+    <comment ref="C95" authorId="0" shapeId="0">
       <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
-      </text>
-    </comment>
-    <comment ref="C95" authorId="0" shapeId="0">
-      <text>
-        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
-LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
       </text>
     </comment>
     <comment ref="C96" authorId="0" shapeId="0">
@@ -794,29 +794,29 @@
     </comment>
     <comment ref="C97" authorId="0" shapeId="0">
       <text>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+      </text>
+    </comment>
+    <comment ref="C98" authorId="0" shapeId="0">
+      <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C98" authorId="0" shapeId="0">
+    <comment ref="C99" authorId="0" shapeId="0">
       <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
 NORMAS: NBR 16401, Portaria INMETRO de eficiencia
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
-    <comment ref="C99" authorId="0" shapeId="0">
+    <comment ref="C100" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-      </text>
-    </comment>
-    <comment ref="C100" authorId="0" shapeId="0">
-      <text>
-        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
-LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
       </text>
     </comment>
     <comment ref="C101" authorId="0" shapeId="0">
@@ -841,63 +841,61 @@
     </comment>
     <comment ref="C104" authorId="0" shapeId="0">
       <text>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+      </text>
+    </comment>
+    <comment ref="C105" authorId="0" shapeId="0">
+      <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
       </text>
     </comment>
-    <comment ref="C105" authorId="0" shapeId="0">
+    <comment ref="C106" authorId="0" shapeId="0">
       <text>
         <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
 NORMAS: NBR 11702, NBR 13245</t>
       </text>
     </comment>
-    <comment ref="C106" authorId="0" shapeId="0">
+    <comment ref="C107" authorId="0" shapeId="0">
       <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C107" authorId="0" shapeId="0">
+    <comment ref="C108" authorId="0" shapeId="0">
       <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
       </text>
     </comment>
-    <comment ref="C108" authorId="0" shapeId="0">
+    <comment ref="C109" authorId="0" shapeId="0">
+      <text>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+      </text>
+    </comment>
+    <comment ref="C110" authorId="0" shapeId="0">
       <text>
         <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
 NORMAS: NBR 11702, NBR 13245</t>
       </text>
     </comment>
-    <comment ref="C109" authorId="0" shapeId="0">
+    <comment ref="C111" authorId="0" shapeId="0">
       <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
 NORMAS: NBR 16401, Portaria INMETRO de eficiencia
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
-    <comment ref="C110" authorId="0" shapeId="0">
+    <comment ref="C112" authorId="0" shapeId="0">
       <text>
         <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
 NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
 LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
-      </text>
-    </comment>
-    <comment ref="C111" authorId="0" shapeId="0">
-      <text>
-        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
-NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
-LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
-      </text>
-    </comment>
-    <comment ref="C112" authorId="0" shapeId="0">
-      <text>
-        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
-NORMAS: NBR 16401, Portaria INMETRO de eficiencia
-LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
     <comment ref="C113" authorId="0" shapeId="0">
@@ -909,29 +907,29 @@
     </comment>
     <comment ref="C114" authorId="0" shapeId="0">
       <text>
+        <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A
+NORMAS: NBR 16401, Portaria INMETRO de eficiencia
+LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+      </text>
+    </comment>
+    <comment ref="C115" authorId="0" shapeId="0">
+      <text>
+        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
+NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
+LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+      </text>
+    </comment>
+    <comment ref="C116" authorId="0" shapeId="0">
+      <text>
         <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
 LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
       </text>
     </comment>
-    <comment ref="C115" authorId="0" shapeId="0">
+    <comment ref="C117" authorId="0" shapeId="0">
       <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
-      </text>
-    </comment>
-    <comment ref="C116" authorId="0" shapeId="0">
-      <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-      </text>
-    </comment>
-    <comment ref="C117" authorId="0" shapeId="0">
-      <text>
-        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
-NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
-LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
     <comment ref="C118" authorId="0" shapeId="0">
@@ -943,107 +941,108 @@
     </comment>
     <comment ref="C119" authorId="0" shapeId="0">
       <text>
+        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
+NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
+LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+      </text>
+    </comment>
+    <comment ref="C120" authorId="0" shapeId="0">
+      <text>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+      </text>
+    </comment>
+    <comment ref="C121" authorId="0" shapeId="0">
+      <text>
         <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
 NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
 LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
-    <comment ref="C120" authorId="0" shapeId="0">
+    <comment ref="C122" authorId="0" shapeId="0">
       <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C121" authorId="0" shapeId="0">
+    <comment ref="C123" authorId="0" shapeId="0">
+      <text>
+        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
+LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+      </text>
+    </comment>
+    <comment ref="C124" authorId="0" shapeId="0">
       <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
-    <comment ref="C122" authorId="0" shapeId="0">
+    <comment ref="C125" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C123" authorId="0" shapeId="0">
+    <comment ref="C126" authorId="0" shapeId="0">
       <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
-    <comment ref="C124" authorId="0" shapeId="0">
+    <comment ref="C127" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C125" authorId="0" shapeId="0">
+    <comment ref="C128" authorId="0" shapeId="0">
       <text>
         <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
 NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
-    <comment ref="C126" authorId="0" shapeId="0">
-      <text>
-        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
-LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
-      </text>
-    </comment>
-    <comment ref="C127" authorId="0" shapeId="0">
+    <comment ref="C129" authorId="0" shapeId="0">
       <text>
         <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
 NORMAS: NBR 11702, NBR 13245</t>
       </text>
     </comment>
-    <comment ref="C128" authorId="0" shapeId="0">
+    <comment ref="C130" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C129" authorId="0" shapeId="0">
-      <text>
-        <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
-LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
-      </text>
-    </comment>
-    <comment ref="C130" authorId="0" shapeId="0">
+    <comment ref="C131" authorId="0" shapeId="0">
       <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
-    <comment ref="C131" authorId="0" shapeId="0">
+    <comment ref="C132" authorId="0" shapeId="0">
       <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
       </text>
     </comment>
-    <comment ref="C132" authorId="0" shapeId="0">
+    <comment ref="C133" authorId="0" shapeId="0">
       <text>
         <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
 NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
 LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C133" authorId="0" shapeId="0">
+    <comment ref="C134" authorId="0" shapeId="0">
       <text>
         <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra
 NORMAS: NBR 13818, NBR 15463
 LACUNA: linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
-      </text>
-    </comment>
-    <comment ref="C134" authorId="0" shapeId="0">
-      <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
     <comment ref="C135" authorId="0" shapeId="0">
@@ -1055,97 +1054,97 @@
     </comment>
     <comment ref="C136" authorId="0" shapeId="0">
       <text>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+      </text>
+    </comment>
+    <comment ref="C137" authorId="0" shapeId="0">
+      <text>
         <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
 NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
-    <comment ref="C137" authorId="0" shapeId="0">
+    <comment ref="C138" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C138" authorId="0" shapeId="0">
+    <comment ref="C139" authorId="0" shapeId="0">
       <text>
         <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
 NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
 LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
-    <comment ref="C139" authorId="0" shapeId="0">
+    <comment ref="C140" authorId="0" shapeId="0">
       <text>
         <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
 NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
 LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C140" authorId="0" shapeId="0">
+    <comment ref="C141" authorId="0" shapeId="0">
       <text>
         <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
 NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
 LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
-    <comment ref="C141" authorId="0" shapeId="0">
+    <comment ref="C142" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C142" authorId="0" shapeId="0">
+    <comment ref="C143" authorId="0" shapeId="0">
       <text>
         <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
 NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
 LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C143" authorId="0" shapeId="0">
+    <comment ref="C144" authorId="0" shapeId="0">
       <text>
         <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
 NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
-    <comment ref="C144" authorId="0" shapeId="0">
+    <comment ref="C145" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C145" authorId="0" shapeId="0">
+    <comment ref="C146" authorId="0" shapeId="0">
       <text>
         <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
 NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
-    <comment ref="C146" authorId="0" shapeId="0">
+    <comment ref="C147" authorId="0" shapeId="0">
       <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
       </text>
     </comment>
-    <comment ref="C147" authorId="0" shapeId="0">
+    <comment ref="C148" authorId="0" shapeId="0">
       <text>
         <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
 NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
 LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
-    <comment ref="C148" authorId="0" shapeId="0">
+    <comment ref="C149" authorId="0" shapeId="0">
       <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
-      </text>
-    </comment>
-    <comment ref="C149" authorId="0" shapeId="0">
-      <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
     <comment ref="C150" authorId="0" shapeId="0">
@@ -1164,40 +1163,47 @@
     </comment>
     <comment ref="C152" authorId="0" shapeId="0">
       <text>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+      </text>
+    </comment>
+    <comment ref="C153" authorId="0" shapeId="0">
+      <text>
         <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
 NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
 LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
-    <comment ref="C153" authorId="0" shapeId="0">
+    <comment ref="C154" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C154" authorId="0" shapeId="0">
+    <comment ref="C155" authorId="0" shapeId="0">
       <text>
         <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
 NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
 LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
-    <comment ref="C155" authorId="0" shapeId="0">
+    <comment ref="C156" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
-    <comment ref="C156" authorId="0" shapeId="0">
+    <comment ref="C157" authorId="0" shapeId="0">
       <text>
         <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
 NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
 LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
-    <comment ref="C157" authorId="0" shapeId="0">
+    <comment ref="C158" authorId="0" shapeId="0">
       <text>
         <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
 NORMAS: NBR 14136, NBR 5410</t>
@@ -1513,7 +1519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R70</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R71</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V161"/>
+  <dimension ref="A1:V162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1770,11 +1776,11 @@
         </is>
       </c>
       <c r="Q2" s="4">
-        <f>COUNTIF(V4:V157,"COMPLETO")&amp;" de "&amp;154&amp;" itens com 5 propostas"</f>
+        <f>COUNTIF(V4:V158,"COMPLETO")&amp;" de "&amp;155&amp;" itens com 5 propostas"</f>
         <v/>
       </c>
       <c r="T2" s="7">
-        <f>IF(I158=0,0,SUMIF(V4:V157,"COMPLETO",I4:I157)/I158)</f>
+        <f>IF(I159=0,0,SUMIF(V4:V158,"COMPLETO",I4:I158)/I159)</f>
         <v/>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -8673,17 +8679,17 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>REV-PISO</t>
+          <t>MAR-ARM</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Piso interno (porcelanato retificado)</t>
+          <t>Armario de MDF sob medida (frente)</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -8692,7 +8698,7 @@
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>355.6</v>
+        <v>48.64</v>
       </c>
       <c r="F93" s="13" t="n">
         <v>0</v>
@@ -8702,7 +8708,7 @@
         <v/>
       </c>
       <c r="H93" s="15" t="n">
-        <v>118</v>
+        <v>980</v>
       </c>
       <c r="I93" s="16">
         <f>G93*H93</f>
@@ -8749,26 +8755,26 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>FV-MODULO</t>
+          <t>REV-PISO</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Modulo fotovoltaico 550 Wp</t>
+          <t>Piso interno (porcelanato retificado)</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E94" s="12" t="n">
-        <v>29</v>
+        <v>355.6</v>
       </c>
       <c r="F94" s="13" t="n">
         <v>0</v>
@@ -8778,7 +8784,7 @@
         <v/>
       </c>
       <c r="H94" s="15" t="n">
-        <v>780</v>
+        <v>118</v>
       </c>
       <c r="I94" s="16">
         <f>G94*H94</f>
@@ -8825,26 +8831,26 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>MAR-GAB</t>
+          <t>FV-MODULO</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Gabinete sob bancada, sob medida</t>
+          <t>Modulo fotovoltaico 550 Wp</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F95" s="13" t="n">
         <v>0</v>
@@ -8854,7 +8860,7 @@
         <v/>
       </c>
       <c r="H95" s="15" t="n">
-        <v>1450</v>
+        <v>780</v>
       </c>
       <c r="I95" s="16">
         <f>G95*H95</f>
@@ -8977,26 +8983,26 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>REV-PAREDE</t>
+          <t>MAR-GAB</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Revestimento ceramico de parede em area molhada</t>
+          <t>Gabinete sob bancada, sob medida</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>155.5</v>
+        <v>11.4</v>
       </c>
       <c r="F97" s="13" t="n">
         <v>0</v>
@@ -9006,7 +9012,7 @@
         <v/>
       </c>
       <c r="H97" s="15" t="n">
-        <v>96</v>
+        <v>1450</v>
       </c>
       <c r="I97" s="16">
         <f>G97*H97</f>
@@ -9053,26 +9059,26 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT18</t>
+          <t>REV-PAREDE</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 18.000 BTU/h</t>
+          <t>Revestimento ceramico de parede em area molhada</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E98" s="12" t="n">
-        <v>4</v>
+        <v>155.5</v>
       </c>
       <c r="F98" s="13" t="n">
         <v>0</v>
@@ -9082,7 +9088,7 @@
         <v/>
       </c>
       <c r="H98" s="15" t="n">
-        <v>3200</v>
+        <v>96</v>
       </c>
       <c r="I98" s="16">
         <f>G98*H98</f>
@@ -9129,26 +9135,26 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>LOU-BOX</t>
+          <t>EQP-SPLIT18</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Box de vidro temperado 8 mm, 1.900 mm de altura</t>
+          <t>Split inverter 18.000 BTU/h</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E99" s="12" t="n">
-        <v>16.1</v>
+        <v>4</v>
       </c>
       <c r="F99" s="13" t="n">
         <v>0</v>
@@ -9158,7 +9164,7 @@
         <v/>
       </c>
       <c r="H99" s="15" t="n">
-        <v>620</v>
+        <v>3200</v>
       </c>
       <c r="I99" s="16">
         <f>G99*H99</f>
@@ -9205,17 +9211,17 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>MAR-ARM</t>
+          <t>LOU-BOX</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Armario de MDF sob medida</t>
+          <t>Box de vidro temperado 8 mm, 1.900 mm de altura</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -9224,7 +9230,7 @@
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>9.42</v>
+        <v>16.1</v>
       </c>
       <c r="F100" s="13" t="n">
         <v>0</v>
@@ -9234,7 +9240,7 @@
         <v/>
       </c>
       <c r="H100" s="15" t="n">
-        <v>980</v>
+        <v>620</v>
       </c>
       <c r="I100" s="16">
         <f>G100*H100</f>
@@ -9357,7 +9363,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>MAR-TAMPO</t>
+          <t>MAR-PRAT</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -9367,16 +9373,16 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Tampo de bancada (quartzo/granito)</t>
+          <t>Prateleira aberta, por metro de prateleira</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E102" s="12" t="n">
-        <v>7.17</v>
+        <v>35.19</v>
       </c>
       <c r="F102" s="13" t="n">
         <v>0</v>
@@ -9386,7 +9392,7 @@
         <v/>
       </c>
       <c r="H102" s="15" t="n">
-        <v>1250</v>
+        <v>260</v>
       </c>
       <c r="I102" s="16">
         <f>G102*H102</f>
@@ -9509,17 +9515,17 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>FV-ESTRUTURA</t>
+          <t>MAR-TAMPO</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Estrutura de fixacao em aluminio sobre terca</t>
+          <t>Tampo de bancada (quartzo/granito)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -9528,7 +9534,7 @@
         </is>
       </c>
       <c r="E104" s="12" t="n">
-        <v>86.2</v>
+        <v>6.84</v>
       </c>
       <c r="F104" s="13" t="n">
         <v>0</v>
@@ -9538,7 +9544,7 @@
         <v/>
       </c>
       <c r="H104" s="15" t="n">
-        <v>95</v>
+        <v>1250</v>
       </c>
       <c r="I104" s="16">
         <f>G104*H104</f>
@@ -9585,26 +9591,26 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>PIN-TINTA</t>
+          <t>FV-ESTRUTURA</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
+          <t>Estrutura de fixacao em aluminio sobre terca</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E105" s="12" t="n">
-        <v>179.6</v>
+        <v>86.2</v>
       </c>
       <c r="F105" s="13" t="n">
         <v>0</v>
@@ -9614,7 +9620,7 @@
         <v/>
       </c>
       <c r="H105" s="15" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="I105" s="16">
         <f>G105*H105</f>
@@ -9661,26 +9667,26 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>REV-RODAPE</t>
+          <t>PIN-TINTA</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Rodape (poliestireno 100 mm, pintado)</t>
+          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>220.9</v>
+        <v>179.6</v>
       </c>
       <c r="F106" s="13" t="n">
         <v>0</v>
@@ -9690,7 +9696,7 @@
         <v/>
       </c>
       <c r="H106" s="15" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I106" s="16">
         <f>G106*H106</f>
@@ -9737,26 +9743,26 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>FV-INVERSOR</t>
+          <t>REV-RODAPE</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Inversor string 12 kW, trifasico 220 V</t>
+          <t>Rodape (poliestireno 100 mm, pintado)</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E107" s="12" t="n">
-        <v>12</v>
+        <v>220.9</v>
       </c>
       <c r="F107" s="13" t="n">
         <v>0</v>
@@ -9766,7 +9772,7 @@
         <v/>
       </c>
       <c r="H107" s="15" t="n">
-        <v>620</v>
+        <v>34</v>
       </c>
       <c r="I107" s="16">
         <f>G107*H107</f>
@@ -9813,26 +9819,26 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>PIN-FORRO</t>
+          <t>FV-INVERSOR</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Pintura de forro (latex PVA fosco)</t>
+          <t>Inversor string 12 kW, trifasico 220 V</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>kW</t>
         </is>
       </c>
       <c r="E108" s="12" t="n">
-        <v>257</v>
+        <v>12</v>
       </c>
       <c r="F108" s="13" t="n">
         <v>0</v>
@@ -9842,7 +9848,7 @@
         <v/>
       </c>
       <c r="H108" s="15" t="n">
-        <v>26</v>
+        <v>620</v>
       </c>
       <c r="I108" s="16">
         <f>G108*H108</f>
@@ -9889,26 +9895,26 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT9</t>
+          <t>MAR-CABEC</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 9.000 BTU/h</t>
+          <t>Cabeceira estofada</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
-        <v>3</v>
+        <v>10.96</v>
       </c>
       <c r="F109" s="13" t="n">
         <v>0</v>
@@ -9918,7 +9924,7 @@
         <v/>
       </c>
       <c r="H109" s="15" t="n">
-        <v>2100</v>
+        <v>650</v>
       </c>
       <c r="I109" s="16">
         <f>G109*H109</f>
@@ -9965,26 +9971,26 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>SPD-CAPTOR</t>
+          <t>PIN-FORRO</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
+          <t>Pintura de forro (latex PVA fosco)</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E110" s="12" t="n">
-        <v>160.8</v>
+        <v>257</v>
       </c>
       <c r="F110" s="13" t="n">
         <v>0</v>
@@ -9994,7 +10000,7 @@
         <v/>
       </c>
       <c r="H110" s="15" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="I110" s="16">
         <f>G110*H110</f>
@@ -10041,17 +10047,17 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>LUM-DOWNLIGHT18</t>
+          <t>EQP-SPLIT9</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Downlight LED embutido 18 W</t>
+          <t>Split inverter 9.000 BTU/h</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -10060,7 +10066,7 @@
         </is>
       </c>
       <c r="E111" s="12" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="F111" s="13" t="n">
         <v>0</v>
@@ -10070,7 +10076,7 @@
         <v/>
       </c>
       <c r="H111" s="15" t="n">
-        <v>128</v>
+        <v>2100</v>
       </c>
       <c r="I111" s="16">
         <f>G111*H111</f>
@@ -10117,26 +10123,26 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT30</t>
+          <t>SPD-CAPTOR</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 30.000 BTU/h</t>
+          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E112" s="12" t="n">
-        <v>1</v>
+        <v>160.8</v>
       </c>
       <c r="F112" s="13" t="n">
         <v>0</v>
@@ -10146,7 +10152,7 @@
         <v/>
       </c>
       <c r="H112" s="15" t="n">
-        <v>5400</v>
+        <v>38</v>
       </c>
       <c r="I112" s="16">
         <f>G112*H112</f>
@@ -10193,7 +10199,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>LUM-DOWNLIGHT24</t>
+          <t>LUM-DOWNLIGHT18</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -10203,7 +10209,7 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Downlight LED embutido 24 W</t>
+          <t>Downlight LED embutido 18 W</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -10212,7 +10218,7 @@
         </is>
       </c>
       <c r="E113" s="12" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F113" s="13" t="n">
         <v>0</v>
@@ -10222,7 +10228,7 @@
         <v/>
       </c>
       <c r="H113" s="15" t="n">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="I113" s="16">
         <f>G113*H113</f>
@@ -10269,26 +10275,26 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>MAR-CORT</t>
+          <t>EQP-SPLIT30</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Cortina blackout com trilho, dormitorios</t>
+          <t>Split inverter 30.000 BTU/h</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E114" s="12" t="n">
-        <v>13.2</v>
+        <v>1</v>
       </c>
       <c r="F114" s="13" t="n">
         <v>0</v>
@@ -10298,7 +10304,7 @@
         <v/>
       </c>
       <c r="H114" s="15" t="n">
-        <v>380</v>
+        <v>5400</v>
       </c>
       <c r="I114" s="16">
         <f>G114*H114</f>
@@ -10345,26 +10351,26 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>REV-REJ</t>
+          <t>LUM-DOWNLIGHT24</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Rejunte epoxi/acrilico</t>
+          <t>Downlight LED embutido 24 W</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
-        <v>511.1</v>
+        <v>31</v>
       </c>
       <c r="F115" s="13" t="n">
         <v>0</v>
@@ -10374,7 +10380,7 @@
         <v/>
       </c>
       <c r="H115" s="15" t="n">
-        <v>9</v>
+        <v>165</v>
       </c>
       <c r="I115" s="16">
         <f>G115*H115</f>
@@ -10421,26 +10427,26 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>LOU-VASO</t>
+          <t>MAR-CORT</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Bacia sanitaria com caixa acoplada</t>
+          <t>Cortina blackout com trilho, dormitorios</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E116" s="12" t="n">
-        <v>5</v>
+        <v>13.2</v>
       </c>
       <c r="F116" s="13" t="n">
         <v>0</v>
@@ -10450,7 +10456,7 @@
         <v/>
       </c>
       <c r="H116" s="15" t="n">
-        <v>780</v>
+        <v>380</v>
       </c>
       <c r="I116" s="16">
         <f>G116*H116</f>
@@ -10497,26 +10503,26 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>LUM-LINEAR</t>
+          <t>REV-REJ</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Perfil linear LED 18 W/m com difusor (tarefa)</t>
+          <t>Rejunte epoxi/acrilico</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
-        <v>15.6</v>
+        <v>511.1</v>
       </c>
       <c r="F117" s="13" t="n">
         <v>0</v>
@@ -10526,7 +10532,7 @@
         <v/>
       </c>
       <c r="H117" s="15" t="n">
-        <v>210</v>
+        <v>9</v>
       </c>
       <c r="I117" s="16">
         <f>G117*H117</f>
@@ -10573,7 +10579,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN</t>
+          <t>LOU-VASO</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -10583,7 +10589,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Torneira de bancada (lavatorio e cuba)</t>
+          <t>Bacia sanitaria com caixa acoplada</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -10592,7 +10598,7 @@
         </is>
       </c>
       <c r="E118" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F118" s="13" t="n">
         <v>0</v>
@@ -10602,7 +10608,7 @@
         <v/>
       </c>
       <c r="H118" s="15" t="n">
-        <v>340</v>
+        <v>780</v>
       </c>
       <c r="I118" s="16">
         <f>G118*H118</f>
@@ -10649,7 +10655,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>SPD-ANEL</t>
+          <t>LUM-LINEAR</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -10659,7 +10665,7 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Anel de aterramento: cobre nu 50 mm2 no perimetro do radier</t>
+          <t>Perfil linear LED 18 W/m com difusor (tarefa)</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -10668,7 +10674,7 @@
         </is>
       </c>
       <c r="E119" s="12" t="n">
-        <v>63.6</v>
+        <v>15.6</v>
       </c>
       <c r="F119" s="13" t="n">
         <v>0</v>
@@ -10678,7 +10684,7 @@
         <v/>
       </c>
       <c r="H119" s="15" t="n">
-        <v>46</v>
+        <v>210</v>
       </c>
       <c r="I119" s="16">
         <f>G119*H119</f>
@@ -10725,26 +10731,26 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>REV-FORRO-ACUST</t>
+          <t>MET-TORN</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Forro absorvente perfurado (alfa 0,70), acabado de fabrica</t>
+          <t>Torneira de bancada (lavatorio e cuba)</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E120" s="12" t="n">
-        <v>30.2</v>
+        <v>9</v>
       </c>
       <c r="F120" s="13" t="n">
         <v>0</v>
@@ -10754,7 +10760,7 @@
         <v/>
       </c>
       <c r="H120" s="15" t="n">
-        <v>96</v>
+        <v>340</v>
       </c>
       <c r="I120" s="16">
         <f>G120*H120</f>
@@ -10801,26 +10807,26 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>EQP-PISC</t>
+          <t>SPD-ANEL</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
+          <t>Anel de aterramento: cobre nu 50 mm2 no perimetro do radier</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>cj</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
-        <v>1</v>
+        <v>63.6</v>
       </c>
       <c r="F121" s="13" t="n">
         <v>0</v>
@@ -10830,7 +10836,7 @@
         <v/>
       </c>
       <c r="H121" s="15" t="n">
-        <v>2800</v>
+        <v>46</v>
       </c>
       <c r="I121" s="16">
         <f>G121*H121</f>
@@ -10877,26 +10883,26 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>LOU-LAV</t>
+          <t>REV-FORRO-ACUST</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Lavatorio / cuba de banheiro</t>
+          <t>Forro absorvente perfurado (alfa 0,70), acabado de fabrica</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E122" s="12" t="n">
-        <v>6</v>
+        <v>30.2</v>
       </c>
       <c r="F122" s="13" t="n">
         <v>0</v>
@@ -10906,7 +10912,7 @@
         <v/>
       </c>
       <c r="H122" s="15" t="n">
-        <v>420</v>
+        <v>96</v>
       </c>
       <c r="I122" s="16">
         <f>G122*H122</f>
@@ -10953,26 +10959,26 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>EQP-PORTAO</t>
+          <t>MAR-PAINEL</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Automatizador de portao de correr</t>
+          <t>Painel ripado de TV</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
-        <v>1</v>
+        <v>6.71</v>
       </c>
       <c r="F123" s="13" t="n">
         <v>0</v>
@@ -10982,7 +10988,7 @@
         <v/>
       </c>
       <c r="H123" s="15" t="n">
-        <v>2400</v>
+        <v>420</v>
       </c>
       <c r="I123" s="16">
         <f>G123*H123</f>
@@ -11029,26 +11035,26 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>MET-ACESS</t>
+          <t>EQP-PISC</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
+          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>cj</t>
         </is>
       </c>
       <c r="E124" s="12" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F124" s="13" t="n">
         <v>0</v>
@@ -11058,7 +11064,7 @@
         <v/>
       </c>
       <c r="H124" s="15" t="n">
-        <v>85</v>
+        <v>2800</v>
       </c>
       <c r="I124" s="16">
         <f>G124*H124</f>
@@ -11105,17 +11111,17 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUG</t>
+          <t>LOU-LAV</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Tomada 2P+T 10 A com placa</t>
+          <t>Lavatorio / cuba de banheiro</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -11124,7 +11130,7 @@
         </is>
       </c>
       <c r="E125" s="12" t="n">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="F125" s="13" t="n">
         <v>0</v>
@@ -11134,7 +11140,7 @@
         <v/>
       </c>
       <c r="H125" s="15" t="n">
-        <v>28</v>
+        <v>420</v>
       </c>
       <c r="I125" s="16">
         <f>G125*H125</f>
@@ -11181,26 +11187,26 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>MAR-PRAT</t>
+          <t>EQP-PORTAO</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Prateleira e nicho</t>
+          <t>Automatizador de portao de correr</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E126" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="F126" s="13" t="n">
         <v>0</v>
@@ -11210,7 +11216,7 @@
         <v/>
       </c>
       <c r="H126" s="15" t="n">
-        <v>260</v>
+        <v>2400</v>
       </c>
       <c r="I126" s="16">
         <f>G126*H126</f>
@@ -11257,26 +11263,26 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>PIN-SELADOR</t>
+          <t>MET-ACESS</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Selador acrilico</t>
+          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
-        <v>74.8</v>
+        <v>28</v>
       </c>
       <c r="F127" s="13" t="n">
         <v>0</v>
@@ -11286,7 +11292,7 @@
         <v/>
       </c>
       <c r="H127" s="15" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="I127" s="16">
         <f>G127*H127</f>
@@ -11333,17 +11339,17 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>LOU-CUBA</t>
+          <t>ELE-TUG</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
+          <t>Tomada 2P+T 10 A com placa</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -11352,7 +11358,7 @@
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="F128" s="13" t="n">
         <v>0</v>
@@ -11362,7 +11368,7 @@
         <v/>
       </c>
       <c r="H128" s="15" t="n">
-        <v>690</v>
+        <v>28</v>
       </c>
       <c r="I128" s="16">
         <f>G128*H128</f>
@@ -11409,26 +11415,26 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>MAR-CAB</t>
+          <t>PIN-SELADOR</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Cabideiro e gaveteiro de closet</t>
+          <t>Selador acrilico</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
-        <v>6</v>
+        <v>74.8</v>
       </c>
       <c r="F129" s="13" t="n">
         <v>0</v>
@@ -11438,7 +11444,7 @@
         <v/>
       </c>
       <c r="H129" s="15" t="n">
-        <v>320</v>
+        <v>28</v>
       </c>
       <c r="I129" s="16">
         <f>G129*H129</f>
@@ -11485,17 +11491,17 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>EQP-EXAUST</t>
+          <t>LOU-CUBA</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Exaustor / coifa</t>
+          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -11504,7 +11510,7 @@
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F130" s="13" t="n">
         <v>0</v>
@@ -11514,7 +11520,7 @@
         <v/>
       </c>
       <c r="H130" s="15" t="n">
-        <v>260</v>
+        <v>690</v>
       </c>
       <c r="I130" s="16">
         <f>G130*H130</f>
@@ -11561,17 +11567,17 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>FV-HOMOLOG</t>
+          <t>EQP-EXAUST</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Projeto e homologacao na concessionaria (REN 1.000)</t>
+          <t>Exaustor / coifa</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -11580,7 +11586,7 @@
         </is>
       </c>
       <c r="E131" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F131" s="13" t="n">
         <v>0</v>
@@ -11590,7 +11596,7 @@
         <v/>
       </c>
       <c r="H131" s="15" t="n">
-        <v>1800</v>
+        <v>260</v>
       </c>
       <c r="I131" s="16">
         <f>G131*H131</f>
@@ -11637,7 +11643,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>LUM-SOBREPOR24</t>
+          <t>FV-HOMOLOG</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -11647,7 +11653,7 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Plafon LED de sobrepor 24 W</t>
+          <t>Projeto e homologacao na concessionaria (REN 1.000)</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -11656,7 +11662,7 @@
         </is>
       </c>
       <c r="E132" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F132" s="13" t="n">
         <v>0</v>
@@ -11666,7 +11672,7 @@
         <v/>
       </c>
       <c r="H132" s="15" t="n">
-        <v>175</v>
+        <v>1800</v>
       </c>
       <c r="I132" s="16">
         <f>G132*H132</f>
@@ -11713,17 +11719,17 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>REV-NICHO</t>
+          <t>LUM-SOBREPOR24</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Nicho de box 300 x 900 mm entre montantes (RU + ceramica)</t>
+          <t>Plafon LED de sobrepor 24 W</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
@@ -11732,7 +11738,7 @@
         </is>
       </c>
       <c r="E133" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F133" s="13" t="n">
         <v>0</v>
@@ -11742,7 +11748,7 @@
         <v/>
       </c>
       <c r="H133" s="15" t="n">
-        <v>420</v>
+        <v>175</v>
       </c>
       <c r="I133" s="16">
         <f>G133*H133</f>
@@ -11789,7 +11795,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>MET-REG</t>
+          <t>REV-NICHO</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -11799,7 +11805,7 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Registro de gaveta e de pressao</t>
+          <t>Nicho de box 300 x 900 mm entre montantes (RU + ceramica)</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
@@ -11808,7 +11814,7 @@
         </is>
       </c>
       <c r="E134" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F134" s="13" t="n">
         <v>0</v>
@@ -11818,7 +11824,7 @@
         <v/>
       </c>
       <c r="H134" s="15" t="n">
-        <v>95</v>
+        <v>420</v>
       </c>
       <c r="I134" s="16">
         <f>G134*H134</f>
@@ -11865,7 +11871,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>MET-CHUV</t>
+          <t>MET-REG</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -11875,7 +11881,7 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Chuveiro eletrico 220 V</t>
+          <t>Registro de gaveta e de pressao</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -11884,7 +11890,7 @@
         </is>
       </c>
       <c r="E135" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F135" s="13" t="n">
         <v>0</v>
@@ -11894,7 +11900,7 @@
         <v/>
       </c>
       <c r="H135" s="15" t="n">
-        <v>320</v>
+        <v>95</v>
       </c>
       <c r="I135" s="16">
         <f>G135*H135</f>
@@ -11941,17 +11947,17 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>ELE-DR</t>
+          <t>MET-CHUV</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor diferencial residual 30 mA</t>
+          <t>Chuveiro eletrico 220 V</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -11960,7 +11966,7 @@
         </is>
       </c>
       <c r="E136" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F136" s="13" t="n">
         <v>0</v>
@@ -11970,7 +11976,7 @@
         <v/>
       </c>
       <c r="H136" s="15" t="n">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="I136" s="16">
         <f>G136*H136</f>
@@ -12017,17 +12023,17 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>MET-DUCHA</t>
+          <t>ELE-DR</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Ducha higienica com registro</t>
+          <t>Disjuntor diferencial residual 30 mA</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -12036,7 +12042,7 @@
         </is>
       </c>
       <c r="E137" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F137" s="13" t="n">
         <v>0</v>
@@ -12046,7 +12052,7 @@
         <v/>
       </c>
       <c r="H137" s="15" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="I137" s="16">
         <f>G137*H137</f>
@@ -12093,17 +12099,17 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>SPD-DESCIDA</t>
+          <t>MET-DUCHA</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Descida natural pela estrutura LSF: conector de teste e ligacao</t>
+          <t>Ducha higienica com registro</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -12112,7 +12118,7 @@
         </is>
       </c>
       <c r="E138" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F138" s="13" t="n">
         <v>0</v>
@@ -12122,7 +12128,7 @@
         <v/>
       </c>
       <c r="H138" s="15" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="I138" s="16">
         <f>G138*H138</f>
@@ -12169,7 +12175,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>LUM-ARANDELA</t>
+          <t>SPD-DESCIDA</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -12179,7 +12185,7 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Arandela LED IP44 de espelho, 8 W</t>
+          <t>Descida natural pela estrutura LSF: conector de teste e ligacao</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
@@ -12188,7 +12194,7 @@
         </is>
       </c>
       <c r="E139" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F139" s="13" t="n">
         <v>0</v>
@@ -12198,7 +12204,7 @@
         <v/>
       </c>
       <c r="H139" s="15" t="n">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="I139" s="16">
         <f>G139*H139</f>
@@ -12245,7 +12251,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>SPD-DPS1</t>
+          <t>LUM-ARANDELA</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -12255,7 +12261,7 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>DPS classe I, 12,5 kA, 3F+N, na entrada</t>
+          <t>Arandela LED IP44 de espelho, 8 W</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -12264,7 +12270,7 @@
         </is>
       </c>
       <c r="E140" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F140" s="13" t="n">
         <v>0</v>
@@ -12274,7 +12280,7 @@
         <v/>
       </c>
       <c r="H140" s="15" t="n">
-        <v>890</v>
+        <v>160</v>
       </c>
       <c r="I140" s="16">
         <f>G140*H140</f>
@@ -12321,17 +12327,17 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>MET-DUCHA-TETO</t>
+          <t>SPD-DPS1</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Ducha de teto 250 mm com desviador (box &gt;= 1.400)</t>
+          <t>DPS classe I, 12,5 kA, 3F+N, na entrada</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -12397,17 +12403,17 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>LUM-PENDENTE40</t>
+          <t>MET-DUCHA-TETO</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Pendente LED de pe-direito duplo, 40 W</t>
+          <t>Ducha de teto 250 mm com desviador (box &gt;= 1.400)</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
@@ -12416,7 +12422,7 @@
         </is>
       </c>
       <c r="E142" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F142" s="13" t="n">
         <v>0</v>
@@ -12426,7 +12432,7 @@
         <v/>
       </c>
       <c r="H142" s="15" t="n">
-        <v>420</v>
+        <v>890</v>
       </c>
       <c r="I142" s="16">
         <f>G142*H142</f>
@@ -12473,7 +12479,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>ELE-INT</t>
+          <t>LUM-PENDENTE40</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -12483,7 +12489,7 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Interruptor simples e paralelo com placa</t>
+          <t>Pendente LED de pe-direito duplo, 40 W</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
@@ -12492,7 +12498,7 @@
         </is>
       </c>
       <c r="E143" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F143" s="13" t="n">
         <v>0</v>
@@ -12502,7 +12508,7 @@
         <v/>
       </c>
       <c r="H143" s="15" t="n">
-        <v>32</v>
+        <v>420</v>
       </c>
       <c r="I143" s="16">
         <f>G143*H143</f>
@@ -12549,17 +12555,17 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>LOU-ASSENTO</t>
+          <t>ELE-INT</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Assento sanitario com amortecedor</t>
+          <t>Interruptor simples e paralelo com placa</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
@@ -12568,7 +12574,7 @@
         </is>
       </c>
       <c r="E144" s="12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F144" s="13" t="n">
         <v>0</v>
@@ -12578,7 +12584,7 @@
         <v/>
       </c>
       <c r="H144" s="15" t="n">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="I144" s="16">
         <f>G144*H144</f>
@@ -12625,17 +12631,17 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUE</t>
+          <t>LOU-ASSENTO</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Tomada de uso especifico 20 A com placa</t>
+          <t>Assento sanitario com amortecedor</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
@@ -12644,7 +12650,7 @@
         </is>
       </c>
       <c r="E145" s="12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F145" s="13" t="n">
         <v>0</v>
@@ -12654,7 +12660,7 @@
         <v/>
       </c>
       <c r="H145" s="15" t="n">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="I145" s="16">
         <f>G145*H145</f>
@@ -12701,7 +12707,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>FV-STRINGBOX</t>
+          <t>ELE-TUE</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -12711,7 +12717,7 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>String box CC com DPS e seccionadora</t>
+          <t>Tomada de uso especifico 20 A com placa</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
@@ -12720,7 +12726,7 @@
         </is>
       </c>
       <c r="E146" s="12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F146" s="13" t="n">
         <v>0</v>
@@ -12730,7 +12736,7 @@
         <v/>
       </c>
       <c r="H146" s="15" t="n">
-        <v>680</v>
+        <v>28</v>
       </c>
       <c r="I146" s="16">
         <f>G146*H146</f>
@@ -12777,7 +12783,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>SPD-ENSAIO</t>
+          <t>FV-STRINGBOX</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
@@ -12787,7 +12793,7 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Ensaio de continuidade e resistencia de aterramento</t>
+          <t>String box CC com DPS e seccionadora</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
@@ -12806,7 +12812,7 @@
         <v/>
       </c>
       <c r="H147" s="15" t="n">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="I147" s="16">
         <f>G147*H147</f>
@@ -12853,7 +12859,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>FV-CABO</t>
+          <t>SPD-ENSAIO</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
@@ -12863,16 +12869,16 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
+          <t>Ensaio de continuidade e resistencia de aterramento</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E148" s="12" t="n">
-        <v>46.3</v>
+        <v>1</v>
       </c>
       <c r="F148" s="13" t="n">
         <v>0</v>
@@ -12882,7 +12888,7 @@
         <v/>
       </c>
       <c r="H148" s="15" t="n">
-        <v>14</v>
+        <v>650</v>
       </c>
       <c r="I148" s="16">
         <f>G148*H148</f>
@@ -12929,26 +12935,26 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>LOU-TANQUE</t>
+          <t>FV-CABO</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Tanque de lavanderia</t>
+          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
-        <v>2</v>
+        <v>46.3</v>
       </c>
       <c r="F149" s="13" t="n">
         <v>0</v>
@@ -12958,7 +12964,7 @@
         <v/>
       </c>
       <c r="H149" s="15" t="n">
-        <v>320</v>
+        <v>14</v>
       </c>
       <c r="I149" s="16">
         <f>G149*H149</f>
@@ -13005,7 +13011,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN-T</t>
+          <t>LOU-TANQUE</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
@@ -13015,7 +13021,7 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>Torneira de tanque e de jardim</t>
+          <t>Tanque de lavanderia</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
@@ -13024,7 +13030,7 @@
         </is>
       </c>
       <c r="E150" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F150" s="13" t="n">
         <v>0</v>
@@ -13034,7 +13040,7 @@
         <v/>
       </c>
       <c r="H150" s="15" t="n">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="I150" s="16">
         <f>G150*H150</f>
@@ -13081,7 +13087,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>MET-ENGATE</t>
+          <t>MET-TORN-T</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
@@ -13091,7 +13097,7 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Engate flexivel</t>
+          <t>Torneira de tanque e de jardim</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
@@ -13100,7 +13106,7 @@
         </is>
       </c>
       <c r="E151" s="12" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F151" s="13" t="n">
         <v>0</v>
@@ -13110,7 +13116,7 @@
         <v/>
       </c>
       <c r="H151" s="15" t="n">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="I151" s="16">
         <f>G151*H151</f>
@@ -13157,17 +13163,17 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>LUM-BALIZADOR</t>
+          <t>MET-ENGATE</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Balizador LED de escada, 3 W</t>
+          <t>Engate flexivel</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
@@ -13176,7 +13182,7 @@
         </is>
       </c>
       <c r="E152" s="12" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F152" s="13" t="n">
         <v>0</v>
@@ -13186,7 +13192,7 @@
         <v/>
       </c>
       <c r="H152" s="15" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="I152" s="16">
         <f>G152*H152</f>
@@ -13233,17 +13239,17 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>MET-VALV</t>
+          <t>LUM-BALIZADOR</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Valvula de escoamento e de lavatorio</t>
+          <t>Balizador LED de escada, 3 W</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
@@ -13252,7 +13258,7 @@
         </is>
       </c>
       <c r="E153" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F153" s="13" t="n">
         <v>0</v>
@@ -13262,7 +13268,7 @@
         <v/>
       </c>
       <c r="H153" s="15" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="I153" s="16">
         <f>G153*H153</f>
@@ -13309,17 +13315,17 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>SPD-BEP</t>
+          <t>MET-VALV</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>Barramento de equipotencializacao principal</t>
+          <t>Valvula de escoamento e de lavatorio</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
@@ -13328,7 +13334,7 @@
         </is>
       </c>
       <c r="E154" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F154" s="13" t="n">
         <v>0</v>
@@ -13338,7 +13344,7 @@
         <v/>
       </c>
       <c r="H154" s="15" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="I154" s="16">
         <f>G154*H154</f>
@@ -13385,17 +13391,17 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>MET-SIFAO</t>
+          <t>SPD-BEP</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Sifao flexivel</t>
+          <t>Barramento de equipotencializacao principal</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
@@ -13404,7 +13410,7 @@
         </is>
       </c>
       <c r="E155" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F155" s="13" t="n">
         <v>0</v>
@@ -13414,7 +13420,7 @@
         <v/>
       </c>
       <c r="H155" s="15" t="n">
-        <v>38</v>
+        <v>420</v>
       </c>
       <c r="I155" s="16">
         <f>G155*H155</f>
@@ -13461,17 +13467,17 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>SPD-HASTE</t>
+          <t>MET-SIFAO</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>Haste de aterramento 5/8 x 2.400 mm</t>
+          <t>Sifao flexivel</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
@@ -13480,7 +13486,7 @@
         </is>
       </c>
       <c r="E156" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F156" s="13" t="n">
         <v>0</v>
@@ -13490,7 +13496,7 @@
         <v/>
       </c>
       <c r="H156" s="15" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="I156" s="16">
         <f>G156*H156</f>
@@ -13537,7 +13543,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>ELE-DPS</t>
+          <t>SPD-HASTE</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
@@ -13547,7 +13553,7 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Dispositivo de protecao contra surtos</t>
+          <t>Haste de aterramento 5/8 x 2.400 mm</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
@@ -13556,7 +13562,7 @@
         </is>
       </c>
       <c r="E157" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F157" s="13" t="n">
         <v>0</v>
@@ -13566,7 +13572,7 @@
         <v/>
       </c>
       <c r="H157" s="15" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="I157" s="16">
         <f>G157*H157</f>
@@ -13611,59 +13617,135 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="22" t="n"/>
-      <c r="B158" s="22" t="n"/>
-      <c r="C158" s="23" t="inlineStr">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>ELE-DPS</t>
+        </is>
+      </c>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>eletrica</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="inlineStr">
+        <is>
+          <t>Dispositivo de protecao contra surtos</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F158" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="14">
+        <f>E158*(1+F158)</f>
+        <v/>
+      </c>
+      <c r="H158" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="I158" s="16">
+        <f>G158*H158</f>
+        <v/>
+      </c>
+      <c r="J158" s="17" t="n"/>
+      <c r="K158" s="17" t="n"/>
+      <c r="L158" s="17" t="n"/>
+      <c r="M158" s="17" t="n"/>
+      <c r="N158" s="17" t="n"/>
+      <c r="O158" s="18">
+        <f>COUNT(J158:N158)</f>
+        <v/>
+      </c>
+      <c r="P158" s="19">
+        <f>IF(O158=0,"",MIN(J158:N158))</f>
+        <v/>
+      </c>
+      <c r="Q158" s="10">
+        <f>IF(O158=0,"",INDEX($J$3:$N$3,MATCH(P158,J158:N158,0)))</f>
+        <v/>
+      </c>
+      <c r="R158" s="16">
+        <f>IF(O158=0,"",AVERAGE(J158:N158))</f>
+        <v/>
+      </c>
+      <c r="S158" s="20">
+        <f>IF(O158&lt;2,"",MAX(J158:N158)/P158)</f>
+        <v/>
+      </c>
+      <c r="T158" s="19">
+        <f>IF(O158=0,"",G158*P158)</f>
+        <v/>
+      </c>
+      <c r="U158" s="21">
+        <f>IF(OR(O158=0,I158=0),"",T158/I158-1)</f>
+        <v/>
+      </c>
+      <c r="V158" s="18">
+        <f>IF(O158=0,"PENDENTE",IF(O158&gt;=5,"COMPLETO","PARCIAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="22" t="n"/>
+      <c r="B159" s="22" t="n"/>
+      <c r="C159" s="23" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="D158" s="22" t="n"/>
-      <c r="E158" s="22" t="n"/>
-      <c r="F158" s="22" t="n"/>
-      <c r="G158" s="22" t="n"/>
-      <c r="H158" s="22" t="n"/>
-      <c r="I158" s="24">
-        <f>SUM(I4:I157)</f>
-        <v/>
-      </c>
-      <c r="J158" s="22" t="n"/>
-      <c r="K158" s="22" t="n"/>
-      <c r="L158" s="22" t="n"/>
-      <c r="M158" s="22" t="n"/>
-      <c r="N158" s="22" t="n"/>
-      <c r="O158" s="22" t="n"/>
-      <c r="P158" s="22" t="n"/>
-      <c r="Q158" s="22" t="n"/>
-      <c r="R158" s="22" t="n"/>
-      <c r="S158" s="22" t="n"/>
-      <c r="T158" s="24">
-        <f>SUM(T4:T157)</f>
-        <v/>
-      </c>
-      <c r="U158" s="25">
-        <f>IF(T158=0,"",T158/I158-1)</f>
-        <v/>
-      </c>
-      <c r="V158" s="22" t="n"/>
-    </row>
-    <row r="160">
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Itens: 154 · linhas cotáveis com especificação completa: 133 · com lacuna a esclarecer com o fornecedor: 91</t>
-        </is>
-      </c>
+      <c r="D159" s="22" t="n"/>
+      <c r="E159" s="22" t="n"/>
+      <c r="F159" s="22" t="n"/>
+      <c r="G159" s="22" t="n"/>
+      <c r="H159" s="22" t="n"/>
+      <c r="I159" s="24">
+        <f>SUM(I4:I158)</f>
+        <v/>
+      </c>
+      <c r="J159" s="22" t="n"/>
+      <c r="K159" s="22" t="n"/>
+      <c r="L159" s="22" t="n"/>
+      <c r="M159" s="22" t="n"/>
+      <c r="N159" s="22" t="n"/>
+      <c r="O159" s="22" t="n"/>
+      <c r="P159" s="22" t="n"/>
+      <c r="Q159" s="22" t="n"/>
+      <c r="R159" s="22" t="n"/>
+      <c r="S159" s="22" t="n"/>
+      <c r="T159" s="24">
+        <f>SUM(T4:T158)</f>
+        <v/>
+      </c>
+      <c r="U159" s="25">
+        <f>IF(T159=0,"",T159/I159-1)</f>
+        <v/>
+      </c>
+      <c r="V159" s="22" t="n"/>
     </row>
     <row r="161">
       <c r="C161" s="2" t="inlineStr">
         <is>
+          <t>Itens: 155 · linhas cotáveis com especificação completa: 134 · com lacuna a esclarecer com o fornecedor: 92</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
           <t>Passe o mouse sobre a DESCRIÇÃO para ver a especificação completa, as normas e a lacuna de cada item.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:V157"/>
-  <conditionalFormatting sqref="V4:V157">
+  <autoFilter ref="A3:V158"/>
+  <conditionalFormatting sqref="V4:V158">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PENDENTE"</formula>
     </cfRule>
@@ -13674,7 +13756,7 @@
       <formula>"COMPLETO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U157">
+  <conditionalFormatting sqref="U4:U158">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0.15</formula>
     </cfRule>
@@ -13682,7 +13764,7 @@
       <formula>-0.15</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S157">
+  <conditionalFormatting sqref="S4:S158">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>1.5</formula>
     </cfRule>
@@ -13783,7 +13865,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A5,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A5,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D5" s="21">
@@ -13795,7 +13877,7 @@
         <v/>
       </c>
       <c r="F5" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A5,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A5,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G5" s="21">
@@ -13803,7 +13885,7 @@
         <v/>
       </c>
       <c r="H5" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A5,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A5,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I5" s="21">
@@ -13821,7 +13903,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A6,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A6,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D6" s="21">
@@ -13833,7 +13915,7 @@
         <v/>
       </c>
       <c r="F6" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A6,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A6,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G6" s="21">
@@ -13841,7 +13923,7 @@
         <v/>
       </c>
       <c r="H6" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A6,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A6,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I6" s="21">
@@ -13852,14 +13934,14 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C7" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A7,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A7,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D7" s="21">
@@ -13871,7 +13953,7 @@
         <v/>
       </c>
       <c r="F7" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A7,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A7,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G7" s="21">
@@ -13879,7 +13961,7 @@
         <v/>
       </c>
       <c r="H7" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A7,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A7,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I7" s="21">
@@ -13890,14 +13972,14 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C8" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A8,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A8,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D8" s="21">
@@ -13909,7 +13991,7 @@
         <v/>
       </c>
       <c r="F8" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A8,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A8,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G8" s="21">
@@ -13917,7 +13999,7 @@
         <v/>
       </c>
       <c r="H8" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A8,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A8,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I8" s="21">
@@ -13928,14 +14010,14 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A9,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A9,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D9" s="21">
@@ -13947,7 +14029,7 @@
         <v/>
       </c>
       <c r="F9" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A9,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A9,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G9" s="21">
@@ -13955,7 +14037,7 @@
         <v/>
       </c>
       <c r="H9" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A9,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A9,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I9" s="21">
@@ -13966,14 +14048,14 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B10" s="18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C10" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A10,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A10,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D10" s="21">
@@ -13985,7 +14067,7 @@
         <v/>
       </c>
       <c r="F10" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A10,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A10,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G10" s="21">
@@ -13993,7 +14075,7 @@
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A10,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A10,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I10" s="21">
@@ -14004,14 +14086,14 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B11" s="18" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C11" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A11,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A11,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D11" s="21">
@@ -14023,7 +14105,7 @@
         <v/>
       </c>
       <c r="F11" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A11,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A11,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G11" s="21">
@@ -14031,7 +14113,7 @@
         <v/>
       </c>
       <c r="H11" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A11,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A11,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I11" s="21">
@@ -14042,14 +14124,14 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>estrutura</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B12" s="18" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C12" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A12,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A12,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D12" s="21">
@@ -14061,7 +14143,7 @@
         <v/>
       </c>
       <c r="F12" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A12,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A12,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G12" s="21">
@@ -14069,7 +14151,7 @@
         <v/>
       </c>
       <c r="H12" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A12,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A12,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I12" s="21">
@@ -14080,14 +14162,14 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>estrutura</t>
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C13" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A13,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A13,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D13" s="21">
@@ -14099,7 +14181,7 @@
         <v/>
       </c>
       <c r="F13" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A13,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A13,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G13" s="21">
@@ -14107,7 +14189,7 @@
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A13,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A13,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I13" s="21">
@@ -14125,7 +14207,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A14,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A14,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D14" s="21">
@@ -14137,7 +14219,7 @@
         <v/>
       </c>
       <c r="F14" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A14,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A14,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G14" s="21">
@@ -14145,7 +14227,7 @@
         <v/>
       </c>
       <c r="H14" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A14,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A14,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I14" s="21">
@@ -14163,7 +14245,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A15,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A15,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D15" s="21">
@@ -14175,7 +14257,7 @@
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A15,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A15,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G15" s="21">
@@ -14183,7 +14265,7 @@
         <v/>
       </c>
       <c r="H15" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A15,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A15,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I15" s="21">
@@ -14201,7 +14283,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A16,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A16,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D16" s="21">
@@ -14213,7 +14295,7 @@
         <v/>
       </c>
       <c r="F16" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A16,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A16,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G16" s="21">
@@ -14221,7 +14303,7 @@
         <v/>
       </c>
       <c r="H16" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A16,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A16,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I16" s="21">
@@ -14239,7 +14321,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A17,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A17,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D17" s="21">
@@ -14251,7 +14333,7 @@
         <v/>
       </c>
       <c r="F17" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A17,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A17,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G17" s="21">
@@ -14259,7 +14341,7 @@
         <v/>
       </c>
       <c r="H17" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A17,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A17,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I17" s="21">
@@ -14277,7 +14359,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A18,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A18,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D18" s="21">
@@ -14289,7 +14371,7 @@
         <v/>
       </c>
       <c r="F18" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A18,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A18,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G18" s="21">
@@ -14297,7 +14379,7 @@
         <v/>
       </c>
       <c r="H18" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A18,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A18,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I18" s="21">
@@ -14315,7 +14397,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A19,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A19,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D19" s="21">
@@ -14327,7 +14409,7 @@
         <v/>
       </c>
       <c r="F19" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A19,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A19,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G19" s="21">
@@ -14335,7 +14417,7 @@
         <v/>
       </c>
       <c r="H19" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A19,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A19,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I19" s="21">
@@ -14353,7 +14435,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A20,COTAÇÃO!$I$4:$I$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A20,COTAÇÃO!$I$4:$I$158)</f>
         <v/>
       </c>
       <c r="D20" s="21">
@@ -14365,7 +14447,7 @@
         <v/>
       </c>
       <c r="F20" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$157,$A20,COTAÇÃO!$T$4:$T$157)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$158,$A20,COTAÇÃO!$T$4:$T$158)</f>
         <v/>
       </c>
       <c r="G20" s="21">
@@ -14373,7 +14455,7 @@
         <v/>
       </c>
       <c r="H20" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$157,$A20,COTAÇÃO!$O$4:$O$157,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$158,$A20,COTAÇÃO!$O$4:$O$158,"&gt;0")</f>
         <v/>
       </c>
       <c r="I20" s="21">
@@ -14546,7 +14628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I173"/>
+  <dimension ref="A1:I174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18237,17 +18319,17 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>REV-PISO</t>
+          <t>MAR-ARM</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Piso interno (porcelanato retificado)</t>
+          <t>Armario de MDF sob medida (frente)</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -18256,21 +18338,17 @@
         </is>
       </c>
       <c r="E93" s="14" t="n">
-        <v>355.6</v>
+        <v>48.64</v>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
-        </is>
-      </c>
-      <c r="G93" s="11" t="inlineStr">
-        <is>
-          <t>NBR 13818, NBR 15463</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="inlineStr"/>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I93" s="18" t="inlineStr">
@@ -18282,40 +18360,40 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>FV-MODULO</t>
+          <t>REV-PISO</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>Modulo fotovoltaico 550 Wp</t>
+          <t>Piso interno (porcelanato retificado)</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
-        <v>29</v>
+        <v>355.6</v>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I94" s="18" t="inlineStr">
@@ -18327,36 +18405,40 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>MAR-GAB</t>
+          <t>FV-MODULO</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Gabinete sob bancada, sob medida</t>
+          <t>Modulo fotovoltaico 550 Wp</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E95" s="14" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G95" s="11" t="inlineStr"/>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+        </is>
+      </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
         </is>
       </c>
       <c r="I95" s="18" t="inlineStr">
@@ -18409,40 +18491,36 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>REV-PAREDE</t>
+          <t>MAR-GAB</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Revestimento ceramico de parede em area molhada</t>
+          <t>Gabinete sob bancada, sob medida</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E97" s="14" t="n">
-        <v>155.5</v>
+        <v>11.4</v>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
-        </is>
-      </c>
-      <c r="G97" s="11" t="inlineStr">
-        <is>
-          <t>NBR 13818, NBR 15463</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G97" s="11" t="inlineStr"/>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I97" s="18" t="inlineStr">
@@ -18454,40 +18532,40 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT18</t>
+          <t>REV-PAREDE</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 18.000 BTU/h</t>
+          <t>Revestimento ceramico de parede em area molhada</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
-        <v>4</v>
+        <v>155.5</v>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
-          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I98" s="18" t="inlineStr">
@@ -18499,40 +18577,40 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>LOU-BOX</t>
+          <t>EQP-SPLIT18</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Box de vidro temperado 8 mm, 1.900 mm de altura</t>
+          <t>Split inverter 18.000 BTU/h</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E99" s="14" t="n">
-        <v>16.1</v>
+        <v>4</v>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I99" s="18" t="inlineStr">
@@ -18544,17 +18622,17 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>MAR-ARM</t>
+          <t>LOU-BOX</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>Armario de MDF sob medida</t>
+          <t>Box de vidro temperado 8 mm, 1.900 mm de altura</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -18563,17 +18641,21 @@
         </is>
       </c>
       <c r="E100" s="14" t="n">
-        <v>9.42</v>
+        <v>16.1</v>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G100" s="11" t="inlineStr"/>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I100" s="18" t="inlineStr">
@@ -18630,7 +18712,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>MAR-TAMPO</t>
+          <t>MAR-PRAT</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -18640,16 +18722,16 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>Tampo de bancada (quartzo/granito)</t>
+          <t>Prateleira aberta, por metro de prateleira</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
-        <v>7.17</v>
+        <v>35.19</v>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
@@ -18716,17 +18798,17 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>FV-ESTRUTURA</t>
+          <t>MAR-TAMPO</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>Estrutura de fixacao em aluminio sobre terca</t>
+          <t>Tampo de bancada (quartzo/granito)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -18735,21 +18817,17 @@
         </is>
       </c>
       <c r="E104" s="14" t="n">
-        <v>86.2</v>
+        <v>6.84</v>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
-        </is>
-      </c>
-      <c r="G104" s="11" t="inlineStr">
-        <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="inlineStr"/>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I104" s="18" t="inlineStr">
@@ -18761,38 +18839,42 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>PIN-TINTA</t>
+          <t>FV-ESTRUTURA</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
+          <t>Estrutura de fixacao em aluminio sobre terca</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E105" s="14" t="n">
-        <v>179.6</v>
+        <v>86.2</v>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>NBR 11702, NBR 13245</t>
-        </is>
-      </c>
-      <c r="H105" s="11" t="inlineStr"/>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+        </is>
+      </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18802,42 +18884,38 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>REV-RODAPE</t>
+          <t>PIN-TINTA</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Rodape (poliestireno 100 mm, pintado)</t>
+          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
-        <v>220.9</v>
+        <v>179.6</v>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
+          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
-          <t>NBR 13818, NBR 15463</t>
-        </is>
-      </c>
-      <c r="H106" s="11" t="inlineStr">
-        <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
-        </is>
-      </c>
+          <t>NBR 11702, NBR 13245</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr"/>
       <c r="I106" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18847,40 +18925,40 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>FV-INVERSOR</t>
+          <t>REV-RODAPE</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Inversor string 12 kW, trifasico 220 V</t>
+          <t>Rodape (poliestireno 100 mm, pintado)</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E107" s="14" t="n">
-        <v>12</v>
+        <v>220.9</v>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I107" s="18" t="inlineStr">
@@ -18892,38 +18970,42 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>PIN-FORRO</t>
+          <t>FV-INVERSOR</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>Pintura de forro (latex PVA fosco)</t>
+          <t>Inversor string 12 kW, trifasico 220 V</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>kW</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
-        <v>257</v>
+        <v>12</v>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>NBR 11702, NBR 13245</t>
-        </is>
-      </c>
-      <c r="H108" s="11" t="inlineStr"/>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+        </is>
+      </c>
       <c r="I108" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -18933,40 +19015,36 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT9</t>
+          <t>MAR-CABEC</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 9.000 BTU/h</t>
+          <t>Cabeceira estofada</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E109" s="14" t="n">
-        <v>3</v>
+        <v>10.96</v>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
-        </is>
-      </c>
-      <c r="G109" s="11" t="inlineStr">
-        <is>
-          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr"/>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I109" s="18" t="inlineStr">
@@ -18978,42 +19056,38 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>SPD-CAPTOR</t>
+          <t>PIN-FORRO</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
+          <t>Pintura de forro (latex PVA fosco)</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
-        <v>160.8</v>
+        <v>257</v>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
-        </is>
-      </c>
-      <c r="H110" s="11" t="inlineStr">
-        <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
-        </is>
-      </c>
+          <t>NBR 11702, NBR 13245</t>
+        </is>
+      </c>
+      <c r="H110" s="11" t="inlineStr"/>
       <c r="I110" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -19023,17 +19097,17 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>LUM-DOWNLIGHT18</t>
+          <t>EQP-SPLIT9</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Downlight LED embutido 18 W</t>
+          <t>Split inverter 9.000 BTU/h</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -19042,21 +19116,21 @@
         </is>
       </c>
       <c r="E111" s="14" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I111" s="18" t="inlineStr">
@@ -19068,40 +19142,40 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>EQP-SPLIT30</t>
+          <t>SPD-CAPTOR</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>Split inverter 30.000 BTU/h</t>
+          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
-        <v>1</v>
+        <v>160.8</v>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
         </is>
       </c>
       <c r="I112" s="18" t="inlineStr">
@@ -19113,7 +19187,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>LUM-DOWNLIGHT24</t>
+          <t>LUM-DOWNLIGHT18</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -19123,7 +19197,7 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Downlight LED embutido 24 W</t>
+          <t>Downlight LED embutido 18 W</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -19132,7 +19206,7 @@
         </is>
       </c>
       <c r="E113" s="14" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
@@ -19158,36 +19232,40 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>MAR-CORT</t>
+          <t>EQP-SPLIT30</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>Cortina blackout com trilho, dormitorios</t>
+          <t>Split inverter 30.000 BTU/h</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
-        <v>13.2</v>
+        <v>1</v>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G114" s="11" t="inlineStr"/>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado; inverter, ciclo frio, R-32 ou R-410A, classe A</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>NBR 16401, Portaria INMETRO de eficiencia</t>
+        </is>
+      </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I114" s="18" t="inlineStr">
@@ -19199,40 +19277,40 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>REV-REJ</t>
+          <t>LUM-DOWNLIGHT24</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Rejunte epoxi/acrilico</t>
+          <t>Downlight LED embutido 24 W</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E115" s="14" t="n">
-        <v>511.1</v>
+        <v>31</v>
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>NBR 13818, NBR 15463</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I115" s="18" t="inlineStr">
@@ -19244,40 +19322,36 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>LOU-VASO</t>
+          <t>MAR-CORT</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>Bacia sanitaria com caixa acoplada</t>
+          <t>Cortina blackout com trilho, dormitorios</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
-        <v>5</v>
+        <v>13.2</v>
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
-        </is>
-      </c>
-      <c r="G116" s="11" t="inlineStr">
-        <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr"/>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I116" s="18" t="inlineStr">
@@ -19289,40 +19363,40 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>LUM-LINEAR</t>
+          <t>REV-REJ</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Perfil linear LED 18 W/m com difusor (tarefa)</t>
+          <t>Rejunte epoxi/acrilico</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E117" s="14" t="n">
-        <v>15.6</v>
+        <v>511.1</v>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I117" s="18" t="inlineStr">
@@ -19334,7 +19408,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN</t>
+          <t>LOU-VASO</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -19344,7 +19418,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>Torneira de bancada (lavatorio e cuba)</t>
+          <t>Bacia sanitaria com caixa acoplada</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -19353,7 +19427,7 @@
         </is>
       </c>
       <c r="E118" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
@@ -19379,7 +19453,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>SPD-ANEL</t>
+          <t>LUM-LINEAR</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -19389,7 +19463,7 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Anel de aterramento: cobre nu 50 mm2 no perimetro do radier</t>
+          <t>Perfil linear LED 18 W/m com difusor (tarefa)</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -19398,21 +19472,21 @@
         </is>
       </c>
       <c r="E119" s="14" t="n">
-        <v>63.6</v>
+        <v>15.6</v>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I119" s="18" t="inlineStr">
@@ -19424,40 +19498,40 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>REV-FORRO-ACUST</t>
+          <t>MET-TORN</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>Forro absorvente perfurado (alfa 0,70), acabado de fabrica</t>
+          <t>Torneira de bancada (lavatorio e cuba)</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
-        <v>30.2</v>
+        <v>9</v>
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr">
         <is>
-          <t>NBR 13818, NBR 15463</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I120" s="18" t="inlineStr">
@@ -19469,36 +19543,40 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>EQP-PISC</t>
+          <t>SPD-ANEL</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
+          <t>Anel de aterramento: cobre nu 50 mm2 no perimetro do radier</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>cj</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E121" s="14" t="n">
-        <v>1</v>
+        <v>63.6</v>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
-        </is>
-      </c>
-      <c r="G121" s="11" t="inlineStr"/>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+        </is>
+      </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
         </is>
       </c>
       <c r="I121" s="18" t="inlineStr">
@@ -19510,40 +19588,40 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>LOU-LAV</t>
+          <t>REV-FORRO-ACUST</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>Lavatorio / cuba de banheiro</t>
+          <t>Forro absorvente perfurado (alfa 0,70), acabado de fabrica</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
-        <v>6</v>
+        <v>30.2</v>
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I122" s="18" t="inlineStr">
@@ -19555,36 +19633,36 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>EQP-PORTAO</t>
+          <t>MAR-PAINEL</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Automatizador de portao de correr</t>
+          <t>Painel ripado de TV</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E123" s="14" t="n">
-        <v>1</v>
+        <v>6.71</v>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr"/>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I123" s="18" t="inlineStr">
@@ -19596,40 +19674,36 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>MET-ACESS</t>
+          <t>EQP-PISC</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
+          <t>Conjunto da piscina: bomba, filtro e tratamento</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>cj</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
-        </is>
-      </c>
-      <c r="G124" s="11" t="inlineStr">
-        <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
+        </is>
+      </c>
+      <c r="G124" s="11" t="inlineStr"/>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I124" s="18" t="inlineStr">
@@ -19641,17 +19715,17 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUG</t>
+          <t>LOU-LAV</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Tomada 2P+T 10 A com placa</t>
+          <t>Lavatorio / cuba de banheiro</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -19660,19 +19734,23 @@
         </is>
       </c>
       <c r="E125" s="14" t="n">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I125" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -19682,36 +19760,36 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>MAR-PRAT</t>
+          <t>EQP-PORTAO</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>Prateleira e nicho</t>
+          <t>Automatizador de portao de correr</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr"/>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I126" s="18" t="inlineStr">
@@ -19723,38 +19801,42 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>PIN-SELADOR</t>
+          <t>MET-ACESS</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Selador acrilico</t>
+          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E127" s="14" t="n">
-        <v>74.8</v>
+        <v>28</v>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>NBR 11702, NBR 13245</t>
-        </is>
-      </c>
-      <c r="H127" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I127" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -19764,17 +19846,17 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>LOU-CUBA</t>
+          <t>ELE-TUG</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
+          <t>Tomada 2P+T 10 A com placa</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -19783,23 +19865,19 @@
         </is>
       </c>
       <c r="E128" s="14" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
-      <c r="H128" s="11" t="inlineStr">
-        <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr"/>
       <c r="I128" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -19809,38 +19887,38 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>MAR-CAB</t>
+          <t>PIN-SELADOR</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Cabideiro e gaveteiro de closet</t>
+          <t>Selador acrilico</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E129" s="14" t="n">
-        <v>6</v>
+        <v>74.8</v>
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G129" s="11" t="inlineStr"/>
-      <c r="H129" s="11" t="inlineStr">
-        <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
-        </is>
-      </c>
+          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>NBR 11702, NBR 13245</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr"/>
       <c r="I129" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -19850,17 +19928,17 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>EQP-EXAUST</t>
+          <t>LOU-CUBA</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Exaustor / coifa</t>
+          <t>Cuba de cozinha / gourmet / lavanderia em inox</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -19869,17 +19947,21 @@
         </is>
       </c>
       <c r="E130" s="14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
-        </is>
-      </c>
-      <c r="G130" s="11" t="inlineStr"/>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I130" s="18" t="inlineStr">
@@ -19891,17 +19973,17 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>FV-HOMOLOG</t>
+          <t>EQP-EXAUST</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Projeto e homologacao na concessionaria (REN 1.000)</t>
+          <t>Exaustor / coifa</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
@@ -19910,21 +19992,17 @@
         </is>
       </c>
       <c r="E131" s="14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
-        </is>
-      </c>
-      <c r="G131" s="11" t="inlineStr">
-        <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
-        </is>
-      </c>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr"/>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I131" s="18" t="inlineStr">
@@ -19936,7 +20014,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>LUM-SOBREPOR24</t>
+          <t>FV-HOMOLOG</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -19946,7 +20024,7 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Plafon LED de sobrepor 24 W</t>
+          <t>Projeto e homologacao na concessionaria (REN 1.000)</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -19955,21 +20033,21 @@
         </is>
       </c>
       <c r="E132" s="14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
         </is>
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
         </is>
       </c>
       <c r="I132" s="18" t="inlineStr">
@@ -19981,17 +20059,17 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>REV-NICHO</t>
+          <t>LUM-SOBREPOR24</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Nicho de box 300 x 900 mm entre montantes (RU + ceramica)</t>
+          <t>Plafon LED de sobrepor 24 W</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
@@ -20000,21 +20078,21 @@
         </is>
       </c>
       <c r="E133" s="14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>NBR 13818, NBR 15463</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I133" s="18" t="inlineStr">
@@ -20026,7 +20104,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>MET-REG</t>
+          <t>REV-NICHO</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -20036,7 +20114,7 @@
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>Registro de gaveta e de pressao</t>
+          <t>Nicho de box 300 x 900 mm entre montantes (RU + ceramica)</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
@@ -20045,21 +20123,21 @@
         </is>
       </c>
       <c r="E134" s="14" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>revestimento ceramico conforme quadro de acabamentos por ambiente; area ja com 10 % de perda de corte e quebra</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 13818, NBR 15463</t>
         </is>
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>linha, formato e PEI: o modelo define o TIPO por ambiente, a linha e escolha de acabamento</t>
         </is>
       </c>
       <c r="I134" s="18" t="inlineStr">
@@ -20071,7 +20149,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>MET-CHUV</t>
+          <t>MET-REG</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -20081,7 +20159,7 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Chuveiro eletrico 220 V</t>
+          <t>Registro de gaveta e de pressao</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
@@ -20090,7 +20168,7 @@
         </is>
       </c>
       <c r="E135" s="14" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
@@ -20116,17 +20194,17 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>ELE-DR</t>
+          <t>MET-CHUV</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor diferencial residual 30 mA</t>
+          <t>Chuveiro eletrico 220 V</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -20135,19 +20213,23 @@
         </is>
       </c>
       <c r="E136" s="14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H136" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I136" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -20157,17 +20239,17 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>MET-DUCHA</t>
+          <t>ELE-DR</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Ducha higienica com registro</t>
+          <t>Disjuntor diferencial residual 30 mA</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -20176,23 +20258,19 @@
         </is>
       </c>
       <c r="E137" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
-      <c r="H137" s="11" t="inlineStr">
-        <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr"/>
       <c r="I137" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -20202,17 +20280,17 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>SPD-DESCIDA</t>
+          <t>MET-DUCHA</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>Descida natural pela estrutura LSF: conector de teste e ligacao</t>
+          <t>Ducha higienica com registro</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -20221,21 +20299,21 @@
         </is>
       </c>
       <c r="E138" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H138" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I138" s="18" t="inlineStr">
@@ -20247,7 +20325,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>LUM-ARANDELA</t>
+          <t>SPD-DESCIDA</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -20257,7 +20335,7 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Arandela LED IP44 de espelho, 8 W</t>
+          <t>Descida natural pela estrutura LSF: conector de teste e ligacao</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
@@ -20266,21 +20344,21 @@
         </is>
       </c>
       <c r="E139" s="14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
         </is>
       </c>
       <c r="I139" s="18" t="inlineStr">
@@ -20292,7 +20370,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>SPD-DPS1</t>
+          <t>LUM-ARANDELA</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -20302,7 +20380,7 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>DPS classe I, 12,5 kA, 3F+N, na entrada</t>
+          <t>Arandela LED IP44 de espelho, 8 W</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -20311,21 +20389,21 @@
         </is>
       </c>
       <c r="E140" s="14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F140" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H140" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I140" s="18" t="inlineStr">
@@ -20337,17 +20415,17 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>MET-DUCHA-TETO</t>
+          <t>SPD-DPS1</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>Ducha de teto 250 mm com desviador (box &gt;= 1.400)</t>
+          <t>DPS classe I, 12,5 kA, 3F+N, na entrada</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -20360,17 +20438,17 @@
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
         </is>
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
         </is>
       </c>
       <c r="I141" s="18" t="inlineStr">
@@ -20382,17 +20460,17 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>LUM-PENDENTE40</t>
+          <t>MET-DUCHA-TETO</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>Pendente LED de pe-direito duplo, 40 W</t>
+          <t>Ducha de teto 250 mm com desviador (box &gt;= 1.400)</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
@@ -20401,21 +20479,21 @@
         </is>
       </c>
       <c r="E142" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F142" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H142" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I142" s="18" t="inlineStr">
@@ -20427,7 +20505,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>ELE-INT</t>
+          <t>LUM-PENDENTE40</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -20437,7 +20515,7 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Interruptor simples e paralelo com placa</t>
+          <t>Pendente LED de pe-direito duplo, 40 W</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
@@ -20446,19 +20524,23 @@
         </is>
       </c>
       <c r="E143" s="14" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H143" s="11" t="inlineStr"/>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+        </is>
+      </c>
       <c r="I143" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -20468,17 +20550,17 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>LOU-ASSENTO</t>
+          <t>ELE-INT</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>Assento sanitario com amortecedor</t>
+          <t>Interruptor simples e paralelo com placa</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
@@ -20487,23 +20569,19 @@
         </is>
       </c>
       <c r="E144" s="14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F144" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
-      <c r="H144" s="11" t="inlineStr">
-        <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H144" s="11" t="inlineStr"/>
       <c r="I144" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -20513,17 +20591,17 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUE</t>
+          <t>LOU-ASSENTO</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>Tomada de uso especifico 20 A com placa</t>
+          <t>Assento sanitario com amortecedor</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
@@ -20532,19 +20610,23 @@
         </is>
       </c>
       <c r="E145" s="14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H145" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I145" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -20554,7 +20636,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>FV-STRINGBOX</t>
+          <t>ELE-TUE</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -20564,7 +20646,7 @@
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>String box CC com DPS e seccionadora</t>
+          <t>Tomada de uso especifico 20 A com placa</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
@@ -20573,23 +20655,19 @@
         </is>
       </c>
       <c r="E146" s="14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
-        </is>
-      </c>
-      <c r="H146" s="11" t="inlineStr">
-        <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H146" s="11" t="inlineStr"/>
       <c r="I146" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -20599,7 +20677,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>SPD-ENSAIO</t>
+          <t>FV-STRINGBOX</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
@@ -20609,7 +20687,7 @@
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>Ensaio de continuidade e resistencia de aterramento</t>
+          <t>String box CC com DPS e seccionadora</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
@@ -20622,17 +20700,17 @@
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
         </is>
       </c>
       <c r="I147" s="18" t="inlineStr">
@@ -20644,7 +20722,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>FV-CABO</t>
+          <t>SPD-ENSAIO</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
@@ -20654,30 +20732,30 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
+          <t>Ensaio de continuidade e resistencia de aterramento</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E148" s="14" t="n">
-        <v>46.3</v>
+        <v>1</v>
       </c>
       <c r="F148" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
         </is>
       </c>
       <c r="H148" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
         </is>
       </c>
       <c r="I148" s="18" t="inlineStr">
@@ -20689,40 +20767,40 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>LOU-TANQUE</t>
+          <t>FV-CABO</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>Tanque de lavanderia</t>
+          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E149" s="14" t="n">
-        <v>2</v>
+        <v>46.3</v>
       </c>
       <c r="F149" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
         </is>
       </c>
       <c r="I149" s="18" t="inlineStr">
@@ -20734,7 +20812,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN-T</t>
+          <t>LOU-TANQUE</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
@@ -20744,7 +20822,7 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>Torneira de tanque e de jardim</t>
+          <t>Tanque de lavanderia</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
@@ -20753,7 +20831,7 @@
         </is>
       </c>
       <c r="E150" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F150" s="11" t="inlineStr">
         <is>
@@ -20779,7 +20857,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>MET-ENGATE</t>
+          <t>MET-TORN-T</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
@@ -20789,7 +20867,7 @@
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>Engate flexivel</t>
+          <t>Torneira de tanque e de jardim</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
@@ -20798,7 +20876,7 @@
         </is>
       </c>
       <c r="E151" s="14" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
@@ -20824,17 +20902,17 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>LUM-BALIZADOR</t>
+          <t>MET-ENGATE</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>Balizador LED de escada, 3 W</t>
+          <t>Engate flexivel</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
@@ -20843,21 +20921,21 @@
         </is>
       </c>
       <c r="E152" s="14" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F152" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H152" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I152" s="18" t="inlineStr">
@@ -20869,17 +20947,17 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>MET-VALV</t>
+          <t>LUM-BALIZADOR</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Valvula de escoamento e de lavatorio</t>
+          <t>Balizador LED de escada, 3 W</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
@@ -20888,21 +20966,21 @@
         </is>
       </c>
       <c r="E153" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I153" s="18" t="inlineStr">
@@ -20914,17 +20992,17 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>SPD-BEP</t>
+          <t>MET-VALV</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>Barramento de equipotencializacao principal</t>
+          <t>Valvula de escoamento e de lavatorio</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
@@ -20933,21 +21011,21 @@
         </is>
       </c>
       <c r="E154" s="14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F154" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I154" s="18" t="inlineStr">
@@ -20959,17 +21037,17 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>MET-SIFAO</t>
+          <t>SPD-BEP</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Sifao flexivel</t>
+          <t>Barramento de equipotencializacao principal</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
@@ -20978,21 +21056,21 @@
         </is>
       </c>
       <c r="E155" s="14" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F155" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
         </is>
       </c>
       <c r="I155" s="18" t="inlineStr">
@@ -21004,17 +21082,17 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>SPD-HASTE</t>
+          <t>MET-SIFAO</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>Haste de aterramento 5/8 x 2.400 mm</t>
+          <t>Sifao flexivel</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
@@ -21023,21 +21101,21 @@
         </is>
       </c>
       <c r="E156" s="14" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F156" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H156" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I156" s="18" t="inlineStr">
@@ -21049,129 +21127,144 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
+          <t>SPD-HASTE</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>eletrica</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>Haste de aterramento 5/8 x 2.400 mm</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E157" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F157" s="11" t="inlineStr">
+        <is>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+        </is>
+      </c>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+        </is>
+      </c>
+      <c r="H157" s="11" t="inlineStr">
+        <is>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+        </is>
+      </c>
+      <c r="I157" s="18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
           <t>ELE-DPS</t>
         </is>
       </c>
-      <c r="B157" s="10" t="inlineStr">
+      <c r="B158" s="10" t="inlineStr">
         <is>
           <t>eletrica</t>
         </is>
       </c>
-      <c r="C157" s="11" t="inlineStr">
+      <c r="C158" s="11" t="inlineStr">
         <is>
           <t>Dispositivo de protecao contra surtos</t>
         </is>
       </c>
-      <c r="D157" s="10" t="inlineStr">
+      <c r="D158" s="10" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E157" s="14" t="n">
+      <c r="E158" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F157" s="11" t="inlineStr">
+      <c r="F158" s="11" t="inlineStr">
         <is>
           <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
-      <c r="G157" s="11" t="inlineStr">
+      <c r="G158" s="11" t="inlineStr">
         <is>
           <t>NBR 14136, NBR 5410</t>
         </is>
       </c>
-      <c r="H157" s="11" t="inlineStr"/>
-      <c r="I157" s="18" t="inlineStr">
+      <c r="H158" s="11" t="inlineStr"/>
+      <c r="I158" s="18" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t>ROTA ALTERNATIVA — peça cortada e furada em vez de barra</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Estes itens NÃO entram no total: são a mesma estrutura comprada pronta. Cotar os dois e comparar contra o custo de corte próprio.</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="26" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="26" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="B161" s="26" t="inlineStr">
+      <c r="B162" s="26" t="inlineStr">
         <is>
           <t>DESCRIÇÃO</t>
         </is>
       </c>
-      <c r="C161" s="26" t="inlineStr">
+      <c r="C162" s="26" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="D161" s="26" t="inlineStr">
+      <c r="D162" s="26" t="inlineStr">
         <is>
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E161" s="26" t="inlineStr">
+      <c r="E162" s="26" t="inlineStr">
         <is>
           <t>ESPECIFICAÇÃO</t>
         </is>
       </c>
-      <c r="F161" s="26" t="inlineStr">
+      <c r="F162" s="26" t="inlineStr">
         <is>
           <t>NORMAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="9" t="inlineStr">
-        <is>
-          <t>PF-Ue 90x40x12x0,95</t>
-        </is>
-      </c>
-      <c r="B162" s="11" t="inlineStr">
-        <is>
-          <t>Ue 90x40x12x0,95</t>
-        </is>
-      </c>
-      <c r="C162" s="10" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="D162" s="14" t="n">
-        <v>547</v>
-      </c>
-      <c r="E162" s="11" t="inlineStr">
-        <is>
-          <t>peca cortada e furada conforme Ue 90x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
-        </is>
-      </c>
-      <c r="F162" s="10" t="inlineStr">
-        <is>
-          <t>NBR 15253</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 250x40x15x3,00</t>
+          <t>PF-Ue 90x40x12x0,95</t>
         </is>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Ue 250x40x15x3,00</t>
+          <t>Ue 90x40x12x0,95</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
@@ -21180,11 +21273,11 @@
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>22</v>
+        <v>547</v>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 250x40x15x3,00; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 90x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
@@ -21196,12 +21289,12 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>PF-U 92x38x0,95</t>
+          <t>PF-Ue 250x40x15x3,00</t>
         </is>
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>U 92x38x0,95</t>
+          <t>Ue 250x40x15x3,00</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
@@ -21210,11 +21303,11 @@
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>299</v>
+        <v>22</v>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme U 92x38x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 250x40x15x3,00; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
@@ -21226,12 +21319,12 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 250x40x12x2,25</t>
+          <t>PF-U 92x38x0,95</t>
         </is>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x2,25</t>
+          <t>U 92x38x0,95</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
@@ -21240,11 +21333,11 @@
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>24</v>
+        <v>299</v>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 250x40x12x2,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme U 92x38x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
@@ -21256,12 +21349,12 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 200x40x12x1,25</t>
+          <t>PF-Ue 250x40x12x2,25</t>
         </is>
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x1,25</t>
+          <t>Ue 250x40x12x2,25</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
@@ -21270,11 +21363,11 @@
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 200x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 250x40x12x2,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F166" s="10" t="inlineStr">
@@ -21286,12 +21379,12 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 200x40x12x0,95</t>
+          <t>PF-Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x0,95</t>
+          <t>Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
@@ -21300,11 +21393,11 @@
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 200x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 200x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
@@ -21316,12 +21409,12 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 140x40x12x0,80</t>
+          <t>PF-Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x0,80</t>
+          <t>Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
@@ -21330,11 +21423,11 @@
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 140x40x12x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 200x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F168" s="10" t="inlineStr">
@@ -21346,12 +21439,12 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 90x40x12x1,25</t>
+          <t>PF-Ue 140x40x12x0,80</t>
         </is>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>Ue 90x40x12x1,25</t>
+          <t>Ue 140x40x12x0,80</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
@@ -21360,11 +21453,11 @@
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 90x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 140x40x12x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F169" s="10" t="inlineStr">
@@ -21376,12 +21469,12 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 140x40x12x1,25</t>
+          <t>PF-Ue 90x40x12x1,25</t>
         </is>
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x1,25</t>
+          <t>Ue 90x40x12x1,25</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
@@ -21390,11 +21483,11 @@
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 140x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 90x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F170" s="10" t="inlineStr">
@@ -21406,12 +21499,12 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 250x40x12x1,25</t>
+          <t>PF-Ue 140x40x12x1,25</t>
         </is>
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x1,25</t>
+          <t>Ue 140x40x12x1,25</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
@@ -21420,11 +21513,11 @@
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 250x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 140x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
@@ -21436,12 +21529,12 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>PF-Fita 38x0,80</t>
+          <t>PF-Ue 250x40x12x1,25</t>
         </is>
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>Fita 38x0,80</t>
+          <t>Ue 250x40x12x1,25</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
@@ -21450,11 +21543,11 @@
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Fita 38x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 250x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F172" s="10" t="inlineStr">
@@ -21466,36 +21559,66 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
+          <t>PF-Fita 38x0,80</t>
+        </is>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t>Fita 38x0,80</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="D173" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>peca cortada e furada conforme Fita 38x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+        </is>
+      </c>
+      <c r="F173" s="10" t="inlineStr">
+        <is>
+          <t>NBR 15253</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
           <t>PLACA</t>
         </is>
       </c>
-      <c r="B173" s="11" t="inlineStr">
+      <c r="B174" s="11" t="inlineStr">
         <is>
           <t>Placa (gesso, RU e cimenticia)</t>
         </is>
       </c>
-      <c r="C173" s="10" t="inlineStr">
+      <c r="C174" s="10" t="inlineStr">
         <is>
           <t>pc</t>
         </is>
       </c>
-      <c r="D173" s="14" t="n">
+      <c r="D174" s="14" t="n">
         <v>837</v>
       </c>
-      <c r="E173" s="11" t="inlineStr">
+      <c r="E174" s="11" t="inlineStr">
         <is>
           <t>placa inteira, por formato — rota alternativa a compra por m2; formatos: 1200 x 2400, 1200 x 25000, 600 x 1250</t>
         </is>
       </c>
-      <c r="F173" s="10" t="inlineStr">
+      <c r="F174" s="10" t="inlineStr">
         <is>
           <t>NBR 15758</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I157"/>
-  <conditionalFormatting sqref="I4:I157">
+  <autoFilter ref="A3:I158"/>
+  <conditionalFormatting sqref="I4:I158">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"com lacuna"</formula>
     </cfRule>
@@ -21942,7 +22065,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B14" s="18" t="n">
@@ -21950,17 +22073,17 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Schneider / Pial Legrand</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Marcenarias de Manaus</t>
+        </is>
+      </c>
+      <c r="D14" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>tomada, interruptor e placa</t>
+          <t>movel sob medida</t>
         </is>
       </c>
       <c r="F14" s="37" t="n"/>
@@ -21975,7 +22098,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B15" s="18" t="n">
@@ -21983,7 +22106,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Steck</t>
+          <t>Todeschini / Dell Anno</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -21993,7 +22116,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>dispositivos e quadros</t>
+          <t>movel planejado, rede</t>
         </is>
       </c>
       <c r="F15" s="37" t="n"/>
@@ -22008,7 +22131,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B16" s="18" t="n">
@@ -22016,7 +22139,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>WEG</t>
+          <t>Italinea / Favorita</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -22026,7 +22149,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>disjuntor, DR e DPS</t>
+          <t>movel planejado</t>
         </is>
       </c>
       <c r="F16" s="37" t="n"/>
@@ -22041,7 +22164,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B17" s="18" t="n">
@@ -22049,17 +22172,17 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Philips / Osram / Stella</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Marmorarias de Manaus</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED</t>
+          <t>tampo em quartzo e granito</t>
         </is>
       </c>
       <c r="F17" s="37" t="n"/>
@@ -22074,7 +22197,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B18" s="18" t="n">
@@ -22082,17 +22205,17 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Distribuidores eletricos de Manaus</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Duratex / Guararapes</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>material eletrico</t>
+          <t>MDF, fabricante de chapa</t>
         </is>
       </c>
       <c r="F18" s="37" t="n"/>
@@ -22107,7 +22230,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="B19" s="18" t="n">
@@ -22115,17 +22238,17 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Metalurgica Aluminova</t>
-        </is>
-      </c>
-      <c r="D19" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Schneider / Pial Legrand</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>ripado e brise em aluminio</t>
+          <t>tomada, interruptor e placa</t>
         </is>
       </c>
       <c r="F19" s="37" t="n"/>
@@ -22140,7 +22263,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="B20" s="18" t="n">
@@ -22148,7 +22271,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Alubrasil / Hydro</t>
+          <t>Steck</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -22158,7 +22281,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>perfil de aluminio extrudado</t>
+          <t>dispositivos e quadros</t>
         </is>
       </c>
       <c r="F20" s="37" t="n"/>
@@ -22173,7 +22296,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="B21" s="18" t="n">
@@ -22181,7 +22304,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Fabricantes de brise movel</t>
+          <t>WEG</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -22191,7 +22314,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>mecanismo e guia</t>
+          <t>disjuntor, DR e DPS</t>
         </is>
       </c>
       <c r="F21" s="37" t="n"/>
@@ -22206,7 +22329,7 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="B22" s="18" t="n">
@@ -22214,17 +22337,17 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Serralherias de Manaus</t>
-        </is>
-      </c>
-      <c r="D22" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Philips / Osram / Stella</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>montagem e fixacao</t>
+          <t>luminaria LED</t>
         </is>
       </c>
       <c r="F22" s="37" t="n"/>
@@ -22239,7 +22362,7 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="B23" s="18" t="n">
@@ -22247,7 +22370,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Esquadrias Alufynestra</t>
+          <t>Distribuidores eletricos de Manaus</t>
         </is>
       </c>
       <c r="D23" s="36" t="inlineStr">
@@ -22257,7 +22380,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>perfis e acabamento</t>
+          <t>material eletrico</t>
         </is>
       </c>
       <c r="F23" s="37" t="n"/>
@@ -22272,7 +22395,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B24" s="18" t="n">
@@ -22280,7 +22403,7 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Du Norte Comercio</t>
+          <t>Metalurgica Aluminova</t>
         </is>
       </c>
       <c r="D24" s="36" t="inlineStr">
@@ -22290,7 +22413,7 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>cimento, areia e brita</t>
+          <t>ripado e brise em aluminio</t>
         </is>
       </c>
       <c r="F24" s="37" t="n"/>
@@ -22305,7 +22428,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B25" s="18" t="n">
@@ -22313,17 +22436,17 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Loja do Rei Comercio de Material de Construcao</t>
-        </is>
-      </c>
-      <c r="D25" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Alubrasil / Hydro</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>maior faturamento do setor na praca</t>
+          <t>perfil de aluminio extrudado</t>
         </is>
       </c>
       <c r="F25" s="37" t="n"/>
@@ -22338,7 +22461,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B26" s="18" t="n">
@@ -22346,17 +22469,17 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Bacuri Madeiras e Material de Construcao</t>
-        </is>
-      </c>
-      <c r="D26" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Fabricantes de brise movel</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>insumos</t>
+          <t>mecanismo e guia</t>
         </is>
       </c>
       <c r="F26" s="37" t="n"/>
@@ -22371,7 +22494,7 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B27" s="18" t="n">
@@ -22379,7 +22502,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Concreteiras locais (usinas de Manaus)</t>
+          <t>Serralherias de Manaus</t>
         </is>
       </c>
       <c r="D27" s="36" t="inlineStr">
@@ -22389,7 +22512,7 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>concreto usinado fck 30 com bombeamento</t>
+          <t>montagem e fixacao</t>
         </is>
       </c>
       <c r="F27" s="37" t="n"/>
@@ -22404,7 +22527,7 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B28" s="18" t="n">
@@ -22412,17 +22535,17 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Gerdau / ArcelorMittal</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Esquadrias Alufynestra</t>
+        </is>
+      </c>
+      <c r="D28" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>aco CA-50 e tela soldada</t>
+          <t>perfis e acabamento</t>
         </is>
       </c>
       <c r="F28" s="37" t="n"/>
@@ -22437,7 +22560,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B29" s="18" t="n">
@@ -22455,7 +22578,7 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>porcelanato, argamassa e rejunte</t>
+          <t>cimento, areia e brita</t>
         </is>
       </c>
       <c r="F29" s="37" t="n"/>
@@ -22470,7 +22593,7 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B30" s="18" t="n">
@@ -22478,7 +22601,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Loja do Rei</t>
+          <t>Loja do Rei Comercio de Material de Construcao</t>
         </is>
       </c>
       <c r="D30" s="36" t="inlineStr">
@@ -22488,7 +22611,7 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>revestimento e assentamento</t>
+          <t>maior faturamento do setor na praca</t>
         </is>
       </c>
       <c r="F30" s="37" t="n"/>
@@ -22503,7 +22626,7 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B31" s="18" t="n">
@@ -22511,7 +22634,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Bacuri Materiais</t>
+          <t>Bacuri Madeiras e Material de Construcao</t>
         </is>
       </c>
       <c r="D31" s="36" t="inlineStr">
@@ -22521,7 +22644,7 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>insumos</t>
         </is>
       </c>
       <c r="F31" s="37" t="n"/>
@@ -22536,7 +22659,7 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B32" s="18" t="n">
@@ -22544,17 +22667,17 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Portobello / Eliane / Portinari</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Concreteiras locais (usinas de Manaus)</t>
+        </is>
+      </c>
+      <c r="D32" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>porcelanato, fabricante</t>
+          <t>concreto usinado fck 30 com bombeamento</t>
         </is>
       </c>
       <c r="F32" s="37" t="n"/>
@@ -22569,7 +22692,7 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B33" s="18" t="n">
@@ -22577,7 +22700,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Quartzolit / Votomassa</t>
+          <t>Gerdau / ArcelorMittal</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -22587,7 +22710,7 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>argamassa colante e rejunte</t>
+          <t>aco CA-50 e tela soldada</t>
         </is>
       </c>
       <c r="F33" s="37" t="n"/>
@@ -22602,7 +22725,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B34" s="18" t="n">
@@ -22620,7 +22743,7 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>bloco, areia e brita</t>
+          <t>porcelanato, argamassa e rejunte</t>
         </is>
       </c>
       <c r="F34" s="37" t="n"/>
@@ -22635,7 +22758,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B35" s="18" t="n">
@@ -22653,7 +22776,7 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>bloco de concreto estrutural</t>
+          <t>revestimento e assentamento</t>
         </is>
       </c>
       <c r="F35" s="37" t="n"/>
@@ -22668,7 +22791,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B36" s="18" t="n">
@@ -22676,7 +22799,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>O K Representacao de Material de Construcao</t>
+          <t>Bacuri Materiais</t>
         </is>
       </c>
       <c r="D36" s="36" t="inlineStr">
@@ -22686,7 +22809,7 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>representacao e distribuicao</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="F36" s="37" t="n"/>
@@ -22701,7 +22824,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B37" s="18" t="n">
@@ -22719,7 +22842,7 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>porcelanato externo</t>
+          <t>porcelanato, fabricante</t>
         </is>
       </c>
       <c r="F37" s="37" t="n"/>
@@ -22734,7 +22857,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B38" s="18" t="n">
@@ -22742,7 +22865,7 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Fabricantes de WPC (deck coextrudado)</t>
+          <t>Quartzolit / Votomassa</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -22752,7 +22875,7 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>deck de madeira plastica</t>
+          <t>argamassa colante e rejunte</t>
         </is>
       </c>
       <c r="F38" s="37" t="n"/>
@@ -22767,7 +22890,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>estrutura</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B39" s="18" t="n">
@@ -22775,7 +22898,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Tecnoframe</t>
+          <t>Du Norte Comercio</t>
         </is>
       </c>
       <c r="D39" s="36" t="inlineStr">
@@ -22785,7 +22908,7 @@
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>perfis LSF, fabricante com atuacao local</t>
+          <t>bloco, areia e brita</t>
         </is>
       </c>
       <c r="F39" s="37" t="n"/>
@@ -22800,7 +22923,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>estrutura</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B40" s="18" t="n">
@@ -22808,17 +22931,17 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Barbieri do Brasil</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Loja do Rei</t>
+        </is>
+      </c>
+      <c r="D40" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>perfis galvanizados LSF e drywall</t>
+          <t>bloco de concreto estrutural</t>
         </is>
       </c>
       <c r="F40" s="37" t="n"/>
@@ -22833,7 +22956,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>estrutura</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B41" s="18" t="n">
@@ -22841,17 +22964,17 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Multiperfil</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>O K Representacao de Material de Construcao</t>
+        </is>
+      </c>
+      <c r="D41" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>perfis LSF, venda por distribuidor</t>
+          <t>representacao e distribuicao</t>
         </is>
       </c>
       <c r="F41" s="37" t="n"/>
@@ -22866,7 +22989,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>estrutura</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B42" s="18" t="n">
@@ -22874,7 +22997,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Deville Kerr</t>
+          <t>Portobello / Eliane / Portinari</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -22884,7 +23007,7 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>perfis LSF direto de fabrica</t>
+          <t>porcelanato externo</t>
         </is>
       </c>
       <c r="F42" s="37" t="n"/>
@@ -22899,7 +23022,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>estrutura</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B43" s="18" t="n">
@@ -22907,7 +23030,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Alge Steel / Alge Metalurgica</t>
+          <t>Fabricantes de WPC (deck coextrudado)</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -22917,7 +23040,7 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>perfis steel frame</t>
+          <t>deck de madeira plastica</t>
         </is>
       </c>
       <c r="F43" s="37" t="n"/>
@@ -22930,27 +23053,27 @@
       <c r="M43" s="37" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>estrutura</t>
         </is>
       </c>
       <c r="B44" s="18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>MPS Steel</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Tecnoframe</t>
+        </is>
+      </c>
+      <c r="D44" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>fabricacao e fornecimento de perfis</t>
+          <t>perfis LSF, fabricante com atuacao local</t>
         </is>
       </c>
       <c r="F44" s="37" t="n"/>
@@ -22963,27 +23086,27 @@
       <c r="M44" s="37" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>marcenaria</t>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>estrutura</t>
         </is>
       </c>
       <c r="B45" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Marcenarias de Manaus</t>
-        </is>
-      </c>
-      <c r="D45" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Barbieri do Brasil</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>movel sob medida</t>
+          <t>perfis galvanizados LSF e drywall</t>
         </is>
       </c>
       <c r="F45" s="37" t="n"/>
@@ -22998,15 +23121,15 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>estrutura</t>
         </is>
       </c>
       <c r="B46" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Todeschini / Dell Anno</t>
+          <t>Multiperfil</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -23016,7 +23139,7 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>movel planejado, rede</t>
+          <t>perfis LSF, venda por distribuidor</t>
         </is>
       </c>
       <c r="F46" s="37" t="n"/>
@@ -23031,15 +23154,15 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>estrutura</t>
         </is>
       </c>
       <c r="B47" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Italinea / Favorita</t>
+          <t>Deville Kerr</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -23049,7 +23172,7 @@
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>movel planejado</t>
+          <t>perfis LSF direto de fabrica</t>
         </is>
       </c>
       <c r="F47" s="37" t="n"/>
@@ -23064,25 +23187,25 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>estrutura</t>
         </is>
       </c>
       <c r="B48" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Marmorarias de Manaus</t>
-        </is>
-      </c>
-      <c r="D48" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Alge Steel / Alge Metalurgica</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>tampo em quartzo e granito</t>
+          <t>perfis steel frame</t>
         </is>
       </c>
       <c r="F48" s="37" t="n"/>
@@ -23097,15 +23220,15 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>estrutura</t>
         </is>
       </c>
       <c r="B49" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Duratex / Guararapes</t>
+          <t>MPS Steel</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -23115,7 +23238,7 @@
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>MDF, fabricante de chapa</t>
+          <t>fabricacao e fornecimento de perfis</t>
         </is>
       </c>
       <c r="F49" s="37" t="n"/>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1519,7 +1519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R71</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R72</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1519,7 +1519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R72</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R74</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1519,7 +1519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R74</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R75</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1519,7 +1519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R75</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R77</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1519,7 +1519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R78</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R79</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1507,7 +1507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R80</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R81</t>
         </is>
       </c>
     </row>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -17,9 +17,9 @@
     <sheet name="PEÇAS E CORTE" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COTAÇÃO'!$A$3:$V$185</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ESPECIFICAÇÕES'!$A$3:$I$185</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PEÇAS E CORTE'!$A$4:$F$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COTAÇÃO'!$A$3:$V$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ESPECIFICAÇÕES'!$A$3:$I$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PEÇAS E CORTE'!$A$4:$F$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -348,7 +348,7 @@
   <commentList>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>perfil formado a frio em barra de 6.000 mm; aco ZAR 230, fy 230 MPa, fu 310 MPa; revestimento Z275; massa BRUTA, ja com a perda de corte (10.9 %)
+        <t>perfil formado a frio em barra de 6.000 mm; aco ZAR 230, fy 230 MPa, fu 310 MPa; revestimento Z275; massa BRUTA, ja com a perda de corte (11.1 %)
 NORMAS: NBR 14762, NBR 15253, NBR 7008</t>
       </text>
     </comment>
@@ -621,7 +621,7 @@
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
       </text>
     </comment>
-    <comment ref="C51" authorId="0" shapeId="0">
+    <comment ref="C52" authorId="0" shapeId="0">
       <text>
         <t>tubo, conexao ou condutor conforme descricao
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
@@ -635,13 +635,13 @@
     </comment>
     <comment ref="C54" authorId="0" shapeId="0">
       <text>
-        <t>tubo, conexao ou condutor conforme descricao; DN40
+        <t>tubo, conexao ou condutor conforme descricao; DN50
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
       </text>
     </comment>
-    <comment ref="C55" authorId="0" shapeId="0">
+    <comment ref="C56" authorId="0" shapeId="0">
       <text>
-        <t>tubo, conexao ou condutor conforme descricao; DN50
+        <t>tubo, conexao ou condutor conforme descricao
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
       </text>
     </comment>
@@ -651,13 +651,13 @@
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
       </text>
     </comment>
-    <comment ref="C58" authorId="0" shapeId="0">
+    <comment ref="C59" authorId="0" shapeId="0">
       <text>
-        <t>tubo, conexao ou condutor conforme descricao
+        <t>tubo, conexao ou condutor conforme descricao; DN75
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
       </text>
     </comment>
-    <comment ref="C59" authorId="0" shapeId="0">
+    <comment ref="C60" authorId="0" shapeId="0">
       <text>
         <t>tubo, conexao ou condutor conforme descricao; DN20
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
@@ -665,7 +665,7 @@
     </comment>
     <comment ref="C61" authorId="0" shapeId="0">
       <text>
-        <t>tubo, conexao ou condutor conforme descricao; DN75
+        <t>tubo, conexao ou condutor conforme descricao; DN40
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
       </text>
     </comment>
@@ -681,7 +681,7 @@
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
       </text>
     </comment>
-    <comment ref="C68" authorId="0" shapeId="0">
+    <comment ref="C69" authorId="0" shapeId="0">
       <text>
         <t>tubo, conexao ou condutor conforme descricao
 NORMAS: NBR 5410, NBR 5626, NBR 8160</t>
@@ -718,7 +718,7 @@
 NORMAS: NBR 13245, NBR 15498</t>
       </text>
     </comment>
-    <comment ref="C84" authorId="0" shapeId="0">
+    <comment ref="C83" authorId="0" shapeId="0">
       <text>
         <t>sistema de fachada sobre placa cimenticia: basecoat com tela de fibra de vidro alcali-resistente, junta com selante PU, acabamento acrilico elastomerico LISO com biocida — faixa ate 2.600 mm e face interna da platibanda
 NORMAS: NBR 13245, NBR 15498</t>
@@ -736,7 +736,7 @@
 NORMAS: NBR 13245, NBR 15498</t>
       </text>
     </comment>
-    <comment ref="C87" authorId="0" shapeId="0">
+    <comment ref="C88" authorId="0" shapeId="0">
       <text>
         <t>sistema de fachada sobre placa cimenticia: basecoat com tela de fibra de vidro alcali-resistente, junta com selante PU, acabamento acrilico elastomerico LISO com biocida — faixa ate 2.600 mm e face interna da platibanda
 NORMAS: NBR 13245, NBR 15498</t>
@@ -816,34 +816,35 @@
     </comment>
     <comment ref="C129" authorId="0" shapeId="0">
       <text>
+        <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
+NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
+LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+      </text>
+    </comment>
+    <comment ref="C130" authorId="0" shapeId="0">
+      <text>
         <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
 LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
       </text>
     </comment>
-    <comment ref="C130" authorId="0" shapeId="0">
+    <comment ref="C131" authorId="0" shapeId="0">
       <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
       </text>
     </comment>
-    <comment ref="C131" authorId="0" shapeId="0">
+    <comment ref="C132" authorId="0" shapeId="0">
       <text>
         <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor
 LACUNA: desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
       </text>
     </comment>
-    <comment ref="C132" authorId="0" shapeId="0">
+    <comment ref="C133" authorId="0" shapeId="0">
       <text>
         <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
 NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
 LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
-      </text>
-    </comment>
-    <comment ref="C133" authorId="0" shapeId="0">
-      <text>
-        <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
-NORMAS: NBR 11702, NBR 13245</t>
       </text>
     </comment>
     <comment ref="C134" authorId="0" shapeId="0">
@@ -855,9 +856,8 @@
     </comment>
     <comment ref="C135" authorId="0" shapeId="0">
       <text>
-        <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
-NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
-LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+        <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade
+NORMAS: NBR 11702, NBR 13245</t>
       </text>
     </comment>
     <comment ref="C136" authorId="0" shapeId="0">
@@ -881,16 +881,16 @@
     </comment>
     <comment ref="C139" authorId="0" shapeId="0">
       <text>
-        <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
-NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
-LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
+NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
+LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
     <comment ref="C140" authorId="0" shapeId="0">
       <text>
-        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
-NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
-LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+        <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier
+NORMAS: NBR 5410, NBR 5419-3, NBR 5419-4
+LACUNA: laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
       </text>
     </comment>
     <comment ref="C141" authorId="0" shapeId="0">
@@ -976,21 +976,21 @@
     </comment>
     <comment ref="C153" authorId="0" shapeId="0">
       <text>
+        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
+NORMAS: NBR 14136, NBR 5410</t>
+      </text>
+    </comment>
+    <comment ref="C154" authorId="0" shapeId="0">
+      <text>
         <t>equipamento novo, com garantia de fabrica e instalacao por credenciado
 LACUNA: marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
       </text>
     </comment>
-    <comment ref="C154" authorId="0" shapeId="0">
+    <comment ref="C155" authorId="0" shapeId="0">
       <text>
         <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
 NORMAS: NBR 15097, NBR 15705
 LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
-      </text>
-    </comment>
-    <comment ref="C155" authorId="0" shapeId="0">
-      <text>
-        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
-NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
     <comment ref="C156" authorId="0" shapeId="0">
@@ -1090,15 +1090,15 @@
     </comment>
     <comment ref="C170" authorId="0" shapeId="0">
       <text>
-        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
-NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
-LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
+NORMAS: NBR 14136, NBR 5410</t>
       </text>
     </comment>
     <comment ref="C171" authorId="0" shapeId="0">
       <text>
-        <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
-NORMAS: NBR 14136, NBR 5410</t>
+        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
+NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
+LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
       </text>
     </comment>
     <comment ref="C172" authorId="0" shapeId="0">
@@ -1130,9 +1130,9 @@
     </comment>
     <comment ref="C176" authorId="0" shapeId="0">
       <text>
-        <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
-NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
-LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
+NORMAS: NBR 15097, NBR 15705
+LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
       </text>
     </comment>
     <comment ref="C177" authorId="0" shapeId="0">
@@ -1151,9 +1151,9 @@
     </comment>
     <comment ref="C179" authorId="0" shapeId="0">
       <text>
-        <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo
-NORMAS: NBR 15097, NBR 15705
-LACUNA: linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento
+NORMAS: NBR 16274, NBR 16690, Portaria INMETRO 140/2022
+LACUNA: marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
       </text>
     </comment>
     <comment ref="C180" authorId="0" shapeId="0">
@@ -1192,6 +1192,13 @@
       </text>
     </comment>
     <comment ref="C185" authorId="0" shapeId="0">
+      <text>
+        <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas
+NORMAS: NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)
+LACUNA: marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+      </text>
+    </comment>
+    <comment ref="C186" authorId="0" shapeId="0">
       <text>
         <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto
 NORMAS: NBR 14136, NBR 5410</t>
@@ -1507,7 +1514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 297.36 m² fechados · revisão R81</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 307.08 m² fechados · revisão R82</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V189"/>
+  <dimension ref="A1:V190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1764,11 +1771,11 @@
         </is>
       </c>
       <c r="Q2" s="4">
-        <f>COUNTIF(V4:V185,"COMPLETO")&amp;" de "&amp;182&amp;" itens com 5 propostas"</f>
+        <f>COUNTIF(V4:V186,"COMPLETO")&amp;" de "&amp;183&amp;" itens com 5 propostas"</f>
         <v/>
       </c>
       <c r="T2" s="7">
-        <f>IF(I186=0,0,SUMIF(V4:V185,"COMPLETO",I4:I185)/I186)</f>
+        <f>IF(I187=0,0,SUMIF(V4:V186,"COMPLETO",I4:I186)/I187)</f>
         <v/>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -1922,7 +1929,7 @@
         </is>
       </c>
       <c r="E4" s="12" t="n">
-        <v>6550</v>
+        <v>6698.1</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>0</v>
@@ -1998,7 +2005,7 @@
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>970.1</v>
+        <v>1037.9</v>
       </c>
       <c r="F5" s="13" t="n">
         <v>0</v>
@@ -2074,7 +2081,7 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>184.3</v>
+        <v>157.7</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>0</v>
@@ -2150,7 +2157,7 @@
         </is>
       </c>
       <c r="E7" s="12" t="n">
-        <v>276.1</v>
+        <v>329.4</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>0</v>
@@ -2226,7 +2233,7 @@
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>426.4</v>
+        <v>489.5</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>0</v>
@@ -2302,7 +2309,7 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>276.1</v>
+        <v>329.4</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>0</v>
@@ -2454,7 +2461,7 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>117.4</v>
+        <v>127.1</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>0</v>
@@ -2530,7 +2537,7 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>1074.4</v>
+        <v>1191.6</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>0</v>
@@ -2606,7 +2613,7 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>165.4</v>
+        <v>178.3</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>0</v>
@@ -2682,7 +2689,7 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>370.8</v>
+        <v>394.2</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>0</v>
@@ -2758,7 +2765,7 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>885.5</v>
+        <v>958.8</v>
       </c>
       <c r="F15" s="13" t="n">
         <v>0</v>
@@ -2834,7 +2841,7 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>136.8</v>
+        <v>147</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>0</v>
@@ -2910,7 +2917,7 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>83.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>0</v>
@@ -2986,7 +2993,7 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>38.1</v>
+        <v>43.7</v>
       </c>
       <c r="F18" s="13" t="n">
         <v>0</v>
@@ -3062,7 +3069,7 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>11271</v>
+        <v>12666</v>
       </c>
       <c r="F19" s="13" t="n">
         <v>0</v>
@@ -3138,7 +3145,7 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="F20" s="13" t="n">
         <v>0</v>
@@ -3214,7 +3221,7 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>885.5</v>
+        <v>958.8</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>0</v>
@@ -3290,7 +3297,7 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>160.8</v>
+        <v>147</v>
       </c>
       <c r="F22" s="13" t="n">
         <v>0</v>
@@ -3366,7 +3373,7 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>80.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="F23" s="13" t="n">
         <v>0</v>
@@ -3594,7 +3601,7 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>737</v>
+        <v>630</v>
       </c>
       <c r="F26" s="13" t="n">
         <v>0</v>
@@ -3670,7 +3677,7 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="F27" s="13" t="n">
         <v>0</v>
@@ -3974,7 +3981,7 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>25.92</v>
+        <v>24.48</v>
       </c>
       <c r="F31" s="13" t="n">
         <v>0</v>
@@ -5342,7 +5349,7 @@
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>2474</v>
+        <v>2806</v>
       </c>
       <c r="F49" s="13" t="n">
         <v>0</v>
@@ -5418,7 +5425,7 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1396.4</v>
+        <v>1553.1</v>
       </c>
       <c r="F50" s="13" t="n">
         <v>0</v>
@@ -5475,7 +5482,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>MEP-FRIGO</t>
+          <t>FIX-06</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -5485,16 +5492,16 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Linha frigorigena</t>
+          <t>Bucha passa-fio 25 mm (montante atravessado)</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>56</v>
+        <v>2929</v>
       </c>
       <c r="F51" s="13" t="n">
         <v>0</v>
@@ -5504,7 +5511,7 @@
         <v/>
       </c>
       <c r="H51" s="15" t="n">
-        <v>62</v>
+        <v>1.2</v>
       </c>
       <c r="I51" s="16">
         <f>G51*H51</f>
@@ -5551,7 +5558,7 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>FIX-06</t>
+          <t>MEP-FRIGO</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -5561,16 +5568,16 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Bucha passa-fio 25 mm (montante atravessado)</t>
+          <t>Linha frigorigena</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>2580</v>
+        <v>56</v>
       </c>
       <c r="F52" s="13" t="n">
         <v>0</v>
@@ -5580,7 +5587,7 @@
         <v/>
       </c>
       <c r="H52" s="15" t="n">
-        <v>1.2</v>
+        <v>62</v>
       </c>
       <c r="I52" s="16">
         <f>G52*H52</f>
@@ -5646,7 +5653,7 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F53" s="13" t="n">
         <v>0</v>
@@ -5703,7 +5710,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>MEP-ESGO40</t>
+          <t>MEP-ESGO50</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -5713,7 +5720,7 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Tubo esgoto DN40</t>
+          <t>Tubo esgoto DN50</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -5722,7 +5729,7 @@
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>62.2</v>
+        <v>81</v>
       </c>
       <c r="F54" s="13" t="n">
         <v>0</v>
@@ -5779,7 +5786,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>MEP-ESGO50</t>
+          <t>FIX-13</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -5789,16 +5796,16 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Tubo esgoto DN50</t>
+          <t>Clip de eletroduto no montante (a cada 1.200 mm)</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>60.5</v>
+        <v>1921</v>
       </c>
       <c r="F55" s="13" t="n">
         <v>0</v>
@@ -5808,7 +5815,7 @@
         <v/>
       </c>
       <c r="H55" s="15" t="n">
-        <v>26</v>
+        <v>0.9</v>
       </c>
       <c r="I55" s="16">
         <f>G55*H55</f>
@@ -5855,7 +5862,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>FIX-13</t>
+          <t>MEP-ISOL</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -5865,16 +5872,16 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Clip de eletroduto no montante (a cada 1.200 mm)</t>
+          <t>Isolamento de linha</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1746</v>
+        <v>112</v>
       </c>
       <c r="F56" s="13" t="n">
         <v>0</v>
@@ -5884,7 +5891,7 @@
         <v/>
       </c>
       <c r="H56" s="15" t="n">
-        <v>0.9</v>
+        <v>14</v>
       </c>
       <c r="I56" s="16">
         <f>G56*H56</f>
@@ -5931,7 +5938,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>MEP-ISOL</t>
+          <t>MEP-DISJ</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -5941,16 +5948,16 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Isolamento de linha</t>
+          <t>Disjuntor</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F57" s="13" t="n">
         <v>0</v>
@@ -5960,7 +5967,7 @@
         <v/>
       </c>
       <c r="H57" s="15" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="I57" s="16">
         <f>G57*H57</f>
@@ -6007,7 +6014,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>MEP-DISJ</t>
+          <t>FIX-10</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -6017,7 +6024,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor</t>
+          <t>Caixa de passagem</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -6026,7 +6033,7 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="F58" s="13" t="n">
         <v>0</v>
@@ -6036,7 +6043,7 @@
         <v/>
       </c>
       <c r="H58" s="15" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="I58" s="16">
         <f>G58*H58</f>
@@ -6083,7 +6090,7 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>MEP-PEX20</t>
+          <t>MEP-ESGO75</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -6093,7 +6100,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Tubo PEX DN20 agua fria, pela parede a 400 mm</t>
+          <t>Tubo esgoto DN75</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -6102,7 +6109,7 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>121.5</v>
+        <v>50.2</v>
       </c>
       <c r="F59" s="13" t="n">
         <v>0</v>
@@ -6112,7 +6119,7 @@
         <v/>
       </c>
       <c r="H59" s="15" t="n">
-        <v>9.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="I59" s="16">
         <f>G59*H59</f>
@@ -6159,7 +6166,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>FIX-10</t>
+          <t>MEP-PEX20</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -6169,16 +6176,16 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Caixa de passagem</t>
+          <t>Tubo PEX DN20 agua fria, pela parede a 400 mm</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>130</v>
+        <v>124.2</v>
       </c>
       <c r="F60" s="13" t="n">
         <v>0</v>
@@ -6188,7 +6195,7 @@
         <v/>
       </c>
       <c r="H60" s="15" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I60" s="16">
         <f>G60*H60</f>
@@ -6235,7 +6242,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>MEP-ESGO75</t>
+          <t>MEP-ESGO40</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -6245,7 +6252,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Tubo esgoto DN75</t>
+          <t>Tubo esgoto DN40</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -6254,7 +6261,7 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>38.3</v>
+        <v>46.7</v>
       </c>
       <c r="F61" s="13" t="n">
         <v>0</v>
@@ -6330,7 +6337,7 @@
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="F62" s="13" t="n">
         <v>0</v>
@@ -6406,7 +6413,7 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>39.8</v>
+        <v>42</v>
       </c>
       <c r="F63" s="13" t="n">
         <v>0</v>
@@ -6482,7 +6489,7 @@
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F64" s="13" t="n">
         <v>0</v>
@@ -6634,7 +6641,7 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F66" s="13" t="n">
         <v>0</v>
@@ -6710,7 +6717,7 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F67" s="13" t="n">
         <v>0</v>
@@ -6767,7 +6774,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>MEP-DRENO</t>
+          <t>FIX-01</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -6777,16 +6784,16 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Dreno de condensado</t>
+          <t>Abracadeira de eletroduto no forro/entrepiso (a cada 1.000 mm)</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>44.8</v>
+        <v>162</v>
       </c>
       <c r="F68" s="13" t="n">
         <v>0</v>
@@ -6796,7 +6803,7 @@
         <v/>
       </c>
       <c r="H68" s="15" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="I68" s="16">
         <f>G68*H68</f>
@@ -6843,7 +6850,7 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>FIX-01</t>
+          <t>MEP-DRENO</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -6853,16 +6860,16 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Abracadeira de eletroduto no forro/entrepiso (a cada 1.000 mm)</t>
+          <t>Dreno de condensado</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>161</v>
+        <v>44.8</v>
       </c>
       <c r="F69" s="13" t="n">
         <v>0</v>
@@ -6872,7 +6879,7 @@
         <v/>
       </c>
       <c r="H69" s="15" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="I69" s="16">
         <f>G69*H69</f>
@@ -6995,7 +7002,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>FIX-02</t>
+          <t>FIX-08</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -7005,7 +7012,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Abracadeira de linha frigorigena (a cada 1,0 m)</t>
+          <t>Caixa 4x4</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -7014,7 +7021,7 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="F71" s="13" t="n">
         <v>0</v>
@@ -7024,7 +7031,7 @@
         <v/>
       </c>
       <c r="H71" s="15" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="I71" s="16">
         <f>G71*H71</f>
@@ -7071,7 +7078,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>FIX-08</t>
+          <t>FIX-02</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -7081,7 +7088,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Caixa 4x4</t>
+          <t>Abracadeira de linha frigorigena (a cada 1,0 m)</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -7090,7 +7097,7 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="F72" s="13" t="n">
         <v>0</v>
@@ -7100,7 +7107,7 @@
         <v/>
       </c>
       <c r="H72" s="15" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="I72" s="16">
         <f>G72*H72</f>
@@ -7166,7 +7173,7 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F73" s="13" t="n">
         <v>0</v>
@@ -7242,7 +7249,7 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F74" s="13" t="n">
         <v>0</v>
@@ -7394,7 +7401,7 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F76" s="13" t="n">
         <v>0</v>
@@ -7470,7 +7477,7 @@
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>6070</v>
+        <v>6524</v>
       </c>
       <c r="F77" s="13" t="n">
         <v>0</v>
@@ -7546,7 +7553,7 @@
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F78" s="13" t="n">
         <v>0</v>
@@ -7622,7 +7629,7 @@
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>155.4</v>
+        <v>217.3</v>
       </c>
       <c r="F79" s="13" t="n">
         <v>0</v>
@@ -7698,7 +7705,7 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>279</v>
+        <v>375</v>
       </c>
       <c r="F80" s="13" t="n">
         <v>0</v>
@@ -7774,7 +7781,7 @@
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>192</v>
+        <v>183.4</v>
       </c>
       <c r="F81" s="13" t="n">
         <v>0</v>
@@ -7850,7 +7857,7 @@
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>192</v>
+        <v>183.4</v>
       </c>
       <c r="F82" s="13" t="n">
         <v>0</v>
@@ -7907,7 +7914,7 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>BRI-MEC</t>
+          <t>FAC-JUNTA-SECA</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -7917,16 +7924,16 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Mecanismo de brise movel: guia, roldana e trava</t>
+          <t>Junta seca: perfil EPDM e fundo de junta</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>cj</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>2</v>
+        <v>271.7</v>
       </c>
       <c r="F83" s="13" t="n">
         <v>0</v>
@@ -7936,7 +7943,7 @@
         <v/>
       </c>
       <c r="H83" s="15" t="n">
-        <v>2400</v>
+        <v>22</v>
       </c>
       <c r="I83" s="16">
         <f>G83*H83</f>
@@ -7983,7 +7990,7 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>FAC-JUNTA-SECA</t>
+          <t>BRI-MEC</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -7993,16 +8000,16 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Junta seca: perfil EPDM e fundo de junta</t>
+          <t>Mecanismo de brise movel: guia, roldana e trava</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>cj</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>194.3</v>
+        <v>2</v>
       </c>
       <c r="F84" s="13" t="n">
         <v>0</v>
@@ -8012,7 +8019,7 @@
         <v/>
       </c>
       <c r="H84" s="15" t="n">
-        <v>22</v>
+        <v>2400</v>
       </c>
       <c r="I84" s="16">
         <f>G84*H84</f>
@@ -8078,7 +8085,7 @@
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>54.8</v>
+        <v>52.4</v>
       </c>
       <c r="F85" s="13" t="n">
         <v>0</v>
@@ -8154,7 +8161,7 @@
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>239.9</v>
+        <v>229.3</v>
       </c>
       <c r="F86" s="13" t="n">
         <v>0</v>
@@ -8211,7 +8218,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>FAC-TELA</t>
+          <t>BRI-TRAV</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -8221,16 +8228,16 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Tela de fibra de vidro alcali-resistente, embutida no basecoat</t>
+          <t>Travessa de brise: U 50x25x1,2 aluminio</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>211.2</v>
+        <v>51.6</v>
       </c>
       <c r="F87" s="13" t="n">
         <v>0</v>
@@ -8240,7 +8247,7 @@
         <v/>
       </c>
       <c r="H87" s="15" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="I87" s="16">
         <f>G87*H87</f>
@@ -8287,7 +8294,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>BRI-TRAV</t>
+          <t>FAC-TELA</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -8297,16 +8304,16 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Travessa de brise: U 50x25x1,2 aluminio</t>
+          <t>Tela de fibra de vidro alcali-resistente, embutida no basecoat</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>41.4</v>
+        <v>201.8</v>
       </c>
       <c r="F88" s="13" t="n">
         <v>0</v>
@@ -8316,7 +8323,7 @@
         <v/>
       </c>
       <c r="H88" s="15" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="I88" s="16">
         <f>G88*H88</f>
@@ -8382,7 +8389,7 @@
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="F89" s="13" t="n">
         <v>0</v>
@@ -8458,7 +8465,7 @@
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>3118</v>
+        <v>2917</v>
       </c>
       <c r="F90" s="13" t="n">
         <v>0</v>
@@ -8990,7 +8997,7 @@
         </is>
       </c>
       <c r="E97" s="12" t="n">
-        <v>249.5</v>
+        <v>233.4</v>
       </c>
       <c r="F97" s="13" t="n">
         <v>0</v>
@@ -9579,7 +9586,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>EXT-GRAUTE</t>
+          <t>EXT-PISC-FILTRO</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -9589,16 +9596,16 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Graute de cinta e pilarete do muro</t>
+          <t>Piscina: filtro de areia DE 500 mm com valvula seletora</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E105" s="12" t="n">
-        <v>2.99</v>
+        <v>1</v>
       </c>
       <c r="F105" s="13" t="n">
         <v>0</v>
@@ -9608,7 +9615,7 @@
         <v/>
       </c>
       <c r="H105" s="15" t="n">
-        <v>620</v>
+        <v>1850</v>
       </c>
       <c r="I105" s="16">
         <f>G105*H105</f>
@@ -9655,7 +9662,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-FILTRO</t>
+          <t>EXT-PISC-IMP</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -9665,16 +9672,16 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Piscina: filtro de areia DE 500 mm com valvula seletora</t>
+          <t>Piscina: impermeabilizacao (cristalizante + polimerica)</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1</v>
+        <v>30.43</v>
       </c>
       <c r="F106" s="13" t="n">
         <v>0</v>
@@ -9684,7 +9691,7 @@
         <v/>
       </c>
       <c r="H106" s="15" t="n">
-        <v>1850</v>
+        <v>58</v>
       </c>
       <c r="I106" s="16">
         <f>G106*H106</f>
@@ -9731,7 +9738,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-IMP</t>
+          <t>EXT-GRAUTE</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -9741,16 +9748,16 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Piscina: impermeabilizacao (cristalizante + polimerica)</t>
+          <t>Graute de cinta e pilarete do muro</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E107" s="12" t="n">
-        <v>30.43</v>
+        <v>2.8</v>
       </c>
       <c r="F107" s="13" t="n">
         <v>0</v>
@@ -9760,7 +9767,7 @@
         <v/>
       </c>
       <c r="H107" s="15" t="n">
-        <v>58</v>
+        <v>620</v>
       </c>
       <c r="I107" s="16">
         <f>G107*H107</f>
@@ -10586,7 +10593,7 @@
         </is>
       </c>
       <c r="E118" s="12" t="n">
-        <v>844.7</v>
+        <v>927.5</v>
       </c>
       <c r="F118" s="13" t="n">
         <v>0</v>
@@ -10662,7 +10669,7 @@
         </is>
       </c>
       <c r="E119" s="12" t="n">
-        <v>50</v>
+        <v>54.6</v>
       </c>
       <c r="F119" s="13" t="n">
         <v>0</v>
@@ -10814,7 +10821,7 @@
         </is>
       </c>
       <c r="E121" s="12" t="n">
-        <v>355.6</v>
+        <v>366.3</v>
       </c>
       <c r="F121" s="13" t="n">
         <v>0</v>
@@ -10890,7 +10897,7 @@
         </is>
       </c>
       <c r="E122" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F122" s="13" t="n">
         <v>0</v>
@@ -10966,7 +10973,7 @@
         </is>
       </c>
       <c r="E123" s="12" t="n">
-        <v>640.8</v>
+        <v>701.7</v>
       </c>
       <c r="F123" s="13" t="n">
         <v>0</v>
@@ -11346,7 +11353,7 @@
         </is>
       </c>
       <c r="E128" s="12" t="n">
-        <v>511.1</v>
+        <v>521.8</v>
       </c>
       <c r="F128" s="13" t="n">
         <v>0</v>
@@ -11403,26 +11410,26 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>MAR-PRAT</t>
+          <t>FV-INVERSOR</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Prateleira aberta, por metro de prateleira</t>
+          <t>Inversor string 15 kW, trifasico 220 V</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kW</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
-        <v>35.19</v>
+        <v>15</v>
       </c>
       <c r="F129" s="13" t="n">
         <v>0</v>
@@ -11432,7 +11439,7 @@
         <v/>
       </c>
       <c r="H129" s="15" t="n">
-        <v>260</v>
+        <v>620</v>
       </c>
       <c r="I129" s="16">
         <f>G129*H129</f>
@@ -11479,26 +11486,26 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>FV-INSTAL</t>
+          <t>MAR-PRAT</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Instalacao e comissionamento</t>
+          <t>Prateleira aberta, por metro de prateleira</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>kWp</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E130" s="12" t="n">
-        <v>15.95</v>
+        <v>35.19</v>
       </c>
       <c r="F130" s="13" t="n">
         <v>0</v>
@@ -11508,7 +11515,7 @@
         <v/>
       </c>
       <c r="H130" s="15" t="n">
-        <v>550</v>
+        <v>260</v>
       </c>
       <c r="I130" s="16">
         <f>G130*H130</f>
@@ -11555,26 +11562,26 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>MAR-TAMPO</t>
+          <t>FV-INSTAL</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Tampo de bancada (quartzo/granito)</t>
+          <t>Instalacao e comissionamento</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>kWp</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
-        <v>6.84</v>
+        <v>16.5</v>
       </c>
       <c r="F131" s="13" t="n">
         <v>0</v>
@@ -11584,7 +11591,7 @@
         <v/>
       </c>
       <c r="H131" s="15" t="n">
-        <v>1250</v>
+        <v>550</v>
       </c>
       <c r="I131" s="16">
         <f>G131*H131</f>
@@ -11631,17 +11638,17 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>FV-ESTRUTURA</t>
+          <t>MAR-TAMPO</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Estrutura de fixacao em aluminio sobre terca</t>
+          <t>Tampo de bancada (quartzo/granito)</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -11650,7 +11657,7 @@
         </is>
       </c>
       <c r="E132" s="12" t="n">
-        <v>86.2</v>
+        <v>6.84</v>
       </c>
       <c r="F132" s="13" t="n">
         <v>0</v>
@@ -11660,7 +11667,7 @@
         <v/>
       </c>
       <c r="H132" s="15" t="n">
-        <v>95</v>
+        <v>1250</v>
       </c>
       <c r="I132" s="16">
         <f>G132*H132</f>
@@ -11707,26 +11714,26 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>PIN-TINTA</t>
+          <t>FV-ESTRUTURA</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
+          <t>Estrutura de fixacao em aluminio sobre terca</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
-        <v>179.6</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F133" s="13" t="n">
         <v>0</v>
@@ -11736,7 +11743,7 @@
         <v/>
       </c>
       <c r="H133" s="15" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="I133" s="16">
         <f>G133*H133</f>
@@ -11802,7 +11809,7 @@
         </is>
       </c>
       <c r="E134" s="12" t="n">
-        <v>220.9</v>
+        <v>241.9</v>
       </c>
       <c r="F134" s="13" t="n">
         <v>0</v>
@@ -11859,26 +11866,26 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>FV-INVERSOR</t>
+          <t>PIN-TINTA</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Inversor string 12 kW, trifasico 220 V</t>
+          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
-        <v>12</v>
+        <v>193.7</v>
       </c>
       <c r="F135" s="13" t="n">
         <v>0</v>
@@ -11888,7 +11895,7 @@
         <v/>
       </c>
       <c r="H135" s="15" t="n">
-        <v>620</v>
+        <v>42</v>
       </c>
       <c r="I135" s="16">
         <f>G135*H135</f>
@@ -12030,7 +12037,7 @@
         </is>
       </c>
       <c r="E137" s="12" t="n">
-        <v>257</v>
+        <v>266.8</v>
       </c>
       <c r="F137" s="13" t="n">
         <v>0</v>
@@ -12163,7 +12170,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>SPD-CAPTOR</t>
+          <t>LUM-DOWNLIGHT18</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -12173,16 +12180,16 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
+          <t>Downlight LED embutido 18 W</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
-        <v>160.8</v>
+        <v>45</v>
       </c>
       <c r="F139" s="13" t="n">
         <v>0</v>
@@ -12192,7 +12199,7 @@
         <v/>
       </c>
       <c r="H139" s="15" t="n">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="I139" s="16">
         <f>G139*H139</f>
@@ -12239,7 +12246,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>LUM-DOWNLIGHT18</t>
+          <t>SPD-CAPTOR</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -12249,16 +12256,16 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>Downlight LED embutido 18 W</t>
+          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E140" s="12" t="n">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="F140" s="13" t="n">
         <v>0</v>
@@ -12268,7 +12275,7 @@
         <v/>
       </c>
       <c r="H140" s="15" t="n">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="I140" s="16">
         <f>G140*H140</f>
@@ -12562,7 +12569,7 @@
         </is>
       </c>
       <c r="E144" s="12" t="n">
-        <v>511.1</v>
+        <v>521.8</v>
       </c>
       <c r="F144" s="13" t="n">
         <v>0</v>
@@ -13227,17 +13234,17 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>EQP-PORTAO</t>
+          <t>ELE-TUG</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Automatizador de portao de correr</t>
+          <t>Tomada 2P+T 10 A com placa</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
@@ -13246,7 +13253,7 @@
         </is>
       </c>
       <c r="E153" s="12" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="F153" s="13" t="n">
         <v>0</v>
@@ -13256,7 +13263,7 @@
         <v/>
       </c>
       <c r="H153" s="15" t="n">
-        <v>2400</v>
+        <v>28</v>
       </c>
       <c r="I153" s="16">
         <f>G153*H153</f>
@@ -13303,17 +13310,17 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>MET-ACESS</t>
+          <t>EQP-PORTAO</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
+          <t>Automatizador de portao de correr</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
@@ -13322,7 +13329,7 @@
         </is>
       </c>
       <c r="E154" s="12" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F154" s="13" t="n">
         <v>0</v>
@@ -13332,7 +13339,7 @@
         <v/>
       </c>
       <c r="H154" s="15" t="n">
-        <v>85</v>
+        <v>2400</v>
       </c>
       <c r="I154" s="16">
         <f>G154*H154</f>
@@ -13379,17 +13386,17 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUG</t>
+          <t>MET-ACESS</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Tomada 2P+T 10 A com placa</t>
+          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
@@ -13398,7 +13405,7 @@
         </is>
       </c>
       <c r="E155" s="12" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="F155" s="13" t="n">
         <v>0</v>
@@ -13408,7 +13415,7 @@
         <v/>
       </c>
       <c r="H155" s="15" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="I155" s="16">
         <f>G155*H155</f>
@@ -13474,7 +13481,7 @@
         </is>
       </c>
       <c r="E156" s="12" t="n">
-        <v>74.8</v>
+        <v>80.7</v>
       </c>
       <c r="F156" s="13" t="n">
         <v>0</v>
@@ -14519,7 +14526,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>LUM-PENDENTE40</t>
+          <t>ELE-INT</t>
         </is>
       </c>
       <c r="B170" s="10" t="inlineStr">
@@ -14529,7 +14536,7 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>Pendente LED de pe-direito duplo, 40 W</t>
+          <t>Interruptor simples e paralelo com placa</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
@@ -14538,7 +14545,7 @@
         </is>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F170" s="13" t="n">
         <v>0</v>
@@ -14548,7 +14555,7 @@
         <v/>
       </c>
       <c r="H170" s="15" t="n">
-        <v>420</v>
+        <v>32</v>
       </c>
       <c r="I170" s="16">
         <f>G170*H170</f>
@@ -14595,7 +14602,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>ELE-INT</t>
+          <t>LUM-PENDENTE40</t>
         </is>
       </c>
       <c r="B171" s="10" t="inlineStr">
@@ -14605,7 +14612,7 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>Interruptor simples e paralelo com placa</t>
+          <t>Pendente LED de pe-direito duplo, 40 W</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
@@ -14614,7 +14621,7 @@
         </is>
       </c>
       <c r="E171" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F171" s="13" t="n">
         <v>0</v>
@@ -14624,7 +14631,7 @@
         <v/>
       </c>
       <c r="H171" s="15" t="n">
-        <v>32</v>
+        <v>420</v>
       </c>
       <c r="I171" s="16">
         <f>G171*H171</f>
@@ -14975,26 +14982,26 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>FV-CABO</t>
+          <t>LOU-TANQUE</t>
         </is>
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
+          <t>Tanque de lavanderia</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E176" s="12" t="n">
-        <v>46.3</v>
+        <v>2</v>
       </c>
       <c r="F176" s="13" t="n">
         <v>0</v>
@@ -15004,7 +15011,7 @@
         <v/>
       </c>
       <c r="H176" s="15" t="n">
-        <v>14</v>
+        <v>320</v>
       </c>
       <c r="I176" s="16">
         <f>G176*H176</f>
@@ -15051,7 +15058,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>LOU-TANQUE</t>
+          <t>MET-TORN-T</t>
         </is>
       </c>
       <c r="B177" s="10" t="inlineStr">
@@ -15061,7 +15068,7 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>Tanque de lavanderia</t>
+          <t>Torneira de tanque e de jardim</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
@@ -15070,7 +15077,7 @@
         </is>
       </c>
       <c r="E177" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F177" s="13" t="n">
         <v>0</v>
@@ -15080,7 +15087,7 @@
         <v/>
       </c>
       <c r="H177" s="15" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="I177" s="16">
         <f>G177*H177</f>
@@ -15127,7 +15134,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN-T</t>
+          <t>MET-ENGATE</t>
         </is>
       </c>
       <c r="B178" s="10" t="inlineStr">
@@ -15137,7 +15144,7 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>Torneira de tanque e de jardim</t>
+          <t>Engate flexivel</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
@@ -15146,7 +15153,7 @@
         </is>
       </c>
       <c r="E178" s="12" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F178" s="13" t="n">
         <v>0</v>
@@ -15156,7 +15163,7 @@
         <v/>
       </c>
       <c r="H178" s="15" t="n">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="I178" s="16">
         <f>G178*H178</f>
@@ -15203,26 +15210,26 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>MET-ENGATE</t>
+          <t>FV-CABO</t>
         </is>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>Engate flexivel</t>
+          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E179" s="12" t="n">
-        <v>27</v>
+        <v>40.3</v>
       </c>
       <c r="F179" s="13" t="n">
         <v>0</v>
@@ -15232,7 +15239,7 @@
         <v/>
       </c>
       <c r="H179" s="15" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I179" s="16">
         <f>G179*H179</f>
@@ -15659,7 +15666,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>ELE-DPS</t>
+          <t>LUM-DOWNLIGHT12</t>
         </is>
       </c>
       <c r="B185" s="10" t="inlineStr">
@@ -15669,7 +15676,7 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>Dispositivo de protecao contra surtos</t>
+          <t>Downlight LED embutido 12 W</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
@@ -15678,7 +15685,7 @@
         </is>
       </c>
       <c r="E185" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F185" s="13" t="n">
         <v>0</v>
@@ -15688,7 +15695,7 @@
         <v/>
       </c>
       <c r="H185" s="15" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="I185" s="16">
         <f>G185*H185</f>
@@ -15733,59 +15740,135 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="22" t="n"/>
-      <c r="B186" s="22" t="n"/>
-      <c r="C186" s="23" t="inlineStr">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>ELE-DPS</t>
+        </is>
+      </c>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>eletrica</t>
+        </is>
+      </c>
+      <c r="C186" s="11" t="inlineStr">
+        <is>
+          <t>Dispositivo de protecao contra surtos</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E186" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F186" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" s="14">
+        <f>E186*(1+F186)</f>
+        <v/>
+      </c>
+      <c r="H186" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="I186" s="16">
+        <f>G186*H186</f>
+        <v/>
+      </c>
+      <c r="J186" s="17" t="n"/>
+      <c r="K186" s="17" t="n"/>
+      <c r="L186" s="17" t="n"/>
+      <c r="M186" s="17" t="n"/>
+      <c r="N186" s="17" t="n"/>
+      <c r="O186" s="18">
+        <f>COUNT(J186:N186)</f>
+        <v/>
+      </c>
+      <c r="P186" s="19">
+        <f>IF(O186=0,"",MIN(J186:N186))</f>
+        <v/>
+      </c>
+      <c r="Q186" s="10">
+        <f>IF(O186=0,"",INDEX($J$3:$N$3,MATCH(P186,J186:N186,0)))</f>
+        <v/>
+      </c>
+      <c r="R186" s="16">
+        <f>IF(O186=0,"",AVERAGE(J186:N186))</f>
+        <v/>
+      </c>
+      <c r="S186" s="20">
+        <f>IF(O186&lt;2,"",MAX(J186:N186)/P186)</f>
+        <v/>
+      </c>
+      <c r="T186" s="19">
+        <f>IF(O186=0,"",G186*P186)</f>
+        <v/>
+      </c>
+      <c r="U186" s="21">
+        <f>IF(OR(O186=0,I186=0),"",T186/I186-1)</f>
+        <v/>
+      </c>
+      <c r="V186" s="18">
+        <f>IF(O186=0,"PENDENTE",IF(O186&gt;=5,"COMPLETO","PARCIAL"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="22" t="n"/>
+      <c r="B187" s="22" t="n"/>
+      <c r="C187" s="23" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="D186" s="22" t="n"/>
-      <c r="E186" s="22" t="n"/>
-      <c r="F186" s="22" t="n"/>
-      <c r="G186" s="22" t="n"/>
-      <c r="H186" s="22" t="n"/>
-      <c r="I186" s="24">
-        <f>SUM(I4:I185)</f>
-        <v/>
-      </c>
-      <c r="J186" s="22" t="n"/>
-      <c r="K186" s="22" t="n"/>
-      <c r="L186" s="22" t="n"/>
-      <c r="M186" s="22" t="n"/>
-      <c r="N186" s="22" t="n"/>
-      <c r="O186" s="22" t="n"/>
-      <c r="P186" s="22" t="n"/>
-      <c r="Q186" s="22" t="n"/>
-      <c r="R186" s="22" t="n"/>
-      <c r="S186" s="22" t="n"/>
-      <c r="T186" s="24">
-        <f>SUM(T4:T185)</f>
-        <v/>
-      </c>
-      <c r="U186" s="25">
-        <f>IF(T186=0,"",T186/I186-1)</f>
-        <v/>
-      </c>
-      <c r="V186" s="22" t="n"/>
-    </row>
-    <row r="188">
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>Itens: 182 · linhas cotáveis com especificação completa: 132 · com lacuna a esclarecer com o fornecedor: 121</t>
-        </is>
-      </c>
+      <c r="D187" s="22" t="n"/>
+      <c r="E187" s="22" t="n"/>
+      <c r="F187" s="22" t="n"/>
+      <c r="G187" s="22" t="n"/>
+      <c r="H187" s="22" t="n"/>
+      <c r="I187" s="24">
+        <f>SUM(I4:I186)</f>
+        <v/>
+      </c>
+      <c r="J187" s="22" t="n"/>
+      <c r="K187" s="22" t="n"/>
+      <c r="L187" s="22" t="n"/>
+      <c r="M187" s="22" t="n"/>
+      <c r="N187" s="22" t="n"/>
+      <c r="O187" s="22" t="n"/>
+      <c r="P187" s="22" t="n"/>
+      <c r="Q187" s="22" t="n"/>
+      <c r="R187" s="22" t="n"/>
+      <c r="S187" s="22" t="n"/>
+      <c r="T187" s="24">
+        <f>SUM(T4:T186)</f>
+        <v/>
+      </c>
+      <c r="U187" s="25">
+        <f>IF(T187=0,"",T187/I187-1)</f>
+        <v/>
+      </c>
+      <c r="V187" s="22" t="n"/>
     </row>
     <row r="189">
       <c r="C189" s="2" t="inlineStr">
         <is>
+          <t>Itens: 183 · linhas cotáveis com especificação completa: 133 · com lacuna a esclarecer com o fornecedor: 122</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="C190" s="2" t="inlineStr">
+        <is>
           <t>Passe o mouse sobre a DESCRIÇÃO para ver a especificação completa, as normas e a lacuna de cada item.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:V185"/>
-  <conditionalFormatting sqref="V4:V185">
+  <autoFilter ref="A3:V186"/>
+  <conditionalFormatting sqref="V4:V186">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PENDENTE"</formula>
     </cfRule>
@@ -15796,7 +15879,7 @@
       <formula>"COMPLETO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:U185">
+  <conditionalFormatting sqref="U4:U186">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0.15</formula>
     </cfRule>
@@ -15804,7 +15887,7 @@
       <formula>-0.15</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S185">
+  <conditionalFormatting sqref="S4:S186">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
       <formula>1.5</formula>
     </cfRule>
@@ -15905,7 +15988,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A5,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A5,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D5" s="21">
@@ -15917,7 +16000,7 @@
         <v/>
       </c>
       <c r="F5" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A5,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A5,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G5" s="21">
@@ -15925,7 +16008,7 @@
         <v/>
       </c>
       <c r="H5" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A5,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A5,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I5" s="21">
@@ -15943,7 +16026,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A6,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A6,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D6" s="21">
@@ -15955,7 +16038,7 @@
         <v/>
       </c>
       <c r="F6" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A6,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A6,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G6" s="21">
@@ -15963,7 +16046,7 @@
         <v/>
       </c>
       <c r="H6" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A6,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A6,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I6" s="21">
@@ -15974,14 +16057,14 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C7" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A7,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A7,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D7" s="21">
@@ -15993,7 +16076,7 @@
         <v/>
       </c>
       <c r="F7" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A7,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A7,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G7" s="21">
@@ -16001,7 +16084,7 @@
         <v/>
       </c>
       <c r="H7" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A7,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A7,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I7" s="21">
@@ -16012,14 +16095,14 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B8" s="18" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C8" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A8,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A8,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D8" s="21">
@@ -16031,7 +16114,7 @@
         <v/>
       </c>
       <c r="F8" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A8,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A8,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G8" s="21">
@@ -16039,7 +16122,7 @@
         <v/>
       </c>
       <c r="H8" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A8,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A8,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I8" s="21">
@@ -16054,10 +16137,10 @@
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A9,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A9,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D9" s="21">
@@ -16069,7 +16152,7 @@
         <v/>
       </c>
       <c r="F9" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A9,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A9,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G9" s="21">
@@ -16077,7 +16160,7 @@
         <v/>
       </c>
       <c r="H9" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A9,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A9,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I9" s="21">
@@ -16088,14 +16171,14 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B10" s="18" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C10" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A10,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A10,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D10" s="21">
@@ -16107,7 +16190,7 @@
         <v/>
       </c>
       <c r="F10" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A10,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A10,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G10" s="21">
@@ -16115,7 +16198,7 @@
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A10,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A10,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I10" s="21">
@@ -16126,14 +16209,14 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B11" s="18" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C11" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A11,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A11,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D11" s="21">
@@ -16145,7 +16228,7 @@
         <v/>
       </c>
       <c r="F11" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A11,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A11,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G11" s="21">
@@ -16153,7 +16236,7 @@
         <v/>
       </c>
       <c r="H11" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A11,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A11,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I11" s="21">
@@ -16164,14 +16247,14 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B12" s="18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C12" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A12,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A12,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D12" s="21">
@@ -16183,7 +16266,7 @@
         <v/>
       </c>
       <c r="F12" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A12,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A12,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G12" s="21">
@@ -16191,7 +16274,7 @@
         <v/>
       </c>
       <c r="H12" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A12,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A12,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I12" s="21">
@@ -16209,7 +16292,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A13,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A13,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D13" s="21">
@@ -16221,7 +16304,7 @@
         <v/>
       </c>
       <c r="F13" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A13,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A13,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G13" s="21">
@@ -16229,7 +16312,7 @@
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A13,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A13,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I13" s="21">
@@ -16247,7 +16330,7 @@
         <v>28</v>
       </c>
       <c r="C14" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A14,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A14,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D14" s="21">
@@ -16259,7 +16342,7 @@
         <v/>
       </c>
       <c r="F14" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A14,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A14,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G14" s="21">
@@ -16267,7 +16350,7 @@
         <v/>
       </c>
       <c r="H14" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A14,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A14,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I14" s="21">
@@ -16285,7 +16368,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A15,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A15,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D15" s="21">
@@ -16297,7 +16380,7 @@
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A15,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A15,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G15" s="21">
@@ -16305,7 +16388,7 @@
         <v/>
       </c>
       <c r="H15" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A15,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A15,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I15" s="21">
@@ -16316,14 +16399,14 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C16" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A16,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A16,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D16" s="21">
@@ -16335,7 +16418,7 @@
         <v/>
       </c>
       <c r="F16" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A16,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A16,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G16" s="21">
@@ -16343,7 +16426,7 @@
         <v/>
       </c>
       <c r="H16" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A16,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A16,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I16" s="21">
@@ -16354,14 +16437,14 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C17" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A17,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A17,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D17" s="21">
@@ -16373,7 +16456,7 @@
         <v/>
       </c>
       <c r="F17" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A17,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A17,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G17" s="21">
@@ -16381,7 +16464,7 @@
         <v/>
       </c>
       <c r="H17" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A17,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A17,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I17" s="21">
@@ -16399,7 +16482,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A18,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A18,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D18" s="21">
@@ -16411,7 +16494,7 @@
         <v/>
       </c>
       <c r="F18" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A18,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A18,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G18" s="21">
@@ -16419,7 +16502,7 @@
         <v/>
       </c>
       <c r="H18" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A18,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A18,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I18" s="21">
@@ -16437,7 +16520,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A19,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A19,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D19" s="21">
@@ -16449,7 +16532,7 @@
         <v/>
       </c>
       <c r="F19" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A19,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A19,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G19" s="21">
@@ -16457,7 +16540,7 @@
         <v/>
       </c>
       <c r="H19" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A19,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A19,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I19" s="21">
@@ -16475,7 +16558,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A20,COTAÇÃO!$I$4:$I$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A20,COTAÇÃO!$I$4:$I$186)</f>
         <v/>
       </c>
       <c r="D20" s="21">
@@ -16487,7 +16570,7 @@
         <v/>
       </c>
       <c r="F20" s="27">
-        <f>SUMIF(COTAÇÃO!$B$4:$B$185,$A20,COTAÇÃO!$T$4:$T$185)</f>
+        <f>SUMIF(COTAÇÃO!$B$4:$B$186,$A20,COTAÇÃO!$T$4:$T$186)</f>
         <v/>
       </c>
       <c r="G20" s="21">
@@ -16495,7 +16578,7 @@
         <v/>
       </c>
       <c r="H20" s="18">
-        <f>COUNTIFS(COTAÇÃO!$B$4:$B$185,$A20,COTAÇÃO!$O$4:$O$185,"&gt;0")</f>
+        <f>COUNTIFS(COTAÇÃO!$B$4:$B$186,$A20,COTAÇÃO!$O$4:$O$186,"&gt;0")</f>
         <v/>
       </c>
       <c r="I20" s="21">
@@ -16553,7 +16636,7 @@
         </is>
       </c>
       <c r="C24" s="31" t="n">
-        <v>297.36</v>
+        <v>307.08</v>
       </c>
       <c r="D24" s="32" t="inlineStr">
         <is>
@@ -16668,7 +16751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:I202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16765,11 +16848,11 @@
         </is>
       </c>
       <c r="E4" s="14" t="n">
-        <v>6550</v>
+        <v>6698.1</v>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>perfil formado a frio em barra de 6.000 mm; aco ZAR 230, fy 230 MPa, fu 310 MPa; revestimento Z275; massa BRUTA, ja com a perda de corte (10.9 %)</t>
+          <t>perfil formado a frio em barra de 6.000 mm; aco ZAR 230, fy 230 MPa, fu 310 MPa; revestimento Z275; massa BRUTA, ja com a perda de corte (11.1 %)</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
@@ -16806,7 +16889,7 @@
         </is>
       </c>
       <c r="E5" s="14" t="n">
-        <v>970.1</v>
+        <v>1037.9</v>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
@@ -16847,7 +16930,7 @@
         </is>
       </c>
       <c r="E6" s="14" t="n">
-        <v>184.3</v>
+        <v>157.7</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
@@ -16888,7 +16971,7 @@
         </is>
       </c>
       <c r="E7" s="14" t="n">
-        <v>276.1</v>
+        <v>329.4</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
@@ -16929,7 +17012,7 @@
         </is>
       </c>
       <c r="E8" s="14" t="n">
-        <v>426.4</v>
+        <v>489.5</v>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
@@ -16970,7 +17053,7 @@
         </is>
       </c>
       <c r="E9" s="14" t="n">
-        <v>276.1</v>
+        <v>329.4</v>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
@@ -17052,7 +17135,7 @@
         </is>
       </c>
       <c r="E11" s="14" t="n">
-        <v>117.4</v>
+        <v>127.1</v>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
@@ -17093,7 +17176,7 @@
         </is>
       </c>
       <c r="E12" s="14" t="n">
-        <v>1074.4</v>
+        <v>1191.6</v>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
@@ -17134,7 +17217,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>165.4</v>
+        <v>178.3</v>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
@@ -17175,7 +17258,7 @@
         </is>
       </c>
       <c r="E14" s="14" t="n">
-        <v>370.8</v>
+        <v>394.2</v>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
@@ -17216,7 +17299,7 @@
         </is>
       </c>
       <c r="E15" s="14" t="n">
-        <v>885.5</v>
+        <v>958.8</v>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
@@ -17261,7 +17344,7 @@
         </is>
       </c>
       <c r="E16" s="14" t="n">
-        <v>136.8</v>
+        <v>147</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
@@ -17302,7 +17385,7 @@
         </is>
       </c>
       <c r="E17" s="14" t="n">
-        <v>83.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
@@ -17343,7 +17426,7 @@
         </is>
       </c>
       <c r="E18" s="14" t="n">
-        <v>38.1</v>
+        <v>43.7</v>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
@@ -17384,7 +17467,7 @@
         </is>
       </c>
       <c r="E19" s="14" t="n">
-        <v>11271</v>
+        <v>12666</v>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
@@ -17425,7 +17508,7 @@
         </is>
       </c>
       <c r="E20" s="14" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
@@ -17466,7 +17549,7 @@
         </is>
       </c>
       <c r="E21" s="14" t="n">
-        <v>885.5</v>
+        <v>958.8</v>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
@@ -17511,7 +17594,7 @@
         </is>
       </c>
       <c r="E22" s="14" t="n">
-        <v>160.8</v>
+        <v>147</v>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
@@ -17552,7 +17635,7 @@
         </is>
       </c>
       <c r="E23" s="14" t="n">
-        <v>80.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
@@ -17667,7 +17750,7 @@
         </is>
       </c>
       <c r="E26" s="14" t="n">
-        <v>737</v>
+        <v>630</v>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
@@ -17708,7 +17791,7 @@
         </is>
       </c>
       <c r="E27" s="14" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
@@ -17876,7 +17959,7 @@
         </is>
       </c>
       <c r="E31" s="14" t="n">
-        <v>25.92</v>
+        <v>24.48</v>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
@@ -18642,7 +18725,7 @@
         </is>
       </c>
       <c r="E49" s="14" t="n">
-        <v>2474</v>
+        <v>2806</v>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
@@ -18683,7 +18766,7 @@
         </is>
       </c>
       <c r="E50" s="14" t="n">
-        <v>1396.4</v>
+        <v>1553.1</v>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
@@ -18705,7 +18788,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>MEP-FRIGO</t>
+          <t>FIX-06</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -18715,38 +18798,34 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Linha frigorigena</t>
+          <t>Bucha passa-fio 25 mm (montante atravessado)</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E51" s="14" t="n">
-        <v>56</v>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>tubo, conexao ou condutor conforme descricao</t>
-        </is>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
-        <is>
-          <t>NBR 5410, NBR 5626, NBR 8160</t>
-        </is>
-      </c>
-      <c r="H51" s="11" t="inlineStr"/>
+        <v>2929</v>
+      </c>
+      <c r="F51" s="11" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr"/>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
+        </is>
+      </c>
       <c r="I51" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>FIX-06</t>
+          <t>MEP-FRIGO</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -18756,27 +18835,31 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>Bucha passa-fio 25 mm (montante atravessado)</t>
+          <t>Linha frigorigena</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E52" s="14" t="n">
-        <v>2580</v>
-      </c>
-      <c r="F52" s="11" t="inlineStr"/>
-      <c r="G52" s="11" t="inlineStr"/>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>o modelo nao sabe descrever este item para um fornecedor</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>tubo, conexao ou condutor conforme descricao</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>NBR 5410, NBR 5626, NBR 8160</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr"/>
       <c r="I52" s="18" t="inlineStr">
         <is>
-          <t>com lacuna</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -18802,7 +18885,7 @@
         </is>
       </c>
       <c r="E53" s="14" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
@@ -18824,7 +18907,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>MEP-ESGO40</t>
+          <t>MEP-ESGO50</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -18834,7 +18917,7 @@
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Tubo esgoto DN40</t>
+          <t>Tubo esgoto DN50</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -18843,11 +18926,11 @@
         </is>
       </c>
       <c r="E54" s="14" t="n">
-        <v>62.2</v>
+        <v>81</v>
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>tubo, conexao ou condutor conforme descricao; DN40</t>
+          <t>tubo, conexao ou condutor conforme descricao; DN50</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -18865,7 +18948,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>MEP-ESGO50</t>
+          <t>FIX-13</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -18875,38 +18958,34 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Tubo esgoto DN50</t>
+          <t>Clip de eletroduto no montante (a cada 1.200 mm)</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E55" s="14" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>tubo, conexao ou condutor conforme descricao; DN50</t>
-        </is>
-      </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>NBR 5410, NBR 5626, NBR 8160</t>
-        </is>
-      </c>
-      <c r="H55" s="11" t="inlineStr"/>
+        <v>1921</v>
+      </c>
+      <c r="F55" s="11" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr"/>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
+        </is>
+      </c>
       <c r="I55" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>FIX-13</t>
+          <t>MEP-ISOL</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -18916,34 +18995,38 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Clip de eletroduto no montante (a cada 1.200 mm)</t>
+          <t>Isolamento de linha</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E56" s="14" t="n">
-        <v>1746</v>
-      </c>
-      <c r="F56" s="11" t="inlineStr"/>
-      <c r="G56" s="11" t="inlineStr"/>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>o modelo nao sabe descrever este item para um fornecedor</t>
-        </is>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>tubo, conexao ou condutor conforme descricao</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>NBR 5410, NBR 5626, NBR 8160</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr"/>
       <c r="I56" s="18" t="inlineStr">
         <is>
-          <t>com lacuna</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>MEP-ISOL</t>
+          <t>MEP-DISJ</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -18953,16 +19036,16 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Isolamento de linha</t>
+          <t>Disjuntor</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E57" s="14" t="n">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
@@ -18984,7 +19067,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>MEP-DISJ</t>
+          <t>FIX-10</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -18994,7 +19077,7 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Disjuntor</t>
+          <t>Caixa de passagem</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -19003,29 +19086,25 @@
         </is>
       </c>
       <c r="E58" s="14" t="n">
-        <v>37</v>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>tubo, conexao ou condutor conforme descricao</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>NBR 5410, NBR 5626, NBR 8160</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr"/>
+        <v>147</v>
+      </c>
+      <c r="F58" s="11" t="inlineStr"/>
+      <c r="G58" s="11" t="inlineStr"/>
+      <c r="H58" s="11" t="inlineStr">
+        <is>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
+        </is>
+      </c>
       <c r="I58" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>MEP-PEX20</t>
+          <t>MEP-ESGO75</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -19035,7 +19114,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Tubo PEX DN20 agua fria, pela parede a 400 mm</t>
+          <t>Tubo esgoto DN75</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -19044,11 +19123,11 @@
         </is>
       </c>
       <c r="E59" s="14" t="n">
-        <v>121.5</v>
+        <v>50.2</v>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>tubo, conexao ou condutor conforme descricao; DN20</t>
+          <t>tubo, conexao ou condutor conforme descricao; DN75</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -19066,7 +19145,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>FIX-10</t>
+          <t>MEP-PEX20</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -19076,34 +19155,38 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Caixa de passagem</t>
+          <t>Tubo PEX DN20 agua fria, pela parede a 400 mm</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E60" s="14" t="n">
-        <v>130</v>
-      </c>
-      <c r="F60" s="11" t="inlineStr"/>
-      <c r="G60" s="11" t="inlineStr"/>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>o modelo nao sabe descrever este item para um fornecedor</t>
-        </is>
-      </c>
+        <v>124.2</v>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>tubo, conexao ou condutor conforme descricao; DN20</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>NBR 5410, NBR 5626, NBR 8160</t>
+        </is>
+      </c>
+      <c r="H60" s="11" t="inlineStr"/>
       <c r="I60" s="18" t="inlineStr">
         <is>
-          <t>com lacuna</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>MEP-ESGO75</t>
+          <t>MEP-ESGO40</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -19113,7 +19196,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Tubo esgoto DN75</t>
+          <t>Tubo esgoto DN40</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -19122,11 +19205,11 @@
         </is>
       </c>
       <c r="E61" s="14" t="n">
-        <v>38.3</v>
+        <v>46.7</v>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>tubo, conexao ou condutor conforme descricao; DN75</t>
+          <t>tubo, conexao ou condutor conforme descricao; DN40</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -19163,7 +19246,7 @@
         </is>
       </c>
       <c r="E62" s="14" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
@@ -19204,7 +19287,7 @@
         </is>
       </c>
       <c r="E63" s="14" t="n">
-        <v>39.8</v>
+        <v>42</v>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
@@ -19245,7 +19328,7 @@
         </is>
       </c>
       <c r="E64" s="14" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
       <c r="G64" s="11" t="inlineStr"/>
@@ -19319,7 +19402,7 @@
         </is>
       </c>
       <c r="E66" s="14" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
       <c r="G66" s="11" t="inlineStr"/>
@@ -19356,7 +19439,7 @@
         </is>
       </c>
       <c r="E67" s="14" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
       <c r="G67" s="11" t="inlineStr"/>
@@ -19374,7 +19457,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>MEP-DRENO</t>
+          <t>FIX-01</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -19384,38 +19467,34 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>Dreno de condensado</t>
+          <t>Abracadeira de eletroduto no forro/entrepiso (a cada 1.000 mm)</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E68" s="14" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>tubo, conexao ou condutor conforme descricao</t>
-        </is>
-      </c>
-      <c r="G68" s="11" t="inlineStr">
-        <is>
-          <t>NBR 5410, NBR 5626, NBR 8160</t>
-        </is>
-      </c>
-      <c r="H68" s="11" t="inlineStr"/>
+        <v>162</v>
+      </c>
+      <c r="F68" s="11" t="inlineStr"/>
+      <c r="G68" s="11" t="inlineStr"/>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
+        </is>
+      </c>
       <c r="I68" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>FIX-01</t>
+          <t>MEP-DRENO</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -19425,27 +19504,31 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Abracadeira de eletroduto no forro/entrepiso (a cada 1.000 mm)</t>
+          <t>Dreno de condensado</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E69" s="14" t="n">
-        <v>161</v>
-      </c>
-      <c r="F69" s="11" t="inlineStr"/>
-      <c r="G69" s="11" t="inlineStr"/>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>o modelo nao sabe descrever este item para um fornecedor</t>
-        </is>
-      </c>
+        <v>44.8</v>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>tubo, conexao ou condutor conforme descricao</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>NBR 5410, NBR 5626, NBR 8160</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr"/>
       <c r="I69" s="18" t="inlineStr">
         <is>
-          <t>com lacuna</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19572,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>FIX-02</t>
+          <t>FIX-08</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -19499,7 +19582,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Abracadeira de linha frigorigena (a cada 1,0 m)</t>
+          <t>Caixa 4x4</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -19508,7 +19591,7 @@
         </is>
       </c>
       <c r="E71" s="14" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr"/>
@@ -19526,7 +19609,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>FIX-08</t>
+          <t>FIX-02</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -19536,7 +19619,7 @@
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>Caixa 4x4</t>
+          <t>Abracadeira de linha frigorigena (a cada 1,0 m)</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -19545,7 +19628,7 @@
         </is>
       </c>
       <c r="E72" s="14" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr"/>
@@ -19582,7 +19665,7 @@
         </is>
       </c>
       <c r="E73" s="14" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
       <c r="G73" s="11" t="inlineStr"/>
@@ -19619,7 +19702,7 @@
         </is>
       </c>
       <c r="E74" s="14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
       <c r="G74" s="11" t="inlineStr"/>
@@ -19693,7 +19776,7 @@
         </is>
       </c>
       <c r="E76" s="14" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
       <c r="G76" s="11" t="inlineStr"/>
@@ -19730,7 +19813,7 @@
         </is>
       </c>
       <c r="E77" s="14" t="n">
-        <v>6070</v>
+        <v>6524</v>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
@@ -19771,7 +19854,7 @@
         </is>
       </c>
       <c r="E78" s="14" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
@@ -19812,7 +19895,7 @@
         </is>
       </c>
       <c r="E79" s="14" t="n">
-        <v>155.4</v>
+        <v>217.3</v>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
@@ -19857,7 +19940,7 @@
         </is>
       </c>
       <c r="E80" s="14" t="n">
-        <v>279</v>
+        <v>375</v>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
       <c r="G80" s="11" t="inlineStr"/>
@@ -19894,7 +19977,7 @@
         </is>
       </c>
       <c r="E81" s="14" t="n">
-        <v>192</v>
+        <v>183.4</v>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
@@ -19935,7 +20018,7 @@
         </is>
       </c>
       <c r="E82" s="14" t="n">
-        <v>192</v>
+        <v>183.4</v>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
@@ -19957,7 +20040,7 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>BRI-MEC</t>
+          <t>FAC-JUNTA-SECA</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -19967,34 +20050,38 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Mecanismo de brise movel: guia, roldana e trava</t>
+          <t>Junta seca: perfil EPDM e fundo de junta</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>cj</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E83" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F83" s="11" t="inlineStr"/>
-      <c r="G83" s="11" t="inlineStr"/>
-      <c r="H83" s="11" t="inlineStr">
-        <is>
-          <t>o modelo nao sabe descrever este item para um fornecedor</t>
-        </is>
-      </c>
+        <v>271.7</v>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>sistema de fachada sobre placa cimenticia: basecoat com tela de fibra de vidro alcali-resistente, junta com selante PU, acabamento acrilico elastomerico LISO com biocida — faixa ate 2.600 mm e face interna da platibanda</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>NBR 13245, NBR 15498</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr"/>
       <c r="I83" s="18" t="inlineStr">
         <is>
-          <t>com lacuna</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>FAC-JUNTA-SECA</t>
+          <t>BRI-MEC</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -20004,31 +20091,27 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>Junta seca: perfil EPDM e fundo de junta</t>
+          <t>Mecanismo de brise movel: guia, roldana e trava</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>cj</t>
         </is>
       </c>
       <c r="E84" s="14" t="n">
-        <v>194.3</v>
-      </c>
-      <c r="F84" s="11" t="inlineStr">
-        <is>
-          <t>sistema de fachada sobre placa cimenticia: basecoat com tela de fibra de vidro alcali-resistente, junta com selante PU, acabamento acrilico elastomerico LISO com biocida — faixa ate 2.600 mm e face interna da platibanda</t>
-        </is>
-      </c>
-      <c r="G84" s="11" t="inlineStr">
-        <is>
-          <t>NBR 13245, NBR 15498</t>
-        </is>
-      </c>
-      <c r="H84" s="11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F84" s="11" t="inlineStr"/>
+      <c r="G84" s="11" t="inlineStr"/>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
+        </is>
+      </c>
       <c r="I84" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20137,7 @@
         </is>
       </c>
       <c r="E85" s="14" t="n">
-        <v>54.8</v>
+        <v>52.4</v>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
@@ -20095,7 +20178,7 @@
         </is>
       </c>
       <c r="E86" s="14" t="n">
-        <v>239.9</v>
+        <v>229.3</v>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
@@ -20117,7 +20200,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>FAC-TELA</t>
+          <t>BRI-TRAV</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -20127,38 +20210,34 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Tela de fibra de vidro alcali-resistente, embutida no basecoat</t>
+          <t>Travessa de brise: U 50x25x1,2 aluminio</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E87" s="14" t="n">
-        <v>211.2</v>
-      </c>
-      <c r="F87" s="11" t="inlineStr">
-        <is>
-          <t>sistema de fachada sobre placa cimenticia: basecoat com tela de fibra de vidro alcali-resistente, junta com selante PU, acabamento acrilico elastomerico LISO com biocida — faixa ate 2.600 mm e face interna da platibanda</t>
-        </is>
-      </c>
-      <c r="G87" s="11" t="inlineStr">
-        <is>
-          <t>NBR 13245, NBR 15498</t>
-        </is>
-      </c>
-      <c r="H87" s="11" t="inlineStr"/>
+        <v>51.6</v>
+      </c>
+      <c r="F87" s="11" t="inlineStr"/>
+      <c r="G87" s="11" t="inlineStr"/>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>o modelo nao sabe descrever este item para um fornecedor</t>
+        </is>
+      </c>
       <c r="I87" s="18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>com lacuna</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>BRI-TRAV</t>
+          <t>FAC-TELA</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -20168,27 +20247,31 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>Travessa de brise: U 50x25x1,2 aluminio</t>
+          <t>Tela de fibra de vidro alcali-resistente, embutida no basecoat</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="F88" s="11" t="inlineStr"/>
-      <c r="G88" s="11" t="inlineStr"/>
-      <c r="H88" s="11" t="inlineStr">
-        <is>
-          <t>o modelo nao sabe descrever este item para um fornecedor</t>
-        </is>
-      </c>
+        <v>201.8</v>
+      </c>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>sistema de fachada sobre placa cimenticia: basecoat com tela de fibra de vidro alcali-resistente, junta com selante PU, acabamento acrilico elastomerico LISO com biocida — faixa ate 2.600 mm e face interna da platibanda</t>
+        </is>
+      </c>
+      <c r="G88" s="11" t="inlineStr">
+        <is>
+          <t>NBR 13245, NBR 15498</t>
+        </is>
+      </c>
+      <c r="H88" s="11" t="inlineStr"/>
       <c r="I88" s="18" t="inlineStr">
         <is>
-          <t>com lacuna</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -20214,7 +20297,7 @@
         </is>
       </c>
       <c r="E89" s="14" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
       <c r="G89" s="11" t="inlineStr"/>
@@ -20251,7 +20334,7 @@
         </is>
       </c>
       <c r="E90" s="14" t="n">
-        <v>3118</v>
+        <v>2917</v>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
       <c r="G90" s="11" t="inlineStr"/>
@@ -20510,7 +20593,7 @@
         </is>
       </c>
       <c r="E97" s="14" t="n">
-        <v>249.5</v>
+        <v>233.4</v>
       </c>
       <c r="F97" s="11" t="inlineStr"/>
       <c r="G97" s="11" t="inlineStr"/>
@@ -20787,7 +20870,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>EXT-GRAUTE</t>
+          <t>EXT-PISC-FILTRO</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -20797,16 +20880,16 @@
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Graute de cinta e pilarete do muro</t>
+          <t>Piscina: filtro de areia DE 500 mm com valvula seletora</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E105" s="14" t="n">
-        <v>2.99</v>
+        <v>1</v>
       </c>
       <c r="F105" s="11" t="inlineStr"/>
       <c r="G105" s="11" t="inlineStr"/>
@@ -20824,7 +20907,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-FILTRO</t>
+          <t>EXT-PISC-IMP</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -20834,16 +20917,16 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>Piscina: filtro de areia DE 500 mm com valvula seletora</t>
+          <t>Piscina: impermeabilizacao (cristalizante + polimerica)</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
-        <v>1</v>
+        <v>30.43</v>
       </c>
       <c r="F106" s="11" t="inlineStr"/>
       <c r="G106" s="11" t="inlineStr"/>
@@ -20861,7 +20944,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-IMP</t>
+          <t>EXT-GRAUTE</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -20871,16 +20954,16 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Piscina: impermeabilizacao (cristalizante + polimerica)</t>
+          <t>Graute de cinta e pilarete do muro</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E107" s="14" t="n">
-        <v>30.43</v>
+        <v>2.8</v>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
       <c r="G107" s="11" t="inlineStr"/>
@@ -21287,7 +21370,7 @@
         </is>
       </c>
       <c r="E118" s="14" t="n">
-        <v>844.7</v>
+        <v>927.5</v>
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
@@ -21328,7 +21411,7 @@
         </is>
       </c>
       <c r="E119" s="14" t="n">
-        <v>50</v>
+        <v>54.6</v>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
@@ -21410,7 +21493,7 @@
         </is>
       </c>
       <c r="E121" s="14" t="n">
-        <v>355.6</v>
+        <v>366.3</v>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
@@ -21455,7 +21538,7 @@
         </is>
       </c>
       <c r="E122" s="14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
@@ -21500,7 +21583,7 @@
         </is>
       </c>
       <c r="E123" s="14" t="n">
-        <v>640.8</v>
+        <v>701.7</v>
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
@@ -21717,7 +21800,7 @@
         </is>
       </c>
       <c r="E128" s="14" t="n">
-        <v>511.1</v>
+        <v>521.8</v>
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
@@ -21743,36 +21826,40 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>MAR-PRAT</t>
+          <t>FV-INVERSOR</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Prateleira aberta, por metro de prateleira</t>
+          <t>Inversor string 15 kW, trifasico 220 V</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kW</t>
         </is>
       </c>
       <c r="E129" s="14" t="n">
-        <v>35.19</v>
+        <v>15</v>
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G129" s="11" t="inlineStr"/>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+        </is>
+      </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
         </is>
       </c>
       <c r="I129" s="18" t="inlineStr">
@@ -21784,40 +21871,36 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>FV-INSTAL</t>
+          <t>MAR-PRAT</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>Instalacao e comissionamento</t>
+          <t>Prateleira aberta, por metro de prateleira</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>kWp</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
-        <v>15.95</v>
+        <v>35.19</v>
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
-        </is>
-      </c>
-      <c r="G130" s="11" t="inlineStr">
-        <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G130" s="11" t="inlineStr"/>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I130" s="18" t="inlineStr">
@@ -21829,36 +21912,40 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>MAR-TAMPO</t>
+          <t>FV-INSTAL</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Tampo de bancada (quartzo/granito)</t>
+          <t>Instalacao e comissionamento</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>kWp</t>
         </is>
       </c>
       <c r="E131" s="14" t="n">
-        <v>6.84</v>
+        <v>16.5</v>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
-        </is>
-      </c>
-      <c r="G131" s="11" t="inlineStr"/>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+        </is>
+      </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
         </is>
       </c>
       <c r="I131" s="18" t="inlineStr">
@@ -21870,17 +21957,17 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>FV-ESTRUTURA</t>
+          <t>MAR-TAMPO</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>Estrutura de fixacao em aluminio sobre terca</t>
+          <t>Tampo de bancada (quartzo/granito)</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -21889,21 +21976,17 @@
         </is>
       </c>
       <c r="E132" s="14" t="n">
-        <v>86.2</v>
+        <v>6.84</v>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
-        </is>
-      </c>
-      <c r="G132" s="11" t="inlineStr">
-        <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
-        </is>
-      </c>
+          <t>marcenaria sob medida conforme planta de layout; MDF 18 mm com acabamento em laminado ou pintura PU; ferragem com amortecedor</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr"/>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>desenho executivo de marcenaria: a planta da a extensao e a profundidade, nao o interior do movel</t>
         </is>
       </c>
       <c r="I132" s="18" t="inlineStr">
@@ -21915,38 +21998,42 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>PIN-TINTA</t>
+          <t>FV-ESTRUTURA</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
+          <t>Estrutura de fixacao em aluminio sobre terca</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E133" s="14" t="n">
-        <v>179.6</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>NBR 11702, NBR 13245</t>
-        </is>
-      </c>
-      <c r="H133" s="11" t="inlineStr"/>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+        </is>
+      </c>
       <c r="I133" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -21975,7 +22062,7 @@
         </is>
       </c>
       <c r="E134" s="14" t="n">
-        <v>220.9</v>
+        <v>241.9</v>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
@@ -22001,42 +22088,38 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>FV-INVERSOR</t>
+          <t>PIN-TINTA</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Inversor string 12 kW, trifasico 220 V</t>
+          <t>Tinta latex (2 demaos, rendimento 10 m2/L)</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E135" s="14" t="n">
-        <v>12</v>
+        <v>193.7</v>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+          <t>tinta e mao de obra conforme especificacao de acabamento; 2 demaos sobre selador; rendimento declarado na quantidade</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
-        </is>
-      </c>
-      <c r="H135" s="11" t="inlineStr">
-        <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
-        </is>
-      </c>
+          <t>NBR 11702, NBR 13245</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr"/>
       <c r="I135" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -22106,7 +22189,7 @@
         </is>
       </c>
       <c r="E137" s="14" t="n">
-        <v>257</v>
+        <v>266.8</v>
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
@@ -22173,7 +22256,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>SPD-CAPTOR</t>
+          <t>LUM-DOWNLIGHT18</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -22183,30 +22266,30 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
+          <t>Downlight LED embutido 18 W</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E139" s="14" t="n">
-        <v>160.8</v>
+        <v>45</v>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
         </is>
       </c>
       <c r="I139" s="18" t="inlineStr">
@@ -22218,7 +22301,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>LUM-DOWNLIGHT18</t>
+          <t>SPD-CAPTOR</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -22228,30 +22311,30 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>Downlight LED embutido 18 W</t>
+          <t>Captor: cabo de aluminio 70 mm2 no perimetro da cobertura</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="F140" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>SPDA conforme NBR 5419-3, classe IV: captor em anel no perimetro da cobertura, descidas naturais pela estrutura de aco com continuidade ensaiada, anel de aterramento no radier</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+          <t>NBR 5410, NBR 5419-3, NBR 5419-4</t>
         </is>
       </c>
       <c r="H140" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+          <t>laudo de continuidade eletrica da estrutura e medicao de resistencia de aterramento apos a execucao</t>
         </is>
       </c>
       <c r="I140" s="18" t="inlineStr">
@@ -22413,7 +22496,7 @@
         </is>
       </c>
       <c r="E144" s="14" t="n">
-        <v>511.1</v>
+        <v>521.8</v>
       </c>
       <c r="F144" s="11" t="inlineStr">
         <is>
@@ -22791,17 +22874,17 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>EQP-PORTAO</t>
+          <t>ELE-TUG</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Automatizador de portao de correr</t>
+          <t>Tomada 2P+T 10 A com placa</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
@@ -22810,19 +22893,19 @@
         </is>
       </c>
       <c r="E153" s="14" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
-          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
-        </is>
-      </c>
-      <c r="G153" s="11" t="inlineStr"/>
-      <c r="H153" s="11" t="inlineStr">
-        <is>
-          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
-        </is>
-      </c>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+        </is>
+      </c>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H153" s="11" t="inlineStr"/>
       <c r="I153" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -22832,17 +22915,17 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>MET-ACESS</t>
+          <t>EQP-PORTAO</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
+          <t>Automatizador de portao de correr</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
@@ -22851,21 +22934,17 @@
         </is>
       </c>
       <c r="E154" s="14" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F154" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
-        </is>
-      </c>
-      <c r="G154" s="11" t="inlineStr">
-        <is>
-          <t>NBR 15097, NBR 15705</t>
-        </is>
-      </c>
+          <t>equipamento novo, com garantia de fabrica e instalacao por credenciado</t>
+        </is>
+      </c>
+      <c r="G154" s="11" t="inlineStr"/>
       <c r="H154" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo: a capacidade esta dimensionada, a escolha do equipamento e do proprietario</t>
         </is>
       </c>
       <c r="I154" s="18" t="inlineStr">
@@ -22877,17 +22956,17 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>ELE-TUG</t>
+          <t>MET-ACESS</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Tomada 2P+T 10 A com placa</t>
+          <t>Acessorios (papeleira, cabide, saboneteira, toalheiro)</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
@@ -22896,19 +22975,23 @@
         </is>
       </c>
       <c r="E155" s="14" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="F155" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H155" s="11" t="inlineStr"/>
+          <t>NBR 15097, NBR 15705</t>
+        </is>
+      </c>
+      <c r="H155" s="11" t="inlineStr">
+        <is>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+        </is>
+      </c>
       <c r="I155" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -22937,7 +23020,7 @@
         </is>
       </c>
       <c r="E156" s="14" t="n">
-        <v>74.8</v>
+        <v>80.7</v>
       </c>
       <c r="F156" s="11" t="inlineStr">
         <is>
@@ -23536,7 +23619,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>LUM-PENDENTE40</t>
+          <t>ELE-INT</t>
         </is>
       </c>
       <c r="B170" s="10" t="inlineStr">
@@ -23546,7 +23629,7 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>Pendente LED de pe-direito duplo, 40 W</t>
+          <t>Interruptor simples e paralelo com placa</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
@@ -23555,23 +23638,19 @@
         </is>
       </c>
       <c r="E170" s="14" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F170" s="11" t="inlineStr">
         <is>
-          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr">
         <is>
-          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
-        </is>
-      </c>
-      <c r="H170" s="11" t="inlineStr">
-        <is>
-          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
-        </is>
-      </c>
+          <t>NBR 14136, NBR 5410</t>
+        </is>
+      </c>
+      <c r="H170" s="11" t="inlineStr"/>
       <c r="I170" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -23581,7 +23660,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>ELE-INT</t>
+          <t>LUM-PENDENTE40</t>
         </is>
       </c>
       <c r="B171" s="10" t="inlineStr">
@@ -23591,7 +23670,7 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>Interruptor simples e paralelo com placa</t>
+          <t>Pendente LED de pe-direito duplo, 40 W</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
@@ -23600,19 +23679,23 @@
         </is>
       </c>
       <c r="E171" s="14" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F171" s="11" t="inlineStr">
         <is>
-          <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>NBR 14136, NBR 5410</t>
-        </is>
-      </c>
-      <c r="H171" s="11" t="inlineStr"/>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+        </is>
+      </c>
+      <c r="H171" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+        </is>
+      </c>
       <c r="I171" s="18" t="inlineStr">
         <is>
           <t>sim</t>
@@ -23798,40 +23881,40 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>FV-CABO</t>
+          <t>LOU-TANQUE</t>
         </is>
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>eletrica</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
+          <t>Tanque de lavanderia</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E176" s="14" t="n">
-        <v>46.3</v>
+        <v>2</v>
       </c>
       <c r="F176" s="11" t="inlineStr">
         <is>
-          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
+          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
-          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
+          <t>NBR 15097, NBR 15705</t>
         </is>
       </c>
       <c r="H176" s="11" t="inlineStr">
         <is>
-          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
+          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
         </is>
       </c>
       <c r="I176" s="18" t="inlineStr">
@@ -23843,7 +23926,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>LOU-TANQUE</t>
+          <t>MET-TORN-T</t>
         </is>
       </c>
       <c r="B177" s="10" t="inlineStr">
@@ -23853,7 +23936,7 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>Tanque de lavanderia</t>
+          <t>Torneira de tanque e de jardim</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
@@ -23862,7 +23945,7 @@
         </is>
       </c>
       <c r="E177" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F177" s="11" t="inlineStr">
         <is>
@@ -23888,7 +23971,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>MET-TORN-T</t>
+          <t>MET-ENGATE</t>
         </is>
       </c>
       <c r="B178" s="10" t="inlineStr">
@@ -23898,7 +23981,7 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>Torneira de tanque e de jardim</t>
+          <t>Engate flexivel</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
@@ -23907,7 +23990,7 @@
         </is>
       </c>
       <c r="E178" s="14" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F178" s="11" t="inlineStr">
         <is>
@@ -23933,40 +24016,40 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>MET-ENGATE</t>
+          <t>FV-CABO</t>
         </is>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>eletrica</t>
         </is>
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>Engate flexivel</t>
+          <t>Cabo solar 6 mm2 e eletroduto ate o inversor</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E179" s="14" t="n">
-        <v>27</v>
+        <v>40.3</v>
       </c>
       <c r="F179" s="11" t="inlineStr">
         <is>
-          <t>louca / metal sanitario de linha comercial, cor branca para louca e acabamento cromado para metal; quantidade contada das pecas LOCADAS em planta, nao estimada por comodo</t>
+          <t>sistema fotovoltaico conectado a rede (on-grid), microgeracao REN ANEEL 1.000/2021; modulos monocristalinos, inversor string trifasico com monitoramento</t>
         </is>
       </c>
       <c r="G179" s="11" t="inlineStr">
         <is>
-          <t>NBR 15097, NBR 15705</t>
+          <t>NBR 16274, NBR 16690, Portaria INMETRO 140/2022</t>
         </is>
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>linha e fabricante: louca e metal sao decisao de acabamento do proprietario, e a mesma peca varia 3x de preco entre linhas</t>
+          <t>marca e modelo de modulo e inversor; a potencia e a area estao dimensionadas, o produto e cotacao</t>
         </is>
       </c>
       <c r="I179" s="18" t="inlineStr">
@@ -24203,129 +24286,144 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
+          <t>LUM-DOWNLIGHT12</t>
+        </is>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
+        <is>
+          <t>eletrica</t>
+        </is>
+      </c>
+      <c r="C185" s="11" t="inlineStr">
+        <is>
+          <t>Downlight LED embutido 12 W</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="E185" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F185" s="11" t="inlineStr">
+        <is>
+          <t>luminaria LED de linha, IRC &gt;= 80 (&gt;= 90 no closet), eficacia &gt;= 80 lm/W, driver com garantia &gt;= 3 anos; temperatura de cor por ambiente conforme o quadro luminotecnico: 2.700 K intimo, 3.000 K social, 4.000 K tarefa; quantidade pelo METODO DOS LUMENS por ambiente e malha de uniformidade (SHR 1,2); tarefa contada das pecas</t>
+        </is>
+      </c>
+      <c r="G185" s="11" t="inlineStr">
+        <is>
+          <t>NBR ISO/CIE 8995-1, Portaria INMETRO 20/2017 (LED)</t>
+        </is>
+      </c>
+      <c r="H185" s="11" t="inlineStr">
+        <is>
+          <t>marca e modelo: o fluxo e a potencia de cada tipo estao declarados; o produto e escolha de acabamento</t>
+        </is>
+      </c>
+      <c r="I185" s="18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
           <t>ELE-DPS</t>
         </is>
       </c>
-      <c r="B185" s="10" t="inlineStr">
+      <c r="B186" s="10" t="inlineStr">
         <is>
           <t>eletrica</t>
         </is>
       </c>
-      <c r="C185" s="11" t="inlineStr">
+      <c r="C186" s="11" t="inlineStr">
         <is>
           <t>Dispositivo de protecao contra surtos</t>
         </is>
       </c>
-      <c r="D185" s="10" t="inlineStr">
+      <c r="D186" s="10" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E185" s="14" t="n">
+      <c r="E186" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F185" s="11" t="inlineStr">
+      <c r="F186" s="11" t="inlineStr">
         <is>
           <t>dispositivo de embutir em caixa 4x2 / 4x4, linha unica em toda a casa; tensao 127 V para TUG e 220 V para TUE, conforme esquema declarado no projeto</t>
         </is>
       </c>
-      <c r="G185" s="11" t="inlineStr">
+      <c r="G186" s="11" t="inlineStr">
         <is>
           <t>NBR 14136, NBR 5410</t>
         </is>
       </c>
-      <c r="H185" s="11" t="inlineStr"/>
-      <c r="I185" s="18" t="inlineStr">
+      <c r="H186" s="11" t="inlineStr"/>
+      <c r="I186" s="18" t="inlineStr">
         <is>
           <t>sim</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="3" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
         <is>
           <t>ROTA ALTERNATIVA — peça cortada e furada em vez de barra</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>Estes itens NÃO entram no total: são a mesma estrutura comprada pronta. Cotar os dois e comparar contra o custo de corte próprio.</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="26" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="26" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="B189" s="26" t="inlineStr">
+      <c r="B190" s="26" t="inlineStr">
         <is>
           <t>DESCRIÇÃO</t>
         </is>
       </c>
-      <c r="C189" s="26" t="inlineStr">
+      <c r="C190" s="26" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="D189" s="26" t="inlineStr">
+      <c r="D190" s="26" t="inlineStr">
         <is>
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E189" s="26" t="inlineStr">
+      <c r="E190" s="26" t="inlineStr">
         <is>
           <t>ESPECIFICAÇÃO</t>
         </is>
       </c>
-      <c r="F189" s="26" t="inlineStr">
+      <c r="F190" s="26" t="inlineStr">
         <is>
           <t>NORMAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="9" t="inlineStr">
-        <is>
-          <t>PF-Ue 90x40x12x0,95</t>
-        </is>
-      </c>
-      <c r="B190" s="11" t="inlineStr">
-        <is>
-          <t>Ue 90x40x12x0,95</t>
-        </is>
-      </c>
-      <c r="C190" s="10" t="inlineStr">
-        <is>
-          <t>pc</t>
-        </is>
-      </c>
-      <c r="D190" s="14" t="n">
-        <v>547</v>
-      </c>
-      <c r="E190" s="11" t="inlineStr">
-        <is>
-          <t>peca cortada e furada conforme Ue 90x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
-        </is>
-      </c>
-      <c r="F190" s="10" t="inlineStr">
-        <is>
-          <t>NBR 15253</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 250x40x15x3,00</t>
+          <t>PF-Ue 90x40x12x0,95</t>
         </is>
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>Ue 250x40x15x3,00</t>
+          <t>Ue 90x40x12x0,95</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
@@ -24334,11 +24432,11 @@
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>22</v>
+        <v>588</v>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 250x40x15x3,00; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 90x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F191" s="10" t="inlineStr">
@@ -24350,12 +24448,12 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>PF-U 92x38x0,95</t>
+          <t>PF-Ue 250x40x15x3,00</t>
         </is>
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>U 92x38x0,95</t>
+          <t>Ue 250x40x15x3,00</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
@@ -24364,11 +24462,11 @@
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>299</v>
+        <v>22</v>
       </c>
       <c r="E192" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme U 92x38x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 250x40x15x3,00; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F192" s="10" t="inlineStr">
@@ -24380,12 +24478,12 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 250x40x12x2,25</t>
+          <t>PF-U 92x38x0,95</t>
         </is>
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x2,25</t>
+          <t>U 92x38x0,95</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
@@ -24394,11 +24492,11 @@
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>24</v>
+        <v>335</v>
       </c>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 250x40x12x2,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme U 92x38x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F193" s="10" t="inlineStr">
@@ -24410,12 +24508,12 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 200x40x12x1,25</t>
+          <t>PF-Ue 250x40x12x2,25</t>
         </is>
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x1,25</t>
+          <t>Ue 250x40x12x2,25</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
@@ -24424,11 +24522,11 @@
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E194" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 200x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 250x40x12x2,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F194" s="10" t="inlineStr">
@@ -24440,12 +24538,12 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 200x40x12x0,95</t>
+          <t>PF-Ue 140x40x12x0,80</t>
         </is>
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x0,95</t>
+          <t>Ue 140x40x12x0,80</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
@@ -24454,11 +24552,11 @@
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="E195" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 200x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 140x40x12x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F195" s="10" t="inlineStr">
@@ -24470,12 +24568,12 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 140x40x12x0,80</t>
+          <t>PF-Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x0,80</t>
+          <t>Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
@@ -24484,11 +24582,11 @@
         </is>
       </c>
       <c r="D196" s="14" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E196" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 140x40x12x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 200x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F196" s="10" t="inlineStr">
@@ -24500,12 +24598,12 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 90x40x12x1,25</t>
+          <t>PF-Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>Ue 90x40x12x1,25</t>
+          <t>Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
@@ -24514,11 +24612,11 @@
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E197" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 90x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 200x40x12x0,95; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F197" s="10" t="inlineStr">
@@ -24530,12 +24628,12 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 140x40x12x1,25</t>
+          <t>PF-Ue 90x40x12x1,25</t>
         </is>
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x1,25</t>
+          <t>Ue 90x40x12x1,25</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
@@ -24544,11 +24642,11 @@
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="E198" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 140x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 90x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F198" s="10" t="inlineStr">
@@ -24560,12 +24658,12 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>PF-Ue 250x40x12x1,25</t>
+          <t>PF-Ue 140x40x12x1,25</t>
         </is>
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x1,25</t>
+          <t>Ue 140x40x12x1,25</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
@@ -24574,11 +24672,11 @@
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E199" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Ue 250x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 140x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F199" s="10" t="inlineStr">
@@ -24590,12 +24688,12 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>PF-Fita 38x0,80</t>
+          <t>PF-Ue 250x40x12x1,25</t>
         </is>
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>Fita 38x0,80</t>
+          <t>Ue 250x40x12x1,25</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
@@ -24604,11 +24702,11 @@
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="E200" s="11" t="inlineStr">
         <is>
-          <t>peca cortada e furada conforme Fita 38x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+          <t>peca cortada e furada conforme Ue 250x40x12x1,25; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
         </is>
       </c>
       <c r="F200" s="10" t="inlineStr">
@@ -24620,36 +24718,66 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
+          <t>PF-Fita 38x0,80</t>
+        </is>
+      </c>
+      <c r="B201" s="11" t="inlineStr">
+        <is>
+          <t>Fita 38x0,80</t>
+        </is>
+      </c>
+      <c r="C201" s="10" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="D201" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="E201" s="11" t="inlineStr">
+        <is>
+          <t>peca cortada e furada conforme Fita 38x0,80; rota ALTERNATIVA a barra: cotar peca pronta so faz sentido contra o custo de corte proprio</t>
+        </is>
+      </c>
+      <c r="F201" s="10" t="inlineStr">
+        <is>
+          <t>NBR 15253</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="inlineStr">
+        <is>
           <t>PLACA</t>
         </is>
       </c>
-      <c r="B201" s="11" t="inlineStr">
+      <c r="B202" s="11" t="inlineStr">
         <is>
           <t>Placa (gesso, RU e cimenticia)</t>
         </is>
       </c>
-      <c r="C201" s="10" t="inlineStr">
+      <c r="C202" s="10" t="inlineStr">
         <is>
           <t>pc</t>
         </is>
       </c>
-      <c r="D201" s="14" t="n">
-        <v>837</v>
-      </c>
-      <c r="E201" s="11" t="inlineStr">
+      <c r="D202" s="14" t="n">
+        <v>944</v>
+      </c>
+      <c r="E202" s="11" t="inlineStr">
         <is>
           <t>placa inteira, por formato — rota alternativa a compra por m2; formatos: 1200 x 2400, 1200 x 25000, 600 x 1250</t>
         </is>
       </c>
-      <c r="F201" s="10" t="inlineStr">
+      <c r="F202" s="10" t="inlineStr">
         <is>
           <t>NBR 15758</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:I185"/>
-  <conditionalFormatting sqref="I4:I185">
+  <autoFilter ref="A3:I186"/>
+  <conditionalFormatting sqref="I4:I186">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"com lacuna"</formula>
     </cfRule>
@@ -25096,7 +25224,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B14" s="18" t="n">
@@ -25104,7 +25232,7 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Marcenarias de Manaus</t>
+          <t>Metalurgica Aluminova</t>
         </is>
       </c>
       <c r="D14" s="36" t="inlineStr">
@@ -25114,7 +25242,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>movel sob medida</t>
+          <t>ripado e brise em aluminio</t>
         </is>
       </c>
       <c r="F14" s="37" t="n"/>
@@ -25129,7 +25257,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B15" s="18" t="n">
@@ -25137,7 +25265,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Todeschini / Dell Anno</t>
+          <t>Alubrasil / Hydro</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -25147,7 +25275,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>movel planejado, rede</t>
+          <t>perfil de aluminio extrudado</t>
         </is>
       </c>
       <c r="F15" s="37" t="n"/>
@@ -25162,7 +25290,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B16" s="18" t="n">
@@ -25170,7 +25298,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Italinea / Favorita</t>
+          <t>Fabricantes de brise movel</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -25180,7 +25308,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>movel planejado</t>
+          <t>mecanismo e guia</t>
         </is>
       </c>
       <c r="F16" s="37" t="n"/>
@@ -25195,7 +25323,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B17" s="18" t="n">
@@ -25203,7 +25331,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Marmorarias de Manaus</t>
+          <t>Serralherias de Manaus</t>
         </is>
       </c>
       <c r="D17" s="36" t="inlineStr">
@@ -25213,7 +25341,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>tampo em quartzo e granito</t>
+          <t>montagem e fixacao</t>
         </is>
       </c>
       <c r="F17" s="37" t="n"/>
@@ -25228,7 +25356,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>marcenaria</t>
+          <t>fachada</t>
         </is>
       </c>
       <c r="B18" s="18" t="n">
@@ -25236,17 +25364,17 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Duratex / Guararapes</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Esquadrias Alufynestra</t>
+        </is>
+      </c>
+      <c r="D18" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>MDF, fabricante de chapa</t>
+          <t>perfis e acabamento</t>
         </is>
       </c>
       <c r="F18" s="37" t="n"/>
@@ -25261,7 +25389,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B19" s="18" t="n">
@@ -25269,7 +25397,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Du Norte Comercio</t>
+          <t>Marcenarias de Manaus</t>
         </is>
       </c>
       <c r="D19" s="36" t="inlineStr">
@@ -25279,7 +25407,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>bloco, areia e brita</t>
+          <t>movel sob medida</t>
         </is>
       </c>
       <c r="F19" s="37" t="n"/>
@@ -25294,7 +25422,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B20" s="18" t="n">
@@ -25302,17 +25430,17 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Loja do Rei</t>
-        </is>
-      </c>
-      <c r="D20" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Todeschini / Dell Anno</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>bloco de concreto estrutural</t>
+          <t>movel planejado, rede</t>
         </is>
       </c>
       <c r="F20" s="37" t="n"/>
@@ -25327,7 +25455,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B21" s="18" t="n">
@@ -25335,17 +25463,17 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>O K Representacao de Material de Construcao</t>
-        </is>
-      </c>
-      <c r="D21" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Italinea / Favorita</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>representacao e distribuicao</t>
+          <t>movel planejado</t>
         </is>
       </c>
       <c r="F21" s="37" t="n"/>
@@ -25360,7 +25488,7 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B22" s="18" t="n">
@@ -25368,17 +25496,17 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Portobello / Eliane / Portinari</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Marmorarias de Manaus</t>
+        </is>
+      </c>
+      <c r="D22" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>porcelanato externo</t>
+          <t>tampo em quartzo e granito</t>
         </is>
       </c>
       <c r="F22" s="37" t="n"/>
@@ -25393,7 +25521,7 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>externo</t>
+          <t>marcenaria</t>
         </is>
       </c>
       <c r="B23" s="18" t="n">
@@ -25401,7 +25529,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Fabricantes de WPC (deck coextrudado)</t>
+          <t>Duratex / Guararapes</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -25411,7 +25539,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>deck de madeira plastica</t>
+          <t>MDF, fabricante de chapa</t>
         </is>
       </c>
       <c r="F23" s="37" t="n"/>
@@ -25591,7 +25719,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B29" s="18" t="n">
@@ -25599,7 +25727,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Metalurgica Aluminova</t>
+          <t>Du Norte Comercio</t>
         </is>
       </c>
       <c r="D29" s="36" t="inlineStr">
@@ -25609,7 +25737,7 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>ripado e brise em aluminio</t>
+          <t>bloco, areia e brita</t>
         </is>
       </c>
       <c r="F29" s="37" t="n"/>
@@ -25624,7 +25752,7 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B30" s="18" t="n">
@@ -25632,17 +25760,17 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Alubrasil / Hydro</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Loja do Rei</t>
+        </is>
+      </c>
+      <c r="D30" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>perfil de aluminio extrudado</t>
+          <t>bloco de concreto estrutural</t>
         </is>
       </c>
       <c r="F30" s="37" t="n"/>
@@ -25657,7 +25785,7 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B31" s="18" t="n">
@@ -25665,17 +25793,17 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Fabricantes de brise movel</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>O K Representacao de Material de Construcao</t>
+        </is>
+      </c>
+      <c r="D31" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>mecanismo e guia</t>
+          <t>representacao e distribuicao</t>
         </is>
       </c>
       <c r="F31" s="37" t="n"/>
@@ -25690,7 +25818,7 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B32" s="18" t="n">
@@ -25698,17 +25826,17 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Serralherias de Manaus</t>
-        </is>
-      </c>
-      <c r="D32" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Portobello / Eliane / Portinari</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>montagem e fixacao</t>
+          <t>porcelanato externo</t>
         </is>
       </c>
       <c r="F32" s="37" t="n"/>
@@ -25723,7 +25851,7 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>fachada</t>
+          <t>externo</t>
         </is>
       </c>
       <c r="B33" s="18" t="n">
@@ -25731,17 +25859,17 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Esquadrias Alufynestra</t>
-        </is>
-      </c>
-      <c r="D33" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Fabricantes de WPC (deck coextrudado)</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>perfis e acabamento</t>
+          <t>deck de madeira plastica</t>
         </is>
       </c>
       <c r="F33" s="37" t="n"/>
@@ -25756,7 +25884,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B34" s="18" t="n">
@@ -25774,7 +25902,7 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>cimento, areia e brita</t>
+          <t>porcelanato, argamassa e rejunte</t>
         </is>
       </c>
       <c r="F34" s="37" t="n"/>
@@ -25789,7 +25917,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B35" s="18" t="n">
@@ -25797,7 +25925,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Loja do Rei Comercio de Material de Construcao</t>
+          <t>Loja do Rei</t>
         </is>
       </c>
       <c r="D35" s="36" t="inlineStr">
@@ -25807,7 +25935,7 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>maior faturamento do setor na praca</t>
+          <t>revestimento e assentamento</t>
         </is>
       </c>
       <c r="F35" s="37" t="n"/>
@@ -25822,7 +25950,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B36" s="18" t="n">
@@ -25830,7 +25958,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Bacuri Madeiras e Material de Construcao</t>
+          <t>Bacuri Materiais</t>
         </is>
       </c>
       <c r="D36" s="36" t="inlineStr">
@@ -25840,7 +25968,7 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>insumos</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="F36" s="37" t="n"/>
@@ -25855,7 +25983,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B37" s="18" t="n">
@@ -25863,17 +25991,17 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Concreteiras locais (usinas de Manaus)</t>
-        </is>
-      </c>
-      <c r="D37" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Portobello / Eliane / Portinari</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>concreto usinado fck 30 com bombeamento</t>
+          <t>porcelanato, fabricante</t>
         </is>
       </c>
       <c r="F37" s="37" t="n"/>
@@ -25888,7 +26016,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>fundacao</t>
+          <t>revestimento</t>
         </is>
       </c>
       <c r="B38" s="18" t="n">
@@ -25896,7 +26024,7 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Gerdau / ArcelorMittal</t>
+          <t>Quartzolit / Votomassa</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -25906,7 +26034,7 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>aco CA-50 e tela soldada</t>
+          <t>argamassa colante e rejunte</t>
         </is>
       </c>
       <c r="F38" s="37" t="n"/>
@@ -25921,7 +26049,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B39" s="18" t="n">
@@ -25939,7 +26067,7 @@
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>porcelanato, argamassa e rejunte</t>
+          <t>cimento, areia e brita</t>
         </is>
       </c>
       <c r="F39" s="37" t="n"/>
@@ -25954,7 +26082,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B40" s="18" t="n">
@@ -25962,7 +26090,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Loja do Rei</t>
+          <t>Loja do Rei Comercio de Material de Construcao</t>
         </is>
       </c>
       <c r="D40" s="36" t="inlineStr">
@@ -25972,7 +26100,7 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>revestimento e assentamento</t>
+          <t>maior faturamento do setor na praca</t>
         </is>
       </c>
       <c r="F40" s="37" t="n"/>
@@ -25987,7 +26115,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B41" s="18" t="n">
@@ -25995,7 +26123,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Bacuri Materiais</t>
+          <t>Bacuri Madeiras e Material de Construcao</t>
         </is>
       </c>
       <c r="D41" s="36" t="inlineStr">
@@ -26005,7 +26133,7 @@
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>insumos</t>
         </is>
       </c>
       <c r="F41" s="37" t="n"/>
@@ -26020,7 +26148,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B42" s="18" t="n">
@@ -26028,17 +26156,17 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Portobello / Eliane / Portinari</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Concreteiras locais (usinas de Manaus)</t>
+        </is>
+      </c>
+      <c r="D42" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>porcelanato, fabricante</t>
+          <t>concreto usinado fck 30 com bombeamento</t>
         </is>
       </c>
       <c r="F42" s="37" t="n"/>
@@ -26053,7 +26181,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>revestimento</t>
+          <t>fundacao</t>
         </is>
       </c>
       <c r="B43" s="18" t="n">
@@ -26061,7 +26189,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Quartzolit / Votomassa</t>
+          <t>Gerdau / ArcelorMittal</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -26071,7 +26199,7 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>argamassa colante e rejunte</t>
+          <t>aco CA-50 e tela soldada</t>
         </is>
       </c>
       <c r="F43" s="37" t="n"/>
@@ -26614,7 +26742,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B60" s="18" t="n">
@@ -26622,17 +26750,17 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Deca / Duratex</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Empreiteiras de pintura de Manaus</t>
+        </is>
+      </c>
+      <c r="D60" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>louca e metal, fabricante</t>
+          <t>material e mao de obra</t>
         </is>
       </c>
       <c r="F60" s="37" t="n"/>
@@ -26647,7 +26775,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B61" s="18" t="n">
@@ -26655,7 +26783,7 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Docol</t>
+          <t>Suvinil / BASF</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -26665,7 +26793,7 @@
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>metal sanitario</t>
+          <t>tinta, fabricante</t>
         </is>
       </c>
       <c r="F61" s="37" t="n"/>
@@ -26680,7 +26808,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B62" s="18" t="n">
@@ -26688,7 +26816,7 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Roca / Celite</t>
+          <t>Coral / AkzoNobel</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -26698,7 +26826,7 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>louca sanitaria</t>
+          <t>tinta, fabricante</t>
         </is>
       </c>
       <c r="F62" s="37" t="n"/>
@@ -26713,7 +26841,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B63" s="18" t="n">
@@ -26721,17 +26849,17 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Lojas de acabamento de Manaus</t>
-        </is>
-      </c>
-      <c r="D63" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Sherwin-Williams</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>louca e metal</t>
+          <t>tinta, fabricante</t>
         </is>
       </c>
       <c r="F63" s="37" t="n"/>
@@ -26746,7 +26874,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>loucas</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="B64" s="18" t="n">
@@ -26764,7 +26892,7 @@
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>louca, metal e acessorio</t>
+          <t>tinta e material de pintura</t>
         </is>
       </c>
       <c r="F64" s="37" t="n"/>
@@ -26779,7 +26907,7 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B65" s="18" t="n">
@@ -26787,17 +26915,17 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Empreiteiras de pintura de Manaus</t>
-        </is>
-      </c>
-      <c r="D65" s="36" t="inlineStr">
-        <is>
-          <t>Manaus/AM</t>
+          <t>Deca / Duratex</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>material e mao de obra</t>
+          <t>louca e metal, fabricante</t>
         </is>
       </c>
       <c r="F65" s="37" t="n"/>
@@ -26812,7 +26940,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B66" s="18" t="n">
@@ -26820,7 +26948,7 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Suvinil / BASF</t>
+          <t>Docol</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -26830,7 +26958,7 @@
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>tinta, fabricante</t>
+          <t>metal sanitario</t>
         </is>
       </c>
       <c r="F66" s="37" t="n"/>
@@ -26845,7 +26973,7 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B67" s="18" t="n">
@@ -26853,7 +26981,7 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Coral / AkzoNobel</t>
+          <t>Roca / Celite</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -26863,7 +26991,7 @@
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>tinta, fabricante</t>
+          <t>louca sanitaria</t>
         </is>
       </c>
       <c r="F67" s="37" t="n"/>
@@ -26878,7 +27006,7 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B68" s="18" t="n">
@@ -26886,17 +27014,17 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Nacional</t>
+          <t>Lojas de acabamento de Manaus</t>
+        </is>
+      </c>
+      <c r="D68" s="36" t="inlineStr">
+        <is>
+          <t>Manaus/AM</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>tinta, fabricante</t>
+          <t>louca e metal</t>
         </is>
       </c>
       <c r="F68" s="37" t="n"/>
@@ -26911,7 +27039,7 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>loucas</t>
         </is>
       </c>
       <c r="B69" s="18" t="n">
@@ -26929,7 +27057,7 @@
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>tinta e material de pintura</t>
+          <t>louca, metal e acessorio</t>
         </is>
       </c>
       <c r="F69" s="37" t="n"/>
@@ -28166,7 +28294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -28194,7 +28322,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>1100 peças · 549 barras de 6.000 mm · aproveitamento 89.1 % · perda 360.5 m</t>
+          <t>1201 peças · 585 barras de 6.000 mm · aproveitamento 88.9 % · perda 390.0 m</t>
         </is>
       </c>
     </row>
@@ -28240,7 +28368,7 @@
         <v>4623</v>
       </c>
       <c r="C5" s="45" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
@@ -28265,7 +28393,7 @@
         <v>4173</v>
       </c>
       <c r="C6" s="45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
@@ -28290,7 +28418,7 @@
         <v>3764</v>
       </c>
       <c r="C7" s="45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
@@ -28315,7 +28443,7 @@
         <v>3413</v>
       </c>
       <c r="C8" s="45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -28362,18 +28490,18 @@
         </is>
       </c>
       <c r="B10" s="44" t="n">
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="C10" s="45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>blocking, track, travamento</t>
+          <t>travamento</t>
         </is>
       </c>
       <c r="E10" s="46" t="n">
-        <v>7.376</v>
+        <v>8.851000000000001</v>
       </c>
       <c r="F10" s="14">
         <f>C10*E10</f>
@@ -28387,18 +28515,18 @@
         </is>
       </c>
       <c r="B11" s="44" t="n">
-        <v>5490</v>
+        <v>6000</v>
       </c>
       <c r="C11" s="45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>blocking, track</t>
         </is>
       </c>
       <c r="E11" s="46" t="n">
-        <v>6.749</v>
+        <v>7.376</v>
       </c>
       <c r="F11" s="14">
         <f>C11*E11</f>
@@ -28412,18 +28540,18 @@
         </is>
       </c>
       <c r="B12" s="44" t="n">
-        <v>5400</v>
+        <v>5490</v>
       </c>
       <c r="C12" s="45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>blocking, travamento</t>
+          <t>track</t>
         </is>
       </c>
       <c r="E12" s="46" t="n">
-        <v>6.639</v>
+        <v>6.749</v>
       </c>
       <c r="F12" s="14">
         <f>C12*E12</f>
@@ -28437,18 +28565,18 @@
         </is>
       </c>
       <c r="B13" s="44" t="n">
-        <v>4890</v>
+        <v>5400</v>
       </c>
       <c r="C13" s="45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>blocking</t>
+          <t>blocking, travamento</t>
         </is>
       </c>
       <c r="E13" s="46" t="n">
-        <v>6.012</v>
+        <v>6.639</v>
       </c>
       <c r="F13" s="14">
         <f>C13*E13</f>
@@ -28462,18 +28590,18 @@
         </is>
       </c>
       <c r="B14" s="44" t="n">
-        <v>4200</v>
+        <v>4890</v>
       </c>
       <c r="C14" s="45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>blocking, track</t>
+          <t>blocking</t>
         </is>
       </c>
       <c r="E14" s="46" t="n">
-        <v>5.163</v>
+        <v>6.012</v>
       </c>
       <c r="F14" s="14">
         <f>C14*E14</f>
@@ -28487,10 +28615,10 @@
         </is>
       </c>
       <c r="B15" s="44" t="n">
-        <v>3600</v>
+        <v>4200</v>
       </c>
       <c r="C15" s="45" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
@@ -28498,7 +28626,7 @@
         </is>
       </c>
       <c r="E15" s="46" t="n">
-        <v>4.426</v>
+        <v>5.163</v>
       </c>
       <c r="F15" s="14">
         <f>C15*E15</f>
@@ -28512,10 +28640,10 @@
         </is>
       </c>
       <c r="B16" s="44" t="n">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="C16" s="45" t="n">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
@@ -28523,7 +28651,7 @@
         </is>
       </c>
       <c r="E16" s="46" t="n">
-        <v>3.688</v>
+        <v>4.426</v>
       </c>
       <c r="F16" s="14">
         <f>C16*E16</f>
@@ -28537,18 +28665,18 @@
         </is>
       </c>
       <c r="B17" s="44" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="C17" s="45" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>blocking, track</t>
+          <t>blocking, track, travamento</t>
         </is>
       </c>
       <c r="E17" s="46" t="n">
-        <v>2.95</v>
+        <v>3.688</v>
       </c>
       <c r="F17" s="14">
         <f>C17*E17</f>
@@ -28562,18 +28690,18 @@
         </is>
       </c>
       <c r="B18" s="44" t="n">
-        <v>2310</v>
+        <v>2400</v>
       </c>
       <c r="C18" s="45" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>blocking</t>
+          <t>blocking, track</t>
         </is>
       </c>
       <c r="E18" s="46" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="F18" s="14">
         <f>C18*E18</f>
@@ -28587,18 +28715,18 @@
         </is>
       </c>
       <c r="B19" s="44" t="n">
-        <v>2000</v>
+        <v>2310</v>
       </c>
       <c r="C19" s="45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>sill</t>
+          <t>blocking</t>
         </is>
       </c>
       <c r="E19" s="46" t="n">
-        <v>2.459</v>
+        <v>2.84</v>
       </c>
       <c r="F19" s="14">
         <f>C19*E19</f>
@@ -28612,18 +28740,18 @@
         </is>
       </c>
       <c r="B20" s="44" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="C20" s="45" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>blocking, track</t>
+          <t>sill</t>
         </is>
       </c>
       <c r="E20" s="46" t="n">
-        <v>2.213</v>
+        <v>2.459</v>
       </c>
       <c r="F20" s="14">
         <f>C20*E20</f>
@@ -28637,18 +28765,18 @@
         </is>
       </c>
       <c r="B21" s="44" t="n">
-        <v>1710</v>
+        <v>1800</v>
       </c>
       <c r="C21" s="45" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>blocking, track</t>
         </is>
       </c>
       <c r="E21" s="46" t="n">
-        <v>2.102</v>
+        <v>2.213</v>
       </c>
       <c r="F21" s="14">
         <f>C21*E21</f>
@@ -28662,18 +28790,18 @@
         </is>
       </c>
       <c r="B22" s="44" t="n">
-        <v>1400</v>
+        <v>1710</v>
       </c>
       <c r="C22" s="45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>sill</t>
+          <t>track</t>
         </is>
       </c>
       <c r="E22" s="46" t="n">
-        <v>1.721</v>
+        <v>2.102</v>
       </c>
       <c r="F22" s="14">
         <f>C22*E22</f>
@@ -28687,18 +28815,18 @@
         </is>
       </c>
       <c r="B23" s="44" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="C23" s="45" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>sill</t>
         </is>
       </c>
       <c r="E23" s="46" t="n">
-        <v>1.475</v>
+        <v>1.721</v>
       </c>
       <c r="F23" s="14">
         <f>C23*E23</f>
@@ -28712,18 +28840,18 @@
         </is>
       </c>
       <c r="B24" s="44" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="C24" s="45" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>degrau, sill</t>
+          <t>blocking, track</t>
         </is>
       </c>
       <c r="E24" s="46" t="n">
-        <v>1.229</v>
+        <v>1.475</v>
       </c>
       <c r="F24" s="14">
         <f>C24*E24</f>
@@ -28737,18 +28865,18 @@
         </is>
       </c>
       <c r="B25" s="44" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C25" s="45" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>sill</t>
+          <t>degrau, sill</t>
         </is>
       </c>
       <c r="E25" s="46" t="n">
-        <v>0.983</v>
+        <v>1.229</v>
       </c>
       <c r="F25" s="14">
         <f>C25*E25</f>
@@ -28762,18 +28890,18 @@
         </is>
       </c>
       <c r="B26" s="44" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="C26" s="45" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>blocking, track</t>
+          <t>sill</t>
         </is>
       </c>
       <c r="E26" s="46" t="n">
-        <v>0.738</v>
+        <v>0.983</v>
       </c>
       <c r="F26" s="14">
         <f>C26*E26</f>
@@ -28783,22 +28911,22 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x0,80</t>
+          <t>U 92x38x0,95</t>
         </is>
       </c>
       <c r="B27" s="44" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="C27" s="45" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>viga de borda</t>
+          <t>blocking, track</t>
         </is>
       </c>
       <c r="E27" s="46" t="n">
-        <v>9.023999999999999</v>
+        <v>0.738</v>
       </c>
       <c r="F27" s="14">
         <f>C27*E27</f>
@@ -28812,7 +28940,7 @@
         </is>
       </c>
       <c r="B28" s="44" t="n">
-        <v>4800</v>
+        <v>7200</v>
       </c>
       <c r="C28" s="45" t="n">
         <v>2</v>
@@ -28823,7 +28951,7 @@
         </is>
       </c>
       <c r="E28" s="46" t="n">
-        <v>7.219</v>
+        <v>10.829</v>
       </c>
       <c r="F28" s="14">
         <f>C28*E28</f>
@@ -28837,7 +28965,7 @@
         </is>
       </c>
       <c r="B29" s="44" t="n">
-        <v>3600</v>
+        <v>4800</v>
       </c>
       <c r="C29" s="45" t="n">
         <v>2</v>
@@ -28848,7 +28976,7 @@
         </is>
       </c>
       <c r="E29" s="46" t="n">
-        <v>5.414</v>
+        <v>7.219</v>
       </c>
       <c r="F29" s="14">
         <f>C29*E29</f>
@@ -28862,18 +28990,18 @@
         </is>
       </c>
       <c r="B30" s="44" t="n">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="C30" s="45" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>viga, viga de borda</t>
+          <t>viga de borda</t>
         </is>
       </c>
       <c r="E30" s="46" t="n">
-        <v>4.512</v>
+        <v>6.768</v>
       </c>
       <c r="F30" s="14">
         <f>C30*E30</f>
@@ -28887,18 +29015,18 @@
         </is>
       </c>
       <c r="B31" s="44" t="n">
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="C31" s="45" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>viga</t>
+          <t>viga de borda</t>
         </is>
       </c>
       <c r="E31" s="46" t="n">
-        <v>3.61</v>
+        <v>5.414</v>
       </c>
       <c r="F31" s="14">
         <f>C31*E31</f>
@@ -28912,10 +29040,10 @@
         </is>
       </c>
       <c r="B32" s="44" t="n">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="C32" s="45" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -28923,7 +29051,7 @@
         </is>
       </c>
       <c r="E32" s="46" t="n">
-        <v>2.707</v>
+        <v>4.512</v>
       </c>
       <c r="F32" s="14">
         <f>C32*E32</f>
@@ -28933,22 +29061,22 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x1,25</t>
+          <t>Ue 140x40x12x0,80</t>
         </is>
       </c>
       <c r="B33" s="44" t="n">
-        <v>4800</v>
+        <v>2400</v>
       </c>
       <c r="C33" s="45" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>viga de borda</t>
+          <t>viga</t>
         </is>
       </c>
       <c r="E33" s="46" t="n">
-        <v>11.109</v>
+        <v>3.61</v>
       </c>
       <c r="F33" s="14">
         <f>C33*E33</f>
@@ -28958,22 +29086,22 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x1,25</t>
+          <t>Ue 140x40x12x0,80</t>
         </is>
       </c>
       <c r="B34" s="44" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="C34" s="45" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>viga de borda</t>
+          <t>viga</t>
         </is>
       </c>
       <c r="E34" s="46" t="n">
-        <v>6.943</v>
+        <v>1.805</v>
       </c>
       <c r="F34" s="14">
         <f>C34*E34</f>
@@ -28987,18 +29115,18 @@
         </is>
       </c>
       <c r="B35" s="44" t="n">
-        <v>2400</v>
+        <v>4800</v>
       </c>
       <c r="C35" s="45" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>viga</t>
+          <t>viga de borda</t>
         </is>
       </c>
       <c r="E35" s="46" t="n">
-        <v>5.554</v>
+        <v>11.109</v>
       </c>
       <c r="F35" s="14">
         <f>C35*E35</f>
@@ -29008,14 +29136,14 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x0,95</t>
+          <t>Ue 140x40x12x1,25</t>
         </is>
       </c>
       <c r="B36" s="44" t="n">
-        <v>5400</v>
+        <v>3000</v>
       </c>
       <c r="C36" s="45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
@@ -29023,7 +29151,7 @@
         </is>
       </c>
       <c r="E36" s="46" t="n">
-        <v>12.027</v>
+        <v>6.943</v>
       </c>
       <c r="F36" s="14">
         <f>C36*E36</f>
@@ -29033,14 +29161,14 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x0,95</t>
+          <t>Ue 140x40x12x1,25</t>
         </is>
       </c>
       <c r="B37" s="44" t="n">
-        <v>4800</v>
+        <v>2400</v>
       </c>
       <c r="C37" s="45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
@@ -29048,7 +29176,7 @@
         </is>
       </c>
       <c r="E37" s="46" t="n">
-        <v>10.69</v>
+        <v>5.554</v>
       </c>
       <c r="F37" s="14">
         <f>C37*E37</f>
@@ -29058,14 +29186,14 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x1,25</t>
+          <t>Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="B38" s="44" t="n">
-        <v>7800</v>
+        <v>5400</v>
       </c>
       <c r="C38" s="45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -29073,7 +29201,7 @@
         </is>
       </c>
       <c r="E38" s="46" t="n">
-        <v>22.644</v>
+        <v>12.027</v>
       </c>
       <c r="F38" s="14">
         <f>C38*E38</f>
@@ -29083,22 +29211,22 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x1,25</t>
+          <t>Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="B39" s="44" t="n">
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="C39" s="45" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>viga, viga de borda</t>
+          <t>viga</t>
         </is>
       </c>
       <c r="E39" s="46" t="n">
-        <v>17.419</v>
+        <v>10.69</v>
       </c>
       <c r="F39" s="14">
         <f>C39*E39</f>
@@ -29108,22 +29236,22 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x1,25</t>
+          <t>Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="B40" s="44" t="n">
-        <v>3012</v>
+        <v>7800</v>
       </c>
       <c r="C40" s="45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>viga de escada</t>
+          <t>viga de borda</t>
         </is>
       </c>
       <c r="E40" s="46" t="n">
-        <v>10.222</v>
+        <v>22.644</v>
       </c>
       <c r="F40" s="14">
         <f>C40*E40</f>
@@ -29133,22 +29261,22 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x2,25</t>
+          <t>Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="B41" s="44" t="n">
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="C41" s="45" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>viga de borda</t>
+          <t>viga</t>
         </is>
       </c>
       <c r="E41" s="46" t="n">
-        <v>32.366</v>
+        <v>17.419</v>
       </c>
       <c r="F41" s="14">
         <f>C41*E41</f>
@@ -29158,22 +29286,22 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x2,25</t>
+          <t>Ue 250x40x12x1,25</t>
         </is>
       </c>
       <c r="B42" s="44" t="n">
-        <v>4800</v>
+        <v>3012</v>
       </c>
       <c r="C42" s="45" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>viga</t>
+          <t>viga de escada</t>
         </is>
       </c>
       <c r="E42" s="46" t="n">
-        <v>28.77</v>
+        <v>10.222</v>
       </c>
       <c r="F42" s="14">
         <f>C42*E42</f>
@@ -29183,14 +29311,14 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Ue 250x40x15x3,00</t>
+          <t>Ue 250x40x12x2,25</t>
         </is>
       </c>
       <c r="B43" s="44" t="n">
-        <v>7800</v>
+        <v>5400</v>
       </c>
       <c r="C43" s="45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
@@ -29198,7 +29326,7 @@
         </is>
       </c>
       <c r="E43" s="46" t="n">
-        <v>62.539</v>
+        <v>32.366</v>
       </c>
       <c r="F43" s="14">
         <f>C43*E43</f>
@@ -29208,11 +29336,11 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Ue 250x40x15x3,00</t>
+          <t>Ue 250x40x12x2,25</t>
         </is>
       </c>
       <c r="B44" s="44" t="n">
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="C44" s="45" t="n">
         <v>20</v>
@@ -29223,7 +29351,7 @@
         </is>
       </c>
       <c r="E44" s="46" t="n">
-        <v>48.107</v>
+        <v>28.77</v>
       </c>
       <c r="F44" s="14">
         <f>C44*E44</f>
@@ -29233,22 +29361,22 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Ue 90x40x12x0,95</t>
+          <t>Ue 250x40x15x3,00</t>
         </is>
       </c>
       <c r="B45" s="44" t="n">
-        <v>2900</v>
+        <v>7800</v>
       </c>
       <c r="C45" s="45" t="n">
-        <v>325</v>
+        <v>2</v>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>king stud, stud</t>
+          <t>viga de borda</t>
         </is>
       </c>
       <c r="E45" s="46" t="n">
-        <v>4.08</v>
+        <v>62.539</v>
       </c>
       <c r="F45" s="14">
         <f>C45*E45</f>
@@ -29258,22 +29386,22 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Ue 90x40x12x0,95</t>
+          <t>Ue 250x40x15x3,00</t>
         </is>
       </c>
       <c r="B46" s="44" t="n">
-        <v>2800</v>
+        <v>6000</v>
       </c>
       <c r="C46" s="45" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>jack stud</t>
+          <t>viga</t>
         </is>
       </c>
       <c r="E46" s="46" t="n">
-        <v>3.939</v>
+        <v>48.107</v>
       </c>
       <c r="F46" s="14">
         <f>C46*E46</f>
@@ -29287,18 +29415,18 @@
         </is>
       </c>
       <c r="B47" s="44" t="n">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="C47" s="45" t="n">
-        <v>20</v>
+        <v>363</v>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>jack stud</t>
+          <t>king stud, stud</t>
         </is>
       </c>
       <c r="E47" s="46" t="n">
-        <v>3.376</v>
+        <v>4.08</v>
       </c>
       <c r="F47" s="14">
         <f>C47*E47</f>
@@ -29312,10 +29440,10 @@
         </is>
       </c>
       <c r="B48" s="44" t="n">
-        <v>2300</v>
+        <v>2800</v>
       </c>
       <c r="C48" s="45" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -29323,7 +29451,7 @@
         </is>
       </c>
       <c r="E48" s="46" t="n">
-        <v>3.236</v>
+        <v>3.939</v>
       </c>
       <c r="F48" s="14">
         <f>C48*E48</f>
@@ -29337,10 +29465,10 @@
         </is>
       </c>
       <c r="B49" s="44" t="n">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="C49" s="45" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
@@ -29348,7 +29476,7 @@
         </is>
       </c>
       <c r="E49" s="46" t="n">
-        <v>2.954</v>
+        <v>3.376</v>
       </c>
       <c r="F49" s="14">
         <f>C49*E49</f>
@@ -29362,18 +29490,18 @@
         </is>
       </c>
       <c r="B50" s="44" t="n">
-        <v>1408</v>
+        <v>2300</v>
       </c>
       <c r="C50" s="45" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>cripple inferior</t>
+          <t>jack stud</t>
         </is>
       </c>
       <c r="E50" s="46" t="n">
-        <v>1.981</v>
+        <v>3.236</v>
       </c>
       <c r="F50" s="14">
         <f>C50*E50</f>
@@ -29387,18 +29515,18 @@
         </is>
       </c>
       <c r="B51" s="44" t="n">
-        <v>1008</v>
+        <v>2100</v>
       </c>
       <c r="C51" s="45" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>cripple inferior</t>
+          <t>jack stud</t>
         </is>
       </c>
       <c r="E51" s="46" t="n">
-        <v>1.418</v>
+        <v>2.954</v>
       </c>
       <c r="F51" s="14">
         <f>C51*E51</f>
@@ -29412,18 +29540,18 @@
         </is>
       </c>
       <c r="B52" s="44" t="n">
-        <v>710</v>
+        <v>1408</v>
       </c>
       <c r="C52" s="45" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>cripple superior</t>
+          <t>cripple inferior</t>
         </is>
       </c>
       <c r="E52" s="46" t="n">
-        <v>0.999</v>
+        <v>1.981</v>
       </c>
       <c r="F52" s="14">
         <f>C52*E52</f>
@@ -29437,18 +29565,18 @@
         </is>
       </c>
       <c r="B53" s="44" t="n">
-        <v>510</v>
+        <v>1008</v>
       </c>
       <c r="C53" s="45" t="n">
         <v>39</v>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>cripple superior</t>
+          <t>cripple inferior</t>
         </is>
       </c>
       <c r="E53" s="46" t="n">
-        <v>0.717</v>
+        <v>1.418</v>
       </c>
       <c r="F53" s="14">
         <f>C53*E53</f>
@@ -29462,10 +29590,10 @@
         </is>
       </c>
       <c r="B54" s="44" t="n">
-        <v>410</v>
+        <v>710</v>
       </c>
       <c r="C54" s="45" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
@@ -29473,7 +29601,7 @@
         </is>
       </c>
       <c r="E54" s="46" t="n">
-        <v>0.577</v>
+        <v>0.999</v>
       </c>
       <c r="F54" s="14">
         <f>C54*E54</f>
@@ -29487,10 +29615,10 @@
         </is>
       </c>
       <c r="B55" s="44" t="n">
-        <v>210</v>
+        <v>510</v>
       </c>
       <c r="C55" s="45" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
@@ -29498,7 +29626,7 @@
         </is>
       </c>
       <c r="E55" s="46" t="n">
-        <v>0.295</v>
+        <v>0.717</v>
       </c>
       <c r="F55" s="14">
         <f>C55*E55</f>
@@ -29508,22 +29636,22 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Ue 90x40x12x1,25</t>
+          <t>Ue 90x40x12x0,95</t>
         </is>
       </c>
       <c r="B56" s="44" t="n">
-        <v>6000</v>
+        <v>410</v>
       </c>
       <c r="C56" s="45" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>cripple superior</t>
         </is>
       </c>
       <c r="E56" s="46" t="n">
-        <v>10.942</v>
+        <v>0.577</v>
       </c>
       <c r="F56" s="14">
         <f>C56*E56</f>
@@ -29533,22 +29661,22 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Ue 90x40x12x1,25</t>
+          <t>Ue 90x40x12x0,95</t>
         </is>
       </c>
       <c r="B57" s="44" t="n">
-        <v>5600</v>
+        <v>210</v>
       </c>
       <c r="C57" s="45" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>cripple superior</t>
         </is>
       </c>
       <c r="E57" s="46" t="n">
-        <v>10.213</v>
+        <v>0.295</v>
       </c>
       <c r="F57" s="14">
         <f>C57*E57</f>
@@ -29562,18 +29690,18 @@
         </is>
       </c>
       <c r="B58" s="44" t="n">
-        <v>2900</v>
+        <v>6000</v>
       </c>
       <c r="C58" s="45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>king stud</t>
+          <t>header</t>
         </is>
       </c>
       <c r="E58" s="46" t="n">
-        <v>5.289</v>
+        <v>10.942</v>
       </c>
       <c r="F58" s="14">
         <f>C58*E58</f>
@@ -29587,18 +29715,18 @@
         </is>
       </c>
       <c r="B59" s="44" t="n">
-        <v>2600</v>
+        <v>5600</v>
       </c>
       <c r="C59" s="45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>header, jack stud</t>
+          <t>header</t>
         </is>
       </c>
       <c r="E59" s="46" t="n">
-        <v>4.742</v>
+        <v>10.213</v>
       </c>
       <c r="F59" s="14">
         <f>C59*E59</f>
@@ -29612,18 +29740,18 @@
         </is>
       </c>
       <c r="B60" s="44" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="C60" s="45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>king stud</t>
         </is>
       </c>
       <c r="E60" s="46" t="n">
-        <v>4.559</v>
+        <v>5.289</v>
       </c>
       <c r="F60" s="14">
         <f>C60*E60</f>
@@ -29637,18 +29765,18 @@
         </is>
       </c>
       <c r="B61" s="44" t="n">
-        <v>2100</v>
+        <v>2600</v>
       </c>
       <c r="C61" s="45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>jack stud</t>
+          <t>header, jack stud</t>
         </is>
       </c>
       <c r="E61" s="46" t="n">
-        <v>3.83</v>
+        <v>4.742</v>
       </c>
       <c r="F61" s="14">
         <f>C61*E61</f>
@@ -29662,10 +29790,10 @@
         </is>
       </c>
       <c r="B62" s="44" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="C62" s="45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
@@ -29673,7 +29801,7 @@
         </is>
       </c>
       <c r="E62" s="46" t="n">
-        <v>3.647</v>
+        <v>4.559</v>
       </c>
       <c r="F62" s="14">
         <f>C62*E62</f>
@@ -29687,18 +29815,18 @@
         </is>
       </c>
       <c r="B63" s="44" t="n">
-        <v>1400</v>
+        <v>2300</v>
       </c>
       <c r="C63" s="45" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>jack stud</t>
         </is>
       </c>
       <c r="E63" s="46" t="n">
-        <v>2.553</v>
+        <v>4.195</v>
       </c>
       <c r="F63" s="14">
         <f>C63*E63</f>
@@ -29712,18 +29840,18 @@
         </is>
       </c>
       <c r="B64" s="44" t="n">
-        <v>1200</v>
+        <v>2100</v>
       </c>
       <c r="C64" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>jack stud</t>
         </is>
       </c>
       <c r="E64" s="46" t="n">
-        <v>2.188</v>
+        <v>3.83</v>
       </c>
       <c r="F64" s="14">
         <f>C64*E64</f>
@@ -29737,10 +29865,10 @@
         </is>
       </c>
       <c r="B65" s="44" t="n">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="C65" s="45" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
@@ -29748,7 +29876,7 @@
         </is>
       </c>
       <c r="E65" s="46" t="n">
-        <v>2.006</v>
+        <v>3.647</v>
       </c>
       <c r="F65" s="14">
         <f>C65*E65</f>
@@ -29762,10 +29890,10 @@
         </is>
       </c>
       <c r="B66" s="44" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="C66" s="45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
@@ -29773,7 +29901,7 @@
         </is>
       </c>
       <c r="E66" s="46" t="n">
-        <v>1.824</v>
+        <v>2.553</v>
       </c>
       <c r="F66" s="14">
         <f>C66*E66</f>
@@ -29787,7 +29915,7 @@
         </is>
       </c>
       <c r="B67" s="44" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="C67" s="45" t="n">
         <v>1</v>
@@ -29798,7 +29926,7 @@
         </is>
       </c>
       <c r="E67" s="46" t="n">
-        <v>1.459</v>
+        <v>2.188</v>
       </c>
       <c r="F67" s="14">
         <f>C67*E67</f>
@@ -29806,142 +29934,178 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="n"/>
-      <c r="B68" s="22" t="n"/>
-      <c r="C68" s="28">
-        <f>SUM(C5:C67)</f>
-        <v/>
-      </c>
-      <c r="D68" s="47" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Ue 90x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="B68" s="44" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C68" s="45" t="n">
+        <v>13</v>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+      <c r="E68" s="46" t="n">
+        <v>2.006</v>
+      </c>
+      <c r="F68" s="14">
+        <f>C68*E68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>Ue 90x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="B69" s="44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C69" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+      <c r="E69" s="46" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="F69" s="14">
+        <f>C69*E69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>Ue 90x40x12x1,25</t>
+        </is>
+      </c>
+      <c r="B70" s="44" t="n">
+        <v>800</v>
+      </c>
+      <c r="C70" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+      <c r="E70" s="46" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="F70" s="14">
+        <f>C70*E70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="n"/>
+      <c r="B71" s="22" t="n"/>
+      <c r="C71" s="28">
+        <f>SUM(C5:C70)</f>
+        <v/>
+      </c>
+      <c r="D71" s="47" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E68" s="22" t="n"/>
-      <c r="F68" s="48">
-        <f>SUM(F5:F67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="E71" s="22" t="n"/>
+      <c r="F71" s="48">
+        <f>SUM(F5:F70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>BARRAS POR PERFIL</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="26" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="26" t="inlineStr">
         <is>
           <t>PERFIL</t>
         </is>
       </c>
-      <c r="B71" s="26" t="inlineStr">
+      <c r="B74" s="26" t="inlineStr">
         <is>
           <t>BARRAS DE 6.000 mm</t>
         </is>
       </c>
-      <c r="C71" s="26" t="inlineStr">
+      <c r="C74" s="26" t="inlineStr">
         <is>
           <t>PEÇAS CORTADAS</t>
         </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>Fita 38x0,80</t>
-        </is>
-      </c>
-      <c r="B72" s="45" t="n">
-        <v>28</v>
-      </c>
-      <c r="C72" s="18" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>U 92x38x0,95</t>
-        </is>
-      </c>
-      <c r="B73" s="45" t="n">
-        <v>158</v>
-      </c>
-      <c r="C73" s="18" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>Ue 140x40x12x0,80</t>
-        </is>
-      </c>
-      <c r="B74" s="45" t="n">
-        <v>26</v>
-      </c>
-      <c r="C74" s="18" t="n">
-        <v>53</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Ue 140x40x12x1,25</t>
+          <t>Fita 38x0,80</t>
         </is>
       </c>
       <c r="B75" s="45" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C75" s="18" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x0,95</t>
+          <t>U 92x38x0,95</t>
         </is>
       </c>
       <c r="B76" s="45" t="n">
-        <v>24</v>
+        <v>169</v>
       </c>
       <c r="C76" s="18" t="n">
-        <v>24</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Ue 200x40x12x1,25</t>
+          <t>Ue 140x40x12x0,80</t>
         </is>
       </c>
       <c r="B77" s="45" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C77" s="18" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x1,25</t>
+          <t>Ue 140x40x12x1,25</t>
         </is>
       </c>
       <c r="B78" s="45" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C78" s="18" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Ue 250x40x12x2,25</t>
+          <t>Ue 200x40x12x0,95</t>
         </is>
       </c>
       <c r="B79" s="45" t="n">
@@ -29954,51 +30118,90 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>Ue 250x40x15x3,00</t>
+          <t>Ue 200x40x12x1,25</t>
         </is>
       </c>
       <c r="B80" s="45" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C80" s="18" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Ue 90x40x12x0,95</t>
+          <t>Ue 250x40x12x1,25</t>
         </is>
       </c>
       <c r="B81" s="45" t="n">
-        <v>209</v>
+        <v>4</v>
       </c>
       <c r="C81" s="18" t="n">
-        <v>547</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
+          <t>Ue 250x40x12x2,25</t>
+        </is>
+      </c>
+      <c r="B82" s="45" t="n">
+        <v>24</v>
+      </c>
+      <c r="C82" s="18" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Ue 250x40x15x3,00</t>
+        </is>
+      </c>
+      <c r="B83" s="45" t="n">
+        <v>20</v>
+      </c>
+      <c r="C83" s="18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Ue 90x40x12x0,95</t>
+        </is>
+      </c>
+      <c r="B84" s="45" t="n">
+        <v>228</v>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
           <t>Ue 90x40x12x1,25</t>
         </is>
       </c>
-      <c r="B82" s="45" t="n">
+      <c r="B85" s="45" t="n">
         <v>18</v>
       </c>
-      <c r="C82" s="18" t="n">
+      <c r="C85" s="18" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Esta lista NÃO substitui o nesting codificado do fabricante (pendência 8): ela é de estudo, e o fabricante corta pela dele.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F67"/>
+  <autoFilter ref="A4:F70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1514,7 +1514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 307.08 m² fechados · revisão R83</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 307.08 m² fechados · revisão R84</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>EXT-BLOCO</t>
+          <t>EXT-PISO2</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -8456,16 +8456,16 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
+          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>2750</v>
+        <v>50.4</v>
       </c>
       <c r="F90" s="13" t="n">
         <v>0</v>
@@ -8475,7 +8475,7 @@
         <v/>
       </c>
       <c r="H90" s="15" t="n">
-        <v>4.8</v>
+        <v>320</v>
       </c>
       <c r="I90" s="16">
         <f>G90*H90</f>
@@ -8522,7 +8522,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO2</t>
+          <t>EXT-BLOCO</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -8532,16 +8532,16 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
+          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>33.12</v>
+        <v>2750</v>
       </c>
       <c r="F91" s="13" t="n">
         <v>0</v>
@@ -8551,7 +8551,7 @@
         <v/>
       </c>
       <c r="H91" s="15" t="n">
-        <v>320</v>
+        <v>4.8</v>
       </c>
       <c r="I91" s="16">
         <f>G91*H91</f>
@@ -8598,7 +8598,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-EST</t>
+          <t>EXT-PISO1</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -8608,16 +8608,16 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Piscina: casca de concreto armado 150 mm</t>
+          <t>faixa seca da piscina: WPC coextrudado claro</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4.57</v>
+        <v>24.3</v>
       </c>
       <c r="F92" s="13" t="n">
         <v>0</v>
@@ -8627,7 +8627,7 @@
         <v/>
       </c>
       <c r="H92" s="15" t="n">
-        <v>1450</v>
+        <v>320</v>
       </c>
       <c r="I92" s="16">
         <f>G92*H92</f>
@@ -8674,7 +8674,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO4</t>
+          <t>EXT-PISC-EST</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -8684,16 +8684,16 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>patio e deck descoberto: porcelanato externo claro R11</t>
+          <t>Piscina: casca de concreto armado 150 mm</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>43.2</v>
+        <v>4.57</v>
       </c>
       <c r="F93" s="13" t="n">
         <v>0</v>
@@ -8703,7 +8703,7 @@
         <v/>
       </c>
       <c r="H93" s="15" t="n">
-        <v>148</v>
+        <v>1450</v>
       </c>
       <c r="I93" s="16">
         <f>G93*H93</f>
@@ -9206,7 +9206,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO1</t>
+          <t>EXT-PISO4</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>faixa seca da piscina: porcelanato externo claro R11</t>
+          <t>patio da churrasqueira: porcelanato externo claro R11</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>24.3</v>
+        <v>25.92</v>
       </c>
       <c r="F100" s="13" t="n">
         <v>0</v>
@@ -20923,7 +20923,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>EXT-BLOCO</t>
+          <t>EXT-PISO2</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -20933,16 +20933,16 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
+          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
-        <v>2750</v>
+        <v>50.4</v>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
       <c r="G90" s="11" t="inlineStr"/>
@@ -20960,7 +20960,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO2</t>
+          <t>EXT-BLOCO</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -20970,16 +20970,16 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
+          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E91" s="14" t="n">
-        <v>33.12</v>
+        <v>2750</v>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
       <c r="G91" s="11" t="inlineStr"/>
@@ -20997,7 +20997,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-EST</t>
+          <t>EXT-PISO1</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -21007,16 +21007,16 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>Piscina: casca de concreto armado 150 mm</t>
+          <t>faixa seca da piscina: WPC coextrudado claro</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
-        <v>4.57</v>
+        <v>24.3</v>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
       <c r="G92" s="11" t="inlineStr"/>
@@ -21034,7 +21034,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO4</t>
+          <t>EXT-PISC-EST</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -21044,16 +21044,16 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>patio e deck descoberto: porcelanato externo claro R11</t>
+          <t>Piscina: casca de concreto armado 150 mm</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E93" s="14" t="n">
-        <v>43.2</v>
+        <v>4.57</v>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
       <c r="G93" s="11" t="inlineStr"/>
@@ -21293,7 +21293,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO1</t>
+          <t>EXT-PISO4</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -21303,7 +21303,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>faixa seca da piscina: porcelanato externo claro R11</t>
+          <t>patio da churrasqueira: porcelanato externo claro R11</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -21312,7 +21312,7 @@
         </is>
       </c>
       <c r="E100" s="14" t="n">
-        <v>24.3</v>
+        <v>25.92</v>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
       <c r="G100" s="11" t="inlineStr"/>

--- a/porto-real/out/PORTO_REAL_COTACAO.xlsx
+++ b/porto-real/out/PORTO_REAL_COTACAO.xlsx
@@ -1514,7 +1514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 307.08 m² fechados · revisão R84</t>
+          <t>Residência unifamiliar em Light Steel Frame · Manaus/AM · 307.08 m² fechados · revisão R85</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO2</t>
+          <t>EXT-BLOCO</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -8456,16 +8456,16 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
+          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E90" s="12" t="n">
-        <v>50.4</v>
+        <v>2750</v>
       </c>
       <c r="F90" s="13" t="n">
         <v>0</v>
@@ -8475,7 +8475,7 @@
         <v/>
       </c>
       <c r="H90" s="15" t="n">
-        <v>320</v>
+        <v>4.8</v>
       </c>
       <c r="I90" s="16">
         <f>G90*H90</f>
@@ -8522,7 +8522,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>EXT-BLOCO</t>
+          <t>EXT-PISO2</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -8532,16 +8532,16 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
+          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E91" s="12" t="n">
-        <v>2750</v>
+        <v>33.12</v>
       </c>
       <c r="F91" s="13" t="n">
         <v>0</v>
@@ -8551,7 +8551,7 @@
         <v/>
       </c>
       <c r="H91" s="15" t="n">
-        <v>4.8</v>
+        <v>320</v>
       </c>
       <c r="I91" s="16">
         <f>G91*H91</f>
@@ -8598,7 +8598,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO1</t>
+          <t>EXT-PISC-EST</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -8608,16 +8608,16 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>faixa seca da piscina: WPC coextrudado claro</t>
+          <t>Piscina: casca de concreto armado 150 mm</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>24.3</v>
+        <v>4.57</v>
       </c>
       <c r="F92" s="13" t="n">
         <v>0</v>
@@ -8627,7 +8627,7 @@
         <v/>
       </c>
       <c r="H92" s="15" t="n">
-        <v>320</v>
+        <v>1450</v>
       </c>
       <c r="I92" s="16">
         <f>G92*H92</f>
@@ -8674,7 +8674,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-EST</t>
+          <t>EXT-PISO4</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -8684,16 +8684,16 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Piscina: casca de concreto armado 150 mm</t>
+          <t>patio e deck descoberto: porcelanato externo claro R11</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>4.57</v>
+        <v>43.2</v>
       </c>
       <c r="F93" s="13" t="n">
         <v>0</v>
@@ -8703,7 +8703,7 @@
         <v/>
       </c>
       <c r="H93" s="15" t="n">
-        <v>1450</v>
+        <v>148</v>
       </c>
       <c r="I93" s="16">
         <f>G93*H93</f>
@@ -9206,7 +9206,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO4</t>
+          <t>EXT-PISO1</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>patio da churrasqueira: porcelanato externo claro R11</t>
+          <t>faixa seca da piscina: porcelanato externo claro R11</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="E100" s="12" t="n">
-        <v>25.92</v>
+        <v>24.3</v>
       </c>
       <c r="F100" s="13" t="n">
         <v>0</v>
@@ -20923,7 +20923,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO2</t>
+          <t>EXT-BLOCO</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -20933,16 +20933,16 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
+          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
-        <v>50.4</v>
+        <v>2750</v>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
       <c r="G90" s="11" t="inlineStr"/>
@@ -20960,7 +20960,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>EXT-BLOCO</t>
+          <t>EXT-PISO2</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
@@ -20970,16 +20970,16 @@
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Muro: bloco de concreto estrutural 14 x 19 x 39 ap</t>
+          <t>lounge e circulacao do deck: WPC coextrudado claro</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E91" s="14" t="n">
-        <v>2750</v>
+        <v>33.12</v>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
       <c r="G91" s="11" t="inlineStr"/>
@@ -20997,7 +20997,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO1</t>
+          <t>EXT-PISC-EST</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -21007,16 +21007,16 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>faixa seca da piscina: WPC coextrudado claro</t>
+          <t>Piscina: casca de concreto armado 150 mm</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
-        <v>24.3</v>
+        <v>4.57</v>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
       <c r="G92" s="11" t="inlineStr"/>
@@ -21034,7 +21034,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISC-EST</t>
+          <t>EXT-PISO4</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -21044,16 +21044,16 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Piscina: casca de concreto armado 150 mm</t>
+          <t>patio e deck descoberto: porcelanato externo claro R11</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="E93" s="14" t="n">
-        <v>4.57</v>
+        <v>43.2</v>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
       <c r="G93" s="11" t="inlineStr"/>
@@ -21293,7 +21293,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>EXT-PISO4</t>
+          <t>EXT-PISO1</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -21303,7 +21303,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>patio da churrasqueira: porcelanato externo claro R11</t>
+          <t>faixa seca da piscina: porcelanato externo claro R11</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -21312,7 +21312,7 @@
         </is>
       </c>
       <c r="E100" s="14" t="n">
-        <v>25.92</v>
+        <v>24.3</v>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
       <c r="G100" s="11" t="inlineStr"/>
